--- a/data/processed/eksposur_pontianak_0408.xlsx
+++ b/data/processed/eksposur_pontianak_0408.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30002"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lndpontianak\data\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1E380E3-4E01-4D97-B50D-1BA9DCA76966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Government" sheetId="4" r:id="rId1"/>
@@ -22,7 +21,7 @@
     <sheet name="Drainage" sheetId="6" r:id="rId7"/>
     <sheet name="Commerce" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="631">
   <si>
     <t>No</t>
   </si>
@@ -1813,9 +1812,6 @@
   </si>
   <si>
     <t>Dinas Terkait</t>
-  </si>
-  <si>
-    <t>Alamat/Nama Lokasi</t>
   </si>
   <si>
     <t xml:space="preserve">Elevasi Tanah </t>
@@ -1947,7 +1943,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
@@ -2825,17 +2821,20 @@
     <xf numFmtId="165" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2846,11 +2845,24 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2864,18 +2876,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2885,60 +2885,56 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="48">
-    <cellStyle name="20% - Aksen1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Aksen2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Aksen3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Aksen4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Aksen5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Aksen6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Aksen6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Aksen6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Aksen1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Aksen2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Aksen3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Aksen4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Aksen5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Aksen6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Baik" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Buruk" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Catatan" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Comma 2" xfId="42" xr:uid="{071DFD07-A886-4C11-96A5-6176808154D1}"/>
-    <cellStyle name="Judul" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Judul 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Judul 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Judul 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Judul 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Keluaran" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Masukan" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Netral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma 2" xfId="42"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="43" xr:uid="{4E188F66-CAA9-416A-BC93-00605C60F9D7}"/>
-    <cellStyle name="Normal 2 2" xfId="44" xr:uid="{976B63DB-F82F-4DB4-8F9C-4DF64240E1C5}"/>
-    <cellStyle name="Normal 3" xfId="46" xr:uid="{147433F4-047F-41AE-910E-8F970A8C42C3}"/>
-    <cellStyle name="Normal 4" xfId="45" xr:uid="{962C83EE-A302-4754-944F-516A7951F0BC}"/>
-    <cellStyle name="Normal 4 2" xfId="47" xr:uid="{26DC9524-C075-454E-A1FD-E56F75C07D23}"/>
-    <cellStyle name="Perhitungan" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Sel Periksa" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Sel Tertaut" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Teks Penjelasan" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Teks Peringatan" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Normal 2" xfId="43"/>
+    <cellStyle name="Normal 2 2" xfId="44"/>
+    <cellStyle name="Normal 3" xfId="46"/>
+    <cellStyle name="Normal 4" xfId="45"/>
+    <cellStyle name="Normal 4 2" xfId="47"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3269,71 +3265,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{741E0914-794E-4459-9DF3-6A5AD35A0FD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P53"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="16384" width="9.1640625" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="51" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="51" t="s">
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="52"/>
-    </row>
-    <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="55"/>
-      <c r="B2" s="49" t="s">
+      <c r="P1" s="50"/>
+    </row>
+    <row r="2" spans="1:16" ht="34.5">
+      <c r="A2" s="56"/>
+      <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53" t="s">
+      <c r="J2" s="50"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="54"/>
-      <c r="M2" s="52"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="50"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -3344,15 +3340,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
+    <row r="3" spans="1:16" ht="57.5">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -3374,7 +3370,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16" ht="36">
+    <row r="4" spans="1:16" ht="34.5">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3418,7 +3414,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16" ht="48">
+    <row r="5" spans="1:16" ht="46">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3462,7 +3458,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="48">
+    <row r="6" spans="1:16" ht="46">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3506,7 +3502,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="60">
+    <row r="7" spans="1:16" ht="57.5">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -3550,7 +3546,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" ht="84">
+    <row r="8" spans="1:16" ht="80.5">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -3594,7 +3590,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" ht="96">
+    <row r="9" spans="1:16" ht="92">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -3638,7 +3634,7 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="60">
+    <row r="10" spans="1:16" ht="57.5">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -3682,7 +3678,7 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="84">
+    <row r="11" spans="1:16" ht="80.5">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -3726,7 +3722,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" ht="48">
+    <row r="12" spans="1:16" ht="57.5">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -3770,7 +3766,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" ht="96">
+    <row r="13" spans="1:16" ht="92">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -3814,7 +3810,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:16" ht="108">
+    <row r="14" spans="1:16" ht="103.5">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -3858,7 +3854,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16" ht="108">
+    <row r="15" spans="1:16" ht="103.5">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -3902,7 +3898,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" ht="72">
+    <row r="16" spans="1:16" ht="69">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -3946,7 +3942,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" ht="108">
+    <row r="17" spans="1:16" ht="103.5">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -3990,7 +3986,7 @@
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="1:16" ht="120">
+    <row r="18" spans="1:16" ht="103.5">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -4034,7 +4030,7 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" ht="60">
+    <row r="19" spans="1:16" ht="57.5">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -4078,7 +4074,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" ht="36">
+    <row r="20" spans="1:16" ht="34.5">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -4122,7 +4118,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" ht="48">
+    <row r="21" spans="1:16" ht="34.5">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -4166,7 +4162,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" ht="36">
+    <row r="22" spans="1:16" ht="34.5">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -4210,7 +4206,7 @@
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" ht="48">
+    <row r="23" spans="1:16" ht="34.5">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -4254,7 +4250,7 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16" ht="84">
+    <row r="24" spans="1:16" ht="80.5">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -4298,7 +4294,7 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" ht="108">
+    <row r="25" spans="1:16" ht="92">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -4342,7 +4338,7 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
     </row>
-    <row r="26" spans="1:16" ht="60">
+    <row r="26" spans="1:16" ht="57.5">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -4386,7 +4382,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" ht="48">
+    <row r="27" spans="1:16" ht="46">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -4430,7 +4426,7 @@
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" ht="48">
+    <row r="28" spans="1:16" ht="46">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -4474,7 +4470,7 @@
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16" ht="48">
+    <row r="29" spans="1:16" ht="34.5">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -4518,7 +4514,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="48">
+    <row r="30" spans="1:16" ht="34.5">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -4548,7 +4544,7 @@
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
     </row>
-    <row r="31" spans="1:16" ht="48">
+    <row r="31" spans="1:16" ht="34.5">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -4574,7 +4570,7 @@
       <c r="O31" s="15"/>
       <c r="P31" s="15"/>
     </row>
-    <row r="32" spans="1:16" ht="48">
+    <row r="32" spans="1:16" ht="34.5">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -4600,7 +4596,7 @@
       <c r="O32" s="15"/>
       <c r="P32" s="15"/>
     </row>
-    <row r="33" spans="1:16" ht="48">
+    <row r="33" spans="1:16" ht="34.5">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -4626,7 +4622,7 @@
       <c r="O33" s="15"/>
       <c r="P33" s="15"/>
     </row>
-    <row r="34" spans="1:16" ht="48">
+    <row r="34" spans="1:16" ht="34.5">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -4652,7 +4648,7 @@
       <c r="O34" s="15"/>
       <c r="P34" s="15"/>
     </row>
-    <row r="35" spans="1:16" ht="48">
+    <row r="35" spans="1:16" ht="34.5">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -4678,7 +4674,7 @@
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
     </row>
-    <row r="36" spans="1:16" ht="48">
+    <row r="36" spans="1:16" ht="34.5">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -4704,7 +4700,7 @@
       <c r="O36" s="15"/>
       <c r="P36" s="15"/>
     </row>
-    <row r="37" spans="1:16" ht="48">
+    <row r="37" spans="1:16" ht="34.5">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -4730,7 +4726,7 @@
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
     </row>
-    <row r="38" spans="1:16" ht="48">
+    <row r="38" spans="1:16" ht="46">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -4756,7 +4752,7 @@
       <c r="O38" s="15"/>
       <c r="P38" s="15"/>
     </row>
-    <row r="39" spans="1:16" ht="24">
+    <row r="39" spans="1:16" ht="23">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -4782,7 +4778,7 @@
       <c r="O39" s="15"/>
       <c r="P39" s="15"/>
     </row>
-    <row r="40" spans="1:16" ht="48">
+    <row r="40" spans="1:16" ht="34.5">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -4808,7 +4804,7 @@
       <c r="O40" s="15"/>
       <c r="P40" s="15"/>
     </row>
-    <row r="41" spans="1:16" ht="48">
+    <row r="41" spans="1:16" ht="34.5">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -4834,7 +4830,7 @@
       <c r="O41" s="15"/>
       <c r="P41" s="15"/>
     </row>
-    <row r="42" spans="1:16" ht="24">
+    <row r="42" spans="1:16" ht="23">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -4860,7 +4856,7 @@
       <c r="O42" s="15"/>
       <c r="P42" s="15"/>
     </row>
-    <row r="43" spans="1:16" ht="24">
+    <row r="43" spans="1:16" ht="23">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -4886,7 +4882,7 @@
       <c r="O43" s="15"/>
       <c r="P43" s="15"/>
     </row>
-    <row r="44" spans="1:16" ht="24">
+    <row r="44" spans="1:16" ht="23">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -4912,7 +4908,7 @@
       <c r="O44" s="15"/>
       <c r="P44" s="15"/>
     </row>
-    <row r="45" spans="1:16" ht="24">
+    <row r="45" spans="1:16" ht="23">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -4938,7 +4934,7 @@
       <c r="O45" s="15"/>
       <c r="P45" s="15"/>
     </row>
-    <row r="46" spans="1:16" ht="24">
+    <row r="46" spans="1:16" ht="23">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -4964,7 +4960,7 @@
       <c r="O46" s="15"/>
       <c r="P46" s="15"/>
     </row>
-    <row r="47" spans="1:16" ht="24">
+    <row r="47" spans="1:16" ht="23">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -4990,7 +4986,7 @@
       <c r="O47" s="15"/>
       <c r="P47" s="15"/>
     </row>
-    <row r="48" spans="1:16" ht="24">
+    <row r="48" spans="1:16" ht="23">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -5016,7 +5012,7 @@
       <c r="O48" s="15"/>
       <c r="P48" s="15"/>
     </row>
-    <row r="49" spans="1:16" ht="24">
+    <row r="49" spans="1:16" ht="23">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -5042,7 +5038,7 @@
       <c r="O49" s="15"/>
       <c r="P49" s="15"/>
     </row>
-    <row r="50" spans="1:16" ht="24">
+    <row r="50" spans="1:16" ht="23">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -5068,7 +5064,7 @@
       <c r="O50" s="15"/>
       <c r="P50" s="15"/>
     </row>
-    <row r="51" spans="1:16" ht="24">
+    <row r="51" spans="1:16" ht="23">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -5094,7 +5090,7 @@
       <c r="O51" s="15"/>
       <c r="P51" s="15"/>
     </row>
-    <row r="52" spans="1:16" ht="24">
+    <row r="52" spans="1:16" ht="23">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -5120,7 +5116,7 @@
       <c r="O52" s="15"/>
       <c r="P52" s="15"/>
     </row>
-    <row r="53" spans="1:16" ht="24">
+    <row r="53" spans="1:16" ht="23">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -5148,6 +5144,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -5158,28 +5157,25 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAA9516-305B-4836-BCCE-9F2C4DDEF1CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="9.140625" style="12"/>
-    <col min="5" max="5" width="9.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="9.140625" style="12"/>
-    <col min="11" max="14" width="9.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.1640625" style="12"/>
+    <col min="5" max="5" width="9.4140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="9.1640625" style="12"/>
+    <col min="11" max="14" width="9.25" style="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="12"/>
+    <col min="16" max="16" width="14.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.1640625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -5208,7 +5204,7 @@
       </c>
       <c r="P1" s="57"/>
     </row>
-    <row r="2" spans="1:16" ht="24">
+    <row r="2" spans="1:16" ht="23">
       <c r="A2" s="57"/>
       <c r="B2" s="57" t="s">
         <v>4</v>
@@ -5250,7 +5246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="60">
+    <row r="3" spans="1:16" ht="57.5">
       <c r="A3" s="57"/>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -5280,7 +5276,7 @@
       <c r="O3" s="57"/>
       <c r="P3" s="57"/>
     </row>
-    <row r="4" spans="1:16" ht="36">
+    <row r="4" spans="1:16" ht="34.5">
       <c r="A4" s="18">
         <v>1</v>
       </c>
@@ -5330,7 +5326,7 @@
         <v>775248795</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="36">
+    <row r="5" spans="1:16" ht="46">
       <c r="A5" s="18">
         <v>2</v>
       </c>
@@ -5380,7 +5376,7 @@
         <v>323473870</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="24">
+    <row r="6" spans="1:16" ht="23">
       <c r="A6" s="18">
         <v>3</v>
       </c>
@@ -5430,7 +5426,7 @@
         <v>485728416</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="36">
+    <row r="7" spans="1:16" ht="34.5">
       <c r="A7" s="18">
         <v>4</v>
       </c>
@@ -5480,7 +5476,7 @@
         <v>356396320</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="48">
+    <row r="8" spans="1:16" ht="46">
       <c r="A8" s="18">
         <v>5</v>
       </c>
@@ -5553,68 +5549,71 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6FE8C78-4599-4F29-B606-1E7F433DA21D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P131"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="51" t="s">
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="51" t="s">
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="70"/>
-    </row>
-    <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="71"/>
-      <c r="B2" s="49" t="s">
+      <c r="P1" s="58"/>
+    </row>
+    <row r="2" spans="1:16" ht="34.5">
+      <c r="A2" s="61"/>
+      <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="70"/>
-      <c r="K2" s="53" t="s">
+      <c r="J2" s="58"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="69"/>
-      <c r="M2" s="70"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="58"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -5625,15 +5624,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="72"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
+    <row r="3" spans="1:16" ht="69">
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -5655,7 +5654,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16" ht="36">
+    <row r="4" spans="1:16" ht="34.5">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -5701,7 +5700,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16" ht="24">
+    <row r="5" spans="1:16" ht="34.5">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -5747,7 +5746,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="36">
+    <row r="6" spans="1:16" ht="34.5">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -5793,7 +5792,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="48">
+    <row r="7" spans="1:16" ht="46">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -5839,7 +5838,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" ht="36">
+    <row r="8" spans="1:16" ht="46">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -5885,7 +5884,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" ht="48">
+    <row r="9" spans="1:16" ht="46">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -5931,7 +5930,7 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="48">
+    <row r="10" spans="1:16" ht="34.5">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -5977,7 +5976,7 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="36">
+    <row r="11" spans="1:16" ht="23">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -6023,7 +6022,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" ht="48">
+    <row r="12" spans="1:16" ht="23">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -6069,7 +6068,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" ht="24">
+    <row r="13" spans="1:16" ht="34.5">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -6115,7 +6114,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:16" ht="36">
+    <row r="14" spans="1:16" ht="34.5">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -6161,7 +6160,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16" ht="48">
+    <row r="15" spans="1:16" ht="34.5">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -6207,7 +6206,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" ht="48">
+    <row r="16" spans="1:16" ht="46">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -6253,7 +6252,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" ht="36">
+    <row r="17" spans="1:16" ht="46">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -6299,7 +6298,7 @@
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="1:16" ht="36">
+    <row r="18" spans="1:16" ht="46">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -6345,7 +6344,7 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" ht="36">
+    <row r="19" spans="1:16" ht="46">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -6391,7 +6390,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" ht="36">
+    <row r="20" spans="1:16" ht="46">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -6437,7 +6436,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" ht="48">
+    <row r="21" spans="1:16" ht="46">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -6483,7 +6482,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" ht="36">
+    <row r="22" spans="1:16" ht="46">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -6529,7 +6528,7 @@
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" ht="48">
+    <row r="23" spans="1:16" ht="34.5">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -6575,7 +6574,7 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16" ht="48">
+    <row r="24" spans="1:16" ht="46">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -6621,7 +6620,7 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" ht="36">
+    <row r="25" spans="1:16" ht="46">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -6667,7 +6666,7 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
     </row>
-    <row r="26" spans="1:16" ht="48">
+    <row r="26" spans="1:16" ht="46">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -6713,7 +6712,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" ht="48">
+    <row r="27" spans="1:16" ht="46">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -6759,7 +6758,7 @@
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" ht="36">
+    <row r="28" spans="1:16" ht="46">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -6805,7 +6804,7 @@
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16" ht="48">
+    <row r="29" spans="1:16" ht="46">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -6851,7 +6850,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="36">
+    <row r="30" spans="1:16" ht="46">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -6897,7 +6896,7 @@
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
     </row>
-    <row r="31" spans="1:16" ht="36">
+    <row r="31" spans="1:16" ht="57.5">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -6943,7 +6942,7 @@
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16" ht="72">
+    <row r="32" spans="1:16" ht="80.5">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -6989,7 +6988,7 @@
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
     </row>
-    <row r="33" spans="1:16" ht="36">
+    <row r="33" spans="1:16" ht="46">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -7035,7 +7034,7 @@
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:16" ht="48">
+    <row r="34" spans="1:16" ht="46">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -7081,7 +7080,7 @@
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:16" ht="36">
+    <row r="35" spans="1:16" ht="46">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -7127,7 +7126,7 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" ht="48">
+    <row r="36" spans="1:16" ht="46">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -7173,7 +7172,7 @@
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" ht="48">
+    <row r="37" spans="1:16" ht="23">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -7219,7 +7218,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:16" ht="48">
+    <row r="38" spans="1:16" ht="46">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -7265,7 +7264,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:16" ht="48">
+    <row r="39" spans="1:16" ht="46">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -7309,7 +7308,7 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:16" ht="36">
+    <row r="40" spans="1:16" ht="34.5">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -7355,7 +7354,7 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
     </row>
-    <row r="41" spans="1:16" ht="72">
+    <row r="41" spans="1:16" ht="69">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -7401,7 +7400,7 @@
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
     </row>
-    <row r="42" spans="1:16" ht="72">
+    <row r="42" spans="1:16" ht="69">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -7447,7 +7446,7 @@
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="1:16" ht="72">
+    <row r="43" spans="1:16" ht="69">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -7493,7 +7492,7 @@
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
     </row>
-    <row r="44" spans="1:16" ht="72">
+    <row r="44" spans="1:16" ht="69">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -7539,7 +7538,7 @@
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
     </row>
-    <row r="45" spans="1:16" ht="72">
+    <row r="45" spans="1:16" ht="69">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -7585,7 +7584,7 @@
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
     </row>
-    <row r="46" spans="1:16" ht="72">
+    <row r="46" spans="1:16" ht="69">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -7631,7 +7630,7 @@
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
     </row>
-    <row r="47" spans="1:16" ht="72">
+    <row r="47" spans="1:16" ht="69">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -7677,7 +7676,7 @@
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
     </row>
-    <row r="48" spans="1:16" ht="72">
+    <row r="48" spans="1:16" ht="69">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -7723,7 +7722,7 @@
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
     </row>
-    <row r="49" spans="1:16" ht="72">
+    <row r="49" spans="1:16" ht="69">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -7769,7 +7768,7 @@
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
     </row>
-    <row r="50" spans="1:16" ht="72">
+    <row r="50" spans="1:16" ht="69">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -7815,7 +7814,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:16" ht="72">
+    <row r="51" spans="1:16" ht="69">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -7861,7 +7860,7 @@
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:16" ht="72">
+    <row r="52" spans="1:16" ht="69">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -7907,7 +7906,7 @@
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
     </row>
-    <row r="53" spans="1:16" ht="72">
+    <row r="53" spans="1:16" ht="69">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -7953,7 +7952,7 @@
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
     </row>
-    <row r="54" spans="1:16" ht="72">
+    <row r="54" spans="1:16" ht="69">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -7999,7 +7998,7 @@
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
     </row>
-    <row r="55" spans="1:16" ht="72">
+    <row r="55" spans="1:16" ht="69">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -8045,7 +8044,7 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
     </row>
-    <row r="56" spans="1:16" ht="72">
+    <row r="56" spans="1:16" ht="69">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -8091,7 +8090,7 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
     </row>
-    <row r="57" spans="1:16" ht="72">
+    <row r="57" spans="1:16" ht="69">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -8137,7 +8136,7 @@
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
     </row>
-    <row r="58" spans="1:16" ht="72">
+    <row r="58" spans="1:16" ht="69">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -8183,7 +8182,7 @@
       <c r="O58" s="3"/>
       <c r="P58" s="3"/>
     </row>
-    <row r="59" spans="1:16" ht="48">
+    <row r="59" spans="1:16" ht="34.5">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -8229,7 +8228,7 @@
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
     </row>
-    <row r="60" spans="1:16" ht="36">
+    <row r="60" spans="1:16" ht="46">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -8275,7 +8274,7 @@
       <c r="O60" s="3"/>
       <c r="P60" s="3"/>
     </row>
-    <row r="61" spans="1:16" ht="36">
+    <row r="61" spans="1:16" ht="34.5">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -8321,7 +8320,7 @@
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
     </row>
-    <row r="62" spans="1:16" ht="48">
+    <row r="62" spans="1:16" ht="34.5">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -8367,7 +8366,7 @@
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
     </row>
-    <row r="63" spans="1:16" ht="36">
+    <row r="63" spans="1:16" ht="34.5">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -8413,7 +8412,7 @@
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
     </row>
-    <row r="64" spans="1:16" ht="48">
+    <row r="64" spans="1:16" ht="34.5">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -8459,7 +8458,7 @@
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
     </row>
-    <row r="65" spans="1:16" ht="48">
+    <row r="65" spans="1:16" ht="34.5">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -8505,7 +8504,7 @@
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
     </row>
-    <row r="66" spans="1:16" ht="48">
+    <row r="66" spans="1:16" ht="23">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -8551,7 +8550,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:16" ht="36">
+    <row r="67" spans="1:16" ht="34.5">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -8597,7 +8596,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:16" ht="36">
+    <row r="68" spans="1:16" ht="34.5">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -8643,7 +8642,7 @@
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
     </row>
-    <row r="69" spans="1:16" ht="36">
+    <row r="69" spans="1:16" ht="46">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -8689,7 +8688,7 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:16" ht="48">
+    <row r="70" spans="1:16" ht="46">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -8735,7 +8734,7 @@
       <c r="O70" s="3"/>
       <c r="P70" s="3"/>
     </row>
-    <row r="71" spans="1:16" ht="72">
+    <row r="71" spans="1:16" ht="69">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -8781,7 +8780,7 @@
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
     </row>
-    <row r="72" spans="1:16" ht="36">
+    <row r="72" spans="1:16" ht="23">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -8827,7 +8826,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="1:16" ht="36">
+    <row r="73" spans="1:16" ht="23">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -8873,7 +8872,7 @@
       <c r="O73" s="3"/>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:16" ht="48">
+    <row r="74" spans="1:16" ht="46">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -8919,7 +8918,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:16" ht="48">
+    <row r="75" spans="1:16" ht="46">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -8965,7 +8964,7 @@
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="1:16" ht="48">
+    <row r="76" spans="1:16" ht="34.5">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -9011,7 +9010,7 @@
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
     </row>
-    <row r="77" spans="1:16" ht="36">
+    <row r="77" spans="1:16" ht="23">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -9057,7 +9056,7 @@
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:16" ht="36">
+    <row r="78" spans="1:16" ht="23">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -9103,7 +9102,7 @@
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
     </row>
-    <row r="79" spans="1:16" ht="48">
+    <row r="79" spans="1:16" ht="23">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -9149,7 +9148,7 @@
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:16" ht="48">
+    <row r="80" spans="1:16" ht="23">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -9195,7 +9194,7 @@
       <c r="O80" s="3"/>
       <c r="P80" s="3"/>
     </row>
-    <row r="81" spans="1:16" ht="48">
+    <row r="81" spans="1:16" ht="57.5">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -9241,7 +9240,7 @@
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:16" ht="48">
+    <row r="82" spans="1:16" ht="57.5">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -9287,7 +9286,7 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="1:16" ht="48">
+    <row r="83" spans="1:16" ht="57.5">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -9333,7 +9332,7 @@
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
     </row>
-    <row r="84" spans="1:16" ht="48">
+    <row r="84" spans="1:16" ht="57.5">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -9379,7 +9378,7 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:16" ht="36">
+    <row r="85" spans="1:16" ht="34.5">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -9425,7 +9424,7 @@
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
     </row>
-    <row r="86" spans="1:16" ht="48">
+    <row r="86" spans="1:16" ht="34.5">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -9471,7 +9470,7 @@
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="1:16" ht="36">
+    <row r="87" spans="1:16" ht="46">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -9517,7 +9516,7 @@
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
     </row>
-    <row r="88" spans="1:16" ht="48">
+    <row r="88" spans="1:16" ht="46">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -9563,7 +9562,7 @@
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
     </row>
-    <row r="89" spans="1:16" ht="48">
+    <row r="89" spans="1:16" ht="34.5">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -9609,7 +9608,7 @@
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:16" ht="48">
+    <row r="90" spans="1:16" ht="46">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -9655,7 +9654,7 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
     </row>
-    <row r="91" spans="1:16" ht="48">
+    <row r="91" spans="1:16" ht="46">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -9701,7 +9700,7 @@
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:16" ht="48">
+    <row r="92" spans="1:16" ht="34.5">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -9747,7 +9746,7 @@
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
     </row>
-    <row r="93" spans="1:16" ht="36">
+    <row r="93" spans="1:16" ht="23">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -9793,7 +9792,7 @@
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
     </row>
-    <row r="94" spans="1:16" ht="48">
+    <row r="94" spans="1:16" ht="34.5">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -9839,7 +9838,7 @@
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:16" ht="36">
+    <row r="95" spans="1:16" ht="34.5">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -9885,7 +9884,7 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:16" ht="36">
+    <row r="96" spans="1:16" ht="34.5">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -9931,7 +9930,7 @@
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:16" ht="48">
+    <row r="97" spans="1:16" ht="57.5">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -9977,7 +9976,7 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:16" ht="36">
+    <row r="98" spans="1:16" ht="34.5">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -10023,7 +10022,7 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
     </row>
-    <row r="99" spans="1:16" ht="48">
+    <row r="99" spans="1:16" ht="23">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -10069,7 +10068,7 @@
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
     </row>
-    <row r="100" spans="1:16" ht="48">
+    <row r="100" spans="1:16" ht="23">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -10115,7 +10114,7 @@
       <c r="O100" s="3"/>
       <c r="P100" s="3"/>
     </row>
-    <row r="101" spans="1:16" ht="48">
+    <row r="101" spans="1:16" ht="23">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -10161,7 +10160,7 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:16" ht="48">
+    <row r="102" spans="1:16" ht="34.5">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -10207,7 +10206,7 @@
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
     </row>
-    <row r="103" spans="1:16" ht="36">
+    <row r="103" spans="1:16" ht="23">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -10253,7 +10252,7 @@
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
     </row>
-    <row r="104" spans="1:16" ht="48">
+    <row r="104" spans="1:16" ht="23">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -10299,7 +10298,7 @@
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
     </row>
-    <row r="105" spans="1:16" ht="36">
+    <row r="105" spans="1:16" ht="23">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -10345,7 +10344,7 @@
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
     </row>
-    <row r="106" spans="1:16" ht="48">
+    <row r="106" spans="1:16" ht="34.5">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -10391,7 +10390,7 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:16" ht="36">
+    <row r="107" spans="1:16" ht="46">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -10437,7 +10436,7 @@
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
     </row>
-    <row r="108" spans="1:16" ht="36">
+    <row r="108" spans="1:16" ht="34.5">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -10483,7 +10482,7 @@
       <c r="O108" s="3"/>
       <c r="P108" s="3"/>
     </row>
-    <row r="109" spans="1:16" ht="48">
+    <row r="109" spans="1:16" ht="34.5">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -10529,7 +10528,7 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:16" ht="48">
+    <row r="110" spans="1:16" ht="57.5">
       <c r="A110" s="3">
         <v>107</v>
       </c>
@@ -10575,7 +10574,7 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:16" ht="48">
+    <row r="111" spans="1:16" ht="34.5">
       <c r="A111" s="3">
         <v>108</v>
       </c>
@@ -10621,7 +10620,7 @@
       <c r="O111" s="3"/>
       <c r="P111" s="3"/>
     </row>
-    <row r="112" spans="1:16" ht="48">
+    <row r="112" spans="1:16" ht="46">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -10667,7 +10666,7 @@
       <c r="O112" s="3"/>
       <c r="P112" s="3"/>
     </row>
-    <row r="113" spans="1:16" ht="48">
+    <row r="113" spans="1:16" ht="57.5">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -10713,7 +10712,7 @@
       <c r="O113" s="3"/>
       <c r="P113" s="3"/>
     </row>
-    <row r="114" spans="1:16" ht="48">
+    <row r="114" spans="1:16" ht="57.5">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -10759,7 +10758,7 @@
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
     </row>
-    <row r="115" spans="1:16" ht="48">
+    <row r="115" spans="1:16" ht="57.5">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -10805,7 +10804,7 @@
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
     </row>
-    <row r="116" spans="1:16" ht="48">
+    <row r="116" spans="1:16" ht="46">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -10851,7 +10850,7 @@
       <c r="O116" s="3"/>
       <c r="P116" s="3"/>
     </row>
-    <row r="117" spans="1:16" ht="48">
+    <row r="117" spans="1:16" ht="23">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -10897,7 +10896,7 @@
       <c r="O117" s="3"/>
       <c r="P117" s="3"/>
     </row>
-    <row r="118" spans="1:16" ht="48">
+    <row r="118" spans="1:16" ht="23">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -10943,7 +10942,7 @@
       <c r="O118" s="3"/>
       <c r="P118" s="3"/>
     </row>
-    <row r="119" spans="1:16" ht="36">
+    <row r="119" spans="1:16" ht="34.5">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -10989,7 +10988,7 @@
       <c r="O119" s="3"/>
       <c r="P119" s="3"/>
     </row>
-    <row r="120" spans="1:16" ht="48">
+    <row r="120" spans="1:16" ht="57.5">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -11035,7 +11034,7 @@
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:16" ht="36">
+    <row r="121" spans="1:16" ht="34.5">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -11081,7 +11080,7 @@
       <c r="O121" s="3"/>
       <c r="P121" s="3"/>
     </row>
-    <row r="122" spans="1:16" ht="48">
+    <row r="122" spans="1:16" ht="57.5">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -11127,7 +11126,7 @@
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
     </row>
-    <row r="123" spans="1:16" ht="36">
+    <row r="123" spans="1:16" ht="46">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -11173,7 +11172,7 @@
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
     </row>
-    <row r="124" spans="1:16" ht="36">
+    <row r="124" spans="1:16" ht="34.5">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -11219,7 +11218,7 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:16" ht="36">
+    <row r="125" spans="1:16" ht="34.5">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -11265,7 +11264,7 @@
       <c r="O125" s="3"/>
       <c r="P125" s="3"/>
     </row>
-    <row r="126" spans="1:16" ht="48">
+    <row r="126" spans="1:16" ht="34.5">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -11311,7 +11310,7 @@
       <c r="O126" s="3"/>
       <c r="P126" s="3"/>
     </row>
-    <row r="127" spans="1:16" ht="36">
+    <row r="127" spans="1:16" ht="34.5">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -11357,7 +11356,7 @@
       <c r="O127" s="3"/>
       <c r="P127" s="3"/>
     </row>
-    <row r="128" spans="1:16" ht="36">
+    <row r="128" spans="1:16" ht="34.5">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -11403,7 +11402,7 @@
       <c r="O128" s="3"/>
       <c r="P128" s="3"/>
     </row>
-    <row r="129" spans="1:16" ht="36">
+    <row r="129" spans="1:16" ht="23">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -11449,7 +11448,7 @@
       <c r="O129" s="3"/>
       <c r="P129" s="3"/>
     </row>
-    <row r="130" spans="1:16" ht="36">
+    <row r="130" spans="1:16" ht="34.5">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -11495,7 +11494,7 @@
       <c r="O130" s="3"/>
       <c r="P130" s="3"/>
     </row>
-    <row r="131" spans="1:16" ht="36">
+    <row r="131" spans="1:16" ht="34.5">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -11543,6 +11542,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -11553,85 +11555,82 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46771BB-89DD-433A-8105-216FBABD0C00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="51" t="s">
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="51" t="s">
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="60" t="s">
+      <c r="P1" s="62"/>
+      <c r="Q1" s="68" t="s">
         <v>360</v>
       </c>
-      <c r="R1" s="61"/>
+      <c r="R1" s="69"/>
       <c r="S1" s="57" t="s">
         <v>361</v>
       </c>
       <c r="T1" s="57"/>
     </row>
-    <row r="2" spans="1:20" ht="36">
+    <row r="2" spans="1:20" ht="34.5">
       <c r="A2" s="65"/>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="63"/>
-      <c r="K2" s="53" t="s">
+      <c r="J2" s="64"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="64"/>
-      <c r="M2" s="63"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="64"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -11641,28 +11640,28 @@
       <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="58" t="s">
+      <c r="Q2" s="66" t="s">
         <v>362</v>
       </c>
-      <c r="R2" s="58" t="s">
+      <c r="R2" s="66" t="s">
         <v>363</v>
       </c>
-      <c r="S2" s="58" t="s">
+      <c r="S2" s="66" t="s">
         <v>362</v>
       </c>
-      <c r="T2" s="58" t="s">
+      <c r="T2" s="66" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="60">
-      <c r="A3" s="62"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+    <row r="3" spans="1:20" ht="69">
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -11683,12 +11682,12 @@
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-    </row>
-    <row r="4" spans="1:20" ht="48">
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+    </row>
+    <row r="4" spans="1:20" ht="23">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -11736,7 +11735,7 @@
       <c r="S4" s="15"/>
       <c r="T4" s="15"/>
     </row>
-    <row r="5" spans="1:20" ht="48">
+    <row r="5" spans="1:20" ht="23">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -11784,7 +11783,7 @@
       <c r="S5" s="15"/>
       <c r="T5" s="15"/>
     </row>
-    <row r="6" spans="1:20" ht="48">
+    <row r="6" spans="1:20" ht="34.5">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -11832,7 +11831,7 @@
       <c r="S6" s="15"/>
       <c r="T6" s="15"/>
     </row>
-    <row r="7" spans="1:20" ht="48">
+    <row r="7" spans="1:20" ht="34.5">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -11880,7 +11879,7 @@
       <c r="S7" s="15"/>
       <c r="T7" s="15"/>
     </row>
-    <row r="8" spans="1:20" ht="48">
+    <row r="8" spans="1:20" ht="46">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -11928,7 +11927,7 @@
       <c r="S8" s="15"/>
       <c r="T8" s="15"/>
     </row>
-    <row r="9" spans="1:20" ht="48">
+    <row r="9" spans="1:20" ht="34.5">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -11976,7 +11975,7 @@
       <c r="S9" s="15"/>
       <c r="T9" s="15"/>
     </row>
-    <row r="10" spans="1:20" ht="36">
+    <row r="10" spans="1:20" ht="34.5">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -12026,7 +12025,7 @@
       <c r="S10" s="18"/>
       <c r="T10" s="18"/>
     </row>
-    <row r="11" spans="1:20" ht="36">
+    <row r="11" spans="1:20" ht="34.5">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -12076,7 +12075,7 @@
       </c>
       <c r="T11" s="18"/>
     </row>
-    <row r="12" spans="1:20" ht="36">
+    <row r="12" spans="1:20" ht="34.5">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -12126,7 +12125,7 @@
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
     </row>
-    <row r="13" spans="1:20" ht="36">
+    <row r="13" spans="1:20" ht="34.5">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -12176,7 +12175,7 @@
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
     </row>
-    <row r="14" spans="1:20" ht="24.75">
+    <row r="14" spans="1:20" ht="23.5">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -12226,7 +12225,7 @@
       <c r="S14" s="18"/>
       <c r="T14" s="18"/>
     </row>
-    <row r="15" spans="1:20" ht="24.75">
+    <row r="15" spans="1:20" ht="23.5">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -12276,7 +12275,7 @@
       </c>
       <c r="T15" s="18"/>
     </row>
-    <row r="16" spans="1:20" ht="24.75">
+    <row r="16" spans="1:20" ht="23.5">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -12326,7 +12325,7 @@
       </c>
       <c r="T16" s="18"/>
     </row>
-    <row r="17" spans="1:20" ht="36">
+    <row r="17" spans="1:20" ht="34.5">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -12376,7 +12375,7 @@
       </c>
       <c r="T17" s="18"/>
     </row>
-    <row r="18" spans="1:20" ht="36">
+    <row r="18" spans="1:20" ht="34.5">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -12426,7 +12425,7 @@
       </c>
       <c r="T18" s="18"/>
     </row>
-    <row r="19" spans="1:20" ht="36">
+    <row r="19" spans="1:20" ht="34.5">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -12476,7 +12475,7 @@
       </c>
       <c r="T19" s="18"/>
     </row>
-    <row r="20" spans="1:20" ht="36">
+    <row r="20" spans="1:20" ht="34.5">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -12526,7 +12525,7 @@
       <c r="S20" s="18"/>
       <c r="T20" s="18"/>
     </row>
-    <row r="21" spans="1:20" ht="24.75">
+    <row r="21" spans="1:20" ht="23.5">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -12576,7 +12575,7 @@
       </c>
       <c r="T21" s="18"/>
     </row>
-    <row r="22" spans="1:20" ht="48">
+    <row r="22" spans="1:20" ht="46">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -12626,7 +12625,7 @@
       </c>
       <c r="T22" s="18"/>
     </row>
-    <row r="23" spans="1:20" ht="48">
+    <row r="23" spans="1:20" ht="46">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -12674,7 +12673,7 @@
       </c>
       <c r="T23" s="18"/>
     </row>
-    <row r="24" spans="1:20" ht="24.75">
+    <row r="24" spans="1:20" ht="23.5">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -12724,7 +12723,7 @@
       </c>
       <c r="T24" s="18"/>
     </row>
-    <row r="25" spans="1:20" ht="36">
+    <row r="25" spans="1:20" ht="34.5">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -12774,7 +12773,7 @@
       </c>
       <c r="T25" s="18"/>
     </row>
-    <row r="26" spans="1:20" ht="24">
+    <row r="26" spans="1:20" ht="23">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -12824,7 +12823,7 @@
       </c>
       <c r="T26" s="18"/>
     </row>
-    <row r="27" spans="1:20" ht="24.75">
+    <row r="27" spans="1:20" ht="23.5">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -12872,7 +12871,7 @@
       <c r="S27" s="18"/>
       <c r="T27" s="18"/>
     </row>
-    <row r="28" spans="1:20" ht="24.75">
+    <row r="28" spans="1:20" ht="23.5">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -12920,7 +12919,7 @@
       <c r="S28" s="18"/>
       <c r="T28" s="18"/>
     </row>
-    <row r="29" spans="1:20" ht="24.75">
+    <row r="29" spans="1:20" ht="34.5">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -12970,7 +12969,7 @@
       </c>
       <c r="T29" s="18"/>
     </row>
-    <row r="30" spans="1:20" ht="48">
+    <row r="30" spans="1:20" ht="46">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -13020,7 +13019,7 @@
       </c>
       <c r="T30" s="18"/>
     </row>
-    <row r="31" spans="1:20" ht="72">
+    <row r="31" spans="1:20" ht="69">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -13068,7 +13067,7 @@
       </c>
       <c r="T31" s="18"/>
     </row>
-    <row r="32" spans="1:20" ht="36">
+    <row r="32" spans="1:20" ht="34.5">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -13118,7 +13117,7 @@
       <c r="S32" s="18"/>
       <c r="T32" s="18"/>
     </row>
-    <row r="33" spans="1:20" ht="24">
+    <row r="33" spans="1:20" ht="23">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -13152,7 +13151,7 @@
       <c r="S33" s="15"/>
       <c r="T33" s="15"/>
     </row>
-    <row r="34" spans="1:20" ht="36">
+    <row r="34" spans="1:20" ht="34.5">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -13186,7 +13185,7 @@
       <c r="S34" s="15"/>
       <c r="T34" s="15"/>
     </row>
-    <row r="35" spans="1:20" ht="24">
+    <row r="35" spans="1:20" ht="23">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -13220,7 +13219,7 @@
       <c r="S35" s="15"/>
       <c r="T35" s="15"/>
     </row>
-    <row r="36" spans="1:20" ht="36">
+    <row r="36" spans="1:20" ht="46">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -13254,7 +13253,7 @@
       <c r="S36" s="15"/>
       <c r="T36" s="15"/>
     </row>
-    <row r="37" spans="1:20" ht="24">
+    <row r="37" spans="1:20" ht="34.5">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -13288,7 +13287,7 @@
       <c r="S37" s="15"/>
       <c r="T37" s="15"/>
     </row>
-    <row r="38" spans="1:20" ht="24">
+    <row r="38" spans="1:20" ht="23">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -13322,7 +13321,7 @@
       <c r="S38" s="15"/>
       <c r="T38" s="15"/>
     </row>
-    <row r="39" spans="1:20" ht="24">
+    <row r="39" spans="1:20" ht="23">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -13356,7 +13355,7 @@
       <c r="S39" s="15"/>
       <c r="T39" s="15"/>
     </row>
-    <row r="40" spans="1:20" ht="24">
+    <row r="40" spans="1:20" ht="23">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -13390,7 +13389,7 @@
       <c r="S40" s="15"/>
       <c r="T40" s="15"/>
     </row>
-    <row r="41" spans="1:20" ht="36">
+    <row r="41" spans="1:20" ht="46">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -13424,7 +13423,7 @@
       <c r="S41" s="15"/>
       <c r="T41" s="15"/>
     </row>
-    <row r="42" spans="1:20" ht="36">
+    <row r="42" spans="1:20" ht="34.5">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -13458,7 +13457,7 @@
       <c r="S42" s="15"/>
       <c r="T42" s="15"/>
     </row>
-    <row r="43" spans="1:20" ht="36">
+    <row r="43" spans="1:20" ht="46">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -13492,7 +13491,7 @@
       <c r="S43" s="15"/>
       <c r="T43" s="15"/>
     </row>
-    <row r="44" spans="1:20" ht="24">
+    <row r="44" spans="1:20" ht="34.5">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -13526,7 +13525,7 @@
       <c r="S44" s="15"/>
       <c r="T44" s="15"/>
     </row>
-    <row r="45" spans="1:20" ht="24">
+    <row r="45" spans="1:20" ht="34.5">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -13560,7 +13559,7 @@
       <c r="S45" s="15"/>
       <c r="T45" s="15"/>
     </row>
-    <row r="46" spans="1:20" ht="24">
+    <row r="46" spans="1:20" ht="34.5">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -13594,7 +13593,7 @@
       <c r="S46" s="15"/>
       <c r="T46" s="15"/>
     </row>
-    <row r="47" spans="1:20" ht="60">
+    <row r="47" spans="1:20" ht="57.5">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -13628,7 +13627,7 @@
       <c r="S47" s="15"/>
       <c r="T47" s="15"/>
     </row>
-    <row r="48" spans="1:20" ht="36">
+    <row r="48" spans="1:20" ht="34.5">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -13662,7 +13661,7 @@
       <c r="S48" s="15"/>
       <c r="T48" s="15"/>
     </row>
-    <row r="49" spans="1:20" ht="36.75">
+    <row r="49" spans="1:20" ht="46.5">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -13698,6 +13697,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -13708,83 +13716,74 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D9A1422-081A-4032-9119-87607685BE3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P75"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="51" t="s">
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="51" t="s">
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="70"/>
-    </row>
-    <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="71"/>
-      <c r="B2" s="49" t="s">
+      <c r="P1" s="58"/>
+    </row>
+    <row r="2" spans="1:16" ht="34.5">
+      <c r="A2" s="61"/>
+      <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="70"/>
-      <c r="K2" s="53" t="s">
+      <c r="J2" s="58"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="69"/>
-      <c r="M2" s="70"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="58"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -13795,15 +13794,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="72"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
+    <row r="3" spans="1:16" ht="69">
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -13825,7 +13824,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16" ht="36">
+    <row r="4" spans="1:16" ht="23">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -13869,7 +13868,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16" ht="36">
+    <row r="5" spans="1:16" ht="34.5">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -13913,7 +13912,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="24">
+    <row r="6" spans="1:16" ht="23">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -13957,7 +13956,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="24">
+    <row r="7" spans="1:16" ht="23">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -14001,7 +14000,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" ht="24">
+    <row r="8" spans="1:16" ht="23">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -14045,7 +14044,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" ht="24">
+    <row r="9" spans="1:16" ht="23">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -14089,7 +14088,7 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="24">
+    <row r="10" spans="1:16" ht="34.5">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -14133,7 +14132,7 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="24">
+    <row r="11" spans="1:16" ht="23">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -14177,7 +14176,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" ht="24">
+    <row r="12" spans="1:16" ht="23">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -14221,7 +14220,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" ht="24">
+    <row r="13" spans="1:16" ht="23">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -14265,7 +14264,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:16" ht="24">
+    <row r="14" spans="1:16" ht="23">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -14309,7 +14308,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16" ht="24">
+    <row r="15" spans="1:16" ht="23">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -14353,7 +14352,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" ht="36">
+    <row r="16" spans="1:16" ht="34.5">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -14397,7 +14396,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" ht="24">
+    <row r="17" spans="1:16" ht="23">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -14441,7 +14440,7 @@
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="1:16" ht="24">
+    <row r="18" spans="1:16" ht="23">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -14485,7 +14484,7 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" ht="24">
+    <row r="19" spans="1:16" ht="23">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -14529,7 +14528,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" ht="36">
+    <row r="20" spans="1:16" ht="34.5">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -14573,7 +14572,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" ht="24">
+    <row r="21" spans="1:16" ht="23">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -14617,7 +14616,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" ht="24">
+    <row r="22" spans="1:16" ht="23">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -14661,7 +14660,7 @@
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" ht="60">
+    <row r="23" spans="1:16" ht="57.5">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -14705,7 +14704,7 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16" ht="24">
+    <row r="24" spans="1:16" ht="23">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -14749,7 +14748,7 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" ht="24">
+    <row r="25" spans="1:16" ht="23">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -14793,7 +14792,7 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
     </row>
-    <row r="26" spans="1:16" ht="36">
+    <row r="26" spans="1:16" ht="34.5">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -14837,7 +14836,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" ht="24">
+    <row r="27" spans="1:16" ht="23">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -14881,7 +14880,7 @@
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" ht="36">
+    <row r="28" spans="1:16" ht="34.5">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -14925,7 +14924,7 @@
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16" ht="36">
+    <row r="29" spans="1:16" ht="34.5">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -14969,7 +14968,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="24">
+    <row r="30" spans="1:16" ht="34.5">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -15013,7 +15012,7 @@
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
     </row>
-    <row r="31" spans="1:16" ht="24">
+    <row r="31" spans="1:16" ht="34.5">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -15057,7 +15056,7 @@
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16" ht="24">
+    <row r="32" spans="1:16" ht="23">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -15101,7 +15100,7 @@
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
     </row>
-    <row r="33" spans="1:16" ht="24">
+    <row r="33" spans="1:16" ht="23">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -15145,7 +15144,7 @@
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:16" ht="36">
+    <row r="34" spans="1:16" ht="34.5">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -15189,7 +15188,7 @@
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:16" ht="24">
+    <row r="35" spans="1:16" ht="23">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -15233,7 +15232,7 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" ht="24">
+    <row r="36" spans="1:16" ht="23">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -15277,7 +15276,7 @@
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" ht="36">
+    <row r="37" spans="1:16" ht="34.5">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -15321,7 +15320,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:16" ht="36">
+    <row r="38" spans="1:16" ht="34.5">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -15365,7 +15364,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:16" ht="24">
+    <row r="39" spans="1:16" ht="23">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -15409,7 +15408,7 @@
       <c r="O39" s="34"/>
       <c r="P39" s="34"/>
     </row>
-    <row r="40" spans="1:16" s="38" customFormat="1" ht="24.75">
+    <row r="40" spans="1:16" s="38" customFormat="1" ht="23.5">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -15439,7 +15438,7 @@
       <c r="O40" s="18"/>
       <c r="P40" s="18"/>
     </row>
-    <row r="41" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="41" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -15469,7 +15468,7 @@
       <c r="O41" s="18"/>
       <c r="P41" s="18"/>
     </row>
-    <row r="42" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="42" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -15499,7 +15498,7 @@
       <c r="O42" s="18"/>
       <c r="P42" s="18"/>
     </row>
-    <row r="43" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="43" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -15529,7 +15528,7 @@
       <c r="O43" s="18"/>
       <c r="P43" s="18"/>
     </row>
-    <row r="44" spans="1:16" s="38" customFormat="1" ht="24.75">
+    <row r="44" spans="1:16" s="38" customFormat="1" ht="23.5">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -15559,7 +15558,7 @@
       <c r="O44" s="18"/>
       <c r="P44" s="18"/>
     </row>
-    <row r="45" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="45" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -15589,7 +15588,7 @@
       <c r="O45" s="18"/>
       <c r="P45" s="18"/>
     </row>
-    <row r="46" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="46" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -15619,7 +15618,7 @@
       <c r="O46" s="18"/>
       <c r="P46" s="18"/>
     </row>
-    <row r="47" spans="1:16" s="38" customFormat="1" ht="24.75">
+    <row r="47" spans="1:16" s="38" customFormat="1" ht="23.5">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -15649,7 +15648,7 @@
       <c r="O47" s="18"/>
       <c r="P47" s="18"/>
     </row>
-    <row r="48" spans="1:16" s="38" customFormat="1" ht="24.75">
+    <row r="48" spans="1:16" s="38" customFormat="1" ht="23.5">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -15679,7 +15678,7 @@
       <c r="O48" s="18"/>
       <c r="P48" s="18"/>
     </row>
-    <row r="49" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="49" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -15709,7 +15708,7 @@
       <c r="O49" s="18"/>
       <c r="P49" s="18"/>
     </row>
-    <row r="50" spans="1:16" s="38" customFormat="1" ht="24.75">
+    <row r="50" spans="1:16" s="38" customFormat="1" ht="23.5">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -15739,7 +15738,7 @@
       <c r="O50" s="18"/>
       <c r="P50" s="18"/>
     </row>
-    <row r="51" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="51" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -15769,7 +15768,7 @@
       <c r="O51" s="18"/>
       <c r="P51" s="18"/>
     </row>
-    <row r="52" spans="1:16" s="38" customFormat="1" ht="24.75">
+    <row r="52" spans="1:16" s="38" customFormat="1" ht="23.5">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -15799,7 +15798,7 @@
       <c r="O52" s="18"/>
       <c r="P52" s="18"/>
     </row>
-    <row r="53" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="53" spans="1:16" s="38" customFormat="1" ht="46.5">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -15829,7 +15828,7 @@
       <c r="O53" s="18"/>
       <c r="P53" s="18"/>
     </row>
-    <row r="54" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="54" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -15859,7 +15858,7 @@
       <c r="O54" s="18"/>
       <c r="P54" s="18"/>
     </row>
-    <row r="55" spans="1:16" s="38" customFormat="1" ht="24.75">
+    <row r="55" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -15889,7 +15888,7 @@
       <c r="O55" s="18"/>
       <c r="P55" s="18"/>
     </row>
-    <row r="56" spans="1:16" s="38" customFormat="1" ht="24.75">
+    <row r="56" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -15919,7 +15918,7 @@
       <c r="O56" s="18"/>
       <c r="P56" s="18"/>
     </row>
-    <row r="57" spans="1:16" s="38" customFormat="1" ht="24.75">
+    <row r="57" spans="1:16" s="38" customFormat="1" ht="23.5">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -15949,7 +15948,7 @@
       <c r="O57" s="18"/>
       <c r="P57" s="18"/>
     </row>
-    <row r="58" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="58" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -15979,7 +15978,7 @@
       <c r="O58" s="18"/>
       <c r="P58" s="18"/>
     </row>
-    <row r="59" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="59" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -16009,7 +16008,7 @@
       <c r="O59" s="18"/>
       <c r="P59" s="18"/>
     </row>
-    <row r="60" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="60" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -16039,7 +16038,7 @@
       <c r="O60" s="18"/>
       <c r="P60" s="18"/>
     </row>
-    <row r="61" spans="1:16" ht="36">
+    <row r="61" spans="1:16" ht="34.5">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -16083,7 +16082,7 @@
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
     </row>
-    <row r="62" spans="1:16" ht="24">
+    <row r="62" spans="1:16" ht="23">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -16127,7 +16126,7 @@
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
     </row>
-    <row r="63" spans="1:16" ht="48">
+    <row r="63" spans="1:16" ht="46">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -16171,7 +16170,7 @@
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
     </row>
-    <row r="64" spans="1:16" ht="36">
+    <row r="64" spans="1:16" ht="34.5">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -16215,7 +16214,7 @@
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
     </row>
-    <row r="65" spans="1:16" ht="24">
+    <row r="65" spans="1:16" ht="23">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -16259,7 +16258,7 @@
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
     </row>
-    <row r="66" spans="1:16" ht="24">
+    <row r="66" spans="1:16" ht="23">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -16303,7 +16302,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:16" ht="48">
+    <row r="67" spans="1:16" ht="46">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -16347,7 +16346,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:16" ht="24">
+    <row r="68" spans="1:16" ht="23">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -16391,7 +16390,7 @@
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
     </row>
-    <row r="69" spans="1:16" ht="24">
+    <row r="69" spans="1:16" ht="23">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -16435,7 +16434,7 @@
       <c r="O69" s="34"/>
       <c r="P69" s="34"/>
     </row>
-    <row r="70" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="70" spans="1:16" s="38" customFormat="1" ht="46.5">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -16465,7 +16464,7 @@
       <c r="O70" s="18"/>
       <c r="P70" s="18"/>
     </row>
-    <row r="71" spans="1:16" s="38" customFormat="1" ht="24.75">
+    <row r="71" spans="1:16" s="38" customFormat="1" ht="23.5">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -16495,7 +16494,7 @@
       <c r="O71" s="18"/>
       <c r="P71" s="18"/>
     </row>
-    <row r="72" spans="1:16" s="38" customFormat="1" ht="48.75">
+    <row r="72" spans="1:16" s="38" customFormat="1" ht="58">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -16525,7 +16524,7 @@
       <c r="O72" s="18"/>
       <c r="P72" s="18"/>
     </row>
-    <row r="73" spans="1:16" s="38" customFormat="1" ht="36.75">
+    <row r="73" spans="1:16" s="38" customFormat="1" ht="35">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -16555,7 +16554,7 @@
       <c r="O73" s="15"/>
       <c r="P73" s="15"/>
     </row>
-    <row r="74" spans="1:16" ht="24">
+    <row r="74" spans="1:16" ht="23">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -16599,7 +16598,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:16" ht="48">
+    <row r="75" spans="1:16" ht="46">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -16645,6 +16644,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -16655,9 +16657,6 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16665,48 +16664,48 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB463F11-FE12-4B34-ACD4-CF4C05A95709}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:16" s="12" customFormat="1" ht="12">
+    <row r="1" spans="1:16" s="12" customFormat="1" ht="11.5">
       <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
       <c r="I1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
       <c r="O1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="67"/>
-    </row>
-    <row r="2" spans="1:16" s="12" customFormat="1" ht="36">
-      <c r="A2" s="67"/>
+      <c r="P1" s="71"/>
+    </row>
+    <row r="2" spans="1:16" s="12" customFormat="1" ht="34.5">
+      <c r="A2" s="71"/>
       <c r="B2" s="57" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="72" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="57" t="s">
@@ -16721,12 +16720,12 @@
       <c r="I2" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="67"/>
+      <c r="J2" s="71"/>
       <c r="K2" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -16737,15 +16736,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="12" customFormat="1" ht="60">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+    <row r="3" spans="1:16" s="12" customFormat="1" ht="69">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -16767,7 +16766,7 @@
       <c r="O3" s="14"/>
       <c r="P3" s="14"/>
     </row>
-    <row r="4" spans="1:16" ht="24.75">
+    <row r="4" spans="1:16" ht="23.5">
       <c r="A4" s="18">
         <v>1</v>
       </c>
@@ -16797,7 +16796,7 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:16" ht="36">
+    <row r="5" spans="1:16" ht="34.5">
       <c r="A5" s="18">
         <v>2</v>
       </c>
@@ -16827,7 +16826,7 @@
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:16" ht="36">
+    <row r="6" spans="1:16" ht="34.5">
       <c r="A6" s="18">
         <v>3</v>
       </c>
@@ -16857,7 +16856,7 @@
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:16" ht="24.75">
+    <row r="7" spans="1:16" ht="23.5">
       <c r="A7" s="18">
         <v>4</v>
       </c>
@@ -16887,7 +16886,7 @@
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:16" ht="60">
+    <row r="8" spans="1:16" ht="57.5">
       <c r="A8" s="18">
         <v>5</v>
       </c>
@@ -16917,7 +16916,7 @@
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:16" ht="48">
+    <row r="9" spans="1:16" ht="46">
       <c r="A9" s="18">
         <v>6</v>
       </c>
@@ -16947,7 +16946,7 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:16" ht="24.75">
+    <row r="10" spans="1:16" ht="23.5">
       <c r="A10" s="18">
         <v>7</v>
       </c>
@@ -16977,7 +16976,7 @@
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
     </row>
-    <row r="11" spans="1:16" ht="36">
+    <row r="11" spans="1:16" ht="34.5">
       <c r="A11" s="18">
         <v>8</v>
       </c>
@@ -17009,6 +17008,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -17019,29 +17021,26 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B33F83-065C-49D4-A474-92075A5F6A86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R22"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="9.140625" style="12"/>
-    <col min="5" max="5" width="12.28515625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="9.140625" style="12"/>
-    <col min="13" max="13" width="9.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="12"/>
-    <col min="15" max="15" width="9.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="1" width="9.4140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.1640625" style="12"/>
+    <col min="5" max="5" width="12.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.58203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="9.1640625" style="12"/>
+    <col min="13" max="13" width="9.4140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.1640625" style="12"/>
+    <col min="15" max="15" width="9.4140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.1640625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="31" customFormat="1">
@@ -17072,7 +17071,7 @@
       <c r="Q1" s="57"/>
       <c r="R1" s="57"/>
     </row>
-    <row r="2" spans="1:18" s="31" customFormat="1" ht="24">
+    <row r="2" spans="1:18" s="31" customFormat="1" ht="23">
       <c r="A2" s="57"/>
       <c r="B2" s="57" t="s">
         <v>4</v>
@@ -17081,7 +17080,7 @@
         <v>588</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>589</v>
+        <v>5</v>
       </c>
       <c r="E2" s="57" t="s">
         <v>6</v>
@@ -17090,7 +17089,7 @@
         <v>7</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H2" s="57" t="s">
         <v>9</v>
@@ -17111,14 +17110,14 @@
         <v>13</v>
       </c>
       <c r="P2" s="57" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q2" s="57" t="s">
         <v>591</v>
       </c>
-      <c r="Q2" s="57" t="s">
-        <v>592</v>
-      </c>
       <c r="R2" s="57"/>
     </row>
-    <row r="3" spans="1:18" s="31" customFormat="1" ht="36">
+    <row r="3" spans="1:18" s="31" customFormat="1" ht="34.5">
       <c r="A3" s="57"/>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -17138,32 +17137,32 @@
         <v>18</v>
       </c>
       <c r="M3" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="N3" s="14" t="s">
         <v>593</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="O3" s="14" t="s">
         <v>594</v>
-      </c>
-      <c r="O3" s="14" t="s">
-        <v>595</v>
       </c>
       <c r="P3" s="57"/>
       <c r="Q3" s="14" t="s">
+        <v>595</v>
+      </c>
+      <c r="R3" s="14" t="s">
         <v>596</v>
       </c>
-      <c r="R3" s="14" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="36">
+    </row>
+    <row r="4" spans="1:18" ht="34.5">
       <c r="A4" s="18">
         <v>1</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22" t="s">
+        <v>597</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>598</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>599</v>
       </c>
       <c r="E4" s="18">
         <v>-2.6519999999999998E-2</v>
@@ -17179,17 +17178,17 @@
         <v>25</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="K4" s="22" t="s">
         <v>600</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>601</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="45">
         <v>825</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O4" s="18">
         <v>2025</v>
@@ -17200,13 +17199,13 @@
       <c r="Q4" s="22"/>
       <c r="R4" s="22"/>
     </row>
-    <row r="5" spans="1:18" ht="36">
+    <row r="5" spans="1:18" ht="34.5">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>451</v>
@@ -17222,20 +17221,20 @@
         <v>451</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="K5" s="22" t="s">
         <v>600</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>601</v>
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="45">
         <v>4500</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O5" s="18">
         <v>2025</v>
@@ -17246,16 +17245,16 @@
       <c r="Q5" s="22"/>
       <c r="R5" s="22"/>
     </row>
-    <row r="6" spans="1:18" ht="36">
+    <row r="6" spans="1:18" ht="34.5">
       <c r="A6" s="18">
         <v>3</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E6" s="18">
         <v>-5.6816999999999999E-2</v>
@@ -17268,20 +17267,20 @@
         <v>456</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="K6" s="22" t="s">
         <v>600</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>601</v>
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="45">
         <v>3800</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O6" s="18">
         <v>2025</v>
@@ -17292,16 +17291,16 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="22"/>
     </row>
-    <row r="7" spans="1:18" ht="36">
+    <row r="7" spans="1:18" ht="34.5">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E7" s="18">
         <v>-6.4637E-2</v>
@@ -17314,20 +17313,20 @@
         <v>460</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J7" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="K7" s="22" t="s">
         <v>600</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>601</v>
       </c>
       <c r="L7" s="22"/>
       <c r="M7" s="45">
         <v>4600</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O7" s="18">
         <v>2025</v>
@@ -17338,16 +17337,16 @@
       <c r="Q7" s="22"/>
       <c r="R7" s="22"/>
     </row>
-    <row r="8" spans="1:18" ht="36">
+    <row r="8" spans="1:18" ht="34.5">
       <c r="A8" s="18">
         <v>5</v>
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E8" s="18">
         <v>-7.3205999999999993E-2</v>
@@ -17357,23 +17356,23 @@
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="22" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J8" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="K8" s="22" t="s">
         <v>600</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>601</v>
       </c>
       <c r="L8" s="22"/>
       <c r="M8" s="45">
         <v>6300</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O8" s="18">
         <v>2025</v>
@@ -17384,16 +17383,16 @@
       <c r="Q8" s="22"/>
       <c r="R8" s="22"/>
     </row>
-    <row r="9" spans="1:18" ht="36">
+    <row r="9" spans="1:18" ht="34.5">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E9" s="18">
         <v>-6.6999000000000003E-2</v>
@@ -17403,23 +17402,23 @@
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="22" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J9" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="K9" s="22" t="s">
         <v>600</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>601</v>
       </c>
       <c r="L9" s="22"/>
       <c r="M9" s="45">
         <v>2100</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O9" s="18">
         <v>2025</v>
@@ -17430,16 +17429,16 @@
       <c r="Q9" s="22"/>
       <c r="R9" s="22"/>
     </row>
-    <row r="10" spans="1:18" ht="48">
+    <row r="10" spans="1:18" ht="46">
       <c r="A10" s="18">
         <v>7</v>
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E10" s="18">
         <v>-2.4538889000000001E-2</v>
@@ -17449,13 +17448,13 @@
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="J10" s="22" t="s">
         <v>610</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>611</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>27</v>
@@ -17474,16 +17473,16 @@
       <c r="Q10" s="22"/>
       <c r="R10" s="22"/>
     </row>
-    <row r="11" spans="1:18" ht="48">
+    <row r="11" spans="1:18" ht="46">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E11" s="18">
         <v>-5.7777800000000004E-4</v>
@@ -17493,13 +17492,13 @@
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="J11" s="22" t="s">
         <v>610</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>611</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>27</v>
@@ -17518,16 +17517,16 @@
       <c r="Q11" s="22"/>
       <c r="R11" s="22"/>
     </row>
-    <row r="12" spans="1:18" ht="60">
+    <row r="12" spans="1:18" ht="69">
       <c r="A12" s="18">
         <v>9</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E12" s="18">
         <v>-3.3805556E-2</v>
@@ -17543,7 +17542,7 @@
         <v>383</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>27</v>
@@ -17562,16 +17561,16 @@
       <c r="Q12" s="22"/>
       <c r="R12" s="22"/>
     </row>
-    <row r="13" spans="1:18" ht="72">
+    <row r="13" spans="1:18" ht="69">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E13" s="18">
         <v>-3.3805556E-2</v>
@@ -17581,13 +17580,13 @@
       </c>
       <c r="G13" s="18"/>
       <c r="H13" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="J13" s="22" t="s">
         <v>610</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>611</v>
       </c>
       <c r="K13" s="22" t="s">
         <v>27</v>
@@ -17606,16 +17605,16 @@
       <c r="Q13" s="22"/>
       <c r="R13" s="22"/>
     </row>
-    <row r="14" spans="1:18" ht="60">
+    <row r="14" spans="1:18" ht="57.5">
       <c r="A14" s="18">
         <v>11</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E14" s="18">
         <v>-3.8888900000000001E-4</v>
@@ -17625,13 +17624,13 @@
       </c>
       <c r="G14" s="18"/>
       <c r="H14" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="J14" s="22" t="s">
         <v>610</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="J14" s="22" t="s">
-        <v>611</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>27</v>
@@ -17650,16 +17649,16 @@
       <c r="Q14" s="22"/>
       <c r="R14" s="22"/>
     </row>
-    <row r="15" spans="1:18" ht="60">
+    <row r="15" spans="1:18" ht="69">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E15" s="18">
         <v>-3.3805556E-2</v>
@@ -17675,7 +17674,7 @@
         <v>383</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K15" s="22" t="s">
         <v>27</v>
@@ -17694,16 +17693,16 @@
       <c r="Q15" s="22"/>
       <c r="R15" s="22"/>
     </row>
-    <row r="16" spans="1:18" ht="60">
+    <row r="16" spans="1:18" ht="57.5">
       <c r="A16" s="18">
         <v>13</v>
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E16" s="18">
         <v>-3.5644443999999997E-2</v>
@@ -17713,13 +17712,13 @@
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="J16" s="22" t="s">
         <v>610</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="J16" s="22" t="s">
-        <v>611</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>27</v>
@@ -17738,16 +17737,16 @@
       <c r="Q16" s="22"/>
       <c r="R16" s="22"/>
     </row>
-    <row r="17" spans="1:18" ht="60">
+    <row r="17" spans="1:18" ht="57.5">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E17" s="18">
         <v>-3.1629999999999998E-2</v>
@@ -17757,13 +17756,13 @@
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="22" t="s">
+        <v>609</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="J17" s="22" t="s">
         <v>610</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>611</v>
       </c>
       <c r="K17" s="22" t="s">
         <v>27</v>
@@ -17782,16 +17781,16 @@
       <c r="Q17" s="22"/>
       <c r="R17" s="22"/>
     </row>
-    <row r="18" spans="1:18" ht="72">
+    <row r="18" spans="1:18" ht="69">
       <c r="A18" s="18">
         <v>15</v>
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E18" s="18">
         <v>-6.3280000000000003E-2</v>
@@ -17804,10 +17803,10 @@
         <v>451</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>27</v>
@@ -17826,16 +17825,16 @@
       <c r="Q18" s="22"/>
       <c r="R18" s="22"/>
     </row>
-    <row r="19" spans="1:18" ht="96">
+    <row r="19" spans="1:18" ht="92">
       <c r="A19" s="18">
         <v>16</v>
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E19" s="18">
         <v>-2.9803E-2</v>
@@ -17848,10 +17847,10 @@
         <v>460</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K19" s="22" t="s">
         <v>27</v>
@@ -17870,16 +17869,16 @@
       <c r="Q19" s="22"/>
       <c r="R19" s="22"/>
     </row>
-    <row r="20" spans="1:18" ht="96">
+    <row r="20" spans="1:18" ht="92">
       <c r="A20" s="18">
         <v>17</v>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E20" s="18">
         <v>-1.1709999999999999E-3</v>
@@ -17889,13 +17888,13 @@
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="22" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>98</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K20" s="22" t="s">
         <v>27</v>
@@ -17914,16 +17913,16 @@
       <c r="Q20" s="22"/>
       <c r="R20" s="22"/>
     </row>
-    <row r="21" spans="1:18" ht="84">
+    <row r="21" spans="1:18" ht="80.5">
       <c r="A21" s="18">
         <v>18</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E21" s="18">
         <v>5.3839999999999999E-3</v>
@@ -17939,7 +17938,7 @@
         <v>98</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K21" s="22" t="s">
         <v>27</v>
@@ -17958,16 +17957,16 @@
       <c r="Q21" s="22"/>
       <c r="R21" s="22"/>
     </row>
-    <row r="22" spans="1:18" ht="60">
+    <row r="22" spans="1:18" ht="46">
       <c r="A22" s="18">
         <v>19</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E22" s="18">
         <v>-2.9825000000000001E-2</v>
@@ -17983,7 +17982,7 @@
         <v>98</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K22" s="22" t="s">
         <v>27</v>
@@ -18026,14 +18025,14 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87310F7-40E5-44CA-A68B-9F0CB665F765}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="3" width="9.140625" style="12"/>
-    <col min="4" max="4" width="9.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="9.1640625" style="12"/>
+    <col min="4" max="4" width="9.25" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="12"/>
+    <col min="6" max="16384" width="9.1640625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -18043,37 +18042,37 @@
       <c r="B1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
       <c r="I1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
       <c r="O1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="67"/>
-    </row>
-    <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="67"/>
+      <c r="P1" s="71"/>
+    </row>
+    <row r="2" spans="1:16" ht="34.5">
+      <c r="A2" s="71"/>
       <c r="B2" s="57" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="72" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="57" t="s">
@@ -18088,12 +18087,12 @@
       <c r="I2" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="67"/>
+      <c r="J2" s="71"/>
       <c r="K2" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -18104,15 +18103,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+    <row r="3" spans="1:16" ht="57.5">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -18134,13 +18133,13 @@
       <c r="O3" s="14"/>
       <c r="P3" s="14"/>
     </row>
-    <row r="4" spans="1:16" ht="24">
+    <row r="4" spans="1:16" ht="23">
       <c r="A4" s="27">
         <v>1</v>
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D4" s="47">
         <v>-5.3099999999999996E-3</v>
@@ -18166,13 +18165,13 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:16" ht="24">
+    <row r="5" spans="1:16" ht="23">
       <c r="A5" s="27">
         <v>2</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D5" s="47">
         <v>-3.29E-3</v>
@@ -18198,13 +18197,13 @@
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:16" ht="24">
+    <row r="6" spans="1:16" ht="23">
       <c r="A6" s="27">
         <v>3</v>
       </c>
       <c r="B6" s="25"/>
       <c r="C6" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D6" s="47">
         <v>-6.4999999999999997E-3</v>
@@ -18230,13 +18229,13 @@
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:16" ht="24">
+    <row r="7" spans="1:16" ht="23">
       <c r="A7" s="27">
         <v>4</v>
       </c>
       <c r="B7" s="25"/>
       <c r="C7" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D7" s="47">
         <v>-1.0200000000000001E-2</v>
@@ -18262,13 +18261,13 @@
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:16" ht="24">
+    <row r="8" spans="1:16" ht="23">
       <c r="A8" s="27">
         <v>5</v>
       </c>
       <c r="B8" s="25"/>
       <c r="C8" s="25" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D8" s="47">
         <v>-8.5900000000000004E-3</v>
@@ -18294,13 +18293,13 @@
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:16" ht="24">
+    <row r="9" spans="1:16" ht="23">
       <c r="A9" s="27">
         <v>6</v>
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="25" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D9" s="47">
         <v>-6.2599999999999999E-3</v>
@@ -18326,13 +18325,13 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:16" ht="24">
+    <row r="10" spans="1:16" ht="23">
       <c r="A10" s="27">
         <v>7</v>
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="25" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D10" s="47">
         <v>-6.5300000000000002E-3</v>
@@ -18358,13 +18357,13 @@
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
     </row>
-    <row r="11" spans="1:16" ht="24">
+    <row r="11" spans="1:16" ht="23">
       <c r="A11" s="27">
         <v>8</v>
       </c>
       <c r="B11" s="25"/>
       <c r="C11" s="25" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D11" s="47">
         <v>-3.63E-3</v>
@@ -18390,13 +18389,13 @@
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
     </row>
-    <row r="12" spans="1:16" ht="36">
+    <row r="12" spans="1:16" ht="34.5">
       <c r="A12" s="27">
         <v>9</v>
       </c>
       <c r="B12" s="25"/>
       <c r="C12" s="25" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D12" s="47">
         <v>-3.7399999999999998E-3</v>
@@ -18424,6 +18423,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -18434,35 +18436,12 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumen" ma:contentTypeID="0x010100CCD785251A4E724B934A12AB8BE46060" ma:contentTypeVersion="12" ma:contentTypeDescription="Buat sebuah dokumen baru." ma:contentTypeScope="" ma:versionID="5ae3aba09e4cbefebb89020ec97f4692">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15954fb3-4959-4f5b-ae14-d7aa01180869" xmlns:ns3="4ce1a36b-806a-4732-b893-33b689d3fa0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f158cec65280218b3e83bd78c7c2c412" ns2:_="" ns3:_="">
     <xsd:import namespace="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
@@ -18663,14 +18642,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{495DAE39-1778-4C6E-AEB5-6769AAD718EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF8C012-57B8-49D3-9EF1-E19A730B86BA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
+    <ds:schemaRef ds:uri="4ce1a36b-806a-4732-b893-33b689d3fa0c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5380809C-BC60-49CE-8A28-8AFE265843E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5380809C-BC60-49CE-8A28-8AFE265843E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF8C012-57B8-49D3-9EF1-E19A730B86BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{495DAE39-1778-4C6E-AEB5-6769AAD718EA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
+    <ds:schemaRef ds:uri="4ce1a36b-806a-4732-b893-33b689d3fa0c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/processed/eksposur_pontianak_0408.xlsx
+++ b/data/processed/eksposur_pontianak_0408.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lndpontianak\data\Processed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCE6E2EB-8391-49FD-AAD7-D3691255B5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
   </bookViews>
   <sheets>
     <sheet name="Government" sheetId="4" r:id="rId1"/>
@@ -21,7 +22,7 @@
     <sheet name="Drainage" sheetId="6" r:id="rId7"/>
     <sheet name="Commerce" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="632">
   <si>
     <t>No</t>
   </si>
@@ -1812,6 +1813,9 @@
   </si>
   <si>
     <t>Dinas Terkait</t>
+  </si>
+  <si>
+    <t>Alamat/Nama Lokasi</t>
   </si>
   <si>
     <t xml:space="preserve">Elevasi Tanah </t>
@@ -1943,11 +1947,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -2674,7 +2678,7 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -2750,7 +2754,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2815,10 +2819,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2848,10 +2852,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2885,56 +2885,60 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="48">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma 2" xfId="42"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Aksen1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Aksen2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Aksen3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Aksen4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Aksen5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Aksen6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Baik" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Buruk" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Catatan" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Comma 2" xfId="42" xr:uid="{071DFD07-A886-4C11-96A5-6176808154D1}"/>
+    <cellStyle name="Judul" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Judul 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Judul 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Judul 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Judul 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Keluaran" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Masukan" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Netral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="43"/>
-    <cellStyle name="Normal 2 2" xfId="44"/>
-    <cellStyle name="Normal 3" xfId="46"/>
-    <cellStyle name="Normal 4" xfId="45"/>
-    <cellStyle name="Normal 4 2" xfId="47"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Normal 2" xfId="43" xr:uid="{4E188F66-CAA9-416A-BC93-00605C60F9D7}"/>
+    <cellStyle name="Normal 2 2" xfId="44" xr:uid="{976B63DB-F82F-4DB4-8F9C-4DF64240E1C5}"/>
+    <cellStyle name="Normal 3" xfId="46" xr:uid="{147433F4-047F-41AE-910E-8F970A8C42C3}"/>
+    <cellStyle name="Normal 4" xfId="45" xr:uid="{962C83EE-A302-4754-944F-516A7951F0BC}"/>
+    <cellStyle name="Normal 4 2" xfId="47" xr:uid="{26DC9524-C075-454E-A1FD-E56F75C07D23}"/>
+    <cellStyle name="Perhitungan" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Sel Periksa" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Sel Tertaut" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Teks Penjelasan" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Teks Peringatan" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3265,11 +3269,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{741E0914-794E-4459-9DF3-6A5AD35A0FD3}">
   <dimension ref="A1:P53"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="16384" width="9.1640625" style="13"/>
+    <col min="1" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3298,7 +3302,7 @@
       </c>
       <c r="P1" s="50"/>
     </row>
-    <row r="2" spans="1:16" ht="34.5">
+    <row r="2" spans="1:16" ht="36">
       <c r="A2" s="56"/>
       <c r="B2" s="51" t="s">
         <v>4</v>
@@ -3340,7 +3344,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="57.5">
+    <row r="3" spans="1:16" ht="60">
       <c r="A3" s="52"/>
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
@@ -3370,7 +3374,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16" ht="34.5">
+    <row r="4" spans="1:16" ht="36">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3414,7 +3418,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16" ht="46">
+    <row r="5" spans="1:16" ht="48">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3458,7 +3462,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="46">
+    <row r="6" spans="1:16" ht="48">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3502,7 +3506,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="57.5">
+    <row r="7" spans="1:16" ht="60">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -3546,7 +3550,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" ht="80.5">
+    <row r="8" spans="1:16" ht="84">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -3590,7 +3594,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" ht="92">
+    <row r="9" spans="1:16" ht="96">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -3634,7 +3638,7 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="57.5">
+    <row r="10" spans="1:16" ht="60">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -3678,7 +3682,7 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="80.5">
+    <row r="11" spans="1:16" ht="84">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -3722,7 +3726,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" ht="57.5">
+    <row r="12" spans="1:16" ht="48">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -3766,7 +3770,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" ht="92">
+    <row r="13" spans="1:16" ht="96">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -3810,7 +3814,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:16" ht="103.5">
+    <row r="14" spans="1:16" ht="108">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -3854,7 +3858,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16" ht="103.5">
+    <row r="15" spans="1:16" ht="108">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -3898,7 +3902,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" ht="69">
+    <row r="16" spans="1:16" ht="72">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -3942,7 +3946,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" ht="103.5">
+    <row r="17" spans="1:16" ht="108">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -3986,7 +3990,7 @@
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="1:16" ht="103.5">
+    <row r="18" spans="1:16" ht="120">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -4030,7 +4034,7 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" ht="57.5">
+    <row r="19" spans="1:16" ht="60">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -4074,7 +4078,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" ht="34.5">
+    <row r="20" spans="1:16" ht="36">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -4118,7 +4122,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" ht="34.5">
+    <row r="21" spans="1:16" ht="48">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -4162,7 +4166,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" ht="34.5">
+    <row r="22" spans="1:16" ht="36">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -4206,7 +4210,7 @@
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" ht="34.5">
+    <row r="23" spans="1:16" ht="48">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -4250,7 +4254,7 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16" ht="80.5">
+    <row r="24" spans="1:16" ht="84">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -4294,7 +4298,7 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" ht="92">
+    <row r="25" spans="1:16" ht="108">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -4338,7 +4342,7 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
     </row>
-    <row r="26" spans="1:16" ht="57.5">
+    <row r="26" spans="1:16" ht="60">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -4382,7 +4386,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" ht="46">
+    <row r="27" spans="1:16" ht="48">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -4426,7 +4430,7 @@
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" ht="46">
+    <row r="28" spans="1:16" ht="48">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -4470,7 +4474,7 @@
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16" ht="34.5">
+    <row r="29" spans="1:16" ht="48">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -4514,7 +4518,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="34.5">
+    <row r="30" spans="1:16" ht="48">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -4544,7 +4548,7 @@
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
     </row>
-    <row r="31" spans="1:16" ht="34.5">
+    <row r="31" spans="1:16" ht="48">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -4570,7 +4574,7 @@
       <c r="O31" s="15"/>
       <c r="P31" s="15"/>
     </row>
-    <row r="32" spans="1:16" ht="34.5">
+    <row r="32" spans="1:16" ht="48">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -4596,7 +4600,7 @@
       <c r="O32" s="15"/>
       <c r="P32" s="15"/>
     </row>
-    <row r="33" spans="1:16" ht="34.5">
+    <row r="33" spans="1:16" ht="48">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -4622,7 +4626,7 @@
       <c r="O33" s="15"/>
       <c r="P33" s="15"/>
     </row>
-    <row r="34" spans="1:16" ht="34.5">
+    <row r="34" spans="1:16" ht="48">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -4648,7 +4652,7 @@
       <c r="O34" s="15"/>
       <c r="P34" s="15"/>
     </row>
-    <row r="35" spans="1:16" ht="34.5">
+    <row r="35" spans="1:16" ht="48">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -4674,7 +4678,7 @@
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
     </row>
-    <row r="36" spans="1:16" ht="34.5">
+    <row r="36" spans="1:16" ht="48">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -4700,7 +4704,7 @@
       <c r="O36" s="15"/>
       <c r="P36" s="15"/>
     </row>
-    <row r="37" spans="1:16" ht="34.5">
+    <row r="37" spans="1:16" ht="48">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -4726,7 +4730,7 @@
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
     </row>
-    <row r="38" spans="1:16" ht="46">
+    <row r="38" spans="1:16" ht="48">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -4752,7 +4756,7 @@
       <c r="O38" s="15"/>
       <c r="P38" s="15"/>
     </row>
-    <row r="39" spans="1:16" ht="23">
+    <row r="39" spans="1:16" ht="24">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -4778,7 +4782,7 @@
       <c r="O39" s="15"/>
       <c r="P39" s="15"/>
     </row>
-    <row r="40" spans="1:16" ht="34.5">
+    <row r="40" spans="1:16" ht="48">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -4804,7 +4808,7 @@
       <c r="O40" s="15"/>
       <c r="P40" s="15"/>
     </row>
-    <row r="41" spans="1:16" ht="34.5">
+    <row r="41" spans="1:16" ht="48">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -4830,7 +4834,7 @@
       <c r="O41" s="15"/>
       <c r="P41" s="15"/>
     </row>
-    <row r="42" spans="1:16" ht="23">
+    <row r="42" spans="1:16" ht="24">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -4856,7 +4860,7 @@
       <c r="O42" s="15"/>
       <c r="P42" s="15"/>
     </row>
-    <row r="43" spans="1:16" ht="23">
+    <row r="43" spans="1:16" ht="24">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -4882,7 +4886,7 @@
       <c r="O43" s="15"/>
       <c r="P43" s="15"/>
     </row>
-    <row r="44" spans="1:16" ht="23">
+    <row r="44" spans="1:16" ht="24">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -4908,7 +4912,7 @@
       <c r="O44" s="15"/>
       <c r="P44" s="15"/>
     </row>
-    <row r="45" spans="1:16" ht="23">
+    <row r="45" spans="1:16" ht="24">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -4934,7 +4938,7 @@
       <c r="O45" s="15"/>
       <c r="P45" s="15"/>
     </row>
-    <row r="46" spans="1:16" ht="23">
+    <row r="46" spans="1:16" ht="24">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -4960,7 +4964,7 @@
       <c r="O46" s="15"/>
       <c r="P46" s="15"/>
     </row>
-    <row r="47" spans="1:16" ht="23">
+    <row r="47" spans="1:16" ht="24">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -4986,7 +4990,7 @@
       <c r="O47" s="15"/>
       <c r="P47" s="15"/>
     </row>
-    <row r="48" spans="1:16" ht="23">
+    <row r="48" spans="1:16" ht="24">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -5012,7 +5016,7 @@
       <c r="O48" s="15"/>
       <c r="P48" s="15"/>
     </row>
-    <row r="49" spans="1:16" ht="23">
+    <row r="49" spans="1:16" ht="24">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -5038,7 +5042,7 @@
       <c r="O49" s="15"/>
       <c r="P49" s="15"/>
     </row>
-    <row r="50" spans="1:16" ht="23">
+    <row r="50" spans="1:16" ht="24">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -5064,7 +5068,7 @@
       <c r="O50" s="15"/>
       <c r="P50" s="15"/>
     </row>
-    <row r="51" spans="1:16" ht="23">
+    <row r="51" spans="1:16" ht="24">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -5090,7 +5094,7 @@
       <c r="O51" s="15"/>
       <c r="P51" s="15"/>
     </row>
-    <row r="52" spans="1:16" ht="23">
+    <row r="52" spans="1:16" ht="24">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -5116,7 +5120,7 @@
       <c r="O52" s="15"/>
       <c r="P52" s="15"/>
     </row>
-    <row r="53" spans="1:16" ht="23">
+    <row r="53" spans="1:16" ht="24">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -5163,19 +5167,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAA9516-305B-4836-BCCE-9F2C4DDEF1CF}">
   <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="9.1640625" style="12"/>
-    <col min="5" max="5" width="9.4140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="9.1640625" style="12"/>
-    <col min="11" max="14" width="9.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.140625" style="12"/>
+    <col min="5" max="5" width="9.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="9.140625" style="12"/>
+    <col min="11" max="14" width="9.28515625" style="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.1640625" style="12"/>
+    <col min="16" max="16" width="14.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -5204,7 +5208,7 @@
       </c>
       <c r="P1" s="57"/>
     </row>
-    <row r="2" spans="1:16" ht="23">
+    <row r="2" spans="1:16" ht="24">
       <c r="A2" s="57"/>
       <c r="B2" s="57" t="s">
         <v>4</v>
@@ -5246,7 +5250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="57.5">
+    <row r="3" spans="1:16" ht="60">
       <c r="A3" s="57"/>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -5276,7 +5280,7 @@
       <c r="O3" s="57"/>
       <c r="P3" s="57"/>
     </row>
-    <row r="4" spans="1:16" ht="34.5">
+    <row r="4" spans="1:16" ht="36">
       <c r="A4" s="18">
         <v>1</v>
       </c>
@@ -5326,7 +5330,7 @@
         <v>775248795</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="46">
+    <row r="5" spans="1:16" ht="36">
       <c r="A5" s="18">
         <v>2</v>
       </c>
@@ -5376,7 +5380,7 @@
         <v>323473870</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="23">
+    <row r="6" spans="1:16" ht="24">
       <c r="A6" s="18">
         <v>3</v>
       </c>
@@ -5426,7 +5430,7 @@
         <v>485728416</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="34.5">
+    <row r="7" spans="1:16" ht="36">
       <c r="A7" s="18">
         <v>4</v>
       </c>
@@ -5476,7 +5480,7 @@
         <v>356396320</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="46">
+    <row r="8" spans="1:16" ht="48">
       <c r="A8" s="18">
         <v>5</v>
       </c>
@@ -5549,12 +5553,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6FE8C78-4599-4F29-B606-1E7F433DA21D}">
   <dimension ref="A1:P131"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="51" t="s">
@@ -5563,27 +5564,27 @@
       <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="58"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="58"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="70"/>
       <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="58"/>
-    </row>
-    <row r="2" spans="1:16" ht="34.5">
-      <c r="A2" s="61"/>
+      <c r="P1" s="70"/>
+    </row>
+    <row r="2" spans="1:16" ht="36">
+      <c r="A2" s="71"/>
       <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
@@ -5608,12 +5609,12 @@
       <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="60"/>
-      <c r="M2" s="58"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -5624,15 +5625,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="69">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
+    <row r="3" spans="1:16" ht="60">
+      <c r="A3" s="72"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -5654,7 +5655,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16" ht="34.5">
+    <row r="4" spans="1:16" ht="36">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -5700,7 +5701,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16" ht="34.5">
+    <row r="5" spans="1:16" ht="24">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -5746,7 +5747,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="34.5">
+    <row r="6" spans="1:16" ht="36">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -5792,7 +5793,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="46">
+    <row r="7" spans="1:16" ht="48">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -5838,7 +5839,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" ht="46">
+    <row r="8" spans="1:16" ht="36">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -5884,7 +5885,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" ht="46">
+    <row r="9" spans="1:16" ht="48">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -5930,7 +5931,7 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="34.5">
+    <row r="10" spans="1:16" ht="48">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -5976,7 +5977,7 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="23">
+    <row r="11" spans="1:16" ht="36">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -6022,7 +6023,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" ht="23">
+    <row r="12" spans="1:16" ht="48">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -6068,7 +6069,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" ht="34.5">
+    <row r="13" spans="1:16" ht="24">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -6114,7 +6115,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:16" ht="34.5">
+    <row r="14" spans="1:16" ht="36">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -6160,7 +6161,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16" ht="34.5">
+    <row r="15" spans="1:16" ht="48">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -6206,7 +6207,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" ht="46">
+    <row r="16" spans="1:16" ht="48">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -6252,7 +6253,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" ht="46">
+    <row r="17" spans="1:16" ht="36">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -6298,7 +6299,7 @@
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="1:16" ht="46">
+    <row r="18" spans="1:16" ht="36">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -6344,7 +6345,7 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" ht="46">
+    <row r="19" spans="1:16" ht="36">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -6390,7 +6391,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" ht="46">
+    <row r="20" spans="1:16" ht="36">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -6436,7 +6437,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" ht="46">
+    <row r="21" spans="1:16" ht="48">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -6482,7 +6483,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" ht="46">
+    <row r="22" spans="1:16" ht="36">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -6528,7 +6529,7 @@
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" ht="34.5">
+    <row r="23" spans="1:16" ht="48">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -6574,7 +6575,7 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16" ht="46">
+    <row r="24" spans="1:16" ht="48">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -6620,7 +6621,7 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" ht="46">
+    <row r="25" spans="1:16" ht="36">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -6666,7 +6667,7 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
     </row>
-    <row r="26" spans="1:16" ht="46">
+    <row r="26" spans="1:16" ht="48">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -6712,7 +6713,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" ht="46">
+    <row r="27" spans="1:16" ht="48">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -6758,7 +6759,7 @@
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" ht="46">
+    <row r="28" spans="1:16" ht="36">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -6804,7 +6805,7 @@
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16" ht="46">
+    <row r="29" spans="1:16" ht="48">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -6850,7 +6851,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="46">
+    <row r="30" spans="1:16" ht="36">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -6896,7 +6897,7 @@
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
     </row>
-    <row r="31" spans="1:16" ht="57.5">
+    <row r="31" spans="1:16" ht="36">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -6942,7 +6943,7 @@
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16" ht="80.5">
+    <row r="32" spans="1:16" ht="72">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -6988,7 +6989,7 @@
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
     </row>
-    <row r="33" spans="1:16" ht="46">
+    <row r="33" spans="1:16" ht="36">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -7034,7 +7035,7 @@
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:16" ht="46">
+    <row r="34" spans="1:16" ht="48">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -7080,7 +7081,7 @@
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:16" ht="46">
+    <row r="35" spans="1:16" ht="36">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -7126,7 +7127,7 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" ht="46">
+    <row r="36" spans="1:16" ht="48">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -7172,7 +7173,7 @@
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" ht="23">
+    <row r="37" spans="1:16" ht="48">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -7218,7 +7219,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:16" ht="46">
+    <row r="38" spans="1:16" ht="48">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -7264,7 +7265,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:16" ht="46">
+    <row r="39" spans="1:16" ht="48">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -7308,7 +7309,7 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:16" ht="34.5">
+    <row r="40" spans="1:16" ht="36">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -7354,7 +7355,7 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
     </row>
-    <row r="41" spans="1:16" ht="69">
+    <row r="41" spans="1:16" ht="72">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -7400,7 +7401,7 @@
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
     </row>
-    <row r="42" spans="1:16" ht="69">
+    <row r="42" spans="1:16" ht="72">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -7446,7 +7447,7 @@
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="1:16" ht="69">
+    <row r="43" spans="1:16" ht="72">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -7492,7 +7493,7 @@
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
     </row>
-    <row r="44" spans="1:16" ht="69">
+    <row r="44" spans="1:16" ht="72">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -7538,7 +7539,7 @@
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
     </row>
-    <row r="45" spans="1:16" ht="69">
+    <row r="45" spans="1:16" ht="72">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -7584,7 +7585,7 @@
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
     </row>
-    <row r="46" spans="1:16" ht="69">
+    <row r="46" spans="1:16" ht="72">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -7630,7 +7631,7 @@
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
     </row>
-    <row r="47" spans="1:16" ht="69">
+    <row r="47" spans="1:16" ht="72">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -7676,7 +7677,7 @@
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
     </row>
-    <row r="48" spans="1:16" ht="69">
+    <row r="48" spans="1:16" ht="72">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -7722,7 +7723,7 @@
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
     </row>
-    <row r="49" spans="1:16" ht="69">
+    <row r="49" spans="1:16" ht="72">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -7768,7 +7769,7 @@
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
     </row>
-    <row r="50" spans="1:16" ht="69">
+    <row r="50" spans="1:16" ht="72">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -7814,7 +7815,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:16" ht="69">
+    <row r="51" spans="1:16" ht="72">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -7860,7 +7861,7 @@
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:16" ht="69">
+    <row r="52" spans="1:16" ht="72">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -7906,7 +7907,7 @@
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
     </row>
-    <row r="53" spans="1:16" ht="69">
+    <row r="53" spans="1:16" ht="72">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -7952,7 +7953,7 @@
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
     </row>
-    <row r="54" spans="1:16" ht="69">
+    <row r="54" spans="1:16" ht="72">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -7998,7 +7999,7 @@
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
     </row>
-    <row r="55" spans="1:16" ht="69">
+    <row r="55" spans="1:16" ht="72">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -8044,7 +8045,7 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
     </row>
-    <row r="56" spans="1:16" ht="69">
+    <row r="56" spans="1:16" ht="72">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -8090,7 +8091,7 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
     </row>
-    <row r="57" spans="1:16" ht="69">
+    <row r="57" spans="1:16" ht="72">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -8136,7 +8137,7 @@
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
     </row>
-    <row r="58" spans="1:16" ht="69">
+    <row r="58" spans="1:16" ht="72">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -8182,7 +8183,7 @@
       <c r="O58" s="3"/>
       <c r="P58" s="3"/>
     </row>
-    <row r="59" spans="1:16" ht="34.5">
+    <row r="59" spans="1:16" ht="48">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -8228,7 +8229,7 @@
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
     </row>
-    <row r="60" spans="1:16" ht="46">
+    <row r="60" spans="1:16" ht="35.25">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -8251,7 +8252,7 @@
         <v>271</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>271</v>
+        <v>25</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>26</v>
@@ -8274,7 +8275,7 @@
       <c r="O60" s="3"/>
       <c r="P60" s="3"/>
     </row>
-    <row r="61" spans="1:16" ht="34.5">
+    <row r="61" spans="1:16" ht="36">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -8320,7 +8321,7 @@
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
     </row>
-    <row r="62" spans="1:16" ht="34.5">
+    <row r="62" spans="1:16" ht="48">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -8366,7 +8367,7 @@
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
     </row>
-    <row r="63" spans="1:16" ht="34.5">
+    <row r="63" spans="1:16" ht="36">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -8412,7 +8413,7 @@
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
     </row>
-    <row r="64" spans="1:16" ht="34.5">
+    <row r="64" spans="1:16" ht="48">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -8458,7 +8459,7 @@
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
     </row>
-    <row r="65" spans="1:16" ht="34.5">
+    <row r="65" spans="1:16" ht="48">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -8504,7 +8505,7 @@
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
     </row>
-    <row r="66" spans="1:16" ht="23">
+    <row r="66" spans="1:16" ht="48">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -8550,7 +8551,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:16" ht="34.5">
+    <row r="67" spans="1:16" ht="36">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -8596,7 +8597,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:16" ht="34.5">
+    <row r="68" spans="1:16" ht="36">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -8642,7 +8643,7 @@
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
     </row>
-    <row r="69" spans="1:16" ht="46">
+    <row r="69" spans="1:16" ht="36">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -8688,7 +8689,7 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:16" ht="46">
+    <row r="70" spans="1:16" ht="48">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -8734,7 +8735,7 @@
       <c r="O70" s="3"/>
       <c r="P70" s="3"/>
     </row>
-    <row r="71" spans="1:16" ht="69">
+    <row r="71" spans="1:16" ht="72">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -8780,7 +8781,7 @@
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
     </row>
-    <row r="72" spans="1:16" ht="23">
+    <row r="72" spans="1:16" ht="36">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -8826,7 +8827,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="1:16" ht="23">
+    <row r="73" spans="1:16" ht="36">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -8872,7 +8873,7 @@
       <c r="O73" s="3"/>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:16" ht="46">
+    <row r="74" spans="1:16" ht="48">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -8918,7 +8919,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:16" ht="46">
+    <row r="75" spans="1:16" ht="48">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -8964,7 +8965,7 @@
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="1:16" ht="34.5">
+    <row r="76" spans="1:16" ht="48">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -9010,7 +9011,7 @@
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
     </row>
-    <row r="77" spans="1:16" ht="23">
+    <row r="77" spans="1:16" ht="36">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -9056,7 +9057,7 @@
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:16" ht="23">
+    <row r="78" spans="1:16" ht="36">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -9102,7 +9103,7 @@
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
     </row>
-    <row r="79" spans="1:16" ht="23">
+    <row r="79" spans="1:16" ht="48">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -9148,7 +9149,7 @@
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:16" ht="23">
+    <row r="80" spans="1:16" ht="48">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -9194,7 +9195,7 @@
       <c r="O80" s="3"/>
       <c r="P80" s="3"/>
     </row>
-    <row r="81" spans="1:16" ht="57.5">
+    <row r="81" spans="1:16" ht="48">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -9240,7 +9241,7 @@
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:16" ht="57.5">
+    <row r="82" spans="1:16" ht="48">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -9286,7 +9287,7 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="1:16" ht="57.5">
+    <row r="83" spans="1:16" ht="48">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -9332,7 +9333,7 @@
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
     </row>
-    <row r="84" spans="1:16" ht="57.5">
+    <row r="84" spans="1:16" ht="48">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -9378,7 +9379,7 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:16" ht="34.5">
+    <row r="85" spans="1:16" ht="36">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -9424,7 +9425,7 @@
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
     </row>
-    <row r="86" spans="1:16" ht="34.5">
+    <row r="86" spans="1:16" ht="48">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -9470,7 +9471,7 @@
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="1:16" ht="46">
+    <row r="87" spans="1:16" ht="36">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -9516,7 +9517,7 @@
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
     </row>
-    <row r="88" spans="1:16" ht="46">
+    <row r="88" spans="1:16" ht="48">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -9562,7 +9563,7 @@
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
     </row>
-    <row r="89" spans="1:16" ht="34.5">
+    <row r="89" spans="1:16" ht="48">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -9608,7 +9609,7 @@
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:16" ht="46">
+    <row r="90" spans="1:16" ht="48">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -9654,7 +9655,7 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
     </row>
-    <row r="91" spans="1:16" ht="46">
+    <row r="91" spans="1:16" ht="48">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -9700,7 +9701,7 @@
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:16" ht="34.5">
+    <row r="92" spans="1:16" ht="48">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -9746,7 +9747,7 @@
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
     </row>
-    <row r="93" spans="1:16" ht="23">
+    <row r="93" spans="1:16" ht="36">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -9792,7 +9793,7 @@
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
     </row>
-    <row r="94" spans="1:16" ht="34.5">
+    <row r="94" spans="1:16" ht="48">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -9838,7 +9839,7 @@
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:16" ht="34.5">
+    <row r="95" spans="1:16" ht="36">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -9884,7 +9885,7 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:16" ht="34.5">
+    <row r="96" spans="1:16" ht="36">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -9930,7 +9931,7 @@
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:16" ht="57.5">
+    <row r="97" spans="1:16" ht="48">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -9976,7 +9977,7 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:16" ht="34.5">
+    <row r="98" spans="1:16" ht="36">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -10022,7 +10023,7 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
     </row>
-    <row r="99" spans="1:16" ht="23">
+    <row r="99" spans="1:16" ht="48">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -10068,7 +10069,7 @@
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
     </row>
-    <row r="100" spans="1:16" ht="23">
+    <row r="100" spans="1:16" ht="48">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -10114,7 +10115,7 @@
       <c r="O100" s="3"/>
       <c r="P100" s="3"/>
     </row>
-    <row r="101" spans="1:16" ht="23">
+    <row r="101" spans="1:16" ht="48">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -10160,7 +10161,7 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:16" ht="34.5">
+    <row r="102" spans="1:16" ht="48">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -10206,7 +10207,7 @@
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
     </row>
-    <row r="103" spans="1:16" ht="23">
+    <row r="103" spans="1:16" ht="36">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -10252,7 +10253,7 @@
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
     </row>
-    <row r="104" spans="1:16" ht="23">
+    <row r="104" spans="1:16" ht="48">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -10298,7 +10299,7 @@
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
     </row>
-    <row r="105" spans="1:16" ht="23">
+    <row r="105" spans="1:16" ht="36">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -10344,7 +10345,7 @@
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
     </row>
-    <row r="106" spans="1:16" ht="34.5">
+    <row r="106" spans="1:16" ht="48">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -10390,7 +10391,7 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:16" ht="46">
+    <row r="107" spans="1:16" ht="36">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -10436,7 +10437,7 @@
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
     </row>
-    <row r="108" spans="1:16" ht="34.5">
+    <row r="108" spans="1:16" ht="36">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -10482,7 +10483,7 @@
       <c r="O108" s="3"/>
       <c r="P108" s="3"/>
     </row>
-    <row r="109" spans="1:16" ht="34.5">
+    <row r="109" spans="1:16" ht="48">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -10528,7 +10529,7 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:16" ht="57.5">
+    <row r="110" spans="1:16" ht="48">
       <c r="A110" s="3">
         <v>107</v>
       </c>
@@ -10574,7 +10575,7 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:16" ht="34.5">
+    <row r="111" spans="1:16" ht="48">
       <c r="A111" s="3">
         <v>108</v>
       </c>
@@ -10620,7 +10621,7 @@
       <c r="O111" s="3"/>
       <c r="P111" s="3"/>
     </row>
-    <row r="112" spans="1:16" ht="46">
+    <row r="112" spans="1:16" ht="48">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -10666,7 +10667,7 @@
       <c r="O112" s="3"/>
       <c r="P112" s="3"/>
     </row>
-    <row r="113" spans="1:16" ht="57.5">
+    <row r="113" spans="1:16" ht="48">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -10712,7 +10713,7 @@
       <c r="O113" s="3"/>
       <c r="P113" s="3"/>
     </row>
-    <row r="114" spans="1:16" ht="57.5">
+    <row r="114" spans="1:16" ht="48">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -10758,7 +10759,7 @@
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
     </row>
-    <row r="115" spans="1:16" ht="57.5">
+    <row r="115" spans="1:16" ht="48">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -10804,7 +10805,7 @@
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
     </row>
-    <row r="116" spans="1:16" ht="46">
+    <row r="116" spans="1:16" ht="48">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -10850,7 +10851,7 @@
       <c r="O116" s="3"/>
       <c r="P116" s="3"/>
     </row>
-    <row r="117" spans="1:16" ht="23">
+    <row r="117" spans="1:16" ht="48">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -10896,7 +10897,7 @@
       <c r="O117" s="3"/>
       <c r="P117" s="3"/>
     </row>
-    <row r="118" spans="1:16" ht="23">
+    <row r="118" spans="1:16" ht="48">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -10942,7 +10943,7 @@
       <c r="O118" s="3"/>
       <c r="P118" s="3"/>
     </row>
-    <row r="119" spans="1:16" ht="34.5">
+    <row r="119" spans="1:16" ht="36">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -10988,7 +10989,7 @@
       <c r="O119" s="3"/>
       <c r="P119" s="3"/>
     </row>
-    <row r="120" spans="1:16" ht="57.5">
+    <row r="120" spans="1:16" ht="48">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -11034,7 +11035,7 @@
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:16" ht="34.5">
+    <row r="121" spans="1:16" ht="36">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -11080,7 +11081,7 @@
       <c r="O121" s="3"/>
       <c r="P121" s="3"/>
     </row>
-    <row r="122" spans="1:16" ht="57.5">
+    <row r="122" spans="1:16" ht="48">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -11126,7 +11127,7 @@
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
     </row>
-    <row r="123" spans="1:16" ht="46">
+    <row r="123" spans="1:16" ht="36">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -11172,7 +11173,7 @@
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
     </row>
-    <row r="124" spans="1:16" ht="34.5">
+    <row r="124" spans="1:16" ht="36">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -11218,7 +11219,7 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:16" ht="34.5">
+    <row r="125" spans="1:16" ht="36">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -11264,7 +11265,7 @@
       <c r="O125" s="3"/>
       <c r="P125" s="3"/>
     </row>
-    <row r="126" spans="1:16" ht="34.5">
+    <row r="126" spans="1:16" ht="48">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -11310,7 +11311,7 @@
       <c r="O126" s="3"/>
       <c r="P126" s="3"/>
     </row>
-    <row r="127" spans="1:16" ht="34.5">
+    <row r="127" spans="1:16" ht="36">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -11356,7 +11357,7 @@
       <c r="O127" s="3"/>
       <c r="P127" s="3"/>
     </row>
-    <row r="128" spans="1:16" ht="34.5">
+    <row r="128" spans="1:16" ht="36">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -11402,7 +11403,7 @@
       <c r="O128" s="3"/>
       <c r="P128" s="3"/>
     </row>
-    <row r="129" spans="1:16" ht="23">
+    <row r="129" spans="1:16" ht="36">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -11448,7 +11449,7 @@
       <c r="O129" s="3"/>
       <c r="P129" s="3"/>
     </row>
-    <row r="130" spans="1:16" ht="34.5">
+    <row r="130" spans="1:16" ht="36">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -11494,7 +11495,7 @@
       <c r="O130" s="3"/>
       <c r="P130" s="3"/>
     </row>
-    <row r="131" spans="1:16" ht="34.5">
+    <row r="131" spans="1:16" ht="36">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -11561,9 +11562,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46771BB-89DD-433A-8105-216FBABD0C00}">
   <dimension ref="A1:T49"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1">
       <c r="A1" s="51" t="s">
@@ -11572,35 +11573,35 @@
       <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="64"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="60"/>
       <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="64"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="60"/>
       <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="68" t="s">
+      <c r="P1" s="58"/>
+      <c r="Q1" s="64" t="s">
         <v>360</v>
       </c>
-      <c r="R1" s="69"/>
+      <c r="R1" s="65"/>
       <c r="S1" s="57" t="s">
         <v>361</v>
       </c>
       <c r="T1" s="57"/>
     </row>
-    <row r="2" spans="1:20" ht="34.5">
-      <c r="A2" s="65"/>
+    <row r="2" spans="1:20" ht="36">
+      <c r="A2" s="61"/>
       <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
@@ -11625,12 +11626,12 @@
       <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="64"/>
+      <c r="J2" s="60"/>
       <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="62"/>
-      <c r="M2" s="64"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="60"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -11640,28 +11641,28 @@
       <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="66" t="s">
+      <c r="Q2" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="R2" s="66" t="s">
+      <c r="R2" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="S2" s="66" t="s">
+      <c r="S2" s="62" t="s">
         <v>362</v>
       </c>
-      <c r="T2" s="66" t="s">
+      <c r="T2" s="62" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="69">
-      <c r="A3" s="63"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+    <row r="3" spans="1:20" ht="60">
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -11682,12 +11683,12 @@
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-    </row>
-    <row r="4" spans="1:20" ht="23">
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+    </row>
+    <row r="4" spans="1:20" ht="48">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -11735,7 +11736,7 @@
       <c r="S4" s="15"/>
       <c r="T4" s="15"/>
     </row>
-    <row r="5" spans="1:20" ht="23">
+    <row r="5" spans="1:20" ht="48">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -11783,7 +11784,7 @@
       <c r="S5" s="15"/>
       <c r="T5" s="15"/>
     </row>
-    <row r="6" spans="1:20" ht="34.5">
+    <row r="6" spans="1:20" ht="48">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -11831,7 +11832,7 @@
       <c r="S6" s="15"/>
       <c r="T6" s="15"/>
     </row>
-    <row r="7" spans="1:20" ht="34.5">
+    <row r="7" spans="1:20" ht="48">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -11879,7 +11880,7 @@
       <c r="S7" s="15"/>
       <c r="T7" s="15"/>
     </row>
-    <row r="8" spans="1:20" ht="46">
+    <row r="8" spans="1:20" ht="48">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -11927,7 +11928,7 @@
       <c r="S8" s="15"/>
       <c r="T8" s="15"/>
     </row>
-    <row r="9" spans="1:20" ht="34.5">
+    <row r="9" spans="1:20" ht="48">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -11975,7 +11976,7 @@
       <c r="S9" s="15"/>
       <c r="T9" s="15"/>
     </row>
-    <row r="10" spans="1:20" ht="34.5">
+    <row r="10" spans="1:20" ht="36">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -12025,7 +12026,7 @@
       <c r="S10" s="18"/>
       <c r="T10" s="18"/>
     </row>
-    <row r="11" spans="1:20" ht="34.5">
+    <row r="11" spans="1:20" ht="36">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -12075,7 +12076,7 @@
       </c>
       <c r="T11" s="18"/>
     </row>
-    <row r="12" spans="1:20" ht="34.5">
+    <row r="12" spans="1:20" ht="36">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -12125,7 +12126,7 @@
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
     </row>
-    <row r="13" spans="1:20" ht="34.5">
+    <row r="13" spans="1:20" ht="36">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -12175,7 +12176,7 @@
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
     </row>
-    <row r="14" spans="1:20" ht="23.5">
+    <row r="14" spans="1:20" ht="24.75">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -12225,7 +12226,7 @@
       <c r="S14" s="18"/>
       <c r="T14" s="18"/>
     </row>
-    <row r="15" spans="1:20" ht="23.5">
+    <row r="15" spans="1:20" ht="24.75">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -12275,7 +12276,7 @@
       </c>
       <c r="T15" s="18"/>
     </row>
-    <row r="16" spans="1:20" ht="23.5">
+    <row r="16" spans="1:20" ht="24.75">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -12325,7 +12326,7 @@
       </c>
       <c r="T16" s="18"/>
     </row>
-    <row r="17" spans="1:20" ht="34.5">
+    <row r="17" spans="1:20" ht="36">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -12375,7 +12376,7 @@
       </c>
       <c r="T17" s="18"/>
     </row>
-    <row r="18" spans="1:20" ht="34.5">
+    <row r="18" spans="1:20" ht="36">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -12425,7 +12426,7 @@
       </c>
       <c r="T18" s="18"/>
     </row>
-    <row r="19" spans="1:20" ht="34.5">
+    <row r="19" spans="1:20" ht="36">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -12475,7 +12476,7 @@
       </c>
       <c r="T19" s="18"/>
     </row>
-    <row r="20" spans="1:20" ht="34.5">
+    <row r="20" spans="1:20" ht="36">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -12525,7 +12526,7 @@
       <c r="S20" s="18"/>
       <c r="T20" s="18"/>
     </row>
-    <row r="21" spans="1:20" ht="23.5">
+    <row r="21" spans="1:20" ht="24.75">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -12575,7 +12576,7 @@
       </c>
       <c r="T21" s="18"/>
     </row>
-    <row r="22" spans="1:20" ht="46">
+    <row r="22" spans="1:20" ht="48">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -12625,7 +12626,7 @@
       </c>
       <c r="T22" s="18"/>
     </row>
-    <row r="23" spans="1:20" ht="46">
+    <row r="23" spans="1:20" ht="48">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -12673,7 +12674,7 @@
       </c>
       <c r="T23" s="18"/>
     </row>
-    <row r="24" spans="1:20" ht="23.5">
+    <row r="24" spans="1:20" ht="24.75">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -12723,7 +12724,7 @@
       </c>
       <c r="T24" s="18"/>
     </row>
-    <row r="25" spans="1:20" ht="34.5">
+    <row r="25" spans="1:20" ht="36">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -12773,7 +12774,7 @@
       </c>
       <c r="T25" s="18"/>
     </row>
-    <row r="26" spans="1:20" ht="23">
+    <row r="26" spans="1:20" ht="24">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -12823,7 +12824,7 @@
       </c>
       <c r="T26" s="18"/>
     </row>
-    <row r="27" spans="1:20" ht="23.5">
+    <row r="27" spans="1:20" ht="24.75">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -12871,7 +12872,7 @@
       <c r="S27" s="18"/>
       <c r="T27" s="18"/>
     </row>
-    <row r="28" spans="1:20" ht="23.5">
+    <row r="28" spans="1:20" ht="24.75">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -12919,7 +12920,7 @@
       <c r="S28" s="18"/>
       <c r="T28" s="18"/>
     </row>
-    <row r="29" spans="1:20" ht="34.5">
+    <row r="29" spans="1:20" ht="24.75">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -12969,7 +12970,7 @@
       </c>
       <c r="T29" s="18"/>
     </row>
-    <row r="30" spans="1:20" ht="46">
+    <row r="30" spans="1:20" ht="48">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -13019,7 +13020,7 @@
       </c>
       <c r="T30" s="18"/>
     </row>
-    <row r="31" spans="1:20" ht="69">
+    <row r="31" spans="1:20" ht="72">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -13067,7 +13068,7 @@
       </c>
       <c r="T31" s="18"/>
     </row>
-    <row r="32" spans="1:20" ht="34.5">
+    <row r="32" spans="1:20" ht="36">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -13117,7 +13118,7 @@
       <c r="S32" s="18"/>
       <c r="T32" s="18"/>
     </row>
-    <row r="33" spans="1:20" ht="23">
+    <row r="33" spans="1:20" ht="24">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -13151,7 +13152,7 @@
       <c r="S33" s="15"/>
       <c r="T33" s="15"/>
     </row>
-    <row r="34" spans="1:20" ht="34.5">
+    <row r="34" spans="1:20" ht="36">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -13185,7 +13186,7 @@
       <c r="S34" s="15"/>
       <c r="T34" s="15"/>
     </row>
-    <row r="35" spans="1:20" ht="23">
+    <row r="35" spans="1:20" ht="24">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -13219,7 +13220,7 @@
       <c r="S35" s="15"/>
       <c r="T35" s="15"/>
     </row>
-    <row r="36" spans="1:20" ht="46">
+    <row r="36" spans="1:20" ht="36">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -13253,7 +13254,7 @@
       <c r="S36" s="15"/>
       <c r="T36" s="15"/>
     </row>
-    <row r="37" spans="1:20" ht="34.5">
+    <row r="37" spans="1:20" ht="24">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -13287,7 +13288,7 @@
       <c r="S37" s="15"/>
       <c r="T37" s="15"/>
     </row>
-    <row r="38" spans="1:20" ht="23">
+    <row r="38" spans="1:20" ht="24">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -13321,7 +13322,7 @@
       <c r="S38" s="15"/>
       <c r="T38" s="15"/>
     </row>
-    <row r="39" spans="1:20" ht="23">
+    <row r="39" spans="1:20" ht="24">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -13355,7 +13356,7 @@
       <c r="S39" s="15"/>
       <c r="T39" s="15"/>
     </row>
-    <row r="40" spans="1:20" ht="23">
+    <row r="40" spans="1:20" ht="24">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -13389,7 +13390,7 @@
       <c r="S40" s="15"/>
       <c r="T40" s="15"/>
     </row>
-    <row r="41" spans="1:20" ht="46">
+    <row r="41" spans="1:20" ht="36">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -13423,7 +13424,7 @@
       <c r="S41" s="15"/>
       <c r="T41" s="15"/>
     </row>
-    <row r="42" spans="1:20" ht="34.5">
+    <row r="42" spans="1:20" ht="36">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -13457,7 +13458,7 @@
       <c r="S42" s="15"/>
       <c r="T42" s="15"/>
     </row>
-    <row r="43" spans="1:20" ht="46">
+    <row r="43" spans="1:20" ht="36">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -13491,7 +13492,7 @@
       <c r="S43" s="15"/>
       <c r="T43" s="15"/>
     </row>
-    <row r="44" spans="1:20" ht="34.5">
+    <row r="44" spans="1:20" ht="24">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -13525,7 +13526,7 @@
       <c r="S44" s="15"/>
       <c r="T44" s="15"/>
     </row>
-    <row r="45" spans="1:20" ht="34.5">
+    <row r="45" spans="1:20" ht="24">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -13559,7 +13560,7 @@
       <c r="S45" s="15"/>
       <c r="T45" s="15"/>
     </row>
-    <row r="46" spans="1:20" ht="34.5">
+    <row r="46" spans="1:20" ht="24">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -13593,7 +13594,7 @@
       <c r="S46" s="15"/>
       <c r="T46" s="15"/>
     </row>
-    <row r="47" spans="1:20" ht="57.5">
+    <row r="47" spans="1:20" ht="60">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -13627,7 +13628,7 @@
       <c r="S47" s="15"/>
       <c r="T47" s="15"/>
     </row>
-    <row r="48" spans="1:20" ht="34.5">
+    <row r="48" spans="1:20" ht="36">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -13661,7 +13662,7 @@
       <c r="S48" s="15"/>
       <c r="T48" s="15"/>
     </row>
-    <row r="49" spans="1:20" ht="46.5">
+    <row r="49" spans="1:20" ht="36.75">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -13722,38 +13723,38 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D9A1422-081A-4032-9119-87607685BE3D}">
   <dimension ref="A1:P75"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="58"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="58"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="70"/>
       <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="58"/>
-    </row>
-    <row r="2" spans="1:16" ht="34.5">
-      <c r="A2" s="61"/>
+      <c r="P1" s="70"/>
+    </row>
+    <row r="2" spans="1:16" ht="36">
+      <c r="A2" s="71"/>
       <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
@@ -13778,12 +13779,12 @@
       <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="58"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="60"/>
-      <c r="M2" s="58"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -13794,15 +13795,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="69">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
+    <row r="3" spans="1:16" ht="60">
+      <c r="A3" s="72"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -13824,7 +13825,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16" ht="23">
+    <row r="4" spans="1:16" ht="36">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -13868,7 +13869,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16" ht="34.5">
+    <row r="5" spans="1:16" ht="36">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -13912,7 +13913,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="23">
+    <row r="6" spans="1:16" ht="24">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -13956,7 +13957,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="23">
+    <row r="7" spans="1:16" ht="24">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -14000,7 +14001,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" ht="23">
+    <row r="8" spans="1:16" ht="24">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -14044,7 +14045,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" ht="23">
+    <row r="9" spans="1:16" ht="24">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -14088,7 +14089,7 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="34.5">
+    <row r="10" spans="1:16" ht="24">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -14132,7 +14133,7 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="23">
+    <row r="11" spans="1:16" ht="24">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -14176,7 +14177,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" ht="23">
+    <row r="12" spans="1:16" ht="24">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -14220,7 +14221,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" ht="23">
+    <row r="13" spans="1:16" ht="24">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -14264,7 +14265,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:16" ht="23">
+    <row r="14" spans="1:16" ht="24">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -14308,7 +14309,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16" ht="23">
+    <row r="15" spans="1:16" ht="24">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -14352,7 +14353,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" ht="34.5">
+    <row r="16" spans="1:16" ht="36">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -14396,7 +14397,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" ht="23">
+    <row r="17" spans="1:16" ht="24">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -14440,7 +14441,7 @@
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="1:16" ht="23">
+    <row r="18" spans="1:16" ht="24">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -14484,7 +14485,7 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" ht="23">
+    <row r="19" spans="1:16" ht="24">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -14528,7 +14529,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" ht="34.5">
+    <row r="20" spans="1:16" ht="36">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -14572,7 +14573,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" ht="23">
+    <row r="21" spans="1:16" ht="24">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -14616,7 +14617,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" ht="23">
+    <row r="22" spans="1:16" ht="24">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -14660,7 +14661,7 @@
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" ht="57.5">
+    <row r="23" spans="1:16" ht="60">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -14704,7 +14705,7 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16" ht="23">
+    <row r="24" spans="1:16" ht="24">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -14748,7 +14749,7 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" ht="23">
+    <row r="25" spans="1:16" ht="24">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -14792,7 +14793,7 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
     </row>
-    <row r="26" spans="1:16" ht="34.5">
+    <row r="26" spans="1:16" ht="36">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -14836,7 +14837,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" ht="23">
+    <row r="27" spans="1:16" ht="24">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -14880,7 +14881,7 @@
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" ht="34.5">
+    <row r="28" spans="1:16" ht="36">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -14924,7 +14925,7 @@
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16" ht="34.5">
+    <row r="29" spans="1:16" ht="36">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -14968,7 +14969,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="34.5">
+    <row r="30" spans="1:16" ht="24">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -15012,7 +15013,7 @@
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
     </row>
-    <row r="31" spans="1:16" ht="34.5">
+    <row r="31" spans="1:16" ht="24">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -15056,7 +15057,7 @@
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16" ht="23">
+    <row r="32" spans="1:16" ht="24">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -15100,7 +15101,7 @@
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
     </row>
-    <row r="33" spans="1:16" ht="23">
+    <row r="33" spans="1:16" ht="24">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -15144,7 +15145,7 @@
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:16" ht="34.5">
+    <row r="34" spans="1:16" ht="36">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -15188,7 +15189,7 @@
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:16" ht="23">
+    <row r="35" spans="1:16" ht="24">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -15232,7 +15233,7 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" ht="23">
+    <row r="36" spans="1:16" ht="24">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -15276,7 +15277,7 @@
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" ht="34.5">
+    <row r="37" spans="1:16" ht="36">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -15320,7 +15321,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:16" ht="34.5">
+    <row r="38" spans="1:16" ht="36">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -15364,7 +15365,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:16" ht="23">
+    <row r="39" spans="1:16" ht="24">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -15408,7 +15409,7 @@
       <c r="O39" s="34"/>
       <c r="P39" s="34"/>
     </row>
-    <row r="40" spans="1:16" s="38" customFormat="1" ht="23.5">
+    <row r="40" spans="1:16" s="38" customFormat="1" ht="24.75">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -15438,7 +15439,7 @@
       <c r="O40" s="18"/>
       <c r="P40" s="18"/>
     </row>
-    <row r="41" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="41" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -15468,7 +15469,7 @@
       <c r="O41" s="18"/>
       <c r="P41" s="18"/>
     </row>
-    <row r="42" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="42" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -15498,7 +15499,7 @@
       <c r="O42" s="18"/>
       <c r="P42" s="18"/>
     </row>
-    <row r="43" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="43" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -15528,7 +15529,7 @@
       <c r="O43" s="18"/>
       <c r="P43" s="18"/>
     </row>
-    <row r="44" spans="1:16" s="38" customFormat="1" ht="23.5">
+    <row r="44" spans="1:16" s="38" customFormat="1" ht="24.75">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -15558,7 +15559,7 @@
       <c r="O44" s="18"/>
       <c r="P44" s="18"/>
     </row>
-    <row r="45" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="45" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -15588,7 +15589,7 @@
       <c r="O45" s="18"/>
       <c r="P45" s="18"/>
     </row>
-    <row r="46" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="46" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -15618,7 +15619,7 @@
       <c r="O46" s="18"/>
       <c r="P46" s="18"/>
     </row>
-    <row r="47" spans="1:16" s="38" customFormat="1" ht="23.5">
+    <row r="47" spans="1:16" s="38" customFormat="1" ht="24.75">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -15648,7 +15649,7 @@
       <c r="O47" s="18"/>
       <c r="P47" s="18"/>
     </row>
-    <row r="48" spans="1:16" s="38" customFormat="1" ht="23.5">
+    <row r="48" spans="1:16" s="38" customFormat="1" ht="24.75">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -15678,7 +15679,7 @@
       <c r="O48" s="18"/>
       <c r="P48" s="18"/>
     </row>
-    <row r="49" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="49" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -15708,7 +15709,7 @@
       <c r="O49" s="18"/>
       <c r="P49" s="18"/>
     </row>
-    <row r="50" spans="1:16" s="38" customFormat="1" ht="23.5">
+    <row r="50" spans="1:16" s="38" customFormat="1" ht="24.75">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -15738,7 +15739,7 @@
       <c r="O50" s="18"/>
       <c r="P50" s="18"/>
     </row>
-    <row r="51" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="51" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -15768,7 +15769,7 @@
       <c r="O51" s="18"/>
       <c r="P51" s="18"/>
     </row>
-    <row r="52" spans="1:16" s="38" customFormat="1" ht="23.5">
+    <row r="52" spans="1:16" s="38" customFormat="1" ht="24.75">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -15798,7 +15799,7 @@
       <c r="O52" s="18"/>
       <c r="P52" s="18"/>
     </row>
-    <row r="53" spans="1:16" s="38" customFormat="1" ht="46.5">
+    <row r="53" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -15828,7 +15829,7 @@
       <c r="O53" s="18"/>
       <c r="P53" s="18"/>
     </row>
-    <row r="54" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="54" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -15858,7 +15859,7 @@
       <c r="O54" s="18"/>
       <c r="P54" s="18"/>
     </row>
-    <row r="55" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="55" spans="1:16" s="38" customFormat="1" ht="24.75">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -15888,7 +15889,7 @@
       <c r="O55" s="18"/>
       <c r="P55" s="18"/>
     </row>
-    <row r="56" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="56" spans="1:16" s="38" customFormat="1" ht="24.75">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -15918,7 +15919,7 @@
       <c r="O56" s="18"/>
       <c r="P56" s="18"/>
     </row>
-    <row r="57" spans="1:16" s="38" customFormat="1" ht="23.5">
+    <row r="57" spans="1:16" s="38" customFormat="1" ht="24.75">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -15948,7 +15949,7 @@
       <c r="O57" s="18"/>
       <c r="P57" s="18"/>
     </row>
-    <row r="58" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="58" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -15978,7 +15979,7 @@
       <c r="O58" s="18"/>
       <c r="P58" s="18"/>
     </row>
-    <row r="59" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="59" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -16008,7 +16009,7 @@
       <c r="O59" s="18"/>
       <c r="P59" s="18"/>
     </row>
-    <row r="60" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="60" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -16038,7 +16039,7 @@
       <c r="O60" s="18"/>
       <c r="P60" s="18"/>
     </row>
-    <row r="61" spans="1:16" ht="34.5">
+    <row r="61" spans="1:16" ht="36">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -16082,7 +16083,7 @@
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
     </row>
-    <row r="62" spans="1:16" ht="23">
+    <row r="62" spans="1:16" ht="24">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -16126,7 +16127,7 @@
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
     </row>
-    <row r="63" spans="1:16" ht="46">
+    <row r="63" spans="1:16" ht="48">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -16170,7 +16171,7 @@
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
     </row>
-    <row r="64" spans="1:16" ht="34.5">
+    <row r="64" spans="1:16" ht="36">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -16214,7 +16215,7 @@
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
     </row>
-    <row r="65" spans="1:16" ht="23">
+    <row r="65" spans="1:16" ht="24">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -16258,7 +16259,7 @@
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
     </row>
-    <row r="66" spans="1:16" ht="23">
+    <row r="66" spans="1:16" ht="24">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -16302,7 +16303,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:16" ht="46">
+    <row r="67" spans="1:16" ht="48">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -16346,7 +16347,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:16" ht="23">
+    <row r="68" spans="1:16" ht="24">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -16390,7 +16391,7 @@
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
     </row>
-    <row r="69" spans="1:16" ht="23">
+    <row r="69" spans="1:16" ht="24">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -16434,7 +16435,7 @@
       <c r="O69" s="34"/>
       <c r="P69" s="34"/>
     </row>
-    <row r="70" spans="1:16" s="38" customFormat="1" ht="46.5">
+    <row r="70" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -16464,7 +16465,7 @@
       <c r="O70" s="18"/>
       <c r="P70" s="18"/>
     </row>
-    <row r="71" spans="1:16" s="38" customFormat="1" ht="23.5">
+    <row r="71" spans="1:16" s="38" customFormat="1" ht="24.75">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -16494,7 +16495,7 @@
       <c r="O71" s="18"/>
       <c r="P71" s="18"/>
     </row>
-    <row r="72" spans="1:16" s="38" customFormat="1" ht="58">
+    <row r="72" spans="1:16" s="38" customFormat="1" ht="48.75">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -16524,7 +16525,7 @@
       <c r="O72" s="18"/>
       <c r="P72" s="18"/>
     </row>
-    <row r="73" spans="1:16" s="38" customFormat="1" ht="35">
+    <row r="73" spans="1:16" s="38" customFormat="1" ht="36.75">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -16554,7 +16555,7 @@
       <c r="O73" s="15"/>
       <c r="P73" s="15"/>
     </row>
-    <row r="74" spans="1:16" ht="23">
+    <row r="74" spans="1:16" ht="24">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -16598,7 +16599,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:16" ht="46">
+    <row r="75" spans="1:16" ht="48">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -16664,48 +16665,48 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB463F11-FE12-4B34-ACD4-CF4C05A95709}">
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="12" customFormat="1" ht="11.5">
+    <row r="1" spans="1:16" s="12" customFormat="1" ht="12">
       <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
       <c r="O1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="71"/>
-    </row>
-    <row r="2" spans="1:16" s="12" customFormat="1" ht="34.5">
-      <c r="A2" s="71"/>
+      <c r="P1" s="67"/>
+    </row>
+    <row r="2" spans="1:16" s="12" customFormat="1" ht="36">
+      <c r="A2" s="67"/>
       <c r="B2" s="57" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="68" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="57" t="s">
@@ -16720,12 +16721,12 @@
       <c r="I2" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="71"/>
+      <c r="J2" s="67"/>
       <c r="K2" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -16736,15 +16737,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="12" customFormat="1" ht="69">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+    <row r="3" spans="1:16" s="12" customFormat="1" ht="60">
+      <c r="A3" s="67"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -16766,7 +16767,7 @@
       <c r="O3" s="14"/>
       <c r="P3" s="14"/>
     </row>
-    <row r="4" spans="1:16" ht="23.5">
+    <row r="4" spans="1:16" ht="24.75">
       <c r="A4" s="18">
         <v>1</v>
       </c>
@@ -16796,7 +16797,7 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:16" ht="34.5">
+    <row r="5" spans="1:16" ht="36">
       <c r="A5" s="18">
         <v>2</v>
       </c>
@@ -16826,7 +16827,7 @@
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:16" ht="34.5">
+    <row r="6" spans="1:16" ht="36">
       <c r="A6" s="18">
         <v>3</v>
       </c>
@@ -16856,7 +16857,7 @@
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:16" ht="23.5">
+    <row r="7" spans="1:16" ht="24.75">
       <c r="A7" s="18">
         <v>4</v>
       </c>
@@ -16886,7 +16887,7 @@
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:16" ht="57.5">
+    <row r="8" spans="1:16" ht="60">
       <c r="A8" s="18">
         <v>5</v>
       </c>
@@ -16916,7 +16917,7 @@
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:16" ht="46">
+    <row r="9" spans="1:16" ht="48">
       <c r="A9" s="18">
         <v>6</v>
       </c>
@@ -16946,7 +16947,7 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:16" ht="23.5">
+    <row r="10" spans="1:16" ht="24.75">
       <c r="A10" s="18">
         <v>7</v>
       </c>
@@ -16976,7 +16977,7 @@
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
     </row>
-    <row r="11" spans="1:16" ht="34.5">
+    <row r="11" spans="1:16" ht="36">
       <c r="A11" s="18">
         <v>8</v>
       </c>
@@ -17027,20 +17028,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B33F83-065C-49D4-A474-92075A5F6A86}">
   <dimension ref="A1:R22"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="9.4140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="9.1640625" style="12"/>
-    <col min="5" max="5" width="12.25" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.58203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="9.1640625" style="12"/>
-    <col min="13" max="13" width="9.4140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.1640625" style="12"/>
-    <col min="15" max="15" width="9.4140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.25" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.1640625" style="12"/>
+    <col min="1" max="1" width="9.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.140625" style="12"/>
+    <col min="5" max="5" width="12.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="9.140625" style="12"/>
+    <col min="13" max="13" width="9.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="12"/>
+    <col min="15" max="15" width="9.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="31" customFormat="1">
@@ -17071,7 +17072,7 @@
       <c r="Q1" s="57"/>
       <c r="R1" s="57"/>
     </row>
-    <row r="2" spans="1:18" s="31" customFormat="1" ht="23">
+    <row r="2" spans="1:18" s="31" customFormat="1" ht="24">
       <c r="A2" s="57"/>
       <c r="B2" s="57" t="s">
         <v>4</v>
@@ -17080,7 +17081,7 @@
         <v>588</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>5</v>
+        <v>589</v>
       </c>
       <c r="E2" s="57" t="s">
         <v>6</v>
@@ -17089,7 +17090,7 @@
         <v>7</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H2" s="57" t="s">
         <v>9</v>
@@ -17110,14 +17111,14 @@
         <v>13</v>
       </c>
       <c r="P2" s="57" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Q2" s="57" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R2" s="57"/>
     </row>
-    <row r="3" spans="1:18" s="31" customFormat="1" ht="34.5">
+    <row r="3" spans="1:18" s="31" customFormat="1" ht="36">
       <c r="A3" s="57"/>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
@@ -17137,32 +17138,32 @@
         <v>18</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P3" s="57"/>
       <c r="Q3" s="14" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="34.5">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="36">
       <c r="A4" s="18">
         <v>1</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E4" s="18">
         <v>-2.6519999999999998E-2</v>
@@ -17178,17 +17179,17 @@
         <v>25</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="45">
         <v>825</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O4" s="18">
         <v>2025</v>
@@ -17199,13 +17200,13 @@
       <c r="Q4" s="22"/>
       <c r="R4" s="22"/>
     </row>
-    <row r="5" spans="1:18" ht="34.5">
+    <row r="5" spans="1:18" ht="36">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>451</v>
@@ -17221,20 +17222,20 @@
         <v>451</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="45">
         <v>4500</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O5" s="18">
         <v>2025</v>
@@ -17245,16 +17246,16 @@
       <c r="Q5" s="22"/>
       <c r="R5" s="22"/>
     </row>
-    <row r="6" spans="1:18" ht="34.5">
+    <row r="6" spans="1:18" ht="36">
       <c r="A6" s="18">
         <v>3</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E6" s="18">
         <v>-5.6816999999999999E-2</v>
@@ -17267,20 +17268,20 @@
         <v>456</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="45">
         <v>3800</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O6" s="18">
         <v>2025</v>
@@ -17291,16 +17292,16 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="22"/>
     </row>
-    <row r="7" spans="1:18" ht="34.5">
+    <row r="7" spans="1:18" ht="36">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E7" s="18">
         <v>-6.4637E-2</v>
@@ -17313,20 +17314,20 @@
         <v>460</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L7" s="22"/>
       <c r="M7" s="45">
         <v>4600</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O7" s="18">
         <v>2025</v>
@@ -17337,16 +17338,16 @@
       <c r="Q7" s="22"/>
       <c r="R7" s="22"/>
     </row>
-    <row r="8" spans="1:18" ht="34.5">
+    <row r="8" spans="1:18" ht="36">
       <c r="A8" s="18">
         <v>5</v>
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E8" s="18">
         <v>-7.3205999999999993E-2</v>
@@ -17356,23 +17357,23 @@
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="22" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L8" s="22"/>
       <c r="M8" s="45">
         <v>6300</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O8" s="18">
         <v>2025</v>
@@ -17383,16 +17384,16 @@
       <c r="Q8" s="22"/>
       <c r="R8" s="22"/>
     </row>
-    <row r="9" spans="1:18" ht="34.5">
+    <row r="9" spans="1:18" ht="36">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E9" s="18">
         <v>-6.6999000000000003E-2</v>
@@ -17402,23 +17403,23 @@
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="22" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L9" s="22"/>
       <c r="M9" s="45">
         <v>2100</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O9" s="18">
         <v>2025</v>
@@ -17429,16 +17430,16 @@
       <c r="Q9" s="22"/>
       <c r="R9" s="22"/>
     </row>
-    <row r="10" spans="1:18" ht="46">
+    <row r="10" spans="1:18" ht="48">
       <c r="A10" s="18">
         <v>7</v>
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E10" s="18">
         <v>-2.4538889000000001E-2</v>
@@ -17448,13 +17449,13 @@
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="22" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>27</v>
@@ -17473,16 +17474,16 @@
       <c r="Q10" s="22"/>
       <c r="R10" s="22"/>
     </row>
-    <row r="11" spans="1:18" ht="46">
+    <row r="11" spans="1:18" ht="48">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E11" s="18">
         <v>-5.7777800000000004E-4</v>
@@ -17492,13 +17493,13 @@
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="22" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>27</v>
@@ -17517,16 +17518,16 @@
       <c r="Q11" s="22"/>
       <c r="R11" s="22"/>
     </row>
-    <row r="12" spans="1:18" ht="69">
+    <row r="12" spans="1:18" ht="60">
       <c r="A12" s="18">
         <v>9</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E12" s="18">
         <v>-3.3805556E-2</v>
@@ -17542,7 +17543,7 @@
         <v>383</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>27</v>
@@ -17561,16 +17562,16 @@
       <c r="Q12" s="22"/>
       <c r="R12" s="22"/>
     </row>
-    <row r="13" spans="1:18" ht="69">
+    <row r="13" spans="1:18" ht="72">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E13" s="18">
         <v>-3.3805556E-2</v>
@@ -17580,13 +17581,13 @@
       </c>
       <c r="G13" s="18"/>
       <c r="H13" s="22" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K13" s="22" t="s">
         <v>27</v>
@@ -17605,16 +17606,16 @@
       <c r="Q13" s="22"/>
       <c r="R13" s="22"/>
     </row>
-    <row r="14" spans="1:18" ht="57.5">
+    <row r="14" spans="1:18" ht="60">
       <c r="A14" s="18">
         <v>11</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E14" s="18">
         <v>-3.8888900000000001E-4</v>
@@ -17624,13 +17625,13 @@
       </c>
       <c r="G14" s="18"/>
       <c r="H14" s="22" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>27</v>
@@ -17649,16 +17650,16 @@
       <c r="Q14" s="22"/>
       <c r="R14" s="22"/>
     </row>
-    <row r="15" spans="1:18" ht="69">
+    <row r="15" spans="1:18" ht="60">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E15" s="18">
         <v>-3.3805556E-2</v>
@@ -17674,7 +17675,7 @@
         <v>383</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K15" s="22" t="s">
         <v>27</v>
@@ -17693,16 +17694,16 @@
       <c r="Q15" s="22"/>
       <c r="R15" s="22"/>
     </row>
-    <row r="16" spans="1:18" ht="57.5">
+    <row r="16" spans="1:18" ht="60">
       <c r="A16" s="18">
         <v>13</v>
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E16" s="18">
         <v>-3.5644443999999997E-2</v>
@@ -17712,13 +17713,13 @@
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="22" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>27</v>
@@ -17737,16 +17738,16 @@
       <c r="Q16" s="22"/>
       <c r="R16" s="22"/>
     </row>
-    <row r="17" spans="1:18" ht="57.5">
+    <row r="17" spans="1:18" ht="60">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E17" s="18">
         <v>-3.1629999999999998E-2</v>
@@ -17756,13 +17757,13 @@
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="22" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K17" s="22" t="s">
         <v>27</v>
@@ -17781,16 +17782,16 @@
       <c r="Q17" s="22"/>
       <c r="R17" s="22"/>
     </row>
-    <row r="18" spans="1:18" ht="69">
+    <row r="18" spans="1:18" ht="72">
       <c r="A18" s="18">
         <v>15</v>
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E18" s="18">
         <v>-6.3280000000000003E-2</v>
@@ -17803,10 +17804,10 @@
         <v>451</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>27</v>
@@ -17825,16 +17826,16 @@
       <c r="Q18" s="22"/>
       <c r="R18" s="22"/>
     </row>
-    <row r="19" spans="1:18" ht="92">
+    <row r="19" spans="1:18" ht="96">
       <c r="A19" s="18">
         <v>16</v>
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E19" s="18">
         <v>-2.9803E-2</v>
@@ -17847,10 +17848,10 @@
         <v>460</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K19" s="22" t="s">
         <v>27</v>
@@ -17869,16 +17870,16 @@
       <c r="Q19" s="22"/>
       <c r="R19" s="22"/>
     </row>
-    <row r="20" spans="1:18" ht="92">
+    <row r="20" spans="1:18" ht="96">
       <c r="A20" s="18">
         <v>17</v>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E20" s="18">
         <v>-1.1709999999999999E-3</v>
@@ -17888,13 +17889,13 @@
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="22" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>98</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K20" s="22" t="s">
         <v>27</v>
@@ -17913,16 +17914,16 @@
       <c r="Q20" s="22"/>
       <c r="R20" s="22"/>
     </row>
-    <row r="21" spans="1:18" ht="80.5">
+    <row r="21" spans="1:18" ht="84">
       <c r="A21" s="18">
         <v>18</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E21" s="18">
         <v>5.3839999999999999E-3</v>
@@ -17938,7 +17939,7 @@
         <v>98</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K21" s="22" t="s">
         <v>27</v>
@@ -17957,16 +17958,16 @@
       <c r="Q21" s="22"/>
       <c r="R21" s="22"/>
     </row>
-    <row r="22" spans="1:18" ht="46">
+    <row r="22" spans="1:18" ht="60">
       <c r="A22" s="18">
         <v>19</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E22" s="18">
         <v>-2.9825000000000001E-2</v>
@@ -17982,7 +17983,7 @@
         <v>98</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K22" s="22" t="s">
         <v>27</v>
@@ -18025,14 +18026,14 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87310F7-40E5-44CA-A68B-9F0CB665F765}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="3" width="9.1640625" style="12"/>
-    <col min="4" max="4" width="9.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="9.140625" style="12"/>
+    <col min="4" max="4" width="9.28515625" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.1640625" style="12"/>
+    <col min="6" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -18042,37 +18043,37 @@
       <c r="B1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
       <c r="O1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="71"/>
-    </row>
-    <row r="2" spans="1:16" ht="34.5">
-      <c r="A2" s="71"/>
+      <c r="P1" s="67"/>
+    </row>
+    <row r="2" spans="1:16" ht="36">
+      <c r="A2" s="67"/>
       <c r="B2" s="57" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="68" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="57" t="s">
@@ -18087,12 +18088,12 @@
       <c r="I2" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="71"/>
+      <c r="J2" s="67"/>
       <c r="K2" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -18103,15 +18104,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="57.5">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+    <row r="3" spans="1:16" ht="60">
+      <c r="A3" s="67"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -18133,13 +18134,13 @@
       <c r="O3" s="14"/>
       <c r="P3" s="14"/>
     </row>
-    <row r="4" spans="1:16" ht="23">
+    <row r="4" spans="1:16" ht="24">
       <c r="A4" s="27">
         <v>1</v>
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D4" s="47">
         <v>-5.3099999999999996E-3</v>
@@ -18165,13 +18166,13 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:16" ht="23">
+    <row r="5" spans="1:16" ht="24">
       <c r="A5" s="27">
         <v>2</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D5" s="47">
         <v>-3.29E-3</v>
@@ -18197,13 +18198,13 @@
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:16" ht="23">
+    <row r="6" spans="1:16" ht="24">
       <c r="A6" s="27">
         <v>3</v>
       </c>
       <c r="B6" s="25"/>
       <c r="C6" s="25" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D6" s="47">
         <v>-6.4999999999999997E-3</v>
@@ -18229,13 +18230,13 @@
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:16" ht="23">
+    <row r="7" spans="1:16" ht="24">
       <c r="A7" s="27">
         <v>4</v>
       </c>
       <c r="B7" s="25"/>
       <c r="C7" s="25" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D7" s="47">
         <v>-1.0200000000000001E-2</v>
@@ -18261,13 +18262,13 @@
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:16" ht="23">
+    <row r="8" spans="1:16" ht="24">
       <c r="A8" s="27">
         <v>5</v>
       </c>
       <c r="B8" s="25"/>
       <c r="C8" s="25" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D8" s="47">
         <v>-8.5900000000000004E-3</v>
@@ -18293,13 +18294,13 @@
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:16" ht="23">
+    <row r="9" spans="1:16" ht="24">
       <c r="A9" s="27">
         <v>6</v>
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="25" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D9" s="47">
         <v>-6.2599999999999999E-3</v>
@@ -18325,13 +18326,13 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:16" ht="23">
+    <row r="10" spans="1:16" ht="24">
       <c r="A10" s="27">
         <v>7</v>
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="25" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D10" s="47">
         <v>-6.5300000000000002E-3</v>
@@ -18357,13 +18358,13 @@
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
     </row>
-    <row r="11" spans="1:16" ht="23">
+    <row r="11" spans="1:16" ht="24">
       <c r="A11" s="27">
         <v>8</v>
       </c>
       <c r="B11" s="25"/>
       <c r="C11" s="25" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D11" s="47">
         <v>-3.63E-3</v>
@@ -18389,13 +18390,13 @@
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
     </row>
-    <row r="12" spans="1:16" ht="34.5">
+    <row r="12" spans="1:16" ht="36">
       <c r="A12" s="27">
         <v>9</v>
       </c>
       <c r="B12" s="25"/>
       <c r="C12" s="25" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D12" s="47">
         <v>-3.7399999999999998E-3</v>
@@ -18663,39 +18664,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF8C012-57B8-49D3-9EF1-E19A730B86BA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
-    <ds:schemaRef ds:uri="4ce1a36b-806a-4732-b893-33b689d3fa0c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF8C012-57B8-49D3-9EF1-E19A730B86BA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5380809C-BC60-49CE-8A28-8AFE265843E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5380809C-BC60-49CE-8A28-8AFE265843E8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{495DAE39-1778-4C6E-AEB5-6769AAD718EA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
-    <ds:schemaRef ds:uri="4ce1a36b-806a-4732-b893-33b689d3fa0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{495DAE39-1778-4C6E-AEB5-6769AAD718EA}"/>
 </file>
--- a/data/processed/eksposur_pontianak_0408.xlsx
+++ b/data/processed/eksposur_pontianak_0408.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCE6E2EB-8391-49FD-AAD7-D3691255B5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{F1E380E3-4E01-4D97-B50D-1BA9DCA76966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70D2E42F-9F0F-4C1B-90CC-8708D20B9CE7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
   </bookViews>
   <sheets>
     <sheet name="Government" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="622">
   <si>
     <t>No</t>
   </si>
@@ -1365,27 +1365,6 @@
     <t>Atap , Lantai, Plafond</t>
   </si>
   <si>
-    <t>12.26.09.07.01.08.02</t>
-  </si>
-  <si>
-    <t>Puskesmas Pal 3</t>
-  </si>
-  <si>
-    <t>Struktur</t>
-  </si>
-  <si>
-    <t>12.26.09.07.01.08.01</t>
-  </si>
-  <si>
-    <t>Puskesmas Alianyang</t>
-  </si>
-  <si>
-    <t>12.26.09.07.01.08.03</t>
-  </si>
-  <si>
-    <t>Puskesmas Karya Mulia</t>
-  </si>
-  <si>
     <t>12.26.09.07.01.10.00</t>
   </si>
   <si>
@@ -1410,457 +1389,448 @@
     <t>Struktur, Atap, Plafond, Lantai</t>
   </si>
   <si>
-    <t>12.26.09.07.01.13.00</t>
-  </si>
-  <si>
-    <t>Puskesmas Kampung Bangka</t>
+    <t>12.26.09.07.01.13.01</t>
+  </si>
+  <si>
+    <t>Puskesmas Parit H.Husin II</t>
+  </si>
+  <si>
+    <t>Bansir Darat</t>
+  </si>
+  <si>
+    <t>POSYANDU CERIA</t>
+  </si>
+  <si>
+    <t>POSYANDU DHARMA KENCANA</t>
+  </si>
+  <si>
+    <t>POSYANDU TERATAI</t>
+  </si>
+  <si>
+    <t>POSYANDU BOUGENVIL</t>
+  </si>
+  <si>
+    <t>POSYANDU KENANGA</t>
+  </si>
+  <si>
+    <t>POSYANDU ROSELA</t>
+  </si>
+  <si>
+    <t>POSYANDU KEMALA</t>
+  </si>
+  <si>
+    <t>POSYANDU LESTARI</t>
+  </si>
+  <si>
+    <t>POSYANDU ANGGREK BULAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POSYANDU DEWI SARTIKA </t>
+  </si>
+  <si>
+    <t>POSYANDU CEMERLANG</t>
+  </si>
+  <si>
+    <t>POSYANDU KENCANA</t>
+  </si>
+  <si>
+    <t>POSYANDU SAHABAT</t>
+  </si>
+  <si>
+    <t>POSYANDU SRIKANDI</t>
+  </si>
+  <si>
+    <t>POSYANDU BALITA "LANGSAT SEJAHTERA"</t>
+  </si>
+  <si>
+    <t>POSYANDU KURMA MADU</t>
+  </si>
+  <si>
+    <t>POSYANDU KELUARGA CEMARA</t>
+  </si>
+  <si>
+    <t>Masjid Istiqamah</t>
+  </si>
+  <si>
+    <t>± 300–400 m²</t>
+  </si>
+  <si>
+    <t>Masjid Nurul Hidayah</t>
+  </si>
+  <si>
+    <t>± 250–350 m²</t>
+  </si>
+  <si>
+    <t>Masjid At-Tawwabin</t>
+  </si>
+  <si>
+    <t>Masjid Dzakirin</t>
+  </si>
+  <si>
+    <t>Masjid Al-Fajar</t>
+  </si>
+  <si>
+    <t>± 300–450 m²</t>
+  </si>
+  <si>
+    <t>Masjid Al-Mujahid</t>
+  </si>
+  <si>
+    <t>± 110 m²</t>
+  </si>
+  <si>
+    <t>Masjid At-Taqwa Polri</t>
+  </si>
+  <si>
+    <t>± 425 m²</t>
+  </si>
+  <si>
+    <t>Masjid Nursalim</t>
+  </si>
+  <si>
+    <t>144 m²</t>
+  </si>
+  <si>
+    <t>Masjid As-Sirath</t>
+  </si>
+  <si>
+    <t>Masjid Maulidiyah</t>
+  </si>
+  <si>
+    <t>Masjid Al-Hadi</t>
+  </si>
+  <si>
+    <t>Masjid Al-Asyraf</t>
+  </si>
+  <si>
+    <t>Masjid Hidayatush Shalihin</t>
+  </si>
+  <si>
+    <t>Masjid Al Muwafaqah</t>
+  </si>
+  <si>
+    <t>Masjid Ash-Sholihin</t>
+  </si>
+  <si>
+    <t>± 108 m²</t>
+  </si>
+  <si>
+    <t>Masjid Syuhada</t>
+  </si>
+  <si>
+    <t>± 400 m²</t>
+  </si>
+  <si>
+    <t>± 2005–2010</t>
+  </si>
+  <si>
+    <t>Masjid Darul Fallah</t>
+  </si>
+  <si>
+    <t>Masjid Sadar</t>
+  </si>
+  <si>
+    <t>Masjid Baitul Iman</t>
+  </si>
+  <si>
+    <t>Masjid Jami' Al-Kautsar (Ahmadiyah)</t>
+  </si>
+  <si>
+    <t>± 350 m²</t>
+  </si>
+  <si>
+    <t>Masjid Al Muhajirin</t>
+  </si>
+  <si>
+    <t>Masjid Syakirin</t>
+  </si>
+  <si>
+    <t>± 400–500 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masjid Kapal Munzalan </t>
+  </si>
+  <si>
+    <t>± 187 m²</t>
+  </si>
+  <si>
+    <t>± 2018–2020</t>
+  </si>
+  <si>
+    <t>Masjid Al-Hikmah</t>
+  </si>
+  <si>
+    <t>± 1985–1995</t>
+  </si>
+  <si>
+    <t>Masjid Baiturrahmah</t>
+  </si>
+  <si>
+    <t>Masjid Jihadul Muslimin</t>
+  </si>
+  <si>
+    <t>± 100–200 m²</t>
+  </si>
+  <si>
+    <t>± 1990–2005</t>
+  </si>
+  <si>
+    <t>Masjid Al-Qodri</t>
+  </si>
+  <si>
+    <t>± 200 – 350  m²</t>
+  </si>
+  <si>
+    <t>± 1995 – 2010</t>
+  </si>
+  <si>
+    <t>Masjid An Nur</t>
+  </si>
+  <si>
+    <t>± 1995 – 2015</t>
+  </si>
+  <si>
+    <t>Masjid Al-Ihsan</t>
+  </si>
+  <si>
+    <t>Masjid Mabrur</t>
+  </si>
+  <si>
+    <t>± 200‑300 m²</t>
+  </si>
+  <si>
+    <t>Masjid Sirajul Islam</t>
+  </si>
+  <si>
+    <t>600 m²</t>
+  </si>
+  <si>
+    <t>Masjid Al-Khalifah</t>
+  </si>
+  <si>
+    <t>Masjid Al-Manar</t>
+  </si>
+  <si>
+    <t>Masjid An-Nur Pasar Tengah</t>
+  </si>
+  <si>
+    <t>± 350–450 m²</t>
+  </si>
+  <si>
+    <t>± 1980–1990</t>
+  </si>
+  <si>
+    <t>Masjid Babussalam</t>
+  </si>
+  <si>
+    <t>Masjid Al-Ilham</t>
+  </si>
+  <si>
+    <t>MASJID AL MUQIMIN</t>
+  </si>
+  <si>
+    <t>MASJID MIFTAHUL JANNAH</t>
+  </si>
+  <si>
+    <t>MASJID BAITUL IMAN</t>
+  </si>
+  <si>
+    <t>MASJID JANNATUL NAIM</t>
+  </si>
+  <si>
+    <t>MASJID AL HUDA</t>
+  </si>
+  <si>
+    <t>MASJID JAMI'ATUL IMAN</t>
+  </si>
+  <si>
+    <t>MASJID AL JANNATUL NA'IM</t>
+  </si>
+  <si>
+    <t>MASJID AL AMIIN</t>
+  </si>
+  <si>
+    <t>MASJID AL FURQON</t>
+  </si>
+  <si>
+    <t>MASJID NURUL HAMID</t>
+  </si>
+  <si>
+    <t>MASJID AQIMUDIN</t>
+  </si>
+  <si>
+    <t>MASJID SABILUL JANNAH</t>
+  </si>
+  <si>
+    <t>MASJID AL IKHLAS</t>
+  </si>
+  <si>
+    <t>MASJID NUR BAITULLAH</t>
+  </si>
+  <si>
+    <t>MASJID NURUL ZAHANIR</t>
+  </si>
+  <si>
+    <t>MASJID AL MUSTAQIM</t>
+  </si>
+  <si>
+    <t>MASJID AL IKHWANUR</t>
+  </si>
+  <si>
+    <t>MASJID AT TAQWA</t>
+  </si>
+  <si>
+    <t>MASJID NURUL IMAN</t>
+  </si>
+  <si>
+    <t>MASJID ASHABUL KAHFI</t>
+  </si>
+  <si>
+    <t>MASJID NURUL JANNAH</t>
+  </si>
+  <si>
+    <t>Katedral Santo Yosef</t>
+  </si>
+  <si>
+    <t>± 2.000–2.500 m²</t>
+  </si>
+  <si>
+    <t>Santapan Rohani</t>
+  </si>
+  <si>
+    <t>Gereja Sidang Jemaat Kristus</t>
+  </si>
+  <si>
+    <t>GBI El Shaddai</t>
+  </si>
+  <si>
+    <t>GKII Hebron</t>
+  </si>
+  <si>
+    <t>GPI Sidang Kota Baru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">± 2005–2010 </t>
+  </si>
+  <si>
+    <t>Maria Ratu Pencinta Damai Paroki</t>
+  </si>
+  <si>
+    <t>GPIB Siloam</t>
+  </si>
+  <si>
+    <t>± 700–900 m²</t>
+  </si>
+  <si>
+    <t>GPKB Elim</t>
+  </si>
+  <si>
+    <t>± 350–400 m²</t>
+  </si>
+  <si>
+    <t>GEREJA GKTI BUKIT SION</t>
+  </si>
+  <si>
+    <t>GEREJA HKBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEREJA PANTEKOSTA INDONESIA </t>
+  </si>
+  <si>
+    <t>GEREJA BUNDA MARIA</t>
+  </si>
+  <si>
+    <t>Kwang Tie Bio</t>
+  </si>
+  <si>
+    <t>Beton/ Kayu</t>
+  </si>
+  <si>
+    <t>± 500–700 m²</t>
+  </si>
+  <si>
+    <t>Vihara Bodhisatva Karaniya Metta</t>
+  </si>
+  <si>
+    <t>Lapangan RW 22</t>
+  </si>
+  <si>
+    <t>Lapangan Volly Sapta Marga 5</t>
+  </si>
+  <si>
+    <t>Lapangan Komplek WS 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapangan Futsal King </t>
+  </si>
+  <si>
+    <t>Lapangan Futsal pokse Khatulistiwa</t>
+  </si>
+  <si>
+    <t>Gor Badminton Gelanggang Kapuas</t>
+  </si>
+  <si>
+    <t>Muara Kapuas</t>
+  </si>
+  <si>
+    <t>Water Park Muara Kapuas</t>
+  </si>
+  <si>
+    <t>Identitas dan Lokasi Aset</t>
+  </si>
+  <si>
+    <t>Dinas Terkait</t>
+  </si>
+  <si>
+    <t>Alamat/Nama Lokasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elevasi Tanah </t>
+  </si>
+  <si>
+    <t>Biaya Pemeliharaan Rutin/Pembangunan (Rp)</t>
+  </si>
+  <si>
+    <t>Jadwal Historis &amp; Rencana Perbaikan</t>
+  </si>
+  <si>
+    <t>Panjang Bangunan (m)</t>
+  </si>
+  <si>
+    <t>Lebar Bangunan (m)</t>
+  </si>
+  <si>
+    <t>Tahun Dibangun/Normalisasi</t>
+  </si>
+  <si>
+    <t>Waktu</t>
+  </si>
+  <si>
+    <t>Nominal Anggaran Perbaikan</t>
+  </si>
+  <si>
+    <t>BWS Kalimantan I Pontianak</t>
+  </si>
+  <si>
+    <t>Parit Sungai Jawi</t>
+  </si>
+  <si>
+    <t>Saluran Drainase</t>
+  </si>
+  <si>
+    <t>Tanah</t>
+  </si>
+  <si>
+    <t>6 - 9</t>
+  </si>
+  <si>
+    <t>Pontianak Selatan</t>
+  </si>
+  <si>
+    <t>Parit Perdana</t>
   </si>
   <si>
     <t>Bansir Laut</t>
-  </si>
-  <si>
-    <t>Pondasi, Struktur, Lantai, Dinding, Plafond, Atap</t>
-  </si>
-  <si>
-    <t>12.26.09.07.01.13.01</t>
-  </si>
-  <si>
-    <t>Puskesmas Parit H.Husin II</t>
-  </si>
-  <si>
-    <t>Bansir Darat</t>
-  </si>
-  <si>
-    <t>POSYANDU CERIA</t>
-  </si>
-  <si>
-    <t>POSYANDU DHARMA KENCANA</t>
-  </si>
-  <si>
-    <t>POSYANDU TERATAI</t>
-  </si>
-  <si>
-    <t>POSYANDU BOUGENVIL</t>
-  </si>
-  <si>
-    <t>POSYANDU KENANGA</t>
-  </si>
-  <si>
-    <t>POSYANDU ROSELA</t>
-  </si>
-  <si>
-    <t>POSYANDU KEMALA</t>
-  </si>
-  <si>
-    <t>POSYANDU LESTARI</t>
-  </si>
-  <si>
-    <t>POSYANDU ANGGREK BULAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POSYANDU DEWI SARTIKA </t>
-  </si>
-  <si>
-    <t>POSYANDU CEMERLANG</t>
-  </si>
-  <si>
-    <t>POSYANDU KENCANA</t>
-  </si>
-  <si>
-    <t>POSYANDU SAHABAT</t>
-  </si>
-  <si>
-    <t>POSYANDU SRIKANDI</t>
-  </si>
-  <si>
-    <t>POSYANDU BALITA "LANGSAT SEJAHTERA"</t>
-  </si>
-  <si>
-    <t>POSYANDU KURMA MADU</t>
-  </si>
-  <si>
-    <t>POSYANDU KELUARGA CEMARA</t>
-  </si>
-  <si>
-    <t>Masjid Istiqamah</t>
-  </si>
-  <si>
-    <t>± 300–400 m²</t>
-  </si>
-  <si>
-    <t>Masjid Nurul Hidayah</t>
-  </si>
-  <si>
-    <t>± 250–350 m²</t>
-  </si>
-  <si>
-    <t>Masjid At-Tawwabin</t>
-  </si>
-  <si>
-    <t>Masjid Dzakirin</t>
-  </si>
-  <si>
-    <t>Masjid Al-Fajar</t>
-  </si>
-  <si>
-    <t>± 300–450 m²</t>
-  </si>
-  <si>
-    <t>Masjid Al-Mujahid</t>
-  </si>
-  <si>
-    <t>± 110 m²</t>
-  </si>
-  <si>
-    <t>Masjid At-Taqwa Polri</t>
-  </si>
-  <si>
-    <t>± 425 m²</t>
-  </si>
-  <si>
-    <t>Masjid Nursalim</t>
-  </si>
-  <si>
-    <t>144 m²</t>
-  </si>
-  <si>
-    <t>Masjid As-Sirath</t>
-  </si>
-  <si>
-    <t>Masjid Maulidiyah</t>
-  </si>
-  <si>
-    <t>Masjid Al-Hadi</t>
-  </si>
-  <si>
-    <t>Masjid Al-Asyraf</t>
-  </si>
-  <si>
-    <t>Masjid Hidayatush Shalihin</t>
-  </si>
-  <si>
-    <t>Masjid Al Muwafaqah</t>
-  </si>
-  <si>
-    <t>Masjid Ash-Sholihin</t>
-  </si>
-  <si>
-    <t>± 108 m²</t>
-  </si>
-  <si>
-    <t>Masjid Syuhada</t>
-  </si>
-  <si>
-    <t>± 400 m²</t>
-  </si>
-  <si>
-    <t>± 2005–2010</t>
-  </si>
-  <si>
-    <t>Masjid Darul Fallah</t>
-  </si>
-  <si>
-    <t>Masjid Sadar</t>
-  </si>
-  <si>
-    <t>Masjid Baitul Iman</t>
-  </si>
-  <si>
-    <t>Masjid Jami' Al-Kautsar (Ahmadiyah)</t>
-  </si>
-  <si>
-    <t>± 350 m²</t>
-  </si>
-  <si>
-    <t>Masjid Al Muhajirin</t>
-  </si>
-  <si>
-    <t>Masjid Syakirin</t>
-  </si>
-  <si>
-    <t>± 400–500 m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masjid Kapal Munzalan </t>
-  </si>
-  <si>
-    <t>± 187 m²</t>
-  </si>
-  <si>
-    <t>± 2018–2020</t>
-  </si>
-  <si>
-    <t>Masjid Al-Hikmah</t>
-  </si>
-  <si>
-    <t>± 1985–1995</t>
-  </si>
-  <si>
-    <t>Masjid Baiturrahmah</t>
-  </si>
-  <si>
-    <t>Masjid Jihadul Muslimin</t>
-  </si>
-  <si>
-    <t>± 100–200 m²</t>
-  </si>
-  <si>
-    <t>± 1990–2005</t>
-  </si>
-  <si>
-    <t>Masjid Al-Qodri</t>
-  </si>
-  <si>
-    <t>± 200 – 350  m²</t>
-  </si>
-  <si>
-    <t>± 1995 – 2010</t>
-  </si>
-  <si>
-    <t>Masjid An Nur</t>
-  </si>
-  <si>
-    <t>± 1995 – 2015</t>
-  </si>
-  <si>
-    <t>Masjid Al-Ihsan</t>
-  </si>
-  <si>
-    <t>Masjid Mabrur</t>
-  </si>
-  <si>
-    <t>± 200‑300 m²</t>
-  </si>
-  <si>
-    <t>Masjid Sirajul Islam</t>
-  </si>
-  <si>
-    <t>600 m²</t>
-  </si>
-  <si>
-    <t>Masjid Al-Khalifah</t>
-  </si>
-  <si>
-    <t>Masjid Al-Manar</t>
-  </si>
-  <si>
-    <t>Masjid An-Nur Pasar Tengah</t>
-  </si>
-  <si>
-    <t>± 350–450 m²</t>
-  </si>
-  <si>
-    <t>± 1980–1990</t>
-  </si>
-  <si>
-    <t>Masjid Babussalam</t>
-  </si>
-  <si>
-    <t>Masjid Al-Ilham</t>
-  </si>
-  <si>
-    <t>MASJID AL MUQIMIN</t>
-  </si>
-  <si>
-    <t>MASJID MIFTAHUL JANNAH</t>
-  </si>
-  <si>
-    <t>MASJID BAITUL IMAN</t>
-  </si>
-  <si>
-    <t>MASJID JANNATUL NAIM</t>
-  </si>
-  <si>
-    <t>MASJID AL HUDA</t>
-  </si>
-  <si>
-    <t>MASJID JAMI'ATUL IMAN</t>
-  </si>
-  <si>
-    <t>MASJID AL JANNATUL NA'IM</t>
-  </si>
-  <si>
-    <t>MASJID AL AMIIN</t>
-  </si>
-  <si>
-    <t>MASJID AL FURQON</t>
-  </si>
-  <si>
-    <t>MASJID NURUL HAMID</t>
-  </si>
-  <si>
-    <t>MASJID AQIMUDIN</t>
-  </si>
-  <si>
-    <t>MASJID SABILUL JANNAH</t>
-  </si>
-  <si>
-    <t>MASJID AL IKHLAS</t>
-  </si>
-  <si>
-    <t>MASJID NUR BAITULLAH</t>
-  </si>
-  <si>
-    <t>MASJID NURUL ZAHANIR</t>
-  </si>
-  <si>
-    <t>MASJID AL MUSTAQIM</t>
-  </si>
-  <si>
-    <t>MASJID AL IKHWANUR</t>
-  </si>
-  <si>
-    <t>MASJID AT TAQWA</t>
-  </si>
-  <si>
-    <t>MASJID NURUL IMAN</t>
-  </si>
-  <si>
-    <t>MASJID ASHABUL KAHFI</t>
-  </si>
-  <si>
-    <t>MASJID NURUL JANNAH</t>
-  </si>
-  <si>
-    <t>Katedral Santo Yosef</t>
-  </si>
-  <si>
-    <t>± 2.000–2.500 m²</t>
-  </si>
-  <si>
-    <t>Santapan Rohani</t>
-  </si>
-  <si>
-    <t>Gereja Sidang Jemaat Kristus</t>
-  </si>
-  <si>
-    <t>GBI El Shaddai</t>
-  </si>
-  <si>
-    <t>GKII Hebron</t>
-  </si>
-  <si>
-    <t>GPI Sidang Kota Baru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">± 2005–2010 </t>
-  </si>
-  <si>
-    <t>Maria Ratu Pencinta Damai Paroki</t>
-  </si>
-  <si>
-    <t>GPIB Siloam</t>
-  </si>
-  <si>
-    <t>± 700–900 m²</t>
-  </si>
-  <si>
-    <t>GPKB Elim</t>
-  </si>
-  <si>
-    <t>± 350–400 m²</t>
-  </si>
-  <si>
-    <t>GEREJA GKTI BUKIT SION</t>
-  </si>
-  <si>
-    <t>GEREJA HKBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEREJA PANTEKOSTA INDONESIA </t>
-  </si>
-  <si>
-    <t>GEREJA BUNDA MARIA</t>
-  </si>
-  <si>
-    <t>Kwang Tie Bio</t>
-  </si>
-  <si>
-    <t>Beton/ Kayu</t>
-  </si>
-  <si>
-    <t>± 500–700 m²</t>
-  </si>
-  <si>
-    <t>Vihara Bodhisatva Karaniya Metta</t>
-  </si>
-  <si>
-    <t>Lapangan RW 22</t>
-  </si>
-  <si>
-    <t>Lapangan Volly Sapta Marga 5</t>
-  </si>
-  <si>
-    <t>Lapangan Komplek WS 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lapangan Futsal King </t>
-  </si>
-  <si>
-    <t>Lapangan Futsal pokse Khatulistiwa</t>
-  </si>
-  <si>
-    <t>Gor Badminton Gelanggang Kapuas</t>
-  </si>
-  <si>
-    <t>Muara Kapuas</t>
-  </si>
-  <si>
-    <t>Water Park Muara Kapuas</t>
-  </si>
-  <si>
-    <t>Identitas dan Lokasi Aset</t>
-  </si>
-  <si>
-    <t>Dinas Terkait</t>
-  </si>
-  <si>
-    <t>Alamat/Nama Lokasi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elevasi Tanah </t>
-  </si>
-  <si>
-    <t>Biaya Pemeliharaan Rutin/Pembangunan (Rp)</t>
-  </si>
-  <si>
-    <t>Jadwal Historis &amp; Rencana Perbaikan</t>
-  </si>
-  <si>
-    <t>Panjang Bangunan (m)</t>
-  </si>
-  <si>
-    <t>Lebar Bangunan (m)</t>
-  </si>
-  <si>
-    <t>Tahun Dibangun/Normalisasi</t>
-  </si>
-  <si>
-    <t>Waktu</t>
-  </si>
-  <si>
-    <t>Nominal Anggaran Perbaikan</t>
-  </si>
-  <si>
-    <t>BWS Kalimantan I Pontianak</t>
-  </si>
-  <si>
-    <t>Parit Sungai Jawi</t>
-  </si>
-  <si>
-    <t>Saluran Drainase</t>
-  </si>
-  <si>
-    <t>Tanah</t>
-  </si>
-  <si>
-    <t>6 - 9</t>
-  </si>
-  <si>
-    <t>Pontianak Selatan</t>
-  </si>
-  <si>
-    <t>Parit Perdana</t>
   </si>
   <si>
     <t>Parit Sepakat</t>
@@ -2825,16 +2795,22 @@
     <xf numFmtId="166" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2843,22 +2819,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3277,63 +3247,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="49" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49" t="s">
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="50"/>
+      <c r="P1" s="54"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="56"/>
-      <c r="B2" s="51" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="50"/>
-      <c r="K2" s="54" t="s">
+      <c r="J2" s="54"/>
+      <c r="K2" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="50"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="54"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -3345,14 +3315,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -4548,7 +4518,7 @@
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
     </row>
-    <row r="31" spans="1:16" ht="48">
+    <row r="31" spans="1:16" ht="35.25">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -4563,8 +4533,12 @@
         <v>109.30765</v>
       </c>
       <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
+      <c r="G31" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
       <c r="K31" s="15"/>
@@ -4574,7 +4548,7 @@
       <c r="O31" s="15"/>
       <c r="P31" s="15"/>
     </row>
-    <row r="32" spans="1:16" ht="48">
+    <row r="32" spans="1:16" ht="35.25">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -4589,8 +4563,12 @@
         <v>109.30584</v>
       </c>
       <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
+      <c r="G32" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
       <c r="K32" s="15"/>
@@ -4600,7 +4578,7 @@
       <c r="O32" s="15"/>
       <c r="P32" s="15"/>
     </row>
-    <row r="33" spans="1:16" ht="48">
+    <row r="33" spans="1:16" ht="35.25">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -4615,8 +4593,12 @@
         <v>109.31068999999999</v>
       </c>
       <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
+      <c r="G33" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
       <c r="K33" s="15"/>
@@ -4626,7 +4608,7 @@
       <c r="O33" s="15"/>
       <c r="P33" s="15"/>
     </row>
-    <row r="34" spans="1:16" ht="48">
+    <row r="34" spans="1:16" ht="35.25">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -4641,8 +4623,12 @@
         <v>109.31041</v>
       </c>
       <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
+      <c r="G34" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I34" s="15"/>
       <c r="J34" s="15"/>
       <c r="K34" s="15"/>
@@ -4652,7 +4638,7 @@
       <c r="O34" s="15"/>
       <c r="P34" s="15"/>
     </row>
-    <row r="35" spans="1:16" ht="48">
+    <row r="35" spans="1:16" ht="35.25">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -4667,8 +4653,12 @@
         <v>109.30198</v>
       </c>
       <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
+      <c r="G35" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I35" s="15"/>
       <c r="J35" s="15"/>
       <c r="K35" s="15"/>
@@ -4678,7 +4668,7 @@
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
     </row>
-    <row r="36" spans="1:16" ht="48">
+    <row r="36" spans="1:16" ht="35.25">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -4693,8 +4683,12 @@
         <v>109.29903</v>
       </c>
       <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
+      <c r="G36" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I36" s="15"/>
       <c r="J36" s="15"/>
       <c r="K36" s="15"/>
@@ -4704,7 +4698,7 @@
       <c r="O36" s="15"/>
       <c r="P36" s="15"/>
     </row>
-    <row r="37" spans="1:16" ht="48">
+    <row r="37" spans="1:16" ht="35.25">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -4719,8 +4713,12 @@
         <v>109.30185</v>
       </c>
       <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
+      <c r="G37" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I37" s="15"/>
       <c r="J37" s="15"/>
       <c r="K37" s="15"/>
@@ -4730,7 +4728,7 @@
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
     </row>
-    <row r="38" spans="1:16" ht="48">
+    <row r="38" spans="1:16" ht="35.25">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -4745,8 +4743,12 @@
         <v>109.30539</v>
       </c>
       <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
+      <c r="G38" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I38" s="15"/>
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
@@ -4756,7 +4758,7 @@
       <c r="O38" s="15"/>
       <c r="P38" s="15"/>
     </row>
-    <row r="39" spans="1:16" ht="24">
+    <row r="39" spans="1:16" ht="23.25">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -4771,8 +4773,12 @@
         <v>109.28804</v>
       </c>
       <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
+      <c r="G39" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I39" s="15"/>
       <c r="J39" s="15"/>
       <c r="K39" s="15"/>
@@ -4782,7 +4788,7 @@
       <c r="O39" s="15"/>
       <c r="P39" s="15"/>
     </row>
-    <row r="40" spans="1:16" ht="48">
+    <row r="40" spans="1:16" ht="35.25">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -4797,8 +4803,12 @@
         <v>109.30753</v>
       </c>
       <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
+      <c r="G40" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I40" s="15"/>
       <c r="J40" s="15"/>
       <c r="K40" s="15"/>
@@ -4808,7 +4818,7 @@
       <c r="O40" s="15"/>
       <c r="P40" s="15"/>
     </row>
-    <row r="41" spans="1:16" ht="48">
+    <row r="41" spans="1:16" ht="35.25">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -4823,8 +4833,12 @@
         <v>109.31025</v>
       </c>
       <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
+      <c r="G41" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I41" s="15"/>
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
@@ -4834,7 +4848,7 @@
       <c r="O41" s="15"/>
       <c r="P41" s="15"/>
     </row>
-    <row r="42" spans="1:16" ht="24">
+    <row r="42" spans="1:16" ht="23.25">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -4849,8 +4863,12 @@
         <v>109.30794</v>
       </c>
       <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
+      <c r="G42" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I42" s="15"/>
       <c r="J42" s="15"/>
       <c r="K42" s="15"/>
@@ -4860,7 +4878,7 @@
       <c r="O42" s="15"/>
       <c r="P42" s="15"/>
     </row>
-    <row r="43" spans="1:16" ht="24">
+    <row r="43" spans="1:16" ht="23.25">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -4875,8 +4893,12 @@
         <v>109.30727</v>
       </c>
       <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
+      <c r="G43" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I43" s="15"/>
       <c r="J43" s="15"/>
       <c r="K43" s="15"/>
@@ -4886,7 +4908,7 @@
       <c r="O43" s="15"/>
       <c r="P43" s="15"/>
     </row>
-    <row r="44" spans="1:16" ht="24">
+    <row r="44" spans="1:16" ht="23.25">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -4901,8 +4923,12 @@
         <v>109.29986</v>
       </c>
       <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
+      <c r="G44" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I44" s="15"/>
       <c r="J44" s="15"/>
       <c r="K44" s="15"/>
@@ -4912,7 +4938,7 @@
       <c r="O44" s="15"/>
       <c r="P44" s="15"/>
     </row>
-    <row r="45" spans="1:16" ht="24">
+    <row r="45" spans="1:16" ht="23.25">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -4927,8 +4953,12 @@
         <v>109.29454</v>
       </c>
       <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
+      <c r="G45" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I45" s="15"/>
       <c r="J45" s="15"/>
       <c r="K45" s="15"/>
@@ -4938,7 +4968,7 @@
       <c r="O45" s="15"/>
       <c r="P45" s="15"/>
     </row>
-    <row r="46" spans="1:16" ht="24">
+    <row r="46" spans="1:16" ht="23.25">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -4953,8 +4983,12 @@
         <v>109.30671</v>
       </c>
       <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
+      <c r="G46" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I46" s="15"/>
       <c r="J46" s="15"/>
       <c r="K46" s="15"/>
@@ -4964,7 +4998,7 @@
       <c r="O46" s="15"/>
       <c r="P46" s="15"/>
     </row>
-    <row r="47" spans="1:16" ht="24">
+    <row r="47" spans="1:16" ht="23.25">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -4979,8 +5013,12 @@
         <v>109.31034</v>
       </c>
       <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
+      <c r="G47" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H47" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I47" s="15"/>
       <c r="J47" s="15"/>
       <c r="K47" s="15"/>
@@ -4990,7 +5028,7 @@
       <c r="O47" s="15"/>
       <c r="P47" s="15"/>
     </row>
-    <row r="48" spans="1:16" ht="24">
+    <row r="48" spans="1:16" ht="23.25">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -5005,8 +5043,12 @@
         <v>109.30918</v>
       </c>
       <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
+      <c r="G48" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H48" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I48" s="15"/>
       <c r="J48" s="15"/>
       <c r="K48" s="15"/>
@@ -5016,7 +5058,7 @@
       <c r="O48" s="15"/>
       <c r="P48" s="15"/>
     </row>
-    <row r="49" spans="1:16" ht="24">
+    <row r="49" spans="1:16" ht="23.25">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -5031,8 +5073,12 @@
         <v>109.30806</v>
       </c>
       <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
+      <c r="G49" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H49" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I49" s="15"/>
       <c r="J49" s="15"/>
       <c r="K49" s="15"/>
@@ -5042,7 +5088,7 @@
       <c r="O49" s="15"/>
       <c r="P49" s="15"/>
     </row>
-    <row r="50" spans="1:16" ht="24">
+    <row r="50" spans="1:16" ht="23.25">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -5057,8 +5103,12 @@
         <v>109.30887</v>
       </c>
       <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
+      <c r="G50" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H50" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I50" s="15"/>
       <c r="J50" s="15"/>
       <c r="K50" s="15"/>
@@ -5068,7 +5118,7 @@
       <c r="O50" s="15"/>
       <c r="P50" s="15"/>
     </row>
-    <row r="51" spans="1:16" ht="24">
+    <row r="51" spans="1:16" ht="23.25">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -5083,8 +5133,12 @@
         <v>109.30838</v>
       </c>
       <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
+      <c r="G51" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H51" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I51" s="15"/>
       <c r="J51" s="15"/>
       <c r="K51" s="15"/>
@@ -5094,7 +5148,7 @@
       <c r="O51" s="15"/>
       <c r="P51" s="15"/>
     </row>
-    <row r="52" spans="1:16" ht="24">
+    <row r="52" spans="1:16" ht="23.25">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -5109,8 +5163,12 @@
         <v>109.30146000000001</v>
       </c>
       <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
+      <c r="G52" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H52" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I52" s="15"/>
       <c r="J52" s="15"/>
       <c r="K52" s="15"/>
@@ -5120,7 +5178,7 @@
       <c r="O52" s="15"/>
       <c r="P52" s="15"/>
     </row>
-    <row r="53" spans="1:16" ht="24">
+    <row r="53" spans="1:16" ht="23.25">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -5135,8 +5193,12 @@
         <v>109.30079000000001</v>
       </c>
       <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
+      <c r="G53" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="H53" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="I53" s="15"/>
       <c r="J53" s="15"/>
       <c r="K53" s="15"/>
@@ -5558,10 +5620,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="69"/>
@@ -5570,7 +5632,7 @@
       <c r="F1" s="69"/>
       <c r="G1" s="69"/>
       <c r="H1" s="70"/>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="52" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="69"/>
@@ -5578,39 +5640,39 @@
       <c r="L1" s="69"/>
       <c r="M1" s="69"/>
       <c r="N1" s="70"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="52" t="s">
         <v>3</v>
       </c>
       <c r="P1" s="70"/>
     </row>
     <row r="2" spans="1:16" ht="36">
       <c r="A2" s="71"/>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="52" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="70"/>
-      <c r="K2" s="54" t="s">
+      <c r="K2" s="56" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="69"/>
@@ -11563,34 +11625,34 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46771BB-89DD-433A-8105-216FBABD0C00}">
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="49" t="s">
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="49" t="s">
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="58"/>
+      <c r="P1" s="60"/>
       <c r="Q1" s="64" t="s">
         <v>360</v>
       </c>
@@ -11602,36 +11664,36 @@
     </row>
     <row r="2" spans="1:20" ht="36">
       <c r="A2" s="61"/>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="60"/>
-      <c r="K2" s="54" t="s">
+      <c r="J2" s="59"/>
+      <c r="K2" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="58"/>
-      <c r="M2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="59"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -11655,14 +11717,14 @@
       </c>
     </row>
     <row r="3" spans="1:20" ht="60">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -11784,7 +11846,7 @@
       <c r="S5" s="15"/>
       <c r="T5" s="15"/>
     </row>
-    <row r="6" spans="1:20" ht="48">
+    <row r="6" spans="1:20" ht="35.25">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -11832,7 +11894,7 @@
       <c r="S6" s="15"/>
       <c r="T6" s="15"/>
     </row>
-    <row r="7" spans="1:20" ht="48">
+    <row r="7" spans="1:20" ht="35.25">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -11880,7 +11942,7 @@
       <c r="S7" s="15"/>
       <c r="T7" s="15"/>
     </row>
-    <row r="8" spans="1:20" ht="48">
+    <row r="8" spans="1:20" ht="47.25">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -11928,7 +11990,7 @@
       <c r="S8" s="15"/>
       <c r="T8" s="15"/>
     </row>
-    <row r="9" spans="1:20" ht="48">
+    <row r="9" spans="1:20" ht="35.25">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -11976,7 +12038,7 @@
       <c r="S9" s="15"/>
       <c r="T9" s="15"/>
     </row>
-    <row r="10" spans="1:20" ht="36">
+    <row r="10" spans="1:20" ht="23.25">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -12026,7 +12088,7 @@
       <c r="S10" s="18"/>
       <c r="T10" s="18"/>
     </row>
-    <row r="11" spans="1:20" ht="36">
+    <row r="11" spans="1:20" ht="23.25">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -12076,7 +12138,7 @@
       </c>
       <c r="T11" s="18"/>
     </row>
-    <row r="12" spans="1:20" ht="36">
+    <row r="12" spans="1:20" ht="35.25">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -12126,7 +12188,7 @@
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
     </row>
-    <row r="13" spans="1:20" ht="36">
+    <row r="13" spans="1:20" ht="35.25">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -12176,7 +12238,7 @@
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
     </row>
-    <row r="14" spans="1:20" ht="24.75">
+    <row r="14" spans="1:20" ht="23.25">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -12226,7 +12288,7 @@
       <c r="S14" s="18"/>
       <c r="T14" s="18"/>
     </row>
-    <row r="15" spans="1:20" ht="24.75">
+    <row r="15" spans="1:20" ht="23.25">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -12276,7 +12338,7 @@
       </c>
       <c r="T15" s="18"/>
     </row>
-    <row r="16" spans="1:20" ht="24.75">
+    <row r="16" spans="1:20" ht="23.25">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -12326,7 +12388,7 @@
       </c>
       <c r="T16" s="18"/>
     </row>
-    <row r="17" spans="1:20" ht="36">
+    <row r="17" spans="1:20" ht="35.25">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -12376,7 +12438,7 @@
       </c>
       <c r="T17" s="18"/>
     </row>
-    <row r="18" spans="1:20" ht="36">
+    <row r="18" spans="1:20" ht="35.25">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -12426,7 +12488,7 @@
       </c>
       <c r="T18" s="18"/>
     </row>
-    <row r="19" spans="1:20" ht="36">
+    <row r="19" spans="1:20" ht="35.25">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -12476,7 +12538,7 @@
       </c>
       <c r="T19" s="18"/>
     </row>
-    <row r="20" spans="1:20" ht="36">
+    <row r="20" spans="1:20" ht="35.25">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -12526,7 +12588,7 @@
       <c r="S20" s="18"/>
       <c r="T20" s="18"/>
     </row>
-    <row r="21" spans="1:20" ht="24.75">
+    <row r="21" spans="1:20" ht="23.25">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -12576,7 +12638,7 @@
       </c>
       <c r="T21" s="18"/>
     </row>
-    <row r="22" spans="1:20" ht="48">
+    <row r="22" spans="1:20" ht="47.25">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -12626,7 +12688,7 @@
       </c>
       <c r="T22" s="18"/>
     </row>
-    <row r="23" spans="1:20" ht="48">
+    <row r="23" spans="1:20" ht="47.25">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -12674,7 +12736,7 @@
       </c>
       <c r="T23" s="18"/>
     </row>
-    <row r="24" spans="1:20" ht="24.75">
+    <row r="24" spans="1:20" ht="23.25">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -12724,7 +12786,7 @@
       </c>
       <c r="T24" s="18"/>
     </row>
-    <row r="25" spans="1:20" ht="36">
+    <row r="25" spans="1:20" ht="35.25">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -12774,27 +12836,27 @@
       </c>
       <c r="T25" s="18"/>
     </row>
-    <row r="26" spans="1:20" ht="24">
+    <row r="26" spans="1:20" ht="23.25">
       <c r="A26" s="3">
         <v>23</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="15" t="s">
         <v>439</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>440</v>
       </c>
       <c r="D26" s="29">
-        <v>-2.4991666666666669E-2</v>
+        <v>-5.3363888888888891E-2</v>
       </c>
       <c r="E26" s="29">
-        <v>109.3065944444444</v>
+        <v>109.3184055555556</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>395</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>204</v>
+        <v>441</v>
       </c>
       <c r="H26" s="18" t="s">
         <v>25</v>
@@ -12806,25 +12868,25 @@
         <v>27</v>
       </c>
       <c r="K26" s="18">
-        <v>586</v>
+        <v>1360</v>
       </c>
       <c r="L26" s="18">
         <v>2</v>
       </c>
       <c r="M26" s="18"/>
       <c r="N26" s="18">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
       <c r="Q26" s="18"/>
       <c r="R26" s="18"/>
       <c r="S26" s="18" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="T26" s="18"/>
     </row>
-    <row r="27" spans="1:20" ht="24.75">
+    <row r="27" spans="1:20" ht="47.25">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -12835,16 +12897,16 @@
         <v>443</v>
       </c>
       <c r="D27" s="29">
-        <v>-3.2891666666666673E-2</v>
+        <v>-1.108333333333333E-2</v>
       </c>
       <c r="E27" s="29">
-        <v>109.3217027777778</v>
+        <v>109.34288888888889</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>381</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>187</v>
+        <v>444</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>25</v>
@@ -12853,46 +12915,48 @@
         <v>26</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>27</v>
+        <v>411</v>
       </c>
       <c r="K27" s="18">
-        <v>1123</v>
+        <v>315.3</v>
       </c>
       <c r="L27" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27" s="18"/>
-      <c r="N27" s="18">
-        <v>2021</v>
+      <c r="N27" s="18" t="s">
+        <v>445</v>
       </c>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
       <c r="Q27" s="18"/>
       <c r="R27" s="18"/>
-      <c r="S27" s="18"/>
+      <c r="S27" s="18" t="s">
+        <v>446</v>
+      </c>
       <c r="T27" s="18"/>
     </row>
-    <row r="28" spans="1:20" ht="24.75">
+    <row r="28" spans="1:20" ht="35.25">
       <c r="A28" s="3">
         <v>25</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D28" s="29">
-        <v>-5.1333333333333328E-2</v>
+        <v>-7.407777777777777E-2</v>
       </c>
       <c r="E28" s="29">
-        <v>109.2996666666667</v>
+        <v>109.34655833333331</v>
       </c>
       <c r="F28" s="18" t="s">
         <v>381</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>187</v>
+        <v>449</v>
       </c>
       <c r="H28" s="18" t="s">
         <v>25</v>
@@ -12904,14 +12968,16 @@
         <v>27</v>
       </c>
       <c r="K28" s="18">
-        <v>515</v>
+        <v>569.91999999999996</v>
       </c>
       <c r="L28" s="18">
         <v>2</v>
       </c>
-      <c r="M28" s="18"/>
+      <c r="M28" s="18">
+        <v>120</v>
+      </c>
       <c r="N28" s="18">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
@@ -12920,217 +12986,155 @@
       <c r="S28" s="18"/>
       <c r="T28" s="18"/>
     </row>
-    <row r="29" spans="1:20" ht="24.75">
+    <row r="29" spans="1:20" ht="23.25">
       <c r="A29" s="3">
         <v>26</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>447</v>
-      </c>
-      <c r="D29" s="29">
-        <v>-5.3363888888888891E-2</v>
-      </c>
-      <c r="E29" s="29">
-        <v>109.3184055555556</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>395</v>
-      </c>
+      <c r="B29" s="15"/>
+      <c r="C29" s="25" t="s">
+        <v>450</v>
+      </c>
+      <c r="D29" s="16">
+        <v>-4.15E-3</v>
+      </c>
+      <c r="E29" s="16">
+        <v>109.30986</v>
+      </c>
+      <c r="F29" s="15"/>
       <c r="G29" s="18" t="s">
-        <v>448</v>
+        <v>97</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I29" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="J29" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="K29" s="18">
-        <v>1360</v>
-      </c>
-      <c r="L29" s="18">
-        <v>2</v>
-      </c>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18">
-        <v>2014</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
       <c r="O29" s="15"/>
       <c r="P29" s="15"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="18" t="s">
-        <v>404</v>
-      </c>
-      <c r="T29" s="18"/>
-    </row>
-    <row r="30" spans="1:20" ht="48">
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="15"/>
+    </row>
+    <row r="30" spans="1:20" ht="35.25">
       <c r="A30" s="3">
         <v>27</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="D30" s="29">
-        <v>-1.108333333333333E-2</v>
-      </c>
-      <c r="E30" s="29">
-        <v>109.34288888888889</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>381</v>
-      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="25" t="s">
+        <v>451</v>
+      </c>
+      <c r="D30" s="16">
+        <v>-1.073E-2</v>
+      </c>
+      <c r="E30" s="16">
+        <v>109.30561</v>
+      </c>
+      <c r="F30" s="15"/>
       <c r="G30" s="18" t="s">
-        <v>451</v>
+        <v>97</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I30" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="J30" s="18" t="s">
-        <v>411</v>
-      </c>
-      <c r="K30" s="18">
-        <v>315.3</v>
-      </c>
-      <c r="L30" s="18">
-        <v>1</v>
-      </c>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18" t="s">
-        <v>452</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18" t="s">
-        <v>453</v>
-      </c>
-      <c r="T30" s="18"/>
-    </row>
-    <row r="31" spans="1:20" ht="72">
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="15"/>
+    </row>
+    <row r="31" spans="1:20" ht="23.25">
       <c r="A31" s="3">
         <v>28</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>455</v>
-      </c>
-      <c r="D31" s="29">
-        <v>-4.7805555555555559E-2</v>
-      </c>
-      <c r="E31" s="29">
-        <v>109.35799166666671</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>381</v>
-      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="25" t="s">
+        <v>452</v>
+      </c>
+      <c r="D31" s="16">
+        <v>-3.5799999999999998E-3</v>
+      </c>
+      <c r="E31" s="16">
+        <v>109.30098</v>
+      </c>
+      <c r="F31" s="15"/>
       <c r="G31" s="18" t="s">
-        <v>456</v>
+        <v>97</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I31" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="J31" s="18" t="s">
-        <v>411</v>
-      </c>
-      <c r="K31" s="18">
-        <v>571</v>
-      </c>
-      <c r="L31" s="18">
-        <v>2</v>
-      </c>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
+        <v>98</v>
+      </c>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
       <c r="O31" s="15"/>
       <c r="P31" s="15"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18" t="s">
-        <v>457</v>
-      </c>
-      <c r="T31" s="18"/>
-    </row>
-    <row r="32" spans="1:20" ht="36">
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+    </row>
+    <row r="32" spans="1:20" ht="23.25">
       <c r="A32" s="3">
         <v>29</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>459</v>
-      </c>
-      <c r="D32" s="29">
-        <v>-7.407777777777777E-2</v>
-      </c>
-      <c r="E32" s="29">
-        <v>109.34655833333331</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>381</v>
-      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="25" t="s">
+        <v>453</v>
+      </c>
+      <c r="D32" s="16">
+        <v>-4.1399999999999996E-3</v>
+      </c>
+      <c r="E32" s="16">
+        <v>109.29814</v>
+      </c>
+      <c r="F32" s="15"/>
       <c r="G32" s="18" t="s">
-        <v>460</v>
+        <v>97</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I32" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="K32" s="18">
-        <v>569.91999999999996</v>
-      </c>
-      <c r="L32" s="18">
-        <v>2</v>
-      </c>
-      <c r="M32" s="18">
-        <v>120</v>
-      </c>
-      <c r="N32" s="18">
-        <v>2025</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
       <c r="O32" s="15"/>
       <c r="P32" s="15"/>
-      <c r="Q32" s="18"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-    </row>
-    <row r="33" spans="1:20" ht="24">
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+    </row>
+    <row r="33" spans="1:20" ht="23.25">
       <c r="A33" s="3">
         <v>30</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="25" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="D33" s="16">
-        <v>-4.15E-3</v>
+        <v>-1.265E-2</v>
       </c>
       <c r="E33" s="16">
-        <v>109.30986</v>
+        <v>109.30698</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="18" t="s">
@@ -13152,19 +13156,19 @@
       <c r="S33" s="15"/>
       <c r="T33" s="15"/>
     </row>
-    <row r="34" spans="1:20" ht="36">
+    <row r="34" spans="1:20" ht="23.25">
       <c r="A34" s="3">
         <v>31</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="25" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="D34" s="16">
-        <v>-1.073E-2</v>
+        <v>-3.7200000000000002E-3</v>
       </c>
       <c r="E34" s="16">
-        <v>109.30561</v>
+        <v>109.30643999999999</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="18" t="s">
@@ -13186,19 +13190,19 @@
       <c r="S34" s="15"/>
       <c r="T34" s="15"/>
     </row>
-    <row r="35" spans="1:20" ht="24">
+    <row r="35" spans="1:20" ht="23.25">
       <c r="A35" s="3">
         <v>32</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="25" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="D35" s="16">
-        <v>-3.5799999999999998E-3</v>
+        <v>-4.6600000000000001E-3</v>
       </c>
       <c r="E35" s="16">
-        <v>109.30098</v>
+        <v>109.30383</v>
       </c>
       <c r="F35" s="15"/>
       <c r="G35" s="18" t="s">
@@ -13220,19 +13224,19 @@
       <c r="S35" s="15"/>
       <c r="T35" s="15"/>
     </row>
-    <row r="36" spans="1:20" ht="36">
+    <row r="36" spans="1:20" ht="23.25">
       <c r="A36" s="3">
         <v>33</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="25" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="D36" s="16">
-        <v>-4.1399999999999996E-3</v>
+        <v>-1.264E-2</v>
       </c>
       <c r="E36" s="16">
-        <v>109.29814</v>
+        <v>109.30692000000001</v>
       </c>
       <c r="F36" s="15"/>
       <c r="G36" s="18" t="s">
@@ -13254,19 +13258,19 @@
       <c r="S36" s="15"/>
       <c r="T36" s="15"/>
     </row>
-    <row r="37" spans="1:20" ht="24">
+    <row r="37" spans="1:20" ht="35.25">
       <c r="A37" s="3">
         <v>34</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="25" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="D37" s="16">
-        <v>-1.265E-2</v>
+        <v>-4.8199999999999996E-3</v>
       </c>
       <c r="E37" s="16">
-        <v>109.30698</v>
+        <v>109.29704</v>
       </c>
       <c r="F37" s="15"/>
       <c r="G37" s="18" t="s">
@@ -13288,19 +13292,19 @@
       <c r="S37" s="15"/>
       <c r="T37" s="15"/>
     </row>
-    <row r="38" spans="1:20" ht="24">
+    <row r="38" spans="1:20" ht="35.25">
       <c r="A38" s="3">
         <v>35</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="25" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="D38" s="16">
-        <v>-3.7200000000000002E-3</v>
+        <v>-3.79E-3</v>
       </c>
       <c r="E38" s="16">
-        <v>109.30643999999999</v>
+        <v>109.30828</v>
       </c>
       <c r="F38" s="15"/>
       <c r="G38" s="18" t="s">
@@ -13322,19 +13326,19 @@
       <c r="S38" s="15"/>
       <c r="T38" s="15"/>
     </row>
-    <row r="39" spans="1:20" ht="24">
+    <row r="39" spans="1:20" ht="35.25">
       <c r="A39" s="3">
         <v>36</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="25" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D39" s="16">
-        <v>-4.6600000000000001E-3</v>
+        <v>-1.8970000000000001E-2</v>
       </c>
       <c r="E39" s="16">
-        <v>109.30383</v>
+        <v>109.30155000000001</v>
       </c>
       <c r="F39" s="15"/>
       <c r="G39" s="18" t="s">
@@ -13356,19 +13360,19 @@
       <c r="S39" s="15"/>
       <c r="T39" s="15"/>
     </row>
-    <row r="40" spans="1:20" ht="24">
+    <row r="40" spans="1:20" ht="23.25">
       <c r="A40" s="3">
         <v>37</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="25" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="D40" s="16">
-        <v>-1.264E-2</v>
+        <v>-1.222E-2</v>
       </c>
       <c r="E40" s="16">
-        <v>109.30692000000001</v>
+        <v>109.29470000000001</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="18" t="s">
@@ -13390,19 +13394,19 @@
       <c r="S40" s="15"/>
       <c r="T40" s="15"/>
     </row>
-    <row r="41" spans="1:20" ht="36">
+    <row r="41" spans="1:20" ht="23.25">
       <c r="A41" s="3">
         <v>38</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="25" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="D41" s="16">
-        <v>-4.8199999999999996E-3</v>
+        <v>-3.2799999999999999E-3</v>
       </c>
       <c r="E41" s="16">
-        <v>109.29704</v>
+        <v>109.29079</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="18" t="s">
@@ -13424,19 +13428,19 @@
       <c r="S41" s="15"/>
       <c r="T41" s="15"/>
     </row>
-    <row r="42" spans="1:20" ht="36">
+    <row r="42" spans="1:20" ht="23.25">
       <c r="A42" s="3">
         <v>39</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="25" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="D42" s="16">
-        <v>-3.79E-3</v>
+        <v>-5.1000000000000004E-3</v>
       </c>
       <c r="E42" s="16">
-        <v>109.30828</v>
+        <v>109.2987</v>
       </c>
       <c r="F42" s="15"/>
       <c r="G42" s="18" t="s">
@@ -13458,19 +13462,19 @@
       <c r="S42" s="15"/>
       <c r="T42" s="15"/>
     </row>
-    <row r="43" spans="1:20" ht="36">
+    <row r="43" spans="1:20" ht="47.25">
       <c r="A43" s="3">
         <v>40</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="25" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="D43" s="16">
-        <v>-1.8970000000000001E-2</v>
+        <v>-9.0200000000000002E-3</v>
       </c>
       <c r="E43" s="16">
-        <v>109.30155000000001</v>
+        <v>109.29062</v>
       </c>
       <c r="F43" s="15"/>
       <c r="G43" s="18" t="s">
@@ -13492,19 +13496,19 @@
       <c r="S43" s="15"/>
       <c r="T43" s="15"/>
     </row>
-    <row r="44" spans="1:20" ht="24">
+    <row r="44" spans="1:20" ht="35.25">
       <c r="A44" s="3">
         <v>41</v>
       </c>
       <c r="B44" s="15"/>
-      <c r="C44" s="25" t="s">
-        <v>472</v>
+      <c r="C44" s="21" t="s">
+        <v>465</v>
       </c>
       <c r="D44" s="16">
-        <v>-1.222E-2</v>
+        <v>-6.2700000000000004E-3</v>
       </c>
       <c r="E44" s="16">
-        <v>109.29470000000001</v>
+        <v>109.30817</v>
       </c>
       <c r="F44" s="15"/>
       <c r="G44" s="18" t="s">
@@ -13526,19 +13530,19 @@
       <c r="S44" s="15"/>
       <c r="T44" s="15"/>
     </row>
-    <row r="45" spans="1:20" ht="24">
+    <row r="45" spans="1:20" ht="35.25">
       <c r="A45" s="3">
         <v>42</v>
       </c>
       <c r="B45" s="15"/>
-      <c r="C45" s="25" t="s">
-        <v>473</v>
+      <c r="C45" s="17" t="s">
+        <v>466</v>
       </c>
       <c r="D45" s="16">
-        <v>-3.2799999999999999E-3</v>
+        <v>-5.0000000000000001E-3</v>
       </c>
       <c r="E45" s="16">
-        <v>109.29079</v>
+        <v>109.29152999999999</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="18" t="s">
@@ -13560,153 +13564,8 @@
       <c r="S45" s="15"/>
       <c r="T45" s="15"/>
     </row>
-    <row r="46" spans="1:20" ht="24">
-      <c r="A46" s="3">
-        <v>43</v>
-      </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="25" t="s">
-        <v>474</v>
-      </c>
-      <c r="D46" s="16">
-        <v>-5.1000000000000004E-3</v>
-      </c>
-      <c r="E46" s="16">
-        <v>109.2987</v>
-      </c>
-      <c r="F46" s="15"/>
-      <c r="G46" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="H46" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="15"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="15"/>
-      <c r="Q46" s="15"/>
-      <c r="R46" s="15"/>
-      <c r="S46" s="15"/>
-      <c r="T46" s="15"/>
-    </row>
-    <row r="47" spans="1:20" ht="60">
-      <c r="A47" s="3">
-        <v>44</v>
-      </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="25" t="s">
-        <v>475</v>
-      </c>
-      <c r="D47" s="16">
-        <v>-9.0200000000000002E-3</v>
-      </c>
-      <c r="E47" s="16">
-        <v>109.29062</v>
-      </c>
-      <c r="F47" s="15"/>
-      <c r="G47" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="H47" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="15"/>
-      <c r="R47" s="15"/>
-      <c r="S47" s="15"/>
-      <c r="T47" s="15"/>
-    </row>
-    <row r="48" spans="1:20" ht="36">
-      <c r="A48" s="3">
-        <v>45</v>
-      </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="21" t="s">
-        <v>476</v>
-      </c>
-      <c r="D48" s="16">
-        <v>-6.2700000000000004E-3</v>
-      </c>
-      <c r="E48" s="16">
-        <v>109.30817</v>
-      </c>
-      <c r="F48" s="15"/>
-      <c r="G48" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="H48" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="15"/>
-      <c r="R48" s="15"/>
-      <c r="S48" s="15"/>
-      <c r="T48" s="15"/>
-    </row>
-    <row r="49" spans="1:20" ht="36.75">
-      <c r="A49" s="3">
-        <v>46</v>
-      </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="17" t="s">
-        <v>477</v>
-      </c>
-      <c r="D49" s="16">
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E49" s="16">
-        <v>109.29152999999999</v>
-      </c>
-      <c r="F49" s="15"/>
-      <c r="G49" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="H49" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="15"/>
-      <c r="O49" s="15"/>
-      <c r="P49" s="15"/>
-      <c r="Q49" s="15"/>
-      <c r="R49" s="15"/>
-      <c r="S49" s="15"/>
-      <c r="T49" s="15"/>
-    </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -13714,9 +13573,18 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13731,7 +13599,7 @@
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="69"/>
@@ -13740,7 +13608,7 @@
       <c r="F1" s="69"/>
       <c r="G1" s="69"/>
       <c r="H1" s="70"/>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="52" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="69"/>
@@ -13748,39 +13616,39 @@
       <c r="L1" s="69"/>
       <c r="M1" s="69"/>
       <c r="N1" s="70"/>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="52" t="s">
         <v>3</v>
       </c>
       <c r="P1" s="70"/>
     </row>
     <row r="2" spans="1:16" ht="36">
       <c r="A2" s="71"/>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="52" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="70"/>
-      <c r="K2" s="54" t="s">
+      <c r="K2" s="56" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="69"/>
@@ -13831,7 +13699,7 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="D4" s="5">
         <v>-3.305688317259E-2</v>
@@ -13855,7 +13723,7 @@
         <v>27</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="L4" s="3">
         <v>1</v>
@@ -13875,7 +13743,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="D5" s="5">
         <v>-3.0528901570029E-2</v>
@@ -13899,7 +13767,7 @@
         <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="L5" s="3">
         <v>1</v>
@@ -13919,7 +13787,7 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="D6" s="5">
         <v>-2.6897191063444299E-2</v>
@@ -13943,7 +13811,7 @@
         <v>27</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="L6" s="3">
         <v>1</v>
@@ -13963,7 +13831,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="D7" s="5">
         <v>-3.4997461098407297E-2</v>
@@ -13987,7 +13855,7 @@
         <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="L7" s="3">
         <v>1</v>
@@ -14007,7 +13875,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D8" s="5">
         <v>-2.6451944370815599E-2</v>
@@ -14031,7 +13899,7 @@
         <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="L8" s="3">
         <v>1</v>
@@ -14051,7 +13919,7 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="D9" s="5">
         <v>-3.7100312511818501E-2</v>
@@ -14075,7 +13943,7 @@
         <v>27</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="L9" s="3">
         <v>2</v>
@@ -14095,7 +13963,7 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="D10" s="5">
         <v>-3.3023355652657203E-2</v>
@@ -14119,7 +13987,7 @@
         <v>27</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="L10" s="3">
         <v>2</v>
@@ -14139,7 +14007,7 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="D11" s="5">
         <v>-2.93004500107443E-2</v>
@@ -14163,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="L11" s="3">
         <v>1</v>
@@ -14183,7 +14051,7 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="D12" s="5">
         <v>-2.92521702510385E-2</v>
@@ -14207,7 +14075,7 @@
         <v>27</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="L12" s="3">
         <v>1</v>
@@ -14227,7 +14095,7 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="D13" s="5">
         <v>-4.8428432846192603E-2</v>
@@ -14251,7 +14119,7 @@
         <v>27</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="L13" s="3">
         <v>1</v>
@@ -14271,7 +14139,7 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="D14" s="5">
         <v>-4.2825821525160103E-2</v>
@@ -14295,7 +14163,7 @@
         <v>27</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="L14" s="3">
         <v>1</v>
@@ -14315,7 +14183,7 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="D15" s="5">
         <v>-5.9994818618451698E-2</v>
@@ -14339,7 +14207,7 @@
         <v>27</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="L15" s="3">
         <v>1</v>
@@ -14359,7 +14227,7 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="D16" s="5">
         <v>-2.9933451252404E-2</v>
@@ -14383,7 +14251,7 @@
         <v>27</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="L16" s="3">
         <v>1</v>
@@ -14403,7 +14271,7 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="D17" s="5">
         <v>-3.9020773734214503E-2</v>
@@ -14427,7 +14295,7 @@
         <v>27</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="L17" s="3">
         <v>1</v>
@@ -14447,7 +14315,7 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="D18" s="5">
         <v>-3.8434027376651102E-2</v>
@@ -14471,7 +14339,7 @@
         <v>27</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="L18" s="3">
         <v>1</v>
@@ -14491,7 +14359,7 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="D19" s="5">
         <v>-5.0111153476079098E-2</v>
@@ -14515,7 +14383,7 @@
         <v>27</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="L19" s="3">
         <v>1</v>
@@ -14524,7 +14392,7 @@
         <v>29</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -14535,7 +14403,7 @@
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="D20" s="5">
         <v>-4.9407450253117297E-2</v>
@@ -14559,7 +14427,7 @@
         <v>27</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="L20" s="3">
         <v>2</v>
@@ -14568,7 +14436,7 @@
         <v>29</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -14579,7 +14447,7 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="D21" s="5">
         <v>-4.6866890051634601E-2</v>
@@ -14603,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="L21" s="3">
         <v>1</v>
@@ -14612,7 +14480,7 @@
         <v>29</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -14623,7 +14491,7 @@
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="D22" s="5">
         <v>-4.5386311184041898E-2</v>
@@ -14647,7 +14515,7 @@
         <v>27</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="L22" s="3">
         <v>1</v>
@@ -14656,7 +14524,7 @@
         <v>29</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -14667,7 +14535,7 @@
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="D23" s="5">
         <v>-4.4334885592930397E-2</v>
@@ -14691,7 +14559,7 @@
         <v>27</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="L23" s="3">
         <v>1</v>
@@ -14700,7 +14568,7 @@
         <v>29</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -14711,7 +14579,7 @@
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="D24" s="5">
         <v>-4.3176171658923901E-2</v>
@@ -14735,7 +14603,7 @@
         <v>27</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="L24" s="3">
         <v>1</v>
@@ -14744,7 +14612,7 @@
         <v>29</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -14755,7 +14623,7 @@
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="D25" s="5">
         <v>-2.1591782213168102E-2</v>
@@ -14779,7 +14647,7 @@
         <v>27</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="L25" s="3">
         <v>2</v>
@@ -14799,7 +14667,7 @@
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="4" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="D26" s="5">
         <v>-4.1860253497890798E-2</v>
@@ -14823,7 +14691,7 @@
         <v>27</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="L26" s="3">
         <v>1</v>
@@ -14832,7 +14700,7 @@
         <v>29</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -14843,7 +14711,7 @@
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="4" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="D27" s="5">
         <v>-2.9150916876343101E-2</v>
@@ -14867,7 +14735,7 @@
         <v>27</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="L27" s="3">
         <v>1</v>
@@ -14876,7 +14744,7 @@
         <v>29</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -14887,7 +14755,7 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="D28" s="5">
         <v>-2.3198546148105199E-2</v>
@@ -14911,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="L28" s="3">
         <v>2</v>
@@ -14931,7 +14799,7 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="4" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="D29" s="5">
         <v>-2.3848118571305501E-2</v>
@@ -14955,7 +14823,7 @@
         <v>27</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="L29" s="3">
         <v>1</v>
@@ -14964,7 +14832,7 @@
         <v>29</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -14975,7 +14843,7 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="4" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="D30" s="5">
         <v>-2.6623807183040301E-2</v>
@@ -14999,7 +14867,7 @@
         <v>27</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="L30" s="3">
         <v>1</v>
@@ -15008,7 +14876,7 @@
         <v>29</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -15019,7 +14887,7 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="D31" s="5">
         <v>-2.7306108144082498E-2</v>
@@ -15043,7 +14911,7 @@
         <v>27</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="L31" s="3">
         <v>1</v>
@@ -15052,7 +14920,7 @@
         <v>29</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -15063,7 +14931,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="4" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="D32" s="5">
         <v>-2.03463571319339E-2</v>
@@ -15107,7 +14975,7 @@
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="4" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="D33" s="5">
         <v>-2.4389349275525499E-2</v>
@@ -15131,7 +14999,7 @@
         <v>27</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="L33" s="3">
         <v>1</v>
@@ -15151,7 +15019,7 @@
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="4" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D34" s="5">
         <v>-2.4172066931815801E-2</v>
@@ -15175,7 +15043,7 @@
         <v>27</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="L34" s="3">
         <v>2</v>
@@ -15195,7 +15063,7 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="4" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="D35" s="5">
         <v>-2.29838484346527E-2</v>
@@ -15219,7 +15087,7 @@
         <v>27</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="L35" s="3">
         <v>1</v>
@@ -15239,7 +15107,7 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="D36" s="5">
         <v>-2.3058528451606899E-2</v>
@@ -15263,7 +15131,7 @@
         <v>27</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="L36" s="3">
         <v>1</v>
@@ -15283,7 +15151,7 @@
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="4" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="D37" s="5">
         <v>-2.55534044497241E-2</v>
@@ -15307,7 +15175,7 @@
         <v>27</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="L37" s="3">
         <v>1</v>
@@ -15316,7 +15184,7 @@
         <v>29</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
@@ -15327,7 +15195,7 @@
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="4" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="D38" s="5">
         <v>-2.1931081476664199E-2</v>
@@ -15351,7 +15219,7 @@
         <v>27</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="L38" s="3">
         <v>1</v>
@@ -15371,7 +15239,7 @@
       </c>
       <c r="B39" s="34"/>
       <c r="C39" s="41" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="D39" s="40">
         <v>-1.92864235795423E-2</v>
@@ -15395,7 +15263,7 @@
         <v>27</v>
       </c>
       <c r="K39" s="34" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="L39" s="34">
         <v>1</v>
@@ -15415,7 +15283,7 @@
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="15" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="D40" s="42">
         <v>-6.8599999999999998E-3</v>
@@ -15445,7 +15313,7 @@
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="15" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="D41" s="42">
         <v>-3.29E-3</v>
@@ -15475,7 +15343,7 @@
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="15" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="D42" s="42">
         <v>-4.5199999999999997E-3</v>
@@ -15505,7 +15373,7 @@
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="15" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="D43" s="42">
         <v>-1.443E-2</v>
@@ -15535,7 +15403,7 @@
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="15" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="D44" s="42">
         <v>-1.1169999999999999E-2</v>
@@ -15565,7 +15433,7 @@
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="15" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="D45" s="42">
         <v>-5.7000000000000002E-3</v>
@@ -15595,7 +15463,7 @@
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="15" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="D46" s="42">
         <v>-2.5500000000000002E-3</v>
@@ -15625,7 +15493,7 @@
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="15" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="D47" s="42">
         <v>-4.9699999999999996E-3</v>
@@ -15655,7 +15523,7 @@
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="15" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="D48" s="42">
         <v>-8.7000000000000001E-4</v>
@@ -15685,7 +15553,7 @@
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="15" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="D49" s="42">
         <v>-7.9600000000000001E-3</v>
@@ -15715,7 +15583,7 @@
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="15" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="D50" s="42">
         <v>-6.9199999999999999E-3</v>
@@ -15745,7 +15613,7 @@
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="15" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="D51" s="42">
         <v>-8.8800000000000007E-3</v>
@@ -15775,7 +15643,7 @@
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="15" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="D52" s="42">
         <v>-8.2400000000000008E-3</v>
@@ -15805,7 +15673,7 @@
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="15" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="D53" s="42">
         <v>-1.278E-2</v>
@@ -15835,7 +15703,7 @@
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="15" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="D54" s="42">
         <v>-9.0699999999999999E-3</v>
@@ -15865,7 +15733,7 @@
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="15" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="D55" s="42">
         <v>-0.41952</v>
@@ -15895,7 +15763,7 @@
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="15" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="D56" s="42">
         <v>-6.77E-3</v>
@@ -15925,7 +15793,7 @@
       </c>
       <c r="B57" s="18"/>
       <c r="C57" s="15" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="D57" s="42">
         <v>-9.2099999999999994E-3</v>
@@ -15955,7 +15823,7 @@
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="15" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="D58" s="42">
         <v>-4.62E-3</v>
@@ -15985,7 +15853,7 @@
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="15" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="D59" s="42">
         <v>-7.9299999999999995E-3</v>
@@ -16015,7 +15883,7 @@
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="15" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="D60" s="42">
         <v>-1.01E-3</v>
@@ -16045,7 +15913,7 @@
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="4" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="D61" s="5">
         <v>-2.7182175694019099E-2</v>
@@ -16069,7 +15937,7 @@
         <v>27</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="L61" s="3">
         <v>2</v>
@@ -16089,7 +15957,7 @@
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="4" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="D62" s="5">
         <v>-2.9823940361993598E-2</v>
@@ -16133,7 +16001,7 @@
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="4" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="D63" s="5">
         <v>-3.1931255091528297E-2</v>
@@ -16157,7 +16025,7 @@
         <v>27</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="L63" s="3">
         <v>1</v>
@@ -16177,7 +16045,7 @@
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="4" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="D64" s="5">
         <v>-4.8528322280354898E-2</v>
@@ -16221,7 +16089,7 @@
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="4" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="D65" s="5">
         <v>-6.1779094808755097E-2</v>
@@ -16245,7 +16113,7 @@
         <v>27</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="L65" s="3">
         <v>2</v>
@@ -16254,7 +16122,7 @@
         <v>84</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
@@ -16265,7 +16133,7 @@
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="4" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="D66" s="5">
         <v>-4.8171445719323899E-2</v>
@@ -16289,7 +16157,7 @@
         <v>27</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="L66" s="3">
         <v>1</v>
@@ -16298,7 +16166,7 @@
         <v>84</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
@@ -16309,7 +16177,7 @@
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="4" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="D67" s="5">
         <v>-2.85172450700832E-2</v>
@@ -16353,7 +16221,7 @@
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="4" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="D68" s="5">
         <v>-2.4917720963034601E-2</v>
@@ -16377,7 +16245,7 @@
         <v>27</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="L68" s="3">
         <v>1</v>
@@ -16397,7 +16265,7 @@
       </c>
       <c r="B69" s="34"/>
       <c r="C69" s="41" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="D69" s="40">
         <v>-2.1007700520245701E-2</v>
@@ -16421,7 +16289,7 @@
         <v>27</v>
       </c>
       <c r="K69" s="34" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="L69" s="34">
         <v>1</v>
@@ -16441,7 +16309,7 @@
       </c>
       <c r="B70" s="18"/>
       <c r="C70" s="15" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="D70" s="42">
         <v>-5.1900000000000002E-3</v>
@@ -16471,7 +16339,7 @@
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="15" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="D71" s="42">
         <v>-1.1690000000000001E-2</v>
@@ -16501,7 +16369,7 @@
       </c>
       <c r="B72" s="18"/>
       <c r="C72" s="15" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="D72" s="42">
         <v>-8.8800000000000007E-3</v>
@@ -16531,7 +16399,7 @@
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="D73" s="42">
         <v>-5.3099999999999996E-3</v>
@@ -16561,7 +16429,7 @@
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="4" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="D74" s="5">
         <v>-2.8281828567388999E-2</v>
@@ -16582,10 +16450,10 @@
         <v>26</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="L74" s="3">
         <v>1</v>
@@ -16605,7 +16473,7 @@
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="4" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="D75" s="5">
         <v>-2.3534371787800299E-2</v>
@@ -16773,7 +16641,7 @@
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="21" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="D4" s="20">
         <v>-8.5000000000000006E-3</v>
@@ -16803,7 +16671,7 @@
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="21" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="D5" s="20">
         <v>-1.0109999999999999E-2</v>
@@ -16833,7 +16701,7 @@
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="21" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="D6" s="20">
         <v>-8.5699999999999995E-3</v>
@@ -16863,7 +16731,7 @@
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="21" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="D7" s="20">
         <v>-9.1199999999999996E-3</v>
@@ -16893,7 +16761,7 @@
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="21" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="D8" s="20">
         <v>-1.42E-3</v>
@@ -16923,7 +16791,7 @@
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="21" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="D9" s="20">
         <v>-1.6039999999999999E-2</v>
@@ -16953,7 +16821,7 @@
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="19" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="D10" s="20">
         <v>-8.8999999999999995E-4</v>
@@ -16983,7 +16851,7 @@
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="21" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="D11" s="20">
         <v>-2.2100000000000002E-3</v>
@@ -17049,7 +16917,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="C1" s="57"/>
       <c r="D1" s="57"/>
@@ -17078,10 +16946,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="E2" s="57" t="s">
         <v>6</v>
@@ -17090,7 +16958,7 @@
         <v>7</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="H2" s="57" t="s">
         <v>9</v>
@@ -17111,10 +16979,10 @@
         <v>13</v>
       </c>
       <c r="P2" s="57" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="Q2" s="57" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="R2" s="57"/>
     </row>
@@ -17138,20 +17006,20 @@
         <v>18</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="P3" s="57"/>
       <c r="Q3" s="14" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="36">
@@ -17160,10 +17028,10 @@
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="E4" s="18">
         <v>-2.6519999999999998E-2</v>
@@ -17179,17 +17047,17 @@
         <v>25</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="45">
         <v>825</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="O4" s="18">
         <v>2025</v>
@@ -17206,10 +17074,10 @@
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="E5" s="18">
         <v>-5.2181999999999999E-2</v>
@@ -17219,23 +17087,23 @@
       </c>
       <c r="G5" s="18"/>
       <c r="H5" s="22" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="45">
         <v>4500</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="O5" s="18">
         <v>2025</v>
@@ -17252,10 +17120,10 @@
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="E6" s="18">
         <v>-5.6816999999999999E-2</v>
@@ -17265,23 +17133,23 @@
       </c>
       <c r="G6" s="18"/>
       <c r="H6" s="22" t="s">
-        <v>456</v>
+        <v>594</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="45">
         <v>3800</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="O6" s="18">
         <v>2025</v>
@@ -17298,10 +17166,10 @@
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="E7" s="18">
         <v>-6.4637E-2</v>
@@ -17311,23 +17179,23 @@
       </c>
       <c r="G7" s="18"/>
       <c r="H7" s="22" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="L7" s="22"/>
       <c r="M7" s="45">
         <v>4600</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="O7" s="18">
         <v>2025</v>
@@ -17344,10 +17212,10 @@
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="E8" s="18">
         <v>-7.3205999999999993E-2</v>
@@ -17357,23 +17225,23 @@
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="22" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="L8" s="22"/>
       <c r="M8" s="45">
         <v>6300</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="O8" s="18">
         <v>2025</v>
@@ -17390,10 +17258,10 @@
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="E9" s="18">
         <v>-6.6999000000000003E-2</v>
@@ -17403,23 +17271,23 @@
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="22" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="L9" s="22"/>
       <c r="M9" s="45">
         <v>2100</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="O9" s="18">
         <v>2025</v>
@@ -17436,10 +17304,10 @@
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="E10" s="18">
         <v>-2.4538889000000001E-2</v>
@@ -17449,13 +17317,13 @@
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="22" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>27</v>
@@ -17480,10 +17348,10 @@
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="E11" s="18">
         <v>-5.7777800000000004E-4</v>
@@ -17493,13 +17361,13 @@
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="22" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>27</v>
@@ -17524,10 +17392,10 @@
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="E12" s="18">
         <v>-3.3805556E-2</v>
@@ -17543,7 +17411,7 @@
         <v>383</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>27</v>
@@ -17568,10 +17436,10 @@
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="E13" s="18">
         <v>-3.3805556E-2</v>
@@ -17581,13 +17449,13 @@
       </c>
       <c r="G13" s="18"/>
       <c r="H13" s="22" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K13" s="22" t="s">
         <v>27</v>
@@ -17612,10 +17480,10 @@
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="E14" s="18">
         <v>-3.8888900000000001E-4</v>
@@ -17625,13 +17493,13 @@
       </c>
       <c r="G14" s="18"/>
       <c r="H14" s="22" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>27</v>
@@ -17656,10 +17524,10 @@
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="E15" s="18">
         <v>-3.3805556E-2</v>
@@ -17675,7 +17543,7 @@
         <v>383</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K15" s="22" t="s">
         <v>27</v>
@@ -17700,10 +17568,10 @@
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="E16" s="18">
         <v>-3.5644443999999997E-2</v>
@@ -17713,13 +17581,13 @@
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="22" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>27</v>
@@ -17744,10 +17612,10 @@
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="E17" s="18">
         <v>-3.1629999999999998E-2</v>
@@ -17757,13 +17625,13 @@
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="22" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K17" s="22" t="s">
         <v>27</v>
@@ -17788,10 +17656,10 @@
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="E18" s="18">
         <v>-6.3280000000000003E-2</v>
@@ -17801,13 +17669,13 @@
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="22" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>27</v>
@@ -17832,10 +17700,10 @@
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="E19" s="18">
         <v>-2.9803E-2</v>
@@ -17845,13 +17713,13 @@
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="22" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K19" s="22" t="s">
         <v>27</v>
@@ -17876,10 +17744,10 @@
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="E20" s="18">
         <v>-1.1709999999999999E-3</v>
@@ -17889,13 +17757,13 @@
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="22" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>98</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K20" s="22" t="s">
         <v>27</v>
@@ -17920,10 +17788,10 @@
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="E21" s="18">
         <v>5.3839999999999999E-3</v>
@@ -17939,7 +17807,7 @@
         <v>98</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K21" s="22" t="s">
         <v>27</v>
@@ -17964,10 +17832,10 @@
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="E22" s="18">
         <v>-2.9825000000000001E-2</v>
@@ -17983,7 +17851,7 @@
         <v>98</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="K22" s="22" t="s">
         <v>27</v>
@@ -18140,7 +18008,7 @@
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="D4" s="47">
         <v>-5.3099999999999996E-3</v>
@@ -18172,7 +18040,7 @@
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="D5" s="47">
         <v>-3.29E-3</v>
@@ -18204,7 +18072,7 @@
       </c>
       <c r="B6" s="25"/>
       <c r="C6" s="25" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="D6" s="47">
         <v>-6.4999999999999997E-3</v>
@@ -18236,7 +18104,7 @@
       </c>
       <c r="B7" s="25"/>
       <c r="C7" s="25" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="D7" s="47">
         <v>-1.0200000000000001E-2</v>
@@ -18268,7 +18136,7 @@
       </c>
       <c r="B8" s="25"/>
       <c r="C8" s="25" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="D8" s="47">
         <v>-8.5900000000000004E-3</v>
@@ -18300,7 +18168,7 @@
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="25" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="D9" s="47">
         <v>-6.2599999999999999E-3</v>
@@ -18332,7 +18200,7 @@
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="25" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="D10" s="47">
         <v>-6.5300000000000002E-3</v>
@@ -18364,7 +18232,7 @@
       </c>
       <c r="B11" s="25"/>
       <c r="C11" s="25" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="D11" s="47">
         <v>-3.63E-3</v>
@@ -18396,7 +18264,7 @@
       </c>
       <c r="B12" s="25"/>
       <c r="C12" s="25" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="D12" s="47">
         <v>-3.7399999999999998E-3</v>

--- a/data/processed/eksposur_pontianak_0408.xlsx
+++ b/data/processed/eksposur_pontianak_0408.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{F1E380E3-4E01-4D97-B50D-1BA9DCA76966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70D2E42F-9F0F-4C1B-90CC-8708D20B9CE7}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{F1E380E3-4E01-4D97-B50D-1BA9DCA76966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87F50EA6-6CA2-4714-A82E-652D59CDCDF3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
   </bookViews>
   <sheets>
     <sheet name="Government" sheetId="4" r:id="rId1"/>
@@ -1356,15 +1356,6 @@
     <t>Pal Lima</t>
   </si>
   <si>
-    <t>12.26.09.07.01.08.00</t>
-  </si>
-  <si>
-    <t>Puskesmas Kampung Bali</t>
-  </si>
-  <si>
-    <t>Atap , Lantai, Plafond</t>
-  </si>
-  <si>
     <t>12.26.09.07.01.10.00</t>
   </si>
   <si>
@@ -1389,6 +1380,18 @@
     <t>Struktur, Atap, Plafond, Lantai</t>
   </si>
   <si>
+    <t>12.26.09.07.01.13.00</t>
+  </si>
+  <si>
+    <t>Puskesmas Kampung Bangka</t>
+  </si>
+  <si>
+    <t>Bansir Laut</t>
+  </si>
+  <si>
+    <t>Pondasi, Struktur, Lantai, Dinding, Plafond, Atap</t>
+  </si>
+  <si>
     <t>12.26.09.07.01.13.01</t>
   </si>
   <si>
@@ -1828,9 +1831,6 @@
   </si>
   <si>
     <t>Parit Perdana</t>
-  </si>
-  <si>
-    <t>Bansir Laut</t>
   </si>
   <si>
     <t>Parit Sepakat</t>
@@ -2798,28 +2798,40 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2833,18 +2845,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3250,40 +3250,40 @@
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="52" t="s">
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="52" t="s">
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="54"/>
+      <c r="P1" s="52"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="50"/>
+      <c r="A2" s="55"/>
       <c r="B2" s="49" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="49" t="s">
@@ -3295,15 +3295,15 @@
       <c r="H2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="54"/>
-      <c r="K2" s="56" t="s">
+      <c r="J2" s="52"/>
+      <c r="K2" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="53"/>
-      <c r="M2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="52"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -3315,14 +3315,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="51"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -5210,9 +5210,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -5223,6 +5220,9 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5623,7 +5623,7 @@
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="69"/>
@@ -5632,7 +5632,7 @@
       <c r="F1" s="69"/>
       <c r="G1" s="69"/>
       <c r="H1" s="70"/>
-      <c r="I1" s="52" t="s">
+      <c r="I1" s="51" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="69"/>
@@ -5640,7 +5640,7 @@
       <c r="L1" s="69"/>
       <c r="M1" s="69"/>
       <c r="N1" s="70"/>
-      <c r="O1" s="52" t="s">
+      <c r="O1" s="51" t="s">
         <v>3</v>
       </c>
       <c r="P1" s="70"/>
@@ -5653,10 +5653,10 @@
       <c r="C2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="49" t="s">
@@ -5668,11 +5668,11 @@
       <c r="H2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="51" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="70"/>
-      <c r="K2" s="56" t="s">
+      <c r="K2" s="53" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="69"/>
@@ -8291,7 +8291,7 @@
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
     </row>
-    <row r="60" spans="1:16" ht="35.25">
+    <row r="60" spans="1:16" ht="36">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>271</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>25</v>
+        <v>271</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>26</v>
@@ -11605,9 +11605,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -11618,6 +11615,9 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11632,48 +11632,48 @@
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="52" t="s">
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="52" t="s">
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="64" t="s">
+      <c r="P1" s="64"/>
+      <c r="Q1" s="60" t="s">
         <v>360</v>
       </c>
-      <c r="R1" s="65"/>
+      <c r="R1" s="61"/>
       <c r="S1" s="57" t="s">
         <v>361</v>
       </c>
       <c r="T1" s="57"/>
     </row>
     <row r="2" spans="1:20" ht="36">
-      <c r="A2" s="61"/>
+      <c r="A2" s="65"/>
       <c r="B2" s="49" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="49" t="s">
@@ -11685,15 +11685,15 @@
       <c r="H2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="59"/>
-      <c r="K2" s="56" t="s">
+      <c r="J2" s="63"/>
+      <c r="K2" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="60"/>
-      <c r="M2" s="59"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="63"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -11703,28 +11703,28 @@
       <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="62" t="s">
+      <c r="Q2" s="58" t="s">
         <v>362</v>
       </c>
-      <c r="R2" s="62" t="s">
+      <c r="R2" s="58" t="s">
         <v>363</v>
       </c>
-      <c r="S2" s="62" t="s">
+      <c r="S2" s="58" t="s">
         <v>362</v>
       </c>
-      <c r="T2" s="62" t="s">
+      <c r="T2" s="58" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="60">
-      <c r="A3" s="58"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -11745,10 +11745,10 @@
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
     </row>
     <row r="4" spans="1:20" ht="48">
       <c r="A4" s="3">
@@ -12786,27 +12786,27 @@
       </c>
       <c r="T24" s="18"/>
     </row>
-    <row r="25" spans="1:20" ht="35.25">
+    <row r="25" spans="1:20" ht="23.25">
       <c r="A25" s="3">
         <v>22</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="15" t="s">
         <v>436</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>437</v>
       </c>
       <c r="D25" s="29">
-        <v>-2.5419444444444449E-2</v>
+        <v>-5.3363888888888891E-2</v>
       </c>
       <c r="E25" s="29">
-        <v>109.33280000000001</v>
+        <v>109.3184055555556</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="H25" s="18" t="s">
         <v>25</v>
@@ -12815,28 +12815,28 @@
         <v>26</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>411</v>
+        <v>27</v>
       </c>
       <c r="K25" s="18">
-        <v>802.5</v>
+        <v>1360</v>
       </c>
       <c r="L25" s="18">
         <v>2</v>
       </c>
       <c r="M25" s="18"/>
       <c r="N25" s="18">
-        <v>1988</v>
+        <v>2014</v>
       </c>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="18"/>
       <c r="R25" s="18"/>
       <c r="S25" s="18" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="T25" s="18"/>
     </row>
-    <row r="26" spans="1:20" ht="23.25">
+    <row r="26" spans="1:20" ht="47.25">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -12847,13 +12847,13 @@
         <v>440</v>
       </c>
       <c r="D26" s="29">
-        <v>-5.3363888888888891E-2</v>
+        <v>-1.108333333333333E-2</v>
       </c>
       <c r="E26" s="29">
-        <v>109.3184055555556</v>
+        <v>109.34288888888889</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="G26" s="18" t="s">
         <v>441</v>
@@ -12865,48 +12865,48 @@
         <v>26</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>27</v>
+        <v>411</v>
       </c>
       <c r="K26" s="18">
-        <v>1360</v>
+        <v>315.3</v>
       </c>
       <c r="L26" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" s="18"/>
-      <c r="N26" s="18">
-        <v>2014</v>
+      <c r="N26" s="18" t="s">
+        <v>442</v>
       </c>
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
       <c r="Q26" s="18"/>
       <c r="R26" s="18"/>
       <c r="S26" s="18" t="s">
-        <v>404</v>
+        <v>443</v>
       </c>
       <c r="T26" s="18"/>
     </row>
-    <row r="27" spans="1:20" ht="47.25">
+    <row r="27" spans="1:20" ht="70.5">
       <c r="A27" s="3">
         <v>24</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D27" s="29">
-        <v>-1.108333333333333E-2</v>
+        <v>-4.7805555555555559E-2</v>
       </c>
       <c r="E27" s="29">
-        <v>109.34288888888889</v>
+        <v>109.35799166666671</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>381</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>25</v>
@@ -12918,21 +12918,19 @@
         <v>411</v>
       </c>
       <c r="K27" s="18">
-        <v>315.3</v>
+        <v>571</v>
       </c>
       <c r="L27" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="18"/>
-      <c r="N27" s="18" t="s">
-        <v>445</v>
-      </c>
+      <c r="N27" s="18"/>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
       <c r="Q27" s="18"/>
       <c r="R27" s="18"/>
       <c r="S27" s="18" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="T27" s="18"/>
     </row>
@@ -12941,10 +12939,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D28" s="29">
         <v>-7.407777777777777E-2</v>
@@ -12956,7 +12954,7 @@
         <v>381</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H28" s="18" t="s">
         <v>25</v>
@@ -12992,7 +12990,7 @@
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="25" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D29" s="16">
         <v>-4.15E-3</v>
@@ -13026,7 +13024,7 @@
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="25" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D30" s="16">
         <v>-1.073E-2</v>
@@ -13060,7 +13058,7 @@
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="25" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D31" s="16">
         <v>-3.5799999999999998E-3</v>
@@ -13094,7 +13092,7 @@
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D32" s="16">
         <v>-4.1399999999999996E-3</v>
@@ -13128,7 +13126,7 @@
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="25" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D33" s="16">
         <v>-1.265E-2</v>
@@ -13162,7 +13160,7 @@
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="25" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D34" s="16">
         <v>-3.7200000000000002E-3</v>
@@ -13196,7 +13194,7 @@
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="25" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D35" s="16">
         <v>-4.6600000000000001E-3</v>
@@ -13230,7 +13228,7 @@
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="25" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D36" s="16">
         <v>-1.264E-2</v>
@@ -13264,7 +13262,7 @@
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="25" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D37" s="16">
         <v>-4.8199999999999996E-3</v>
@@ -13298,7 +13296,7 @@
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="25" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D38" s="16">
         <v>-3.79E-3</v>
@@ -13332,7 +13330,7 @@
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="25" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D39" s="16">
         <v>-1.8970000000000001E-2</v>
@@ -13366,7 +13364,7 @@
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="25" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D40" s="16">
         <v>-1.222E-2</v>
@@ -13400,7 +13398,7 @@
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="25" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D41" s="16">
         <v>-3.2799999999999999E-3</v>
@@ -13434,7 +13432,7 @@
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="25" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D42" s="16">
         <v>-5.1000000000000004E-3</v>
@@ -13468,7 +13466,7 @@
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="25" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D43" s="16">
         <v>-9.0200000000000002E-3</v>
@@ -13502,7 +13500,7 @@
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="21" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D44" s="16">
         <v>-6.2700000000000004E-3</v>
@@ -13536,7 +13534,7 @@
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="17" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D45" s="16">
         <v>-5.0000000000000001E-3</v>
@@ -13573,18 +13571,18 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="T2:T3"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13599,7 +13597,7 @@
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="69"/>
@@ -13608,7 +13606,7 @@
       <c r="F1" s="69"/>
       <c r="G1" s="69"/>
       <c r="H1" s="70"/>
-      <c r="I1" s="52" t="s">
+      <c r="I1" s="51" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="69"/>
@@ -13616,7 +13614,7 @@
       <c r="L1" s="69"/>
       <c r="M1" s="69"/>
       <c r="N1" s="70"/>
-      <c r="O1" s="52" t="s">
+      <c r="O1" s="51" t="s">
         <v>3</v>
       </c>
       <c r="P1" s="70"/>
@@ -13629,10 +13627,10 @@
       <c r="C2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="49" t="s">
@@ -13644,11 +13642,11 @@
       <c r="H2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="51" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="70"/>
-      <c r="K2" s="56" t="s">
+      <c r="K2" s="53" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="69"/>
@@ -13699,7 +13697,7 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D4" s="5">
         <v>-3.305688317259E-2</v>
@@ -13723,7 +13721,7 @@
         <v>27</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L4" s="3">
         <v>1</v>
@@ -13743,7 +13741,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D5" s="5">
         <v>-3.0528901570029E-2</v>
@@ -13767,7 +13765,7 @@
         <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L5" s="3">
         <v>1</v>
@@ -13787,7 +13785,7 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D6" s="5">
         <v>-2.6897191063444299E-2</v>
@@ -13811,7 +13809,7 @@
         <v>27</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L6" s="3">
         <v>1</v>
@@ -13831,7 +13829,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D7" s="5">
         <v>-3.4997461098407297E-2</v>
@@ -13855,7 +13853,7 @@
         <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L7" s="3">
         <v>1</v>
@@ -13875,7 +13873,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D8" s="5">
         <v>-2.6451944370815599E-2</v>
@@ -13899,7 +13897,7 @@
         <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L8" s="3">
         <v>1</v>
@@ -13919,7 +13917,7 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D9" s="5">
         <v>-3.7100312511818501E-2</v>
@@ -13943,7 +13941,7 @@
         <v>27</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L9" s="3">
         <v>2</v>
@@ -13963,7 +13961,7 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D10" s="5">
         <v>-3.3023355652657203E-2</v>
@@ -13987,7 +13985,7 @@
         <v>27</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L10" s="3">
         <v>2</v>
@@ -14007,7 +14005,7 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D11" s="5">
         <v>-2.93004500107443E-2</v>
@@ -14031,7 +14029,7 @@
         <v>27</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L11" s="3">
         <v>1</v>
@@ -14051,7 +14049,7 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D12" s="5">
         <v>-2.92521702510385E-2</v>
@@ -14075,7 +14073,7 @@
         <v>27</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L12" s="3">
         <v>1</v>
@@ -14095,7 +14093,7 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D13" s="5">
         <v>-4.8428432846192603E-2</v>
@@ -14119,7 +14117,7 @@
         <v>27</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L13" s="3">
         <v>1</v>
@@ -14139,7 +14137,7 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D14" s="5">
         <v>-4.2825821525160103E-2</v>
@@ -14163,7 +14161,7 @@
         <v>27</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L14" s="3">
         <v>1</v>
@@ -14183,7 +14181,7 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D15" s="5">
         <v>-5.9994818618451698E-2</v>
@@ -14207,7 +14205,7 @@
         <v>27</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L15" s="3">
         <v>1</v>
@@ -14227,7 +14225,7 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D16" s="5">
         <v>-2.9933451252404E-2</v>
@@ -14251,7 +14249,7 @@
         <v>27</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L16" s="3">
         <v>1</v>
@@ -14271,7 +14269,7 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D17" s="5">
         <v>-3.9020773734214503E-2</v>
@@ -14295,7 +14293,7 @@
         <v>27</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L17" s="3">
         <v>1</v>
@@ -14315,7 +14313,7 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D18" s="5">
         <v>-3.8434027376651102E-2</v>
@@ -14339,7 +14337,7 @@
         <v>27</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L18" s="3">
         <v>1</v>
@@ -14359,7 +14357,7 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D19" s="5">
         <v>-5.0111153476079098E-2</v>
@@ -14383,7 +14381,7 @@
         <v>27</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L19" s="3">
         <v>1</v>
@@ -14392,7 +14390,7 @@
         <v>29</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -14403,7 +14401,7 @@
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D20" s="5">
         <v>-4.9407450253117297E-2</v>
@@ -14427,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L20" s="3">
         <v>2</v>
@@ -14436,7 +14434,7 @@
         <v>29</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -14447,7 +14445,7 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D21" s="5">
         <v>-4.6866890051634601E-2</v>
@@ -14471,7 +14469,7 @@
         <v>27</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L21" s="3">
         <v>1</v>
@@ -14480,7 +14478,7 @@
         <v>29</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -14491,7 +14489,7 @@
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D22" s="5">
         <v>-4.5386311184041898E-2</v>
@@ -14515,7 +14513,7 @@
         <v>27</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L22" s="3">
         <v>1</v>
@@ -14524,7 +14522,7 @@
         <v>29</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -14535,7 +14533,7 @@
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D23" s="5">
         <v>-4.4334885592930397E-2</v>
@@ -14559,7 +14557,7 @@
         <v>27</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L23" s="3">
         <v>1</v>
@@ -14568,7 +14566,7 @@
         <v>29</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -14579,7 +14577,7 @@
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D24" s="5">
         <v>-4.3176171658923901E-2</v>
@@ -14603,7 +14601,7 @@
         <v>27</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L24" s="3">
         <v>1</v>
@@ -14612,7 +14610,7 @@
         <v>29</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -14623,7 +14621,7 @@
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D25" s="5">
         <v>-2.1591782213168102E-2</v>
@@ -14647,7 +14645,7 @@
         <v>27</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L25" s="3">
         <v>2</v>
@@ -14667,7 +14665,7 @@
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D26" s="5">
         <v>-4.1860253497890798E-2</v>
@@ -14691,7 +14689,7 @@
         <v>27</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L26" s="3">
         <v>1</v>
@@ -14700,7 +14698,7 @@
         <v>29</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -14711,7 +14709,7 @@
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D27" s="5">
         <v>-2.9150916876343101E-2</v>
@@ -14735,7 +14733,7 @@
         <v>27</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L27" s="3">
         <v>1</v>
@@ -14744,7 +14742,7 @@
         <v>29</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -14755,7 +14753,7 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D28" s="5">
         <v>-2.3198546148105199E-2</v>
@@ -14779,7 +14777,7 @@
         <v>27</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L28" s="3">
         <v>2</v>
@@ -14799,7 +14797,7 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D29" s="5">
         <v>-2.3848118571305501E-2</v>
@@ -14823,7 +14821,7 @@
         <v>27</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L29" s="3">
         <v>1</v>
@@ -14832,7 +14830,7 @@
         <v>29</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -14843,7 +14841,7 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D30" s="5">
         <v>-2.6623807183040301E-2</v>
@@ -14867,7 +14865,7 @@
         <v>27</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L30" s="3">
         <v>1</v>
@@ -14876,7 +14874,7 @@
         <v>29</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -14887,7 +14885,7 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D31" s="5">
         <v>-2.7306108144082498E-2</v>
@@ -14911,7 +14909,7 @@
         <v>27</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L31" s="3">
         <v>1</v>
@@ -14920,7 +14918,7 @@
         <v>29</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -14931,7 +14929,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D32" s="5">
         <v>-2.03463571319339E-2</v>
@@ -14975,7 +14973,7 @@
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D33" s="5">
         <v>-2.4389349275525499E-2</v>
@@ -14999,7 +14997,7 @@
         <v>27</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L33" s="3">
         <v>1</v>
@@ -15019,7 +15017,7 @@
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D34" s="5">
         <v>-2.4172066931815801E-2</v>
@@ -15043,7 +15041,7 @@
         <v>27</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L34" s="3">
         <v>2</v>
@@ -15063,7 +15061,7 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D35" s="5">
         <v>-2.29838484346527E-2</v>
@@ -15087,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L35" s="3">
         <v>1</v>
@@ -15107,7 +15105,7 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D36" s="5">
         <v>-2.3058528451606899E-2</v>
@@ -15131,7 +15129,7 @@
         <v>27</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L36" s="3">
         <v>1</v>
@@ -15151,7 +15149,7 @@
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D37" s="5">
         <v>-2.55534044497241E-2</v>
@@ -15175,7 +15173,7 @@
         <v>27</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L37" s="3">
         <v>1</v>
@@ -15184,7 +15182,7 @@
         <v>29</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
@@ -15195,7 +15193,7 @@
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D38" s="5">
         <v>-2.1931081476664199E-2</v>
@@ -15219,7 +15217,7 @@
         <v>27</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L38" s="3">
         <v>1</v>
@@ -15239,7 +15237,7 @@
       </c>
       <c r="B39" s="34"/>
       <c r="C39" s="41" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D39" s="40">
         <v>-1.92864235795423E-2</v>
@@ -15263,7 +15261,7 @@
         <v>27</v>
       </c>
       <c r="K39" s="34" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L39" s="34">
         <v>1</v>
@@ -15283,7 +15281,7 @@
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="15" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D40" s="42">
         <v>-6.8599999999999998E-3</v>
@@ -15313,7 +15311,7 @@
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="15" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D41" s="42">
         <v>-3.29E-3</v>
@@ -15343,7 +15341,7 @@
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="15" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D42" s="42">
         <v>-4.5199999999999997E-3</v>
@@ -15373,7 +15371,7 @@
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D43" s="42">
         <v>-1.443E-2</v>
@@ -15403,7 +15401,7 @@
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D44" s="42">
         <v>-1.1169999999999999E-2</v>
@@ -15433,7 +15431,7 @@
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D45" s="42">
         <v>-5.7000000000000002E-3</v>
@@ -15463,7 +15461,7 @@
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D46" s="42">
         <v>-2.5500000000000002E-3</v>
@@ -15493,7 +15491,7 @@
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="15" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D47" s="42">
         <v>-4.9699999999999996E-3</v>
@@ -15523,7 +15521,7 @@
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D48" s="42">
         <v>-8.7000000000000001E-4</v>
@@ -15553,7 +15551,7 @@
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="15" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D49" s="42">
         <v>-7.9600000000000001E-3</v>
@@ -15583,7 +15581,7 @@
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D50" s="42">
         <v>-6.9199999999999999E-3</v>
@@ -15613,7 +15611,7 @@
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D51" s="42">
         <v>-8.8800000000000007E-3</v>
@@ -15643,7 +15641,7 @@
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D52" s="42">
         <v>-8.2400000000000008E-3</v>
@@ -15673,7 +15671,7 @@
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="15" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D53" s="42">
         <v>-1.278E-2</v>
@@ -15703,7 +15701,7 @@
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="15" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D54" s="42">
         <v>-9.0699999999999999E-3</v>
@@ -15733,7 +15731,7 @@
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D55" s="42">
         <v>-0.41952</v>
@@ -15763,7 +15761,7 @@
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D56" s="42">
         <v>-6.77E-3</v>
@@ -15793,7 +15791,7 @@
       </c>
       <c r="B57" s="18"/>
       <c r="C57" s="15" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D57" s="42">
         <v>-9.2099999999999994E-3</v>
@@ -15823,7 +15821,7 @@
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="15" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D58" s="42">
         <v>-4.62E-3</v>
@@ -15853,7 +15851,7 @@
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="15" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D59" s="42">
         <v>-7.9299999999999995E-3</v>
@@ -15883,7 +15881,7 @@
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="15" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D60" s="42">
         <v>-1.01E-3</v>
@@ -15913,7 +15911,7 @@
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D61" s="5">
         <v>-2.7182175694019099E-2</v>
@@ -15937,7 +15935,7 @@
         <v>27</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L61" s="3">
         <v>2</v>
@@ -15957,7 +15955,7 @@
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D62" s="5">
         <v>-2.9823940361993598E-2</v>
@@ -16001,7 +15999,7 @@
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D63" s="5">
         <v>-3.1931255091528297E-2</v>
@@ -16025,7 +16023,7 @@
         <v>27</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L63" s="3">
         <v>1</v>
@@ -16045,7 +16043,7 @@
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D64" s="5">
         <v>-4.8528322280354898E-2</v>
@@ -16089,7 +16087,7 @@
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D65" s="5">
         <v>-6.1779094808755097E-2</v>
@@ -16113,7 +16111,7 @@
         <v>27</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L65" s="3">
         <v>2</v>
@@ -16122,7 +16120,7 @@
         <v>84</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
@@ -16133,7 +16131,7 @@
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D66" s="5">
         <v>-4.8171445719323899E-2</v>
@@ -16157,7 +16155,7 @@
         <v>27</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L66" s="3">
         <v>1</v>
@@ -16166,7 +16164,7 @@
         <v>84</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
@@ -16177,7 +16175,7 @@
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D67" s="5">
         <v>-2.85172450700832E-2</v>
@@ -16221,7 +16219,7 @@
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D68" s="5">
         <v>-2.4917720963034601E-2</v>
@@ -16245,7 +16243,7 @@
         <v>27</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L68" s="3">
         <v>1</v>
@@ -16265,7 +16263,7 @@
       </c>
       <c r="B69" s="34"/>
       <c r="C69" s="41" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D69" s="40">
         <v>-2.1007700520245701E-2</v>
@@ -16289,7 +16287,7 @@
         <v>27</v>
       </c>
       <c r="K69" s="34" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L69" s="34">
         <v>1</v>
@@ -16309,7 +16307,7 @@
       </c>
       <c r="B70" s="18"/>
       <c r="C70" s="15" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D70" s="42">
         <v>-5.1900000000000002E-3</v>
@@ -16339,7 +16337,7 @@
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="15" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D71" s="42">
         <v>-1.1690000000000001E-2</v>
@@ -16369,7 +16367,7 @@
       </c>
       <c r="B72" s="18"/>
       <c r="C72" s="15" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D72" s="42">
         <v>-8.8800000000000007E-3</v>
@@ -16399,7 +16397,7 @@
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D73" s="42">
         <v>-5.3099999999999996E-3</v>
@@ -16429,7 +16427,7 @@
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D74" s="5">
         <v>-2.8281828567388999E-2</v>
@@ -16450,10 +16448,10 @@
         <v>26</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L74" s="3">
         <v>1</v>
@@ -16473,7 +16471,7 @@
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D75" s="5">
         <v>-2.3534371787800299E-2</v>
@@ -16513,9 +16511,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -16526,6 +16521,9 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16641,7 +16639,7 @@
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="21" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D4" s="20">
         <v>-8.5000000000000006E-3</v>
@@ -16671,7 +16669,7 @@
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="21" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D5" s="20">
         <v>-1.0109999999999999E-2</v>
@@ -16701,7 +16699,7 @@
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="21" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D6" s="20">
         <v>-8.5699999999999995E-3</v>
@@ -16731,7 +16729,7 @@
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="21" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D7" s="20">
         <v>-9.1199999999999996E-3</v>
@@ -16761,7 +16759,7 @@
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="21" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D8" s="20">
         <v>-1.42E-3</v>
@@ -16791,7 +16789,7 @@
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="21" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D9" s="20">
         <v>-1.6039999999999999E-2</v>
@@ -16821,7 +16819,7 @@
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="19" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D10" s="20">
         <v>-8.8999999999999995E-4</v>
@@ -16851,7 +16849,7 @@
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="21" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D11" s="20">
         <v>-2.2100000000000002E-3</v>
@@ -16877,9 +16875,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -16890,6 +16885,9 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16917,7 +16915,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C1" s="57"/>
       <c r="D1" s="57"/>
@@ -16946,10 +16944,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E2" s="57" t="s">
         <v>6</v>
@@ -16958,7 +16956,7 @@
         <v>7</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H2" s="57" t="s">
         <v>9</v>
@@ -16979,10 +16977,10 @@
         <v>13</v>
       </c>
       <c r="P2" s="57" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Q2" s="57" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="R2" s="57"/>
     </row>
@@ -17006,20 +17004,20 @@
         <v>18</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P3" s="57"/>
       <c r="Q3" s="14" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="36">
@@ -17028,10 +17026,10 @@
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E4" s="18">
         <v>-2.6519999999999998E-2</v>
@@ -17047,17 +17045,17 @@
         <v>25</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="45">
         <v>825</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O4" s="18">
         <v>2025</v>
@@ -17074,10 +17072,10 @@
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E5" s="18">
         <v>-5.2181999999999999E-2</v>
@@ -17087,23 +17085,23 @@
       </c>
       <c r="G5" s="18"/>
       <c r="H5" s="22" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="45">
         <v>4500</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O5" s="18">
         <v>2025</v>
@@ -17120,10 +17118,10 @@
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E6" s="18">
         <v>-5.6816999999999999E-2</v>
@@ -17133,23 +17131,23 @@
       </c>
       <c r="G6" s="18"/>
       <c r="H6" s="22" t="s">
-        <v>594</v>
+        <v>446</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="45">
         <v>3800</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O6" s="18">
         <v>2025</v>
@@ -17166,7 +17164,7 @@
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>595</v>
@@ -17179,23 +17177,23 @@
       </c>
       <c r="G7" s="18"/>
       <c r="H7" s="22" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L7" s="22"/>
       <c r="M7" s="45">
         <v>4600</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O7" s="18">
         <v>2025</v>
@@ -17212,7 +17210,7 @@
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D8" s="22" t="s">
         <v>596</v>
@@ -17228,20 +17226,20 @@
         <v>596</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L8" s="22"/>
       <c r="M8" s="45">
         <v>6300</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O8" s="18">
         <v>2025</v>
@@ -17258,7 +17256,7 @@
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D9" s="22" t="s">
         <v>597</v>
@@ -17274,20 +17272,20 @@
         <v>598</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L9" s="22"/>
       <c r="M9" s="45">
         <v>2100</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O9" s="18">
         <v>2025</v>
@@ -17304,7 +17302,7 @@
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D10" s="22" t="s">
         <v>599</v>
@@ -17320,7 +17318,7 @@
         <v>600</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J10" s="22" t="s">
         <v>601</v>
@@ -17348,7 +17346,7 @@
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>602</v>
@@ -17364,7 +17362,7 @@
         <v>600</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J11" s="22" t="s">
         <v>601</v>
@@ -17392,7 +17390,7 @@
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>603</v>
@@ -17436,7 +17434,7 @@
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>604</v>
@@ -17452,7 +17450,7 @@
         <v>600</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J13" s="22" t="s">
         <v>601</v>
@@ -17480,7 +17478,7 @@
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>605</v>
@@ -17496,7 +17494,7 @@
         <v>600</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J14" s="22" t="s">
         <v>601</v>
@@ -17524,7 +17522,7 @@
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D15" s="22" t="s">
         <v>603</v>
@@ -17568,7 +17566,7 @@
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>605</v>
@@ -17584,7 +17582,7 @@
         <v>600</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J16" s="22" t="s">
         <v>601</v>
@@ -17612,7 +17610,7 @@
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D17" s="22" t="s">
         <v>605</v>
@@ -17628,7 +17626,7 @@
         <v>600</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J17" s="22" t="s">
         <v>601</v>
@@ -17656,7 +17654,7 @@
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D18" s="22" t="s">
         <v>606</v>
@@ -17669,10 +17667,10 @@
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="22" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J18" s="22" t="s">
         <v>601</v>
@@ -17700,7 +17698,7 @@
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>607</v>
@@ -17713,7 +17711,7 @@
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="22" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I19" s="22" t="s">
         <v>608</v>
@@ -17744,7 +17742,7 @@
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>609</v>
@@ -17788,7 +17786,7 @@
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D21" s="22" t="s">
         <v>611</v>
@@ -17832,7 +17830,7 @@
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D22" s="44" t="s">
         <v>612</v>
@@ -18292,9 +18290,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -18305,12 +18300,35 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumen" ma:contentTypeID="0x010100CCD785251A4E724B934A12AB8BE46060" ma:contentTypeVersion="12" ma:contentTypeDescription="Buat sebuah dokumen baru." ma:contentTypeScope="" ma:versionID="5ae3aba09e4cbefebb89020ec97f4692">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15954fb3-4959-4f5b-ae14-d7aa01180869" xmlns:ns3="4ce1a36b-806a-4732-b893-33b689d3fa0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f158cec65280218b3e83bd78c7c2c412" ns2:_="" ns3:_="">
     <xsd:import namespace="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
@@ -18511,34 +18529,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF8C012-57B8-49D3-9EF1-E19A730B86BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5380809C-BC60-49CE-8A28-8AFE265843E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{495DAE39-1778-4C6E-AEB5-6769AAD718EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}"/>
 </file>
--- a/data/processed/eksposur_pontianak_0408.xlsx
+++ b/data/processed/eksposur_pontianak_0408.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{F1E380E3-4E01-4D97-B50D-1BA9DCA76966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87F50EA6-6CA2-4714-A82E-652D59CDCDF3}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{F1E380E3-4E01-4D97-B50D-1BA9DCA76966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63839905-15C0-42D5-868C-40B98D72386A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
   </bookViews>
   <sheets>
     <sheet name="Government" sheetId="4" r:id="rId1"/>
@@ -1919,9 +1919,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="166" formatCode="0.000000"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -2648,7 +2648,7 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -2724,7 +2724,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2789,10 +2789,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8291,7 +8291,7 @@
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
     </row>
-    <row r="60" spans="1:16" ht="36">
+    <row r="60" spans="1:16" ht="35.25">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>271</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>271</v>
+        <v>25</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>26</v>
@@ -11846,7 +11846,7 @@
       <c r="S5" s="15"/>
       <c r="T5" s="15"/>
     </row>
-    <row r="6" spans="1:20" ht="35.25">
+    <row r="6" spans="1:20" ht="48">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -11894,7 +11894,7 @@
       <c r="S6" s="15"/>
       <c r="T6" s="15"/>
     </row>
-    <row r="7" spans="1:20" ht="35.25">
+    <row r="7" spans="1:20" ht="48">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -11942,7 +11942,7 @@
       <c r="S7" s="15"/>
       <c r="T7" s="15"/>
     </row>
-    <row r="8" spans="1:20" ht="47.25">
+    <row r="8" spans="1:20" ht="48">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -11990,7 +11990,7 @@
       <c r="S8" s="15"/>
       <c r="T8" s="15"/>
     </row>
-    <row r="9" spans="1:20" ht="35.25">
+    <row r="9" spans="1:20" ht="48">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -12038,7 +12038,7 @@
       <c r="S9" s="15"/>
       <c r="T9" s="15"/>
     </row>
-    <row r="10" spans="1:20" ht="23.25">
+    <row r="10" spans="1:20" ht="36">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -12088,7 +12088,7 @@
       <c r="S10" s="18"/>
       <c r="T10" s="18"/>
     </row>
-    <row r="11" spans="1:20" ht="23.25">
+    <row r="11" spans="1:20" ht="36">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="T11" s="18"/>
     </row>
-    <row r="12" spans="1:20" ht="35.25">
+    <row r="12" spans="1:20" ht="36">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -12188,7 +12188,7 @@
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
     </row>
-    <row r="13" spans="1:20" ht="35.25">
+    <row r="13" spans="1:20" ht="36">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -12238,7 +12238,7 @@
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
     </row>
-    <row r="14" spans="1:20" ht="23.25">
+    <row r="14" spans="1:20" ht="24.75">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -12288,7 +12288,7 @@
       <c r="S14" s="18"/>
       <c r="T14" s="18"/>
     </row>
-    <row r="15" spans="1:20" ht="23.25">
+    <row r="15" spans="1:20" ht="24.75">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="T15" s="18"/>
     </row>
-    <row r="16" spans="1:20" ht="23.25">
+    <row r="16" spans="1:20" ht="24.75">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="T16" s="18"/>
     </row>
-    <row r="17" spans="1:20" ht="35.25">
+    <row r="17" spans="1:20" ht="36">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="T17" s="18"/>
     </row>
-    <row r="18" spans="1:20" ht="35.25">
+    <row r="18" spans="1:20" ht="36">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -12488,7 +12488,7 @@
       </c>
       <c r="T18" s="18"/>
     </row>
-    <row r="19" spans="1:20" ht="35.25">
+    <row r="19" spans="1:20" ht="36">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="T19" s="18"/>
     </row>
-    <row r="20" spans="1:20" ht="35.25">
+    <row r="20" spans="1:20" ht="36">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -12588,7 +12588,7 @@
       <c r="S20" s="18"/>
       <c r="T20" s="18"/>
     </row>
-    <row r="21" spans="1:20" ht="23.25">
+    <row r="21" spans="1:20" ht="24.75">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="T21" s="18"/>
     </row>
-    <row r="22" spans="1:20" ht="47.25">
+    <row r="22" spans="1:20" ht="48">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="T22" s="18"/>
     </row>
-    <row r="23" spans="1:20" ht="47.25">
+    <row r="23" spans="1:20" ht="48">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -12736,7 +12736,7 @@
       </c>
       <c r="T23" s="18"/>
     </row>
-    <row r="24" spans="1:20" ht="23.25">
+    <row r="24" spans="1:20" ht="24.75">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -18309,17 +18309,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -18328,7 +18317,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumen" ma:contentTypeID="0x010100CCD785251A4E724B934A12AB8BE46060" ma:contentTypeVersion="12" ma:contentTypeDescription="Buat sebuah dokumen baru." ma:contentTypeScope="" ma:versionID="5ae3aba09e4cbefebb89020ec97f4692">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15954fb3-4959-4f5b-ae14-d7aa01180869" xmlns:ns3="4ce1a36b-806a-4732-b893-33b689d3fa0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f158cec65280218b3e83bd78c7c2c412" ns2:_="" ns3:_="">
     <xsd:import namespace="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
@@ -18529,14 +18518,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}"/>
 </file>
--- a/data/processed/eksposur_pontianak_0408.xlsx
+++ b/data/processed/eksposur_pontianak_0408.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{F1E380E3-4E01-4D97-B50D-1BA9DCA76966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63839905-15C0-42D5-868C-40B98D72386A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95D6DD61-729F-43FD-8900-F3FE800C69D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
   </bookViews>
   <sheets>
     <sheet name="Government" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="623">
   <si>
     <t>No</t>
   </si>
@@ -494,6 +494,9 @@
   </si>
   <si>
     <t>TK Kemala Bhayangkari 01</t>
+  </si>
+  <si>
+    <t>-0.03353422897000427</t>
   </si>
   <si>
     <t>± 2 meter</t>
@@ -1919,11 +1922,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2117,8 +2120,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Consolas"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2307,6 +2316,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2648,14 +2663,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2724,7 +2739,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2789,11 +2804,17 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2801,11 +2822,8 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2816,11 +2834,20 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2834,18 +2861,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2854,6 +2869,16 @@
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="35" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="35" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3247,63 +3272,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="51" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="51" t="s">
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="52"/>
+      <c r="P1" s="50"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="55"/>
-      <c r="B2" s="49" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53" t="s">
+      <c r="J2" s="50"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="54"/>
-      <c r="M2" s="52"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="50"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -3315,14 +3340,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -5210,6 +5235,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -5220,9 +5248,6 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5492,7 +5517,7 @@
         <v>485728416</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="36">
+    <row r="7" spans="1:16" ht="35.25">
       <c r="A7" s="18">
         <v>4</v>
       </c>
@@ -5502,11 +5527,11 @@
       <c r="C7" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="23">
-        <v>-2.0029999999999999E-2</v>
-      </c>
-      <c r="E7" s="24">
-        <v>109.32897</v>
+      <c r="D7" s="71">
+        <v>-2.0104111659418E-2</v>
+      </c>
+      <c r="E7" s="72">
+        <v>109.329290727692</v>
       </c>
       <c r="F7" s="22">
         <v>1</v>
@@ -5620,63 +5645,63 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="51" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="51" t="s">
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="70"/>
+      <c r="P1" s="74"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="71"/>
-      <c r="B2" s="49" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="70"/>
-      <c r="K2" s="53" t="s">
+      <c r="J2" s="74"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="69"/>
-      <c r="M2" s="70"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="74"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -5688,14 +5713,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="72"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -5809,7 +5834,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="36">
+    <row r="6" spans="1:16" ht="35.25">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -5819,14 +5844,14 @@
       <c r="C6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D6" s="5">
-        <v>-3.5779999999999999E-2</v>
-      </c>
-      <c r="E6" s="5">
-        <v>109.31952</v>
+      <c r="D6" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" s="70">
+        <v>109.321715135997</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>32</v>
@@ -5841,7 +5866,7 @@
         <v>27</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L6" s="3">
         <v>1</v>
@@ -5850,7 +5875,7 @@
         <v>143</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -5863,7 +5888,7 @@
         <v>30108483</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D7" s="5">
         <v>-3.8561999999999999E-2</v>
@@ -5887,7 +5912,7 @@
         <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L7" s="3">
         <v>1</v>
@@ -5896,7 +5921,7 @@
         <v>143</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -5909,7 +5934,7 @@
         <v>30108473</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D8" s="5">
         <v>-3.7995337956296199E-2</v>
@@ -5933,7 +5958,7 @@
         <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L8" s="3">
         <v>2</v>
@@ -5942,7 +5967,7 @@
         <v>143</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
@@ -5955,7 +5980,7 @@
         <v>30108463</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D9" s="5">
         <v>-3.3363694485578098E-2</v>
@@ -5964,7 +5989,7 @@
         <v>109.32483499999999</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>95</v>
@@ -5979,7 +6004,7 @@
         <v>27</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L9" s="3">
         <v>1</v>
@@ -5988,7 +6013,7 @@
         <v>143</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -6001,7 +6026,7 @@
         <v>30108624</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D10" s="5">
         <v>-2.9642694498243499E-2</v>
@@ -6010,7 +6035,7 @@
         <v>109.33351999999999</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>32</v>
@@ -6025,7 +6050,7 @@
         <v>27</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L10" s="3">
         <v>1</v>
@@ -6047,7 +6072,7 @@
         <v>30108484</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D11" s="5">
         <v>-3.8667781005920297E-2</v>
@@ -6056,7 +6081,7 @@
         <v>109.3128</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>32</v>
@@ -6071,7 +6096,7 @@
         <v>27</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L11" s="3">
         <v>1</v>
@@ -6093,7 +6118,7 @@
         <v>30108465</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D12" s="5">
         <v>-2.9790423311429101E-2</v>
@@ -6102,7 +6127,7 @@
         <v>109.304768806607</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>79</v>
@@ -6139,7 +6164,7 @@
         <v>30109347</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D13" s="5">
         <v>-2.76E-2</v>
@@ -6148,7 +6173,7 @@
         <v>109.3369</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
@@ -6163,7 +6188,7 @@
         <v>27</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L13" s="3">
         <v>2</v>
@@ -6172,7 +6197,7 @@
         <v>143</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -6185,7 +6210,7 @@
         <v>30108466</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D14" s="5">
         <v>-2.8762294446453601E-2</v>
@@ -6209,7 +6234,7 @@
         <v>27</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L14" s="3">
         <v>2</v>
@@ -6231,7 +6256,7 @@
         <v>30108478</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D15" s="5">
         <v>-4.1501098126782203E-2</v>
@@ -6240,7 +6265,7 @@
         <v>109.30939636350401</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>32</v>
@@ -6264,7 +6289,7 @@
         <v>143</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -6277,7 +6302,7 @@
         <v>30108474</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D16" s="5">
         <v>-4.1285050298795103E-2</v>
@@ -6286,7 +6311,7 @@
         <v>109.325661567209</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>32</v>
@@ -6301,7 +6326,7 @@
         <v>27</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L16" s="3">
         <v>1</v>
@@ -6310,7 +6335,7 @@
         <v>143</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -6323,7 +6348,7 @@
         <v>30108481</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D17" s="5">
         <v>-2.26441791017877E-2</v>
@@ -6332,7 +6357,7 @@
         <v>109.334865794192</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>32</v>
@@ -6347,7 +6372,7 @@
         <v>27</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L17" s="3">
         <v>1</v>
@@ -6356,7 +6381,7 @@
         <v>143</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -6369,7 +6394,7 @@
         <v>30108480</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D18" s="5">
         <v>-3.1399099968289698E-2</v>
@@ -6378,7 +6403,7 @@
         <v>109.323618194193</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>32</v>
@@ -6393,7 +6418,7 @@
         <v>27</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L18" s="3">
         <v>1</v>
@@ -6402,7 +6427,7 @@
         <v>143</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -6415,7 +6440,7 @@
         <v>30108482</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D19" s="5">
         <v>-2.7092592602462901E-2</v>
@@ -6424,7 +6449,7 @@
         <v>109.33878833652</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
@@ -6439,7 +6464,7 @@
         <v>27</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L19" s="3">
         <v>1</v>
@@ -6448,7 +6473,7 @@
         <v>143</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -6461,7 +6486,7 @@
         <v>30108485</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D20" s="5">
         <v>-3.7682023291372102E-2</v>
@@ -6470,10 +6495,10 @@
         <v>109.314568963504</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>25</v>
@@ -6485,7 +6510,7 @@
         <v>27</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L20" s="3">
         <v>1</v>
@@ -6494,7 +6519,7 @@
         <v>143</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -6507,7 +6532,7 @@
         <v>30108486</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D21" s="5">
         <v>-2.2298550266456399E-2</v>
@@ -6516,7 +6541,7 @@
         <v>109.32635195186501</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>81</v>
@@ -6531,7 +6556,7 @@
         <v>27</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L21" s="3">
         <v>1</v>
@@ -6540,7 +6565,7 @@
         <v>143</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -6553,7 +6578,7 @@
         <v>30108487</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D22" s="5">
         <v>-3.0113582791468401E-2</v>
@@ -6562,7 +6587,7 @@
         <v>109.32922033652</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
@@ -6577,7 +6602,7 @@
         <v>27</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L22" s="3">
         <v>1</v>
@@ -6586,7 +6611,7 @@
         <v>143</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -6599,7 +6624,7 @@
         <v>30108488</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D23" s="5">
         <v>-2.68994736054066E-2</v>
@@ -6608,7 +6633,7 @@
         <v>109.338874173062</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>32</v>
@@ -6623,7 +6648,7 @@
         <v>27</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L23" s="6">
         <v>1</v>
@@ -6632,7 +6657,7 @@
         <v>143</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -6645,7 +6670,7 @@
         <v>30108489</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D24" s="5">
         <v>-2.5534109782796799E-2</v>
@@ -6654,7 +6679,7 @@
         <v>109.335852034667</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>81</v>
@@ -6669,7 +6694,7 @@
         <v>27</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L24" s="3">
         <v>2</v>
@@ -6678,7 +6703,7 @@
         <v>143</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -6691,7 +6716,7 @@
         <v>69811968</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D25" s="5">
         <v>-5.4039638648230803E-2</v>
@@ -6700,7 +6725,7 @@
         <v>109.31151339234</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
@@ -6715,7 +6740,7 @@
         <v>27</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L25" s="3">
         <v>1</v>
@@ -6724,7 +6749,7 @@
         <v>143</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -6737,7 +6762,7 @@
         <v>69903619</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D26" s="5">
         <v>-4.2438723299055799E-2</v>
@@ -6746,7 +6771,7 @@
         <v>109.314721753718</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
@@ -6761,7 +6786,7 @@
         <v>27</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L26" s="3">
         <v>2</v>
@@ -6770,7 +6795,7 @@
         <v>143</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -6783,7 +6808,7 @@
         <v>69903646</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D27" s="5">
         <v>-4.7807180973703602E-2</v>
@@ -6792,7 +6817,7 @@
         <v>109.307685638373</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>32</v>
@@ -6807,7 +6832,7 @@
         <v>27</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L27" s="3">
         <v>1</v>
@@ -6816,7 +6841,7 @@
         <v>143</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -6829,7 +6854,7 @@
         <v>30108483</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D28" s="5">
         <v>-5.0160338641563502E-2</v>
@@ -6838,7 +6863,7 @@
         <v>109.315331294193</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>32</v>
@@ -6853,7 +6878,7 @@
         <v>27</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L28" s="3">
         <v>1</v>
@@ -6862,7 +6887,7 @@
         <v>143</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -6875,7 +6900,7 @@
         <v>30108486</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D29" s="5">
         <v>-2.7508162568052101E-2</v>
@@ -6884,10 +6909,10 @@
         <v>109.321573361079</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>25</v>
@@ -6899,7 +6924,7 @@
         <v>27</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L29" s="3">
         <v>1</v>
@@ -6908,7 +6933,7 @@
         <v>143</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -6921,7 +6946,7 @@
         <v>30108481</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D30" s="5">
         <v>-4.82896791504819E-2</v>
@@ -6930,7 +6955,7 @@
         <v>109.31845026535601</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>32</v>
@@ -6945,7 +6970,7 @@
         <v>27</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L30" s="3">
         <v>1</v>
@@ -6954,7 +6979,7 @@
         <v>143</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -6967,7 +6992,7 @@
         <v>30108478</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D31" s="5">
         <v>-3.8679825126622297E-2</v>
@@ -6976,7 +7001,7 @@
         <v>109.291654921176</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>32</v>
@@ -6991,7 +7016,7 @@
         <v>27</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L31" s="3">
         <v>1</v>
@@ -7000,7 +7025,7 @@
         <v>143</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -7013,7 +7038,7 @@
         <v>69972625</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D32" s="5">
         <v>-2.66330079405016E-2</v>
@@ -7022,7 +7047,7 @@
         <v>109.33240906165101</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
@@ -7037,16 +7062,16 @@
         <v>27</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L32" s="3">
         <v>1</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -7059,7 +7084,7 @@
         <v>69853159</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D33" s="5">
         <v>-3.3671980954025502E-2</v>
@@ -7068,7 +7093,7 @@
         <v>109.311407921176</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>32</v>
@@ -7083,7 +7108,7 @@
         <v>27</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L33" s="3">
         <v>1</v>
@@ -7092,7 +7117,7 @@
         <v>143</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
@@ -7105,7 +7130,7 @@
         <v>69853160</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D34" s="5">
         <v>-2.70032820207428E-2</v>
@@ -7114,7 +7139,7 @@
         <v>109.31727676427499</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>32</v>
@@ -7129,7 +7154,7 @@
         <v>27</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L34" s="3">
         <v>1</v>
@@ -7138,7 +7163,7 @@
         <v>143</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -7151,7 +7176,7 @@
         <v>70006431</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D35" s="5">
         <v>-2.34859852190888E-2</v>
@@ -7160,7 +7185,7 @@
         <v>109.318190161469</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>32</v>
@@ -7175,7 +7200,7 @@
         <v>27</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L35" s="3">
         <v>1</v>
@@ -7184,7 +7209,7 @@
         <v>143</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
@@ -7197,7 +7222,7 @@
         <v>70011642</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D36" s="5">
         <v>-2.43344579381953E-2</v>
@@ -7206,10 +7231,10 @@
         <v>109.31739661139</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>25</v>
@@ -7221,7 +7246,7 @@
         <v>27</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L36" s="3">
         <v>1</v>
@@ -7230,7 +7255,7 @@
         <v>143</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
@@ -7243,7 +7268,7 @@
         <v>69888953</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D37" s="5">
         <v>-3.1355723315320598E-2</v>
@@ -7252,7 +7277,7 @@
         <v>109.329024584678</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>32</v>
@@ -7267,7 +7292,7 @@
         <v>27</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L37" s="3">
         <v>1</v>
@@ -7289,7 +7314,7 @@
         <v>69744576</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D38" s="5">
         <v>-4.86330642905351E-2</v>
@@ -7298,10 +7323,10 @@
         <v>109.316352916032</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>25</v>
@@ -7313,13 +7338,13 @@
         <v>27</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L38" s="3">
         <v>1</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N38" s="3">
         <v>2006</v>
@@ -7335,7 +7360,7 @@
         <v>69955972</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D39" s="5">
         <v>-4.9999744482566798E-2</v>
@@ -7345,7 +7370,7 @@
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>25</v>
@@ -7357,7 +7382,7 @@
         <v>27</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L39" s="3">
         <v>1</v>
@@ -7379,7 +7404,7 @@
         <v>69960241</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D40" s="5">
         <v>-2.5658134930915202E-2</v>
@@ -7388,10 +7413,10 @@
         <v>109.32333026535601</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>25</v>
@@ -7403,7 +7428,7 @@
         <v>27</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L40" s="3">
         <v>1</v>
@@ -7425,7 +7450,7 @@
         <v>30105266</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D41" s="5">
         <v>-2.701108094883E-2</v>
@@ -7437,7 +7462,7 @@
         <v>141</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>25</v>
@@ -7449,16 +7474,16 @@
         <v>27</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L41" s="3">
         <v>1</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
@@ -7471,7 +7496,7 @@
         <v>30105263</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D42" s="5">
         <v>-4.6428340462114498E-2</v>
@@ -7480,7 +7505,7 @@
         <v>109.31649209419299</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>32</v>
@@ -7495,16 +7520,16 @@
         <v>27</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L42" s="3">
         <v>1</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
@@ -7517,7 +7542,7 @@
         <v>30105261</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D43" s="5">
         <v>-5.1460489606070303E-2</v>
@@ -7526,7 +7551,7 @@
         <v>109.31528053255199</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>32</v>
@@ -7541,16 +7566,16 @@
         <v>27</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L43" s="3">
         <v>2</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
@@ -7563,7 +7588,7 @@
         <v>30105270</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D44" s="5">
         <v>-5.9493509828884503E-2</v>
@@ -7572,7 +7597,7 @@
         <v>109.30637652117601</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>32</v>
@@ -7587,16 +7612,16 @@
         <v>27</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L44" s="3">
         <v>1</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
@@ -7609,7 +7634,7 @@
         <v>30108480</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D45" s="5">
         <v>-3.4950280955306501E-2</v>
@@ -7618,10 +7643,10 @@
         <v>109.301090796045</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>25</v>
@@ -7633,16 +7658,16 @@
         <v>27</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L45" s="3">
         <v>1</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
@@ -7655,7 +7680,7 @@
         <v>30108412</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D46" s="5">
         <v>-2.4042152112433799E-2</v>
@@ -7664,7 +7689,7 @@
         <v>109.33026735001199</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>81</v>
@@ -7679,16 +7704,16 @@
         <v>27</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L46" s="3">
         <v>1</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
@@ -7701,7 +7726,7 @@
         <v>30105198</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D47" s="5">
         <v>-2.2703350266828001E-2</v>
@@ -7710,7 +7735,7 @@
         <v>109.33426060583101</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>81</v>
@@ -7731,10 +7756,10 @@
         <v>1</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
@@ -7747,7 +7772,7 @@
         <v>30105195</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D48" s="5">
         <v>-2.5171192599773899E-2</v>
@@ -7756,7 +7781,7 @@
         <v>109.325922165356</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>32</v>
@@ -7771,16 +7796,16 @@
         <v>27</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L48" s="3">
         <v>1</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
@@ -7793,7 +7818,7 @@
         <v>30105200</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D49" s="5">
         <v>-2.1583058224110399E-2</v>
@@ -7802,7 +7827,7 @@
         <v>109.31962333837301</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>79</v>
@@ -7817,16 +7842,16 @@
         <v>27</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L49" s="3">
         <v>1</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
@@ -7839,7 +7864,7 @@
         <v>30105233</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D50" s="5">
         <v>-3.1745607947101503E-2</v>
@@ -7848,7 +7873,7 @@
         <v>109.31300833652</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>79</v>
@@ -7863,16 +7888,16 @@
         <v>27</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L50" s="3">
         <v>1</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -7885,7 +7910,7 @@
         <v>30105245</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D51" s="5">
         <v>-3.8685880959655E-2</v>
@@ -7894,7 +7919,7 @@
         <v>109.314153680701</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>32</v>
@@ -7909,16 +7934,16 @@
         <v>27</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L51" s="3">
         <v>2</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
@@ -7931,7 +7956,7 @@
         <v>30105244</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D52" s="5">
         <v>-2.39336097822061E-2</v>
@@ -7940,7 +7965,7 @@
         <v>109.32199809604499</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>79</v>
@@ -7955,16 +7980,16 @@
         <v>27</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L52" s="3">
         <v>1</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
@@ -7977,7 +8002,7 @@
         <v>30105211</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D53" s="5">
         <v>-3.7968338625721597E-2</v>
@@ -7986,7 +8011,7 @@
         <v>109.316680638373</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>32</v>
@@ -8001,16 +8026,16 @@
         <v>27</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L53" s="3">
         <v>2</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
@@ -8023,7 +8048,7 @@
         <v>30105212</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D54" s="5">
         <v>-3.4398119612401398E-2</v>
@@ -8032,7 +8057,7 @@
         <v>109.31937436720899</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>32</v>
@@ -8047,16 +8072,16 @@
         <v>27</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L54" s="3">
         <v>2</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
@@ -8069,7 +8094,7 @@
         <v>30105350</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D55" s="5">
         <v>-1.9265367451778301E-2</v>
@@ -8078,7 +8103,7 @@
         <v>109.33319022488099</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>95</v>
@@ -8093,16 +8118,16 @@
         <v>27</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L55" s="3">
         <v>1</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
@@ -8115,7 +8140,7 @@
         <v>30105217</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D56" s="5">
         <v>-3.8618679125791901E-2</v>
@@ -8124,7 +8149,7 @@
         <v>109.32736646535599</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>32</v>
@@ -8139,16 +8164,16 @@
         <v>27</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L56" s="3">
         <v>2</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
@@ -8161,7 +8186,7 @@
         <v>30105353</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D57" s="5">
         <v>-3.0730438620000401E-2</v>
@@ -8170,10 +8195,10 @@
         <v>109.321885182554</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>25</v>
@@ -8185,16 +8210,16 @@
         <v>27</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L57" s="3">
         <v>1</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
@@ -8207,7 +8232,7 @@
         <v>30105352</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D58" s="5">
         <v>-2.35367962869126E-2</v>
@@ -8216,7 +8241,7 @@
         <v>109.33611589234</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>81</v>
@@ -8231,16 +8256,16 @@
         <v>27</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L58" s="3">
         <v>1</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O58" s="3"/>
       <c r="P58" s="3"/>
@@ -8253,7 +8278,7 @@
         <v>30208415</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D59" s="5">
         <v>-3.12254232833129E-2</v>
@@ -8262,7 +8287,7 @@
         <v>109.322241423029</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>32</v>
@@ -8283,10 +8308,10 @@
         <v>2</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
@@ -8299,7 +8324,7 @@
         <v>30208420</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D60" s="5">
         <v>-3.71804393187763E-2</v>
@@ -8308,10 +8333,10 @@
         <v>109.331849769352</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>25</v>
@@ -8329,7 +8354,7 @@
         <v>2</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N60" s="3">
         <v>1998</v>
@@ -8345,7 +8370,7 @@
         <v>30208425</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D61" s="5">
         <v>-2.7689750272526899E-2</v>
@@ -8354,7 +8379,7 @@
         <v>109.339861124881</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>24</v>
@@ -8369,16 +8394,16 @@
         <v>27</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L61" s="3">
         <v>2</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
@@ -8391,7 +8416,7 @@
         <v>30208430</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D62" s="5">
         <v>-4.7607277323707599E-2</v>
@@ -8400,7 +8425,7 @@
         <v>109.315977924881</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>32</v>
@@ -8421,10 +8446,10 @@
         <v>2</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
@@ -8437,7 +8462,7 @@
         <v>30208435</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D63" s="5">
         <v>-2.13210116273123E-2</v>
@@ -8446,7 +8471,7 @@
         <v>109.333645667209</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>95</v>
@@ -8467,10 +8492,10 @@
         <v>2</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
@@ -8483,7 +8508,7 @@
         <v>30208440</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D64" s="5">
         <v>-2.7400615610579299E-2</v>
@@ -8492,7 +8517,7 @@
         <v>109.336974328848</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>24</v>
@@ -8507,16 +8532,16 @@
         <v>27</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L64" s="3">
         <v>2</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
@@ -8529,7 +8554,7 @@
         <v>30208445</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D65" s="5">
         <v>-2.5567761922192501E-2</v>
@@ -8538,7 +8563,7 @@
         <v>109.336498167209</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>24</v>
@@ -8559,10 +8584,10 @@
         <v>2</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
@@ -8575,7 +8600,7 @@
         <v>30208450</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D66" s="5">
         <v>-3.0687034939797301E-2</v>
@@ -8584,7 +8609,7 @@
         <v>109.328118465356</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>32</v>
@@ -8599,13 +8624,13 @@
         <v>27</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L66" s="3">
         <v>2</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N66" s="3">
         <v>1997</v>
@@ -8621,7 +8646,7 @@
         <v>30208455</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D67" s="5">
         <v>-5.0460880978708003E-2</v>
@@ -8630,10 +8655,10 @@
         <v>109.304527723029</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>25</v>
@@ -8645,13 +8670,13 @@
         <v>27</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L67" s="3">
         <v>2</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N67" s="3">
         <v>2002</v>
@@ -8667,7 +8692,7 @@
         <v>30208460</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D68" s="5">
         <v>-2.90727195988865E-2</v>
@@ -8676,10 +8701,10 @@
         <v>109.30532202302901</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H68" s="4" t="s">
         <v>25</v>
@@ -8697,7 +8722,7 @@
         <v>2</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N68" s="3">
         <v>2001</v>
@@ -8713,7 +8738,7 @@
         <v>30208465</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D69" s="5">
         <v>-3.2712252119016599E-2</v>
@@ -8722,10 +8747,10 @@
         <v>109.318001376995</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>25</v>
@@ -8737,13 +8762,13 @@
         <v>27</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L69" s="3">
         <v>2</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N69" s="3">
         <v>2000</v>
@@ -8759,7 +8784,7 @@
         <v>30208470</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D70" s="5">
         <v>-3.1791479112974801E-2</v>
@@ -8768,10 +8793,10 @@
         <v>109.328595267209</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>25</v>
@@ -8783,13 +8808,13 @@
         <v>27</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L70" s="3">
         <v>2</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N70" s="3">
         <v>2001</v>
@@ -8805,7 +8830,7 @@
         <v>30208500</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D71" s="5">
         <v>-2.7352594445159299E-2</v>
@@ -8814,10 +8839,10 @@
         <v>109.321750382554</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>25</v>
@@ -8829,7 +8854,7 @@
         <v>27</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L71" s="3">
         <v>2</v>
@@ -8851,7 +8876,7 @@
         <v>30208505</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D72" s="5">
         <v>-4.2363621468670301E-2</v>
@@ -8860,10 +8885,10 @@
         <v>109.314593007684</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>25</v>
@@ -8875,7 +8900,7 @@
         <v>27</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L72" s="3">
         <v>2</v>
@@ -8897,7 +8922,7 @@
         <v>30208510</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D73" s="5">
         <v>-4.6916307978736298E-2</v>
@@ -8906,10 +8931,10 @@
         <v>109.30945286350401</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>25</v>
@@ -8921,7 +8946,7 @@
         <v>27</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L73" s="3">
         <v>2</v>
@@ -8943,7 +8968,7 @@
         <v>30208515</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D74" s="5">
         <v>-5.74041926894511E-2</v>
@@ -8952,10 +8977,10 @@
         <v>109.300500509537</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>25</v>
@@ -8967,7 +8992,7 @@
         <v>27</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L74" s="3">
         <v>2</v>
@@ -8989,7 +9014,7 @@
         <v>30208520</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D75" s="5">
         <v>-2.8511850273675799E-2</v>
@@ -8998,10 +9023,10 @@
         <v>109.334180609537</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>25</v>
@@ -9013,7 +9038,7 @@
         <v>27</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L75" s="3">
         <v>2</v>
@@ -9035,7 +9060,7 @@
         <v>10208525</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D76" s="5">
         <v>-3.07488846316845E-2</v>
@@ -9044,7 +9069,7 @@
         <v>109.327584794193</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>32</v>
@@ -9081,7 +9106,7 @@
         <v>30208530</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D77" s="5">
         <v>-2.1711507936092399E-2</v>
@@ -9090,7 +9115,7 @@
         <v>109.32954778070101</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>95</v>
@@ -9105,7 +9130,7 @@
         <v>27</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L77" s="3">
         <v>2</v>
@@ -9127,7 +9152,7 @@
         <v>30208535</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D78" s="5">
         <v>-2.5001853956734099E-2</v>
@@ -9136,7 +9161,7 @@
         <v>109.32880007699499</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>81</v>
@@ -9151,7 +9176,7 @@
         <v>27</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L78" s="3">
         <v>2</v>
@@ -9173,7 +9198,7 @@
         <v>30208540</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D79" s="5">
         <v>-3.80109689023636E-2</v>
@@ -9182,7 +9207,7 @@
         <v>109.319041405993</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>32</v>
@@ -9197,7 +9222,7 @@
         <v>27</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L79" s="3">
         <v>2</v>
@@ -9219,7 +9244,7 @@
         <v>30208545</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D80" s="5">
         <v>-5.0225049949271398E-2</v>
@@ -9228,7 +9253,7 @@
         <v>109.312299488373</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>32</v>
@@ -9243,7 +9268,7 @@
         <v>27</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L80" s="3">
         <v>2</v>
@@ -9265,7 +9290,7 @@
         <v>20308550</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D81" s="5">
         <v>-3.9720965627975703E-2</v>
@@ -9274,7 +9299,7 @@
         <v>109.314537705831</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>32</v>
@@ -9289,7 +9314,7 @@
         <v>27</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L81" s="3">
         <v>2</v>
@@ -9311,7 +9336,7 @@
         <v>20308555</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D82" s="5">
         <v>-5.2929796308746398E-2</v>
@@ -9320,10 +9345,10 @@
         <v>109.301002451865</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>25</v>
@@ -9335,7 +9360,7 @@
         <v>27</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L82" s="3">
         <v>2</v>
@@ -9357,7 +9382,7 @@
         <v>20308560</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D83" s="5">
         <v>-2.5829107939648599E-2</v>
@@ -9366,7 +9391,7 @@
         <v>109.332609396045</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>81</v>
@@ -9381,7 +9406,7 @@
         <v>27</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L83" s="3">
         <v>3</v>
@@ -9403,7 +9428,7 @@
         <v>20308565</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D84" s="5">
         <v>-2.38168232774052E-2</v>
@@ -9412,7 +9437,7 @@
         <v>109.334426707684</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>81</v>
@@ -9427,7 +9452,7 @@
         <v>27</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L84" s="3">
         <v>2</v>
@@ -9449,7 +9474,7 @@
         <v>30308570</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D85" s="5">
         <v>-4.63328561895925E-2</v>
@@ -9458,7 +9483,7 @@
         <v>109.315155685343</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>32</v>
@@ -9495,7 +9520,7 @@
         <v>30308575</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D86" s="5">
         <v>-2.0190680946197199E-2</v>
@@ -9504,7 +9529,7 @@
         <v>109.334348151865</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>95</v>
@@ -9519,7 +9544,7 @@
         <v>27</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L86" s="3">
         <v>1</v>
@@ -9541,7 +9566,7 @@
         <v>30308580</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D87" s="5">
         <v>-5.9412450358260198E-2</v>
@@ -9550,7 +9575,7 @@
         <v>109.305301380701</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>32</v>
@@ -9587,7 +9612,7 @@
         <v>30105245</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D88" s="5">
         <v>-2.5450307939278001E-2</v>
@@ -9596,10 +9621,10 @@
         <v>109.336880167209</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H88" s="4" t="s">
         <v>25</v>
@@ -9611,13 +9636,13 @@
         <v>27</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L88" s="3">
         <v>2</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N88" s="3">
         <v>1956</v>
@@ -9633,7 +9658,7 @@
         <v>30105253</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D89" s="5">
         <v>-2.1840253956996E-2</v>
@@ -9642,7 +9667,7 @@
         <v>109.329451221176</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>95</v>
@@ -9657,13 +9682,13 @@
         <v>27</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L89" s="3">
         <v>2</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N89" s="3">
         <v>1992</v>
@@ -9679,7 +9704,7 @@
         <v>30105257</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D90" s="5">
         <v>-2.2206788905909301E-2</v>
@@ -9688,10 +9713,10 @@
         <v>109.31317709419299</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>25</v>
@@ -9709,7 +9734,7 @@
         <v>2</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N90" s="3">
         <v>1998</v>
@@ -9725,7 +9750,7 @@
         <v>30105240</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D91" s="5">
         <v>-2.7843336776447899E-2</v>
@@ -9734,10 +9759,10 @@
         <v>109.336276105831</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>25</v>
@@ -9749,13 +9774,13 @@
         <v>27</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L91" s="3">
         <v>3</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N91" s="3">
         <v>1951</v>
@@ -9771,7 +9796,7 @@
         <v>30105264</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D92" s="5">
         <v>-5.0425834998664501E-2</v>
@@ -9780,7 +9805,7 @@
         <v>109.304421878848</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>32</v>
@@ -9795,13 +9820,13 @@
         <v>27</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L92" s="3">
         <v>2</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N92" s="3">
         <v>2005</v>
@@ -9817,7 +9842,7 @@
         <v>69970633</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D93" s="5">
         <v>-3.80555303011757E-2</v>
@@ -9826,10 +9851,10 @@
         <v>109.311065486781</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>25</v>
@@ -9841,13 +9866,13 @@
         <v>27</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L93" s="3">
         <v>3</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N93" s="3">
         <v>2017</v>
@@ -9863,7 +9888,7 @@
         <v>69992187</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D94" s="5">
         <v>-3.6742818535087998E-2</v>
@@ -9872,10 +9897,10 @@
         <v>109.311898718338</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>25</v>
@@ -9887,13 +9912,13 @@
         <v>27</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L94" s="3">
         <v>2</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N94" s="3">
         <v>2019</v>
@@ -9909,7 +9934,7 @@
         <v>69974172</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D95" s="5">
         <v>-2.0788798143694099E-2</v>
@@ -9918,10 +9943,10 @@
         <v>109.321972253345</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>25</v>
@@ -9933,13 +9958,13 @@
         <v>27</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L95" s="3">
         <v>2</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N95" s="3">
         <v>2016</v>
@@ -9955,7 +9980,7 @@
         <v>30105269</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D96" s="5">
         <v>-4.24172656332477E-2</v>
@@ -9964,7 +9989,7 @@
         <v>109.314571550012</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>32</v>
@@ -9985,7 +10010,7 @@
         <v>2</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N96" s="3">
         <v>2004</v>
@@ -10001,7 +10026,7 @@
         <v>69976889</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D97" s="5">
         <v>-3.1848398751727999E-2</v>
@@ -10010,7 +10035,7 @@
         <v>109.328520478587</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>32</v>
@@ -10025,13 +10050,13 @@
         <v>27</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L97" s="3">
         <v>3</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N97" s="3">
         <v>2016</v>
@@ -10047,7 +10072,7 @@
         <v>30105238</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D98" s="5">
         <v>-4.7362824086970602E-2</v>
@@ -10056,7 +10081,7 @@
         <v>109.315756500083</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>32</v>
@@ -10077,7 +10102,7 @@
         <v>2</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N98" s="3">
         <v>1987</v>
@@ -10093,7 +10118,7 @@
         <v>30105146</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D99" s="5">
         <v>-3.1488865615147903E-2</v>
@@ -10102,7 +10127,7 @@
         <v>109.324309778848</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>32</v>
@@ -10117,13 +10142,13 @@
         <v>27</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L99" s="3">
         <v>3</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N99" s="3">
         <v>1978</v>
@@ -10139,7 +10164,7 @@
         <v>30105147</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D100" s="5">
         <v>-4.9743338640881603E-2</v>
@@ -10148,7 +10173,7 @@
         <v>109.31627916350401</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>32</v>
@@ -10163,13 +10188,13 @@
         <v>27</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L100" s="3">
         <v>2</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N100" s="3">
         <v>1980</v>
@@ -10185,7 +10210,7 @@
         <v>30105162</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D101" s="5">
         <v>-2.2865265606942398E-2</v>
@@ -10194,10 +10219,10 @@
         <v>109.323223594193</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>25</v>
@@ -10209,13 +10234,13 @@
         <v>27</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L101" s="3">
         <v>2</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N101" s="3">
         <v>1988</v>
@@ -10231,7 +10256,7 @@
         <v>30105163</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D102" s="5">
         <v>-5.4093282803597403E-2</v>
@@ -10240,7 +10265,7 @@
         <v>109.31165286720901</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>32</v>
@@ -10255,13 +10280,13 @@
         <v>27</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L102" s="3">
         <v>2</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N102" s="3">
         <v>1990</v>
@@ -10277,7 +10302,7 @@
         <v>30105164</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D103" s="5">
         <v>-3.3940723306572898E-2</v>
@@ -10286,10 +10311,10 @@
         <v>109.305935295845</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>25</v>
@@ -10301,13 +10326,13 @@
         <v>27</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L103" s="3">
         <v>2</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N103" s="3">
         <v>1993</v>
@@ -10323,7 +10348,7 @@
         <v>30105165</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D104" s="5">
         <v>-4.3159423300361002E-2</v>
@@ -10332,10 +10357,10 @@
         <v>109.293088740226</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>25</v>
@@ -10347,13 +10372,13 @@
         <v>27</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L104" s="3">
         <v>2</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N104" s="3">
         <v>1995</v>
@@ -10369,7 +10394,7 @@
         <v>30105166</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D105" s="5">
         <v>-5.1613742307202497E-2</v>
@@ -10378,10 +10403,10 @@
         <v>109.300126769093</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>25</v>
@@ -10393,13 +10418,13 @@
         <v>27</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L105" s="3">
         <v>2</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N105" s="3">
         <v>1997</v>
@@ -10415,7 +10440,7 @@
         <v>69978011</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D106" s="5">
         <v>-3.8388309792715299E-2</v>
@@ -10424,10 +10449,10 @@
         <v>109.292016290487</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H106" s="4" t="s">
         <v>25</v>
@@ -10439,13 +10464,13 @@
         <v>27</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L106" s="3">
         <v>2</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N106" s="3">
         <v>2016</v>
@@ -10461,7 +10486,7 @@
         <v>30105221</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D107" s="5">
         <v>-3.3526701804335403E-2</v>
@@ -10470,7 +10495,7 @@
         <v>109.320011324882</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>32</v>
@@ -10485,13 +10510,13 @@
         <v>27</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L107" s="3">
         <v>2</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N107" s="3">
         <v>2004</v>
@@ -10507,7 +10532,7 @@
         <v>30105216</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D108" s="5">
         <v>-5.1267965654192997E-2</v>
@@ -10516,10 +10541,10 @@
         <v>109.298021594193</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H108" s="4" t="s">
         <v>25</v>
@@ -10531,13 +10556,13 @@
         <v>27</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L108" s="3">
         <v>2</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N108" s="3">
         <v>2001</v>
@@ -10553,7 +10578,7 @@
         <v>30105212</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D109" s="5">
         <v>-3.2904138621427499E-2</v>
@@ -10562,10 +10587,10 @@
         <v>109.306290194193</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>25</v>
@@ -10577,13 +10602,13 @@
         <v>27</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L109" s="3">
         <v>3</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N109" s="3">
         <v>1981</v>
@@ -10599,7 +10624,7 @@
         <v>30105233</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D110" s="5">
         <v>-4.7940716740662997E-2</v>
@@ -10608,7 +10633,7 @@
         <v>109.315741238112</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>32</v>
@@ -10623,13 +10648,13 @@
         <v>27</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L110" s="3">
         <v>2</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N110" s="3">
         <v>1985</v>
@@ -10645,7 +10670,7 @@
         <v>30105235</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D111" s="5">
         <v>-2.1786609781630099E-2</v>
@@ -10654,7 +10679,7 @@
         <v>109.32949413652</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>95</v>
@@ -10669,13 +10694,13 @@
         <v>27</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L111" s="3">
         <v>2</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N111" s="3">
         <v>1988</v>
@@ -10691,7 +10716,7 @@
         <v>30105236</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D112" s="5">
         <v>-2.3638780947182601E-2</v>
@@ -10700,10 +10725,10 @@
         <v>109.313551521176</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H112" s="4" t="s">
         <v>25</v>
@@ -10715,13 +10740,13 @@
         <v>27</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L112" s="3">
         <v>2</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N112" s="3">
         <v>1992</v>
@@ -10737,7 +10762,7 @@
         <v>30105240</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D113" s="5">
         <v>-2.7903725122233599E-2</v>
@@ -10746,10 +10771,10 @@
         <v>109.33561727884801</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>25</v>
@@ -10761,13 +10786,13 @@
         <v>27</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L113" s="3">
         <v>3</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N113" s="3">
         <v>1982</v>
@@ -10783,7 +10808,7 @@
         <v>30105241</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D114" s="5">
         <v>-4.7256423308354702E-2</v>
@@ -10792,10 +10817,10 @@
         <v>109.295859278848</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H114" s="4" t="s">
         <v>25</v>
@@ -10807,13 +10832,13 @@
         <v>27</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L114" s="3">
         <v>2</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N114" s="3">
         <v>1994</v>
@@ -10829,7 +10854,7 @@
         <v>69967262</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D115" s="5">
         <v>-5.0447292662055401E-2</v>
@@ -10838,7 +10863,7 @@
         <v>109.304529167209</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>32</v>
@@ -10853,13 +10878,13 @@
         <v>27</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L115" s="3">
         <v>2</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N115" s="3">
         <v>2016</v>
@@ -10875,7 +10900,7 @@
         <v>69977868</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D116" s="5">
         <v>-5.1302263885792697E-2</v>
@@ -10884,10 +10909,10 @@
         <v>109.301671788381</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>25</v>
@@ -10899,13 +10924,13 @@
         <v>27</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L116" s="3">
         <v>2</v>
       </c>
       <c r="M116" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N116" s="3">
         <v>2017</v>
@@ -10921,7 +10946,7 @@
         <v>69966158</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D117" s="5">
         <v>-3.8173528794924499E-2</v>
@@ -10930,10 +10955,10 @@
         <v>109.31103518255399</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>25</v>
@@ -10945,13 +10970,13 @@
         <v>27</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L117" s="3">
         <v>3</v>
       </c>
       <c r="M117" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N117" s="3">
         <v>2015</v>
@@ -10967,7 +10992,7 @@
         <v>69988425</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D118" s="5">
         <v>-1.6354508171746902E-2</v>
@@ -10976,10 +11001,10 @@
         <v>109.32372879486999</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H118" s="4" t="s">
         <v>25</v>
@@ -10991,13 +11016,13 @@
         <v>27</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L118" s="3">
         <v>2</v>
       </c>
       <c r="M118" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N118" s="3">
         <v>2018</v>
@@ -11013,7 +11038,7 @@
         <v>69989264</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D119" s="5">
         <v>-3.5750607953688299E-2</v>
@@ -11022,10 +11047,10 @@
         <v>109.302282978848</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>25</v>
@@ -11037,13 +11062,13 @@
         <v>27</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L119" s="3">
         <v>2</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N119" s="3">
         <v>2019</v>
@@ -11059,7 +11084,7 @@
         <v>30105233</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D120" s="5">
         <v>-4.8070926958971798E-2</v>
@@ -11068,7 +11093,7 @@
         <v>109.31564920583099</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>32</v>
@@ -11083,13 +11108,13 @@
         <v>27</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L120" s="3">
         <v>2</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N120" s="3">
         <v>1985</v>
@@ -11105,7 +11130,7 @@
         <v>30105245</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D121" s="5">
         <v>-4.21698809644361E-2</v>
@@ -11114,7 +11139,7 @@
         <v>109.312686282554</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>32</v>
@@ -11129,13 +11154,13 @@
         <v>27</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L121" s="3">
         <v>2</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N121" s="3">
         <v>1968</v>
@@ -11151,7 +11176,7 @@
         <v>30105247</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D122" s="5">
         <v>-2.36065944423701E-2</v>
@@ -11160,10 +11185,10 @@
         <v>109.31370172488199</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>25</v>
@@ -11175,13 +11200,13 @@
         <v>27</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L122" s="3">
         <v>2</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N122" s="3">
         <v>1995</v>
@@ -11197,7 +11222,7 @@
         <v>30105248</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D123" s="5">
         <v>-3.1916467454929598E-2</v>
@@ -11206,7 +11231,7 @@
         <v>109.324334146306</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>32</v>
@@ -11221,13 +11246,13 @@
         <v>27</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L123" s="3">
         <v>2</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N123" s="3">
         <v>1990</v>
@@ -11243,7 +11268,7 @@
         <v>30105249</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D124" s="5">
         <v>-4.6814189361454497E-2</v>
@@ -11252,7 +11277,7 @@
         <v>109.315129694454</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>32</v>
@@ -11267,13 +11292,13 @@
         <v>27</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L124" s="3">
         <v>2</v>
       </c>
       <c r="M124" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N124" s="3">
         <v>1993</v>
@@ -11289,7 +11314,7 @@
         <v>30113664</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D125" s="5">
         <v>-5.7224208068565902E-2</v>
@@ -11298,7 +11323,7 @@
         <v>109.307384546074</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>32</v>
@@ -11319,7 +11344,7 @@
         <v>2</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N125" s="3">
         <v>1998</v>
@@ -11335,7 +11360,7 @@
         <v>30113665</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D126" s="5">
         <v>-5.391089267515E-2</v>
@@ -11344,7 +11369,7 @@
         <v>109.31156703652</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>32</v>
@@ -11359,13 +11384,13 @@
         <v>27</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L126" s="3">
         <v>2</v>
       </c>
       <c r="M126" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N126" s="3">
         <v>1995</v>
@@ -11381,7 +11406,7 @@
         <v>30113666</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D127" s="5">
         <v>-4.24298627097928E-2</v>
@@ -11390,10 +11415,10 @@
         <v>109.292530846638</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>25</v>
@@ -11411,7 +11436,7 @@
         <v>2</v>
       </c>
       <c r="M127" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N127" s="3">
         <v>1992</v>
@@ -11427,7 +11452,7 @@
         <v>30113667</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D128" s="5">
         <v>-3.3905855910870898E-2</v>
@@ -11436,10 +11461,10 @@
         <v>109.30586762424601</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>25</v>
@@ -11451,13 +11476,13 @@
         <v>27</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L128" s="3">
         <v>2</v>
       </c>
       <c r="M128" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N128" s="3">
         <v>1996</v>
@@ -11473,7 +11498,7 @@
         <v>30113668</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D129" s="5">
         <v>-4.5001338633899803E-2</v>
@@ -11482,7 +11507,7 @@
         <v>109.310037021176</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>32</v>
@@ -11497,13 +11522,13 @@
         <v>27</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L129" s="3">
         <v>2</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N129" s="3">
         <v>1997</v>
@@ -11519,7 +11544,7 @@
         <v>30113669</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D130" s="5">
         <v>-5.13491168548132E-2</v>
@@ -11528,10 +11553,10 @@
         <v>109.300128508016</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>25</v>
@@ -11543,13 +11568,13 @@
         <v>27</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L130" s="3">
         <v>2</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N130" s="3">
         <v>1994</v>
@@ -11565,7 +11590,7 @@
         <v>1.09292263053718E+16</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D131" s="5">
         <v>-3.8270292624759603E-2</v>
@@ -11574,10 +11599,10 @@
         <v>109.292263053718</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>25</v>
@@ -11589,13 +11614,13 @@
         <v>27</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L131" s="3">
         <v>2</v>
       </c>
       <c r="M131" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N131" s="3">
         <v>2008</v>
@@ -11605,6 +11630,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -11615,9 +11643,6 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11629,71 +11654,71 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="51" t="s">
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="51" t="s">
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="60" t="s">
-        <v>360</v>
-      </c>
-      <c r="R1" s="61"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="64" t="s">
+        <v>361</v>
+      </c>
+      <c r="R1" s="65"/>
       <c r="S1" s="57" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T1" s="57"/>
     </row>
     <row r="2" spans="1:20" ht="36">
-      <c r="A2" s="65"/>
-      <c r="B2" s="49" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="63"/>
-      <c r="K2" s="53" t="s">
+      <c r="J2" s="60"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="64"/>
-      <c r="M2" s="63"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="60"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -11703,28 +11728,28 @@
       <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="58" t="s">
-        <v>362</v>
-      </c>
-      <c r="R2" s="58" t="s">
+      <c r="Q2" s="62" t="s">
         <v>363</v>
       </c>
-      <c r="S2" s="58" t="s">
-        <v>362</v>
-      </c>
-      <c r="T2" s="58" t="s">
+      <c r="R2" s="62" t="s">
         <v>364</v>
       </c>
+      <c r="S2" s="62" t="s">
+        <v>363</v>
+      </c>
+      <c r="T2" s="62" t="s">
+        <v>365</v>
+      </c>
     </row>
     <row r="3" spans="1:20" ht="60">
-      <c r="A3" s="62"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -11745,10 +11770,10 @@
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
     </row>
     <row r="4" spans="1:20" ht="48">
       <c r="A4" s="3">
@@ -11756,7 +11781,7 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D4" s="5">
         <v>-3.7306023283371598E-2</v>
@@ -11765,7 +11790,7 @@
         <v>109.329478725182</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>32</v>
@@ -11780,7 +11805,7 @@
         <v>27</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L4" s="3">
         <v>8</v>
@@ -11804,7 +11829,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D5" s="5">
         <v>-1.95937331633412E-2</v>
@@ -11828,7 +11853,7 @@
         <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L5" s="3">
         <v>4</v>
@@ -11852,7 +11877,7 @@
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D6" s="32">
         <v>-3.9292421453211303E-2</v>
@@ -11876,7 +11901,7 @@
         <v>27</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L6" s="18">
         <v>2</v>
@@ -11900,7 +11925,7 @@
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D7" s="32">
         <v>-2.4664565600741799E-2</v>
@@ -11924,7 +11949,7 @@
         <v>27</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L7" s="18">
         <v>2</v>
@@ -11933,7 +11958,7 @@
         <v>84</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O7" s="37"/>
       <c r="P7" s="33"/>
@@ -11948,7 +11973,7 @@
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D8" s="32">
         <v>-2.5131079011639499E-2</v>
@@ -11972,7 +11997,7 @@
         <v>27</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L8" s="18">
         <v>2</v>
@@ -11981,7 +12006,7 @@
         <v>84</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O8" s="37"/>
       <c r="P8" s="33"/>
@@ -11996,7 +12021,7 @@
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D9" s="32">
         <v>-5.09894079828545E-2</v>
@@ -12020,7 +12045,7 @@
         <v>27</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L9" s="18">
         <v>2</v>
@@ -12043,10 +12068,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D10" s="29">
         <v>-1.3611111111111109E-3</v>
@@ -12055,13 +12080,13 @@
         <v>109.33280555555559</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>26</v>
@@ -12093,10 +12118,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D11" s="29">
         <v>-3.3611111111111112E-2</v>
@@ -12105,19 +12130,19 @@
         <v>109.3094722222222</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K11" s="18">
         <v>386.5</v>
@@ -12134,7 +12159,7 @@
       <c r="Q11" s="18"/>
       <c r="R11" s="18"/>
       <c r="S11" s="18" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="T11" s="18"/>
     </row>
@@ -12143,10 +12168,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D12" s="29">
         <v>-1.6083333333333331E-2</v>
@@ -12155,13 +12180,13 @@
         <v>109.3486944444444</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>26</v>
@@ -12193,10 +12218,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D13" s="29">
         <v>-1.4874999999999999E-2</v>
@@ -12205,13 +12230,13 @@
         <v>109.3546083333333</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>26</v>
@@ -12243,10 +12268,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D14" s="29">
         <v>-2.472222222222222E-3</v>
@@ -12255,13 +12280,13 @@
         <v>109.36341666666669</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>26</v>
@@ -12293,10 +12318,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D15" s="29">
         <v>-4.5275000000000003E-2</v>
@@ -12305,13 +12330,13 @@
         <v>109.3667972222222</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>26</v>
@@ -12334,7 +12359,7 @@
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
       <c r="S15" s="18" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="T15" s="18"/>
     </row>
@@ -12343,10 +12368,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D16" s="29">
         <v>-5.4226999999999997E-2</v>
@@ -12355,13 +12380,13 @@
         <v>109.372108</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>26</v>
@@ -12384,7 +12409,7 @@
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
       <c r="S16" s="18" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="T16" s="18"/>
     </row>
@@ -12393,10 +12418,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D17" s="29">
         <v>-4.3363888888888889E-2</v>
@@ -12405,19 +12430,19 @@
         <v>109.3606972222222</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K17" s="18">
         <v>325</v>
@@ -12434,7 +12459,7 @@
       <c r="Q17" s="18"/>
       <c r="R17" s="18"/>
       <c r="S17" s="18" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="T17" s="18"/>
     </row>
@@ -12443,10 +12468,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D18" s="29">
         <v>-3.6080555555555553E-2</v>
@@ -12455,19 +12480,19 @@
         <v>109.3525305555555</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>26</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K18" s="18">
         <v>252</v>
@@ -12484,7 +12509,7 @@
       <c r="Q18" s="18"/>
       <c r="R18" s="18"/>
       <c r="S18" s="18" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="T18" s="18"/>
     </row>
@@ -12493,10 +12518,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D19" s="29">
         <v>-2.7588888888888888E-2</v>
@@ -12505,13 +12530,13 @@
         <v>109.35089444444441</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>26</v>
@@ -12534,7 +12559,7 @@
       <c r="Q19" s="18"/>
       <c r="R19" s="18"/>
       <c r="S19" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="T19" s="18"/>
     </row>
@@ -12543,10 +12568,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D20" s="29">
         <v>-2.6594444444444441E-2</v>
@@ -12555,13 +12580,13 @@
         <v>109.3776361111111</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>26</v>
@@ -12593,10 +12618,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D21" s="29">
         <v>-8.5055555555555561E-3</v>
@@ -12605,10 +12630,10 @@
         <v>109.3120555555556</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>98</v>
@@ -12634,7 +12659,7 @@
       <c r="Q21" s="18"/>
       <c r="R21" s="18"/>
       <c r="S21" s="18" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="T21" s="18"/>
     </row>
@@ -12643,10 +12668,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D22" s="29">
         <v>-6.6555555555555561E-3</v>
@@ -12655,7 +12680,7 @@
         <v>109.3023222222222</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G22" s="18" t="s">
         <v>97</v>
@@ -12667,7 +12692,7 @@
         <v>26</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K22" s="18">
         <v>312.5</v>
@@ -12684,7 +12709,7 @@
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
       <c r="S22" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="T22" s="18"/>
     </row>
@@ -12693,10 +12718,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D23" s="29">
         <v>-1.3599999999999999E-2</v>
@@ -12705,10 +12730,10 @@
         <v>109.32073333333329</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H23" s="18" t="s">
         <v>98</v>
@@ -12717,7 +12742,7 @@
         <v>26</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K23" s="18">
         <v>721.62</v>
@@ -12732,7 +12757,7 @@
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
       <c r="S23" s="18" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="T23" s="18"/>
     </row>
@@ -12741,10 +12766,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D24" s="29">
         <v>-2.3930555555555559E-2</v>
@@ -12753,10 +12778,10 @@
         <v>109.2940722222222</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H24" s="18" t="s">
         <v>98</v>
@@ -12782,7 +12807,7 @@
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="18" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="T24" s="18"/>
     </row>
@@ -12791,10 +12816,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D25" s="29">
         <v>-5.3363888888888891E-2</v>
@@ -12803,10 +12828,10 @@
         <v>109.3184055555556</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H25" s="18" t="s">
         <v>25</v>
@@ -12832,7 +12857,7 @@
       <c r="Q25" s="18"/>
       <c r="R25" s="18"/>
       <c r="S25" s="18" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="T25" s="18"/>
     </row>
@@ -12841,10 +12866,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D26" s="29">
         <v>-1.108333333333333E-2</v>
@@ -12853,10 +12878,10 @@
         <v>109.34288888888889</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H26" s="18" t="s">
         <v>25</v>
@@ -12865,7 +12890,7 @@
         <v>26</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K26" s="18">
         <v>315.3</v>
@@ -12875,14 +12900,14 @@
       </c>
       <c r="M26" s="18"/>
       <c r="N26" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
       <c r="Q26" s="18"/>
       <c r="R26" s="18"/>
       <c r="S26" s="18" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="T26" s="18"/>
     </row>
@@ -12891,10 +12916,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D27" s="29">
         <v>-4.7805555555555559E-2</v>
@@ -12903,10 +12928,10 @@
         <v>109.35799166666671</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>25</v>
@@ -12915,7 +12940,7 @@
         <v>26</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K27" s="18">
         <v>571</v>
@@ -12930,7 +12955,7 @@
       <c r="Q27" s="18"/>
       <c r="R27" s="18"/>
       <c r="S27" s="18" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="T27" s="18"/>
     </row>
@@ -12939,10 +12964,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D28" s="29">
         <v>-7.407777777777777E-2</v>
@@ -12951,10 +12976,10 @@
         <v>109.34655833333331</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H28" s="18" t="s">
         <v>25</v>
@@ -12990,7 +13015,7 @@
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="25" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D29" s="16">
         <v>-4.15E-3</v>
@@ -13024,7 +13049,7 @@
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="25" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D30" s="16">
         <v>-1.073E-2</v>
@@ -13058,7 +13083,7 @@
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D31" s="16">
         <v>-3.5799999999999998E-3</v>
@@ -13092,7 +13117,7 @@
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="25" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D32" s="16">
         <v>-4.1399999999999996E-3</v>
@@ -13126,7 +13151,7 @@
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="25" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D33" s="16">
         <v>-1.265E-2</v>
@@ -13160,7 +13185,7 @@
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="25" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D34" s="16">
         <v>-3.7200000000000002E-3</v>
@@ -13194,7 +13219,7 @@
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="25" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D35" s="16">
         <v>-4.6600000000000001E-3</v>
@@ -13228,7 +13253,7 @@
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="25" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D36" s="16">
         <v>-1.264E-2</v>
@@ -13262,7 +13287,7 @@
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="25" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D37" s="16">
         <v>-4.8199999999999996E-3</v>
@@ -13296,7 +13321,7 @@
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="25" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D38" s="16">
         <v>-3.79E-3</v>
@@ -13330,7 +13355,7 @@
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="25" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D39" s="16">
         <v>-1.8970000000000001E-2</v>
@@ -13364,7 +13389,7 @@
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="25" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D40" s="16">
         <v>-1.222E-2</v>
@@ -13398,7 +13423,7 @@
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="25" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D41" s="16">
         <v>-3.2799999999999999E-3</v>
@@ -13432,7 +13457,7 @@
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="25" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D42" s="16">
         <v>-5.1000000000000004E-3</v>
@@ -13466,7 +13491,7 @@
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="25" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D43" s="16">
         <v>-9.0200000000000002E-3</v>
@@ -13500,7 +13525,7 @@
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D44" s="16">
         <v>-6.2700000000000004E-3</v>
@@ -13534,7 +13559,7 @@
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="17" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D45" s="16">
         <v>-5.0000000000000001E-3</v>
@@ -13564,6 +13589,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -13574,15 +13608,6 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13597,60 +13622,60 @@
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="51" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="51" t="s">
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="70"/>
+      <c r="P1" s="74"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="71"/>
-      <c r="B2" s="49" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="70"/>
-      <c r="K2" s="53" t="s">
+      <c r="J2" s="74"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="69"/>
-      <c r="M2" s="70"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="74"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -13662,14 +13687,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="72"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -13697,7 +13722,7 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D4" s="5">
         <v>-3.305688317259E-2</v>
@@ -13721,7 +13746,7 @@
         <v>27</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L4" s="3">
         <v>1</v>
@@ -13741,7 +13766,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D5" s="5">
         <v>-3.0528901570029E-2</v>
@@ -13765,7 +13790,7 @@
         <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L5" s="3">
         <v>1</v>
@@ -13785,7 +13810,7 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D6" s="5">
         <v>-2.6897191063444299E-2</v>
@@ -13809,7 +13834,7 @@
         <v>27</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L6" s="3">
         <v>1</v>
@@ -13829,7 +13854,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D7" s="5">
         <v>-3.4997461098407297E-2</v>
@@ -13853,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L7" s="3">
         <v>1</v>
@@ -13873,7 +13898,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D8" s="5">
         <v>-2.6451944370815599E-2</v>
@@ -13897,7 +13922,7 @@
         <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L8" s="3">
         <v>1</v>
@@ -13917,7 +13942,7 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D9" s="5">
         <v>-3.7100312511818501E-2</v>
@@ -13941,7 +13966,7 @@
         <v>27</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L9" s="3">
         <v>2</v>
@@ -13961,7 +13986,7 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D10" s="5">
         <v>-3.3023355652657203E-2</v>
@@ -13985,7 +14010,7 @@
         <v>27</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L10" s="3">
         <v>2</v>
@@ -14005,7 +14030,7 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D11" s="5">
         <v>-2.93004500107443E-2</v>
@@ -14029,7 +14054,7 @@
         <v>27</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L11" s="3">
         <v>1</v>
@@ -14049,7 +14074,7 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D12" s="5">
         <v>-2.92521702510385E-2</v>
@@ -14073,7 +14098,7 @@
         <v>27</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L12" s="3">
         <v>1</v>
@@ -14093,7 +14118,7 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D13" s="5">
         <v>-4.8428432846192603E-2</v>
@@ -14117,7 +14142,7 @@
         <v>27</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L13" s="3">
         <v>1</v>
@@ -14137,7 +14162,7 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D14" s="5">
         <v>-4.2825821525160103E-2</v>
@@ -14161,7 +14186,7 @@
         <v>27</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L14" s="3">
         <v>1</v>
@@ -14181,7 +14206,7 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D15" s="5">
         <v>-5.9994818618451698E-2</v>
@@ -14205,7 +14230,7 @@
         <v>27</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L15" s="3">
         <v>1</v>
@@ -14225,7 +14250,7 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D16" s="5">
         <v>-2.9933451252404E-2</v>
@@ -14249,7 +14274,7 @@
         <v>27</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L16" s="3">
         <v>1</v>
@@ -14269,7 +14294,7 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D17" s="5">
         <v>-3.9020773734214503E-2</v>
@@ -14293,7 +14318,7 @@
         <v>27</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L17" s="3">
         <v>1</v>
@@ -14313,7 +14338,7 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D18" s="5">
         <v>-3.8434027376651102E-2</v>
@@ -14337,7 +14362,7 @@
         <v>27</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L18" s="3">
         <v>1</v>
@@ -14357,7 +14382,7 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D19" s="5">
         <v>-5.0111153476079098E-2</v>
@@ -14381,7 +14406,7 @@
         <v>27</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L19" s="3">
         <v>1</v>
@@ -14390,7 +14415,7 @@
         <v>29</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -14401,7 +14426,7 @@
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D20" s="5">
         <v>-4.9407450253117297E-2</v>
@@ -14425,7 +14450,7 @@
         <v>27</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L20" s="3">
         <v>2</v>
@@ -14434,7 +14459,7 @@
         <v>29</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -14445,7 +14470,7 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D21" s="5">
         <v>-4.6866890051634601E-2</v>
@@ -14469,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L21" s="3">
         <v>1</v>
@@ -14478,7 +14503,7 @@
         <v>29</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -14489,7 +14514,7 @@
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D22" s="5">
         <v>-4.5386311184041898E-2</v>
@@ -14513,7 +14538,7 @@
         <v>27</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L22" s="3">
         <v>1</v>
@@ -14522,7 +14547,7 @@
         <v>29</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -14533,7 +14558,7 @@
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D23" s="5">
         <v>-4.4334885592930397E-2</v>
@@ -14557,7 +14582,7 @@
         <v>27</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L23" s="3">
         <v>1</v>
@@ -14566,7 +14591,7 @@
         <v>29</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -14577,7 +14602,7 @@
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D24" s="5">
         <v>-4.3176171658923901E-2</v>
@@ -14601,7 +14626,7 @@
         <v>27</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L24" s="3">
         <v>1</v>
@@ -14610,7 +14635,7 @@
         <v>29</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -14621,7 +14646,7 @@
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D25" s="5">
         <v>-2.1591782213168102E-2</v>
@@ -14645,7 +14670,7 @@
         <v>27</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L25" s="3">
         <v>2</v>
@@ -14665,7 +14690,7 @@
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D26" s="5">
         <v>-4.1860253497890798E-2</v>
@@ -14689,7 +14714,7 @@
         <v>27</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L26" s="3">
         <v>1</v>
@@ -14698,7 +14723,7 @@
         <v>29</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -14709,7 +14734,7 @@
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D27" s="5">
         <v>-2.9150916876343101E-2</v>
@@ -14733,7 +14758,7 @@
         <v>27</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L27" s="3">
         <v>1</v>
@@ -14742,7 +14767,7 @@
         <v>29</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -14753,7 +14778,7 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D28" s="5">
         <v>-2.3198546148105199E-2</v>
@@ -14777,7 +14802,7 @@
         <v>27</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L28" s="3">
         <v>2</v>
@@ -14797,7 +14822,7 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D29" s="5">
         <v>-2.3848118571305501E-2</v>
@@ -14821,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L29" s="3">
         <v>1</v>
@@ -14830,7 +14855,7 @@
         <v>29</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -14841,7 +14866,7 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D30" s="5">
         <v>-2.6623807183040301E-2</v>
@@ -14865,7 +14890,7 @@
         <v>27</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L30" s="3">
         <v>1</v>
@@ -14874,7 +14899,7 @@
         <v>29</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -14885,7 +14910,7 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D31" s="5">
         <v>-2.7306108144082498E-2</v>
@@ -14909,7 +14934,7 @@
         <v>27</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L31" s="3">
         <v>1</v>
@@ -14918,7 +14943,7 @@
         <v>29</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -14929,7 +14954,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D32" s="5">
         <v>-2.03463571319339E-2</v>
@@ -14953,7 +14978,7 @@
         <v>27</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L32" s="3">
         <v>2</v>
@@ -14973,7 +14998,7 @@
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D33" s="5">
         <v>-2.4389349275525499E-2</v>
@@ -14997,7 +15022,7 @@
         <v>27</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L33" s="3">
         <v>1</v>
@@ -15017,7 +15042,7 @@
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D34" s="5">
         <v>-2.4172066931815801E-2</v>
@@ -15041,7 +15066,7 @@
         <v>27</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L34" s="3">
         <v>2</v>
@@ -15061,7 +15086,7 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D35" s="5">
         <v>-2.29838484346527E-2</v>
@@ -15085,7 +15110,7 @@
         <v>27</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L35" s="3">
         <v>1</v>
@@ -15105,7 +15130,7 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D36" s="5">
         <v>-2.3058528451606899E-2</v>
@@ -15129,7 +15154,7 @@
         <v>27</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L36" s="3">
         <v>1</v>
@@ -15149,7 +15174,7 @@
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D37" s="5">
         <v>-2.55534044497241E-2</v>
@@ -15173,7 +15198,7 @@
         <v>27</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L37" s="3">
         <v>1</v>
@@ -15182,7 +15207,7 @@
         <v>29</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
@@ -15193,7 +15218,7 @@
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D38" s="5">
         <v>-2.1931081476664199E-2</v>
@@ -15217,7 +15242,7 @@
         <v>27</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L38" s="3">
         <v>1</v>
@@ -15237,7 +15262,7 @@
       </c>
       <c r="B39" s="34"/>
       <c r="C39" s="41" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D39" s="40">
         <v>-1.92864235795423E-2</v>
@@ -15261,7 +15286,7 @@
         <v>27</v>
       </c>
       <c r="K39" s="34" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L39" s="34">
         <v>1</v>
@@ -15281,7 +15306,7 @@
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="15" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D40" s="42">
         <v>-6.8599999999999998E-3</v>
@@ -15311,7 +15336,7 @@
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="15" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D41" s="42">
         <v>-3.29E-3</v>
@@ -15341,7 +15366,7 @@
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D42" s="42">
         <v>-4.5199999999999997E-3</v>
@@ -15371,7 +15396,7 @@
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D43" s="42">
         <v>-1.443E-2</v>
@@ -15401,7 +15426,7 @@
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D44" s="42">
         <v>-1.1169999999999999E-2</v>
@@ -15431,7 +15456,7 @@
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D45" s="42">
         <v>-5.7000000000000002E-3</v>
@@ -15461,7 +15486,7 @@
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="15" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D46" s="42">
         <v>-2.5500000000000002E-3</v>
@@ -15491,7 +15516,7 @@
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D47" s="42">
         <v>-4.9699999999999996E-3</v>
@@ -15521,7 +15546,7 @@
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="15" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D48" s="42">
         <v>-8.7000000000000001E-4</v>
@@ -15551,7 +15576,7 @@
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D49" s="42">
         <v>-7.9600000000000001E-3</v>
@@ -15581,7 +15606,7 @@
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D50" s="42">
         <v>-6.9199999999999999E-3</v>
@@ -15611,7 +15636,7 @@
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D51" s="42">
         <v>-8.8800000000000007E-3</v>
@@ -15641,7 +15666,7 @@
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="15" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D52" s="42">
         <v>-8.2400000000000008E-3</v>
@@ -15671,7 +15696,7 @@
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="15" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D53" s="42">
         <v>-1.278E-2</v>
@@ -15701,7 +15726,7 @@
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D54" s="42">
         <v>-9.0699999999999999E-3</v>
@@ -15731,7 +15756,7 @@
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D55" s="42">
         <v>-0.41952</v>
@@ -15761,7 +15786,7 @@
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="15" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D56" s="42">
         <v>-6.77E-3</v>
@@ -15791,7 +15816,7 @@
       </c>
       <c r="B57" s="18"/>
       <c r="C57" s="15" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D57" s="42">
         <v>-9.2099999999999994E-3</v>
@@ -15821,7 +15846,7 @@
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="15" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D58" s="42">
         <v>-4.62E-3</v>
@@ -15851,7 +15876,7 @@
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="15" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D59" s="42">
         <v>-7.9299999999999995E-3</v>
@@ -15881,7 +15906,7 @@
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="15" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D60" s="42">
         <v>-1.01E-3</v>
@@ -15911,7 +15936,7 @@
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D61" s="5">
         <v>-2.7182175694019099E-2</v>
@@ -15935,7 +15960,7 @@
         <v>27</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L61" s="3">
         <v>2</v>
@@ -15955,7 +15980,7 @@
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D62" s="5">
         <v>-2.9823940361993598E-2</v>
@@ -15999,7 +16024,7 @@
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D63" s="5">
         <v>-3.1931255091528297E-2</v>
@@ -16023,7 +16048,7 @@
         <v>27</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L63" s="3">
         <v>1</v>
@@ -16043,7 +16068,7 @@
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D64" s="5">
         <v>-4.8528322280354898E-2</v>
@@ -16067,7 +16092,7 @@
         <v>27</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L64" s="3">
         <v>2</v>
@@ -16087,7 +16112,7 @@
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D65" s="5">
         <v>-6.1779094808755097E-2</v>
@@ -16111,7 +16136,7 @@
         <v>27</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L65" s="3">
         <v>2</v>
@@ -16120,7 +16145,7 @@
         <v>84</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
@@ -16131,7 +16156,7 @@
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D66" s="5">
         <v>-4.8171445719323899E-2</v>
@@ -16155,7 +16180,7 @@
         <v>27</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L66" s="3">
         <v>1</v>
@@ -16164,7 +16189,7 @@
         <v>84</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
@@ -16175,7 +16200,7 @@
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D67" s="5">
         <v>-2.85172450700832E-2</v>
@@ -16199,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L67" s="3">
         <v>2</v>
@@ -16219,7 +16244,7 @@
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D68" s="5">
         <v>-2.4917720963034601E-2</v>
@@ -16243,7 +16268,7 @@
         <v>27</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L68" s="3">
         <v>1</v>
@@ -16263,7 +16288,7 @@
       </c>
       <c r="B69" s="34"/>
       <c r="C69" s="41" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D69" s="40">
         <v>-2.1007700520245701E-2</v>
@@ -16287,7 +16312,7 @@
         <v>27</v>
       </c>
       <c r="K69" s="34" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L69" s="34">
         <v>1</v>
@@ -16307,7 +16332,7 @@
       </c>
       <c r="B70" s="18"/>
       <c r="C70" s="15" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D70" s="42">
         <v>-5.1900000000000002E-3</v>
@@ -16337,7 +16362,7 @@
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="15" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D71" s="42">
         <v>-1.1690000000000001E-2</v>
@@ -16367,7 +16392,7 @@
       </c>
       <c r="B72" s="18"/>
       <c r="C72" s="15" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D72" s="42">
         <v>-8.8800000000000007E-3</v>
@@ -16397,7 +16422,7 @@
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D73" s="42">
         <v>-5.3099999999999996E-3</v>
@@ -16427,7 +16452,7 @@
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D74" s="5">
         <v>-2.8281828567388999E-2</v>
@@ -16448,10 +16473,10 @@
         <v>26</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L74" s="3">
         <v>1</v>
@@ -16471,7 +16496,7 @@
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D75" s="5">
         <v>-2.3534371787800299E-2</v>
@@ -16511,6 +16536,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -16521,9 +16549,6 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16639,7 +16664,7 @@
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="21" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D4" s="20">
         <v>-8.5000000000000006E-3</v>
@@ -16669,7 +16694,7 @@
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="21" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D5" s="20">
         <v>-1.0109999999999999E-2</v>
@@ -16699,7 +16724,7 @@
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="21" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D6" s="20">
         <v>-8.5699999999999995E-3</v>
@@ -16729,7 +16754,7 @@
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="21" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D7" s="20">
         <v>-9.1199999999999996E-3</v>
@@ -16759,7 +16784,7 @@
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="21" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D8" s="20">
         <v>-1.42E-3</v>
@@ -16789,7 +16814,7 @@
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="21" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D9" s="20">
         <v>-1.6039999999999999E-2</v>
@@ -16819,7 +16844,7 @@
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="19" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D10" s="20">
         <v>-8.8999999999999995E-4</v>
@@ -16849,7 +16874,7 @@
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="21" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D11" s="20">
         <v>-2.2100000000000002E-3</v>
@@ -16875,6 +16900,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -16885,9 +16913,6 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16915,7 +16940,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C1" s="57"/>
       <c r="D1" s="57"/>
@@ -16944,10 +16969,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E2" s="57" t="s">
         <v>6</v>
@@ -16956,7 +16981,7 @@
         <v>7</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H2" s="57" t="s">
         <v>9</v>
@@ -16977,10 +17002,10 @@
         <v>13</v>
       </c>
       <c r="P2" s="57" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Q2" s="57" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="R2" s="57"/>
     </row>
@@ -17004,20 +17029,20 @@
         <v>18</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P3" s="57"/>
       <c r="Q3" s="14" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="36">
@@ -17026,10 +17051,10 @@
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E4" s="18">
         <v>-2.6519999999999998E-2</v>
@@ -17039,23 +17064,23 @@
       </c>
       <c r="G4" s="18"/>
       <c r="H4" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="45">
         <v>825</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O4" s="18">
         <v>2025</v>
@@ -17072,10 +17097,10 @@
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E5" s="18">
         <v>-5.2181999999999999E-2</v>
@@ -17085,23 +17110,23 @@
       </c>
       <c r="G5" s="18"/>
       <c r="H5" s="22" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="45">
         <v>4500</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O5" s="18">
         <v>2025</v>
@@ -17118,10 +17143,10 @@
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E6" s="18">
         <v>-5.6816999999999999E-2</v>
@@ -17131,23 +17156,23 @@
       </c>
       <c r="G6" s="18"/>
       <c r="H6" s="22" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="45">
         <v>3800</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O6" s="18">
         <v>2025</v>
@@ -17164,10 +17189,10 @@
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E7" s="18">
         <v>-6.4637E-2</v>
@@ -17177,23 +17202,23 @@
       </c>
       <c r="G7" s="18"/>
       <c r="H7" s="22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L7" s="22"/>
       <c r="M7" s="45">
         <v>4600</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O7" s="18">
         <v>2025</v>
@@ -17210,10 +17235,10 @@
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E8" s="18">
         <v>-7.3205999999999993E-2</v>
@@ -17223,23 +17248,23 @@
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="22" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L8" s="22"/>
       <c r="M8" s="45">
         <v>6300</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O8" s="18">
         <v>2025</v>
@@ -17256,10 +17281,10 @@
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E9" s="18">
         <v>-6.6999000000000003E-2</v>
@@ -17269,23 +17294,23 @@
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="22" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L9" s="22"/>
       <c r="M9" s="45">
         <v>2100</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O9" s="18">
         <v>2025</v>
@@ -17302,10 +17327,10 @@
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E10" s="18">
         <v>-2.4538889000000001E-2</v>
@@ -17315,13 +17340,13 @@
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>27</v>
@@ -17346,10 +17371,10 @@
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E11" s="18">
         <v>-5.7777800000000004E-4</v>
@@ -17359,13 +17384,13 @@
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>27</v>
@@ -17390,10 +17415,10 @@
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E12" s="18">
         <v>-3.3805556E-2</v>
@@ -17403,13 +17428,13 @@
       </c>
       <c r="G12" s="18"/>
       <c r="H12" s="22" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>27</v>
@@ -17434,10 +17459,10 @@
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E13" s="18">
         <v>-3.3805556E-2</v>
@@ -17447,13 +17472,13 @@
       </c>
       <c r="G13" s="18"/>
       <c r="H13" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K13" s="22" t="s">
         <v>27</v>
@@ -17478,10 +17503,10 @@
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E14" s="18">
         <v>-3.8888900000000001E-4</v>
@@ -17491,13 +17516,13 @@
       </c>
       <c r="G14" s="18"/>
       <c r="H14" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>27</v>
@@ -17522,10 +17547,10 @@
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E15" s="18">
         <v>-3.3805556E-2</v>
@@ -17535,13 +17560,13 @@
       </c>
       <c r="G15" s="18"/>
       <c r="H15" s="22" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K15" s="22" t="s">
         <v>27</v>
@@ -17566,10 +17591,10 @@
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E16" s="18">
         <v>-3.5644443999999997E-2</v>
@@ -17579,13 +17604,13 @@
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>27</v>
@@ -17610,10 +17635,10 @@
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E17" s="18">
         <v>-3.1629999999999998E-2</v>
@@ -17623,13 +17648,13 @@
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="22" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K17" s="22" t="s">
         <v>27</v>
@@ -17654,10 +17679,10 @@
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E18" s="18">
         <v>-6.3280000000000003E-2</v>
@@ -17667,13 +17692,13 @@
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="22" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>27</v>
@@ -17698,10 +17723,10 @@
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E19" s="18">
         <v>-2.9803E-2</v>
@@ -17711,13 +17736,13 @@
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K19" s="22" t="s">
         <v>27</v>
@@ -17742,10 +17767,10 @@
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E20" s="18">
         <v>-1.1709999999999999E-3</v>
@@ -17755,13 +17780,13 @@
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>98</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K20" s="22" t="s">
         <v>27</v>
@@ -17786,10 +17811,10 @@
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E21" s="18">
         <v>5.3839999999999999E-3</v>
@@ -17805,7 +17830,7 @@
         <v>98</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K21" s="22" t="s">
         <v>27</v>
@@ -17830,10 +17855,10 @@
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E22" s="18">
         <v>-2.9825000000000001E-2</v>
@@ -17843,13 +17868,13 @@
       </c>
       <c r="G22" s="30"/>
       <c r="H22" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I22" s="22" t="s">
         <v>98</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K22" s="22" t="s">
         <v>27</v>
@@ -18006,7 +18031,7 @@
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D4" s="47">
         <v>-5.3099999999999996E-3</v>
@@ -18038,7 +18063,7 @@
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D5" s="47">
         <v>-3.29E-3</v>
@@ -18070,7 +18095,7 @@
       </c>
       <c r="B6" s="25"/>
       <c r="C6" s="25" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D6" s="47">
         <v>-6.4999999999999997E-3</v>
@@ -18102,7 +18127,7 @@
       </c>
       <c r="B7" s="25"/>
       <c r="C7" s="25" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D7" s="47">
         <v>-1.0200000000000001E-2</v>
@@ -18134,7 +18159,7 @@
       </c>
       <c r="B8" s="25"/>
       <c r="C8" s="25" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D8" s="47">
         <v>-8.5900000000000004E-3</v>
@@ -18166,7 +18191,7 @@
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="25" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D9" s="47">
         <v>-6.2599999999999999E-3</v>
@@ -18198,7 +18223,7 @@
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="25" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D10" s="47">
         <v>-6.5300000000000002E-3</v>
@@ -18230,7 +18255,7 @@
       </c>
       <c r="B11" s="25"/>
       <c r="C11" s="25" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D11" s="47">
         <v>-3.63E-3</v>
@@ -18262,7 +18287,7 @@
       </c>
       <c r="B12" s="25"/>
       <c r="C12" s="25" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D12" s="47">
         <v>-3.7399999999999998E-3</v>
@@ -18290,6 +18315,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -18300,9 +18328,6 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18318,6 +18343,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumen" ma:contentTypeID="0x010100CCD785251A4E724B934A12AB8BE46060" ma:contentTypeVersion="12" ma:contentTypeDescription="Buat sebuah dokumen baru." ma:contentTypeScope="" ma:versionID="5ae3aba09e4cbefebb89020ec97f4692">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15954fb3-4959-4f5b-ae14-d7aa01180869" xmlns:ns3="4ce1a36b-806a-4732-b893-33b689d3fa0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f158cec65280218b3e83bd78c7c2c412" ns2:_="" ns3:_="">
     <xsd:import namespace="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
@@ -18518,25 +18554,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}"/>
 </file>
--- a/data/processed/eksposur_pontianak_0408.xlsx
+++ b/data/processed/eksposur_pontianak_0408.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95D6DD61-729F-43FD-8900-F3FE800C69D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F834E40-FC43-4EEF-BF7D-FF1DE50F47A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="4" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
   </bookViews>
   <sheets>
     <sheet name="Government" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="631">
   <si>
     <t>No</t>
   </si>
@@ -511,6 +511,9 @@
     <t>TK Islam Semesta Khatulistiwa</t>
   </si>
   <si>
+    <t>-0.032706885267140766</t>
+  </si>
+  <si>
     <t>± 180 - 220 m²</t>
   </si>
   <si>
@@ -529,6 +532,9 @@
     <t>TKS Aisyiyah Bustanul Athfal 1</t>
   </si>
   <si>
+    <t>-0.021862247525607087</t>
+  </si>
+  <si>
     <t>± 2 – 3 meter</t>
   </si>
   <si>
@@ -541,6 +547,9 @@
     <t>TK Al-Mukaddimah</t>
   </si>
   <si>
+    <t>-0.029849895001585334</t>
+  </si>
+  <si>
     <t>± 2 – 4 m</t>
   </si>
   <si>
@@ -550,6 +559,9 @@
     <t>TKS Kesuma</t>
   </si>
   <si>
+    <t>-0.038857430242735344</t>
+  </si>
+  <si>
     <t>± 166 m²</t>
   </si>
   <si>
@@ -694,6 +706,9 @@
     <t>TK Berkah Quran</t>
   </si>
   <si>
+    <t>-0.024491804306615204</t>
+  </si>
+  <si>
     <t>± 350 – 550 m²</t>
   </si>
   <si>
@@ -710,6 +725,9 @@
   </si>
   <si>
     <t>RA/BA/TA DWP KANWIL KEMENAG</t>
+  </si>
+  <si>
+    <t>-0.05061655410564161</t>
   </si>
   <si>
     <t xml:space="preserve">± 300 </t>
@@ -1461,6 +1479,9 @@
     <t>± 300–400 m²</t>
   </si>
   <si>
+    <t>-0.037450322138884044, 109.31662559227702</t>
+  </si>
+  <si>
     <t>Masjid Nurul Hidayah</t>
   </si>
   <si>
@@ -1471,6 +1492,9 @@
   </si>
   <si>
     <t>Masjid Dzakirin</t>
+  </si>
+  <si>
+    <t>-0.037450322138884044</t>
   </si>
   <si>
     <t>Masjid Al-Fajar</t>
@@ -1926,7 +1950,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00000"/>
     <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2124,6 +2148,12 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -2670,7 +2700,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2810,17 +2840,21 @@
     <xf numFmtId="166" fontId="20" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="35" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="35" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2828,22 +2862,28 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2870,16 +2910,7 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="35" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="35" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3272,63 +3303,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="49" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49" t="s">
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="50"/>
+      <c r="P1" s="60"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="56"/>
-      <c r="B2" s="51" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="50"/>
-      <c r="K2" s="54" t="s">
+      <c r="J2" s="60"/>
+      <c r="K2" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="50"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="60"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -3340,14 +3371,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -5270,82 +5301,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57" t="s">
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57" t="s">
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="57"/>
+      <c r="P1" s="61"/>
     </row>
     <row r="2" spans="1:16" ht="24">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57" t="s">
+      <c r="J2" s="61"/>
+      <c r="K2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="57" t="s">
+      <c r="O2" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="57" t="s">
+      <c r="P2" s="61" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -5364,8 +5395,8 @@
       <c r="N3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="61"/>
     </row>
     <row r="4" spans="1:16" ht="36">
       <c r="A4" s="18">
@@ -5527,10 +5558,10 @@
       <c r="C7" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="51">
         <v>-2.0104111659418E-2</v>
       </c>
-      <c r="E7" s="72">
+      <c r="E7" s="52">
         <v>109.329290727692</v>
       </c>
       <c r="F7" s="22">
@@ -5645,63 +5676,63 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="49" t="s">
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="49" t="s">
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="74"/>
+      <c r="P1" s="75"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="75"/>
-      <c r="B2" s="51" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="74"/>
-      <c r="K2" s="54" t="s">
+      <c r="J2" s="75"/>
+      <c r="K2" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="73"/>
-      <c r="M2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="75"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -5713,14 +5744,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -5844,10 +5875,10 @@
       <c r="C6" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="E6" s="70">
+      <c r="E6" s="50">
         <v>109.321715135997</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -5880,7 +5911,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="48">
+    <row r="7" spans="1:16" ht="35.25">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -5890,11 +5921,11 @@
       <c r="C7" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D7" s="5">
-        <v>-3.8561999999999999E-2</v>
-      </c>
-      <c r="E7" s="5">
-        <v>109.309485</v>
+      <c r="D7" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="50">
+        <v>109.327916682713</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>146</v>
@@ -5912,7 +5943,7 @@
         <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L7" s="3">
         <v>1</v>
@@ -5921,7 +5952,7 @@
         <v>143</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -5934,7 +5965,7 @@
         <v>30108473</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D8" s="5">
         <v>-3.7995337956296199E-2</v>
@@ -5958,7 +5989,7 @@
         <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L8" s="3">
         <v>2</v>
@@ -5967,12 +5998,12 @@
         <v>143</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" ht="48">
+    <row r="9" spans="1:16" ht="35.25">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -5980,16 +6011,16 @@
         <v>30108463</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-3.3363694485578098E-2</v>
-      </c>
-      <c r="E9" s="5">
-        <v>109.32483499999999</v>
+        <v>161</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" s="50">
+        <v>109.328118476204</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>95</v>
@@ -6004,7 +6035,7 @@
         <v>27</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L9" s="3">
         <v>1</v>
@@ -6013,12 +6044,12 @@
         <v>143</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="48">
+    <row r="10" spans="1:16" ht="35.25">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -6026,16 +6057,16 @@
         <v>30108624</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-2.9642694498243499E-2</v>
-      </c>
-      <c r="E10" s="5">
-        <v>109.33351999999999</v>
+        <v>166</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" s="50">
+        <v>109.321654868493</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>32</v>
@@ -6050,7 +6081,7 @@
         <v>27</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L10" s="3">
         <v>1</v>
@@ -6064,7 +6095,7 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="36">
+    <row r="11" spans="1:16" ht="35.25">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -6072,16 +6103,16 @@
         <v>30108484</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-3.8667781005920297E-2</v>
-      </c>
-      <c r="E11" s="5">
-        <v>109.3128</v>
+        <v>170</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="50">
+        <v>109.315605964326</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>32</v>
@@ -6096,7 +6127,7 @@
         <v>27</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L11" s="3">
         <v>1</v>
@@ -6118,7 +6149,7 @@
         <v>30108465</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D12" s="5">
         <v>-2.9790423311429101E-2</v>
@@ -6127,7 +6158,7 @@
         <v>109.304768806607</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>79</v>
@@ -6164,7 +6195,7 @@
         <v>30109347</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D13" s="5">
         <v>-2.76E-2</v>
@@ -6173,7 +6204,7 @@
         <v>109.3369</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
@@ -6188,7 +6219,7 @@
         <v>27</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="L13" s="3">
         <v>2</v>
@@ -6197,7 +6228,7 @@
         <v>143</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -6210,7 +6241,7 @@
         <v>30108466</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D14" s="5">
         <v>-2.8762294446453601E-2</v>
@@ -6234,7 +6265,7 @@
         <v>27</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="L14" s="3">
         <v>2</v>
@@ -6256,7 +6287,7 @@
         <v>30108478</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D15" s="5">
         <v>-4.1501098126782203E-2</v>
@@ -6265,7 +6296,7 @@
         <v>109.30939636350401</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>32</v>
@@ -6289,7 +6320,7 @@
         <v>143</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -6302,7 +6333,7 @@
         <v>30108474</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D16" s="5">
         <v>-4.1285050298795103E-2</v>
@@ -6311,7 +6342,7 @@
         <v>109.325661567209</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>32</v>
@@ -6326,7 +6357,7 @@
         <v>27</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L16" s="3">
         <v>1</v>
@@ -6335,7 +6366,7 @@
         <v>143</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -6348,7 +6379,7 @@
         <v>30108481</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D17" s="5">
         <v>-2.26441791017877E-2</v>
@@ -6357,7 +6388,7 @@
         <v>109.334865794192</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>32</v>
@@ -6372,7 +6403,7 @@
         <v>27</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L17" s="3">
         <v>1</v>
@@ -6381,7 +6412,7 @@
         <v>143</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -6394,7 +6425,7 @@
         <v>30108480</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D18" s="5">
         <v>-3.1399099968289698E-2</v>
@@ -6403,7 +6434,7 @@
         <v>109.323618194193</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>32</v>
@@ -6418,7 +6449,7 @@
         <v>27</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L18" s="3">
         <v>1</v>
@@ -6427,7 +6458,7 @@
         <v>143</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -6440,7 +6471,7 @@
         <v>30108482</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D19" s="5">
         <v>-2.7092592602462901E-2</v>
@@ -6449,7 +6480,7 @@
         <v>109.33878833652</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
@@ -6464,7 +6495,7 @@
         <v>27</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L19" s="3">
         <v>1</v>
@@ -6473,7 +6504,7 @@
         <v>143</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -6486,7 +6517,7 @@
         <v>30108485</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D20" s="5">
         <v>-3.7682023291372102E-2</v>
@@ -6495,10 +6526,10 @@
         <v>109.314568963504</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>25</v>
@@ -6510,7 +6541,7 @@
         <v>27</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L20" s="3">
         <v>1</v>
@@ -6519,7 +6550,7 @@
         <v>143</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -6532,7 +6563,7 @@
         <v>30108486</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D21" s="5">
         <v>-2.2298550266456399E-2</v>
@@ -6541,7 +6572,7 @@
         <v>109.32635195186501</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>81</v>
@@ -6556,7 +6587,7 @@
         <v>27</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L21" s="3">
         <v>1</v>
@@ -6565,7 +6596,7 @@
         <v>143</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -6578,7 +6609,7 @@
         <v>30108487</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D22" s="5">
         <v>-3.0113582791468401E-2</v>
@@ -6587,7 +6618,7 @@
         <v>109.32922033652</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
@@ -6602,7 +6633,7 @@
         <v>27</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L22" s="3">
         <v>1</v>
@@ -6611,7 +6642,7 @@
         <v>143</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -6624,7 +6655,7 @@
         <v>30108488</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D23" s="5">
         <v>-2.68994736054066E-2</v>
@@ -6633,7 +6664,7 @@
         <v>109.338874173062</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>32</v>
@@ -6648,7 +6679,7 @@
         <v>27</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L23" s="6">
         <v>1</v>
@@ -6657,7 +6688,7 @@
         <v>143</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -6670,7 +6701,7 @@
         <v>30108489</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D24" s="5">
         <v>-2.5534109782796799E-2</v>
@@ -6679,7 +6710,7 @@
         <v>109.335852034667</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>81</v>
@@ -6694,7 +6725,7 @@
         <v>27</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L24" s="3">
         <v>2</v>
@@ -6703,7 +6734,7 @@
         <v>143</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -6716,7 +6747,7 @@
         <v>69811968</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D25" s="5">
         <v>-5.4039638648230803E-2</v>
@@ -6725,7 +6756,7 @@
         <v>109.31151339234</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
@@ -6740,7 +6771,7 @@
         <v>27</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L25" s="3">
         <v>1</v>
@@ -6749,7 +6780,7 @@
         <v>143</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -6762,7 +6793,7 @@
         <v>69903619</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D26" s="5">
         <v>-4.2438723299055799E-2</v>
@@ -6771,7 +6802,7 @@
         <v>109.314721753718</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
@@ -6786,7 +6817,7 @@
         <v>27</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L26" s="3">
         <v>2</v>
@@ -6795,7 +6826,7 @@
         <v>143</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -6808,7 +6839,7 @@
         <v>69903646</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D27" s="5">
         <v>-4.7807180973703602E-2</v>
@@ -6817,7 +6848,7 @@
         <v>109.307685638373</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>32</v>
@@ -6832,7 +6863,7 @@
         <v>27</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L27" s="3">
         <v>1</v>
@@ -6841,7 +6872,7 @@
         <v>143</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -6854,7 +6885,7 @@
         <v>30108483</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D28" s="5">
         <v>-5.0160338641563502E-2</v>
@@ -6863,7 +6894,7 @@
         <v>109.315331294193</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>32</v>
@@ -6878,7 +6909,7 @@
         <v>27</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="L28" s="3">
         <v>1</v>
@@ -6887,7 +6918,7 @@
         <v>143</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -6900,7 +6931,7 @@
         <v>30108486</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D29" s="5">
         <v>-2.7508162568052101E-2</v>
@@ -6909,10 +6940,10 @@
         <v>109.321573361079</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>25</v>
@@ -6924,7 +6955,7 @@
         <v>27</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L29" s="3">
         <v>1</v>
@@ -6933,7 +6964,7 @@
         <v>143</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -6946,7 +6977,7 @@
         <v>30108481</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D30" s="5">
         <v>-4.82896791504819E-2</v>
@@ -6955,7 +6986,7 @@
         <v>109.31845026535601</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>32</v>
@@ -6970,7 +7001,7 @@
         <v>27</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L30" s="3">
         <v>1</v>
@@ -6979,7 +7010,7 @@
         <v>143</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -6992,7 +7023,7 @@
         <v>30108478</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D31" s="5">
         <v>-3.8679825126622297E-2</v>
@@ -7001,7 +7032,7 @@
         <v>109.291654921176</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>32</v>
@@ -7016,7 +7047,7 @@
         <v>27</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L31" s="3">
         <v>1</v>
@@ -7025,7 +7056,7 @@
         <v>143</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -7038,7 +7069,7 @@
         <v>69972625</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D32" s="5">
         <v>-2.66330079405016E-2</v>
@@ -7047,7 +7078,7 @@
         <v>109.33240906165101</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
@@ -7062,16 +7093,16 @@
         <v>27</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="L32" s="3">
         <v>1</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -7084,7 +7115,7 @@
         <v>69853159</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D33" s="5">
         <v>-3.3671980954025502E-2</v>
@@ -7093,7 +7124,7 @@
         <v>109.311407921176</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>32</v>
@@ -7108,7 +7139,7 @@
         <v>27</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="L33" s="3">
         <v>1</v>
@@ -7117,7 +7148,7 @@
         <v>143</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
@@ -7130,7 +7161,7 @@
         <v>69853160</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D34" s="5">
         <v>-2.70032820207428E-2</v>
@@ -7139,7 +7170,7 @@
         <v>109.31727676427499</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>32</v>
@@ -7154,7 +7185,7 @@
         <v>27</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="L34" s="3">
         <v>1</v>
@@ -7163,12 +7194,12 @@
         <v>143</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:16" ht="36">
+    <row r="35" spans="1:16" ht="35.25">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -7176,16 +7207,16 @@
         <v>70006431</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-2.34859852190888E-2</v>
-      </c>
-      <c r="E35" s="5">
-        <v>109.318190161469</v>
+        <v>219</v>
+      </c>
+      <c r="D35" s="49" t="s">
+        <v>220</v>
+      </c>
+      <c r="E35" s="50">
+        <v>109.31811961603201</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>32</v>
@@ -7200,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L35" s="3">
         <v>1</v>
@@ -7209,7 +7240,7 @@
         <v>143</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
@@ -7222,7 +7253,7 @@
         <v>70011642</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D36" s="5">
         <v>-2.43344579381953E-2</v>
@@ -7231,10 +7262,10 @@
         <v>109.31739661139</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>25</v>
@@ -7246,7 +7277,7 @@
         <v>27</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L36" s="3">
         <v>1</v>
@@ -7255,7 +7286,7 @@
         <v>143</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
@@ -7268,7 +7299,7 @@
         <v>69888953</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D37" s="5">
         <v>-3.1355723315320598E-2</v>
@@ -7277,7 +7308,7 @@
         <v>109.329024584678</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>32</v>
@@ -7292,7 +7323,7 @@
         <v>27</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="L37" s="3">
         <v>1</v>
@@ -7306,7 +7337,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:16" ht="48">
+    <row r="38" spans="1:16" ht="47.25">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -7314,19 +7345,19 @@
         <v>69744576</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-4.86330642905351E-2</v>
-      </c>
-      <c r="E38" s="5">
-        <v>109.316352916032</v>
+        <v>226</v>
+      </c>
+      <c r="D38" s="49" t="s">
+        <v>227</v>
+      </c>
+      <c r="E38" s="50">
+        <v>109.316787170856</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>25</v>
@@ -7338,13 +7369,13 @@
         <v>27</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="L38" s="3">
         <v>1</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N38" s="3">
         <v>2006</v>
@@ -7360,7 +7391,7 @@
         <v>69955972</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D39" s="5">
         <v>-4.9999744482566798E-2</v>
@@ -7370,7 +7401,7 @@
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>25</v>
@@ -7382,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="L39" s="3">
         <v>1</v>
@@ -7404,7 +7435,7 @@
         <v>69960241</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D40" s="5">
         <v>-2.5658134930915202E-2</v>
@@ -7413,10 +7444,10 @@
         <v>109.32333026535601</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>25</v>
@@ -7428,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L40" s="3">
         <v>1</v>
@@ -7450,7 +7481,7 @@
         <v>30105266</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D41" s="5">
         <v>-2.701108094883E-2</v>
@@ -7462,7 +7493,7 @@
         <v>141</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>25</v>
@@ -7474,16 +7505,16 @@
         <v>27</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L41" s="3">
         <v>1</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
@@ -7496,7 +7527,7 @@
         <v>30105263</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D42" s="5">
         <v>-4.6428340462114498E-2</v>
@@ -7505,7 +7536,7 @@
         <v>109.31649209419299</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>32</v>
@@ -7520,16 +7551,16 @@
         <v>27</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="L42" s="3">
         <v>1</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
@@ -7542,7 +7573,7 @@
         <v>30105261</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D43" s="5">
         <v>-5.1460489606070303E-2</v>
@@ -7551,7 +7582,7 @@
         <v>109.31528053255199</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>32</v>
@@ -7566,16 +7597,16 @@
         <v>27</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="L43" s="3">
         <v>2</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
@@ -7588,7 +7619,7 @@
         <v>30105270</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D44" s="5">
         <v>-5.9493509828884503E-2</v>
@@ -7597,7 +7628,7 @@
         <v>109.30637652117601</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>32</v>
@@ -7612,16 +7643,16 @@
         <v>27</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="L44" s="3">
         <v>1</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
@@ -7634,7 +7665,7 @@
         <v>30108480</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D45" s="5">
         <v>-3.4950280955306501E-2</v>
@@ -7643,10 +7674,10 @@
         <v>109.301090796045</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>25</v>
@@ -7658,16 +7689,16 @@
         <v>27</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L45" s="3">
         <v>1</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
@@ -7680,7 +7711,7 @@
         <v>30108412</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D46" s="5">
         <v>-2.4042152112433799E-2</v>
@@ -7689,7 +7720,7 @@
         <v>109.33026735001199</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>81</v>
@@ -7704,16 +7735,16 @@
         <v>27</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="L46" s="3">
         <v>1</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
@@ -7726,7 +7757,7 @@
         <v>30105198</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D47" s="5">
         <v>-2.2703350266828001E-2</v>
@@ -7735,7 +7766,7 @@
         <v>109.33426060583101</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>81</v>
@@ -7756,10 +7787,10 @@
         <v>1</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
@@ -7772,7 +7803,7 @@
         <v>30105195</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D48" s="5">
         <v>-2.5171192599773899E-2</v>
@@ -7781,7 +7812,7 @@
         <v>109.325922165356</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>32</v>
@@ -7796,16 +7827,16 @@
         <v>27</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="L48" s="3">
         <v>1</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
@@ -7818,7 +7849,7 @@
         <v>30105200</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D49" s="5">
         <v>-2.1583058224110399E-2</v>
@@ -7827,7 +7858,7 @@
         <v>109.31962333837301</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>79</v>
@@ -7842,16 +7873,16 @@
         <v>27</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="L49" s="3">
         <v>1</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
@@ -7864,7 +7895,7 @@
         <v>30105233</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D50" s="5">
         <v>-3.1745607947101503E-2</v>
@@ -7873,7 +7904,7 @@
         <v>109.31300833652</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>79</v>
@@ -7888,16 +7919,16 @@
         <v>27</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="L50" s="3">
         <v>1</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -7910,7 +7941,7 @@
         <v>30105245</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D51" s="5">
         <v>-3.8685880959655E-2</v>
@@ -7919,7 +7950,7 @@
         <v>109.314153680701</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>32</v>
@@ -7934,16 +7965,16 @@
         <v>27</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="L51" s="3">
         <v>2</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
@@ -7956,7 +7987,7 @@
         <v>30105244</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D52" s="5">
         <v>-2.39336097822061E-2</v>
@@ -7965,7 +7996,7 @@
         <v>109.32199809604499</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>79</v>
@@ -7980,16 +8011,16 @@
         <v>27</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="L52" s="3">
         <v>1</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
@@ -8002,7 +8033,7 @@
         <v>30105211</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D53" s="5">
         <v>-3.7968338625721597E-2</v>
@@ -8011,7 +8042,7 @@
         <v>109.316680638373</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>32</v>
@@ -8026,16 +8057,16 @@
         <v>27</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L53" s="3">
         <v>2</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
@@ -8048,7 +8079,7 @@
         <v>30105212</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D54" s="5">
         <v>-3.4398119612401398E-2</v>
@@ -8057,7 +8088,7 @@
         <v>109.31937436720899</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>32</v>
@@ -8072,16 +8103,16 @@
         <v>27</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="L54" s="3">
         <v>2</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
@@ -8094,7 +8125,7 @@
         <v>30105350</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D55" s="5">
         <v>-1.9265367451778301E-2</v>
@@ -8103,7 +8134,7 @@
         <v>109.33319022488099</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>95</v>
@@ -8118,16 +8149,16 @@
         <v>27</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="L55" s="3">
         <v>1</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
@@ -8140,7 +8171,7 @@
         <v>30105217</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D56" s="5">
         <v>-3.8618679125791901E-2</v>
@@ -8149,7 +8180,7 @@
         <v>109.32736646535599</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>32</v>
@@ -8164,16 +8195,16 @@
         <v>27</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="L56" s="3">
         <v>2</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
@@ -8186,7 +8217,7 @@
         <v>30105353</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D57" s="5">
         <v>-3.0730438620000401E-2</v>
@@ -8195,10 +8226,10 @@
         <v>109.321885182554</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>25</v>
@@ -8210,16 +8241,16 @@
         <v>27</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="L57" s="3">
         <v>1</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
@@ -8232,7 +8263,7 @@
         <v>30105352</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D58" s="5">
         <v>-2.35367962869126E-2</v>
@@ -8241,7 +8272,7 @@
         <v>109.33611589234</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>81</v>
@@ -8256,16 +8287,16 @@
         <v>27</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="L58" s="3">
         <v>1</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="O58" s="3"/>
       <c r="P58" s="3"/>
@@ -8278,7 +8309,7 @@
         <v>30208415</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D59" s="5">
         <v>-3.12254232833129E-2</v>
@@ -8287,7 +8318,7 @@
         <v>109.322241423029</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>32</v>
@@ -8308,10 +8339,10 @@
         <v>2</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
@@ -8324,7 +8355,7 @@
         <v>30208420</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D60" s="5">
         <v>-3.71804393187763E-2</v>
@@ -8333,10 +8364,10 @@
         <v>109.331849769352</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>25</v>
@@ -8354,7 +8385,7 @@
         <v>2</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N60" s="3">
         <v>1998</v>
@@ -8370,7 +8401,7 @@
         <v>30208425</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D61" s="5">
         <v>-2.7689750272526899E-2</v>
@@ -8379,7 +8410,7 @@
         <v>109.339861124881</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>24</v>
@@ -8394,16 +8425,16 @@
         <v>27</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="L61" s="3">
         <v>2</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
@@ -8416,7 +8447,7 @@
         <v>30208430</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D62" s="5">
         <v>-4.7607277323707599E-2</v>
@@ -8425,7 +8456,7 @@
         <v>109.315977924881</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>32</v>
@@ -8446,10 +8477,10 @@
         <v>2</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
@@ -8462,7 +8493,7 @@
         <v>30208435</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D63" s="5">
         <v>-2.13210116273123E-2</v>
@@ -8471,7 +8502,7 @@
         <v>109.333645667209</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>95</v>
@@ -8492,10 +8523,10 @@
         <v>2</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
@@ -8508,7 +8539,7 @@
         <v>30208440</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D64" s="5">
         <v>-2.7400615610579299E-2</v>
@@ -8517,7 +8548,7 @@
         <v>109.336974328848</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>24</v>
@@ -8532,16 +8563,16 @@
         <v>27</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="L64" s="3">
         <v>2</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
@@ -8554,7 +8585,7 @@
         <v>30208445</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D65" s="5">
         <v>-2.5567761922192501E-2</v>
@@ -8563,7 +8594,7 @@
         <v>109.336498167209</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>24</v>
@@ -8584,10 +8615,10 @@
         <v>2</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
@@ -8600,7 +8631,7 @@
         <v>30208450</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D66" s="5">
         <v>-3.0687034939797301E-2</v>
@@ -8609,7 +8640,7 @@
         <v>109.328118465356</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>32</v>
@@ -8624,13 +8655,13 @@
         <v>27</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L66" s="3">
         <v>2</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N66" s="3">
         <v>1997</v>
@@ -8646,7 +8677,7 @@
         <v>30208455</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D67" s="5">
         <v>-5.0460880978708003E-2</v>
@@ -8655,10 +8686,10 @@
         <v>109.304527723029</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>25</v>
@@ -8670,13 +8701,13 @@
         <v>27</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="L67" s="3">
         <v>2</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N67" s="3">
         <v>2002</v>
@@ -8692,7 +8723,7 @@
         <v>30208460</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D68" s="5">
         <v>-2.90727195988865E-2</v>
@@ -8701,10 +8732,10 @@
         <v>109.30532202302901</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H68" s="4" t="s">
         <v>25</v>
@@ -8722,7 +8753,7 @@
         <v>2</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N68" s="3">
         <v>2001</v>
@@ -8738,7 +8769,7 @@
         <v>30208465</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D69" s="5">
         <v>-3.2712252119016599E-2</v>
@@ -8747,10 +8778,10 @@
         <v>109.318001376995</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>25</v>
@@ -8762,13 +8793,13 @@
         <v>27</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="L69" s="3">
         <v>2</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N69" s="3">
         <v>2000</v>
@@ -8784,7 +8815,7 @@
         <v>30208470</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D70" s="5">
         <v>-3.1791479112974801E-2</v>
@@ -8793,10 +8824,10 @@
         <v>109.328595267209</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>25</v>
@@ -8808,13 +8839,13 @@
         <v>27</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="L70" s="3">
         <v>2</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N70" s="3">
         <v>2001</v>
@@ -8830,7 +8861,7 @@
         <v>30208500</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D71" s="5">
         <v>-2.7352594445159299E-2</v>
@@ -8839,10 +8870,10 @@
         <v>109.321750382554</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>25</v>
@@ -8854,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L71" s="3">
         <v>2</v>
@@ -8876,7 +8907,7 @@
         <v>30208505</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D72" s="5">
         <v>-4.2363621468670301E-2</v>
@@ -8885,10 +8916,10 @@
         <v>109.314593007684</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>25</v>
@@ -8900,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="L72" s="3">
         <v>2</v>
@@ -8922,7 +8953,7 @@
         <v>30208510</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D73" s="5">
         <v>-4.6916307978736298E-2</v>
@@ -8931,10 +8962,10 @@
         <v>109.30945286350401</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>25</v>
@@ -8946,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="L73" s="3">
         <v>2</v>
@@ -8968,7 +8999,7 @@
         <v>30208515</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D74" s="5">
         <v>-5.74041926894511E-2</v>
@@ -8977,10 +9008,10 @@
         <v>109.300500509537</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>25</v>
@@ -8992,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L74" s="3">
         <v>2</v>
@@ -9014,7 +9045,7 @@
         <v>30208520</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D75" s="5">
         <v>-2.8511850273675799E-2</v>
@@ -9023,10 +9054,10 @@
         <v>109.334180609537</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>25</v>
@@ -9038,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L75" s="3">
         <v>2</v>
@@ -9060,7 +9091,7 @@
         <v>10208525</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D76" s="5">
         <v>-3.07488846316845E-2</v>
@@ -9069,7 +9100,7 @@
         <v>109.327584794193</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>32</v>
@@ -9106,7 +9137,7 @@
         <v>30208530</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D77" s="5">
         <v>-2.1711507936092399E-2</v>
@@ -9115,7 +9146,7 @@
         <v>109.32954778070101</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>95</v>
@@ -9130,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L77" s="3">
         <v>2</v>
@@ -9152,7 +9183,7 @@
         <v>30208535</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D78" s="5">
         <v>-2.5001853956734099E-2</v>
@@ -9161,7 +9192,7 @@
         <v>109.32880007699499</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>81</v>
@@ -9176,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="L78" s="3">
         <v>2</v>
@@ -9198,7 +9229,7 @@
         <v>30208540</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D79" s="5">
         <v>-3.80109689023636E-2</v>
@@ -9207,7 +9238,7 @@
         <v>109.319041405993</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>32</v>
@@ -9222,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L79" s="3">
         <v>2</v>
@@ -9244,7 +9275,7 @@
         <v>30208545</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D80" s="5">
         <v>-5.0225049949271398E-2</v>
@@ -9253,7 +9284,7 @@
         <v>109.312299488373</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>32</v>
@@ -9268,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L80" s="3">
         <v>2</v>
@@ -9290,7 +9321,7 @@
         <v>20308550</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D81" s="5">
         <v>-3.9720965627975703E-2</v>
@@ -9299,7 +9330,7 @@
         <v>109.314537705831</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>32</v>
@@ -9314,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="L81" s="3">
         <v>2</v>
@@ -9336,7 +9367,7 @@
         <v>20308555</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D82" s="5">
         <v>-5.2929796308746398E-2</v>
@@ -9345,10 +9376,10 @@
         <v>109.301002451865</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>25</v>
@@ -9360,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="L82" s="3">
         <v>2</v>
@@ -9382,7 +9413,7 @@
         <v>20308560</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D83" s="5">
         <v>-2.5829107939648599E-2</v>
@@ -9391,7 +9422,7 @@
         <v>109.332609396045</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>81</v>
@@ -9406,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="L83" s="3">
         <v>3</v>
@@ -9428,7 +9459,7 @@
         <v>20308565</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D84" s="5">
         <v>-2.38168232774052E-2</v>
@@ -9437,7 +9468,7 @@
         <v>109.334426707684</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>81</v>
@@ -9452,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="L84" s="3">
         <v>2</v>
@@ -9474,7 +9505,7 @@
         <v>30308570</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D85" s="5">
         <v>-4.63328561895925E-2</v>
@@ -9483,7 +9514,7 @@
         <v>109.315155685343</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>32</v>
@@ -9520,7 +9551,7 @@
         <v>30308575</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D86" s="5">
         <v>-2.0190680946197199E-2</v>
@@ -9529,7 +9560,7 @@
         <v>109.334348151865</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>95</v>
@@ -9544,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="L86" s="3">
         <v>1</v>
@@ -9566,7 +9597,7 @@
         <v>30308580</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="D87" s="5">
         <v>-5.9412450358260198E-2</v>
@@ -9575,7 +9606,7 @@
         <v>109.305301380701</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>32</v>
@@ -9612,7 +9643,7 @@
         <v>30105245</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D88" s="5">
         <v>-2.5450307939278001E-2</v>
@@ -9621,10 +9652,10 @@
         <v>109.336880167209</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="H88" s="4" t="s">
         <v>25</v>
@@ -9636,13 +9667,13 @@
         <v>27</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="L88" s="3">
         <v>2</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N88" s="3">
         <v>1956</v>
@@ -9658,7 +9689,7 @@
         <v>30105253</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D89" s="5">
         <v>-2.1840253956996E-2</v>
@@ -9667,7 +9698,7 @@
         <v>109.329451221176</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>95</v>
@@ -9682,13 +9713,13 @@
         <v>27</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L89" s="3">
         <v>2</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N89" s="3">
         <v>1992</v>
@@ -9704,7 +9735,7 @@
         <v>30105257</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D90" s="5">
         <v>-2.2206788905909301E-2</v>
@@ -9713,10 +9744,10 @@
         <v>109.31317709419299</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>25</v>
@@ -9734,7 +9765,7 @@
         <v>2</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N90" s="3">
         <v>1998</v>
@@ -9750,7 +9781,7 @@
         <v>30105240</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D91" s="5">
         <v>-2.7843336776447899E-2</v>
@@ -9759,10 +9790,10 @@
         <v>109.336276105831</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>25</v>
@@ -9774,13 +9805,13 @@
         <v>27</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="L91" s="3">
         <v>3</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N91" s="3">
         <v>1951</v>
@@ -9796,7 +9827,7 @@
         <v>30105264</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D92" s="5">
         <v>-5.0425834998664501E-2</v>
@@ -9805,7 +9836,7 @@
         <v>109.304421878848</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>32</v>
@@ -9820,13 +9851,13 @@
         <v>27</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L92" s="3">
         <v>2</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N92" s="3">
         <v>2005</v>
@@ -9842,7 +9873,7 @@
         <v>69970633</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D93" s="5">
         <v>-3.80555303011757E-2</v>
@@ -9851,10 +9882,10 @@
         <v>109.311065486781</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>25</v>
@@ -9866,13 +9897,13 @@
         <v>27</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L93" s="3">
         <v>3</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N93" s="3">
         <v>2017</v>
@@ -9888,7 +9919,7 @@
         <v>69992187</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D94" s="5">
         <v>-3.6742818535087998E-2</v>
@@ -9897,10 +9928,10 @@
         <v>109.311898718338</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>25</v>
@@ -9912,13 +9943,13 @@
         <v>27</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="L94" s="3">
         <v>2</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N94" s="3">
         <v>2019</v>
@@ -9934,7 +9965,7 @@
         <v>69974172</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D95" s="5">
         <v>-2.0788798143694099E-2</v>
@@ -9943,10 +9974,10 @@
         <v>109.321972253345</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>25</v>
@@ -9958,13 +9989,13 @@
         <v>27</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="L95" s="3">
         <v>2</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="N95" s="3">
         <v>2016</v>
@@ -9980,7 +10011,7 @@
         <v>30105269</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="D96" s="5">
         <v>-4.24172656332477E-2</v>
@@ -9989,7 +10020,7 @@
         <v>109.314571550012</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>32</v>
@@ -10010,7 +10041,7 @@
         <v>2</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N96" s="3">
         <v>2004</v>
@@ -10026,7 +10057,7 @@
         <v>69976889</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D97" s="5">
         <v>-3.1848398751727999E-2</v>
@@ -10035,7 +10066,7 @@
         <v>109.328520478587</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>32</v>
@@ -10050,13 +10081,13 @@
         <v>27</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="L97" s="3">
         <v>3</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N97" s="3">
         <v>2016</v>
@@ -10072,7 +10103,7 @@
         <v>30105238</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D98" s="5">
         <v>-4.7362824086970602E-2</v>
@@ -10081,7 +10112,7 @@
         <v>109.315756500083</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>32</v>
@@ -10102,7 +10133,7 @@
         <v>2</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N98" s="3">
         <v>1987</v>
@@ -10118,7 +10149,7 @@
         <v>30105146</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D99" s="5">
         <v>-3.1488865615147903E-2</v>
@@ -10127,7 +10158,7 @@
         <v>109.324309778848</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>32</v>
@@ -10142,13 +10173,13 @@
         <v>27</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L99" s="3">
         <v>3</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N99" s="3">
         <v>1978</v>
@@ -10164,7 +10195,7 @@
         <v>30105147</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="D100" s="5">
         <v>-4.9743338640881603E-2</v>
@@ -10173,7 +10204,7 @@
         <v>109.31627916350401</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>32</v>
@@ -10188,13 +10219,13 @@
         <v>27</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="L100" s="3">
         <v>2</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N100" s="3">
         <v>1980</v>
@@ -10210,7 +10241,7 @@
         <v>30105162</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D101" s="5">
         <v>-2.2865265606942398E-2</v>
@@ -10219,10 +10250,10 @@
         <v>109.323223594193</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>25</v>
@@ -10234,13 +10265,13 @@
         <v>27</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L101" s="3">
         <v>2</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N101" s="3">
         <v>1988</v>
@@ -10256,7 +10287,7 @@
         <v>30105163</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D102" s="5">
         <v>-5.4093282803597403E-2</v>
@@ -10265,7 +10296,7 @@
         <v>109.31165286720901</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>32</v>
@@ -10280,13 +10311,13 @@
         <v>27</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L102" s="3">
         <v>2</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N102" s="3">
         <v>1990</v>
@@ -10302,7 +10333,7 @@
         <v>30105164</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D103" s="5">
         <v>-3.3940723306572898E-2</v>
@@ -10311,10 +10342,10 @@
         <v>109.305935295845</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>25</v>
@@ -10326,13 +10357,13 @@
         <v>27</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="L103" s="3">
         <v>2</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N103" s="3">
         <v>1993</v>
@@ -10348,7 +10379,7 @@
         <v>30105165</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D104" s="5">
         <v>-4.3159423300361002E-2</v>
@@ -10357,10 +10388,10 @@
         <v>109.293088740226</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>25</v>
@@ -10372,13 +10403,13 @@
         <v>27</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="L104" s="3">
         <v>2</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N104" s="3">
         <v>1995</v>
@@ -10394,7 +10425,7 @@
         <v>30105166</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D105" s="5">
         <v>-5.1613742307202497E-2</v>
@@ -10403,10 +10434,10 @@
         <v>109.300126769093</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>25</v>
@@ -10418,13 +10449,13 @@
         <v>27</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L105" s="3">
         <v>2</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N105" s="3">
         <v>1997</v>
@@ -10440,7 +10471,7 @@
         <v>69978011</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D106" s="5">
         <v>-3.8388309792715299E-2</v>
@@ -10449,10 +10480,10 @@
         <v>109.292016290487</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H106" s="4" t="s">
         <v>25</v>
@@ -10464,13 +10495,13 @@
         <v>27</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="L106" s="3">
         <v>2</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N106" s="3">
         <v>2016</v>
@@ -10486,7 +10517,7 @@
         <v>30105221</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="D107" s="5">
         <v>-3.3526701804335403E-2</v>
@@ -10495,7 +10526,7 @@
         <v>109.320011324882</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>32</v>
@@ -10510,13 +10541,13 @@
         <v>27</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="L107" s="3">
         <v>2</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N107" s="3">
         <v>2004</v>
@@ -10532,7 +10563,7 @@
         <v>30105216</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D108" s="5">
         <v>-5.1267965654192997E-2</v>
@@ -10541,10 +10572,10 @@
         <v>109.298021594193</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H108" s="4" t="s">
         <v>25</v>
@@ -10556,13 +10587,13 @@
         <v>27</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="L108" s="3">
         <v>2</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N108" s="3">
         <v>2001</v>
@@ -10578,7 +10609,7 @@
         <v>30105212</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D109" s="5">
         <v>-3.2904138621427499E-2</v>
@@ -10587,10 +10618,10 @@
         <v>109.306290194193</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>25</v>
@@ -10602,13 +10633,13 @@
         <v>27</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="L109" s="3">
         <v>3</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N109" s="3">
         <v>1981</v>
@@ -10624,7 +10655,7 @@
         <v>30105233</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="D110" s="5">
         <v>-4.7940716740662997E-2</v>
@@ -10633,7 +10664,7 @@
         <v>109.315741238112</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>32</v>
@@ -10648,13 +10679,13 @@
         <v>27</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="L110" s="3">
         <v>2</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N110" s="3">
         <v>1985</v>
@@ -10670,7 +10701,7 @@
         <v>30105235</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D111" s="5">
         <v>-2.1786609781630099E-2</v>
@@ -10679,7 +10710,7 @@
         <v>109.32949413652</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>95</v>
@@ -10694,13 +10725,13 @@
         <v>27</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="L111" s="3">
         <v>2</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N111" s="3">
         <v>1988</v>
@@ -10716,7 +10747,7 @@
         <v>30105236</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D112" s="5">
         <v>-2.3638780947182601E-2</v>
@@ -10725,10 +10756,10 @@
         <v>109.313551521176</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H112" s="4" t="s">
         <v>25</v>
@@ -10740,13 +10771,13 @@
         <v>27</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="L112" s="3">
         <v>2</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N112" s="3">
         <v>1992</v>
@@ -10762,7 +10793,7 @@
         <v>30105240</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D113" s="5">
         <v>-2.7903725122233599E-2</v>
@@ -10771,10 +10802,10 @@
         <v>109.33561727884801</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>25</v>
@@ -10786,13 +10817,13 @@
         <v>27</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="L113" s="3">
         <v>3</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N113" s="3">
         <v>1982</v>
@@ -10808,7 +10839,7 @@
         <v>30105241</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="D114" s="5">
         <v>-4.7256423308354702E-2</v>
@@ -10817,10 +10848,10 @@
         <v>109.295859278848</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H114" s="4" t="s">
         <v>25</v>
@@ -10832,13 +10863,13 @@
         <v>27</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L114" s="3">
         <v>2</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N114" s="3">
         <v>1994</v>
@@ -10854,7 +10885,7 @@
         <v>69967262</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D115" s="5">
         <v>-5.0447292662055401E-2</v>
@@ -10863,7 +10894,7 @@
         <v>109.304529167209</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>32</v>
@@ -10878,13 +10909,13 @@
         <v>27</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L115" s="3">
         <v>2</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N115" s="3">
         <v>2016</v>
@@ -10900,7 +10931,7 @@
         <v>69977868</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D116" s="5">
         <v>-5.1302263885792697E-2</v>
@@ -10909,10 +10940,10 @@
         <v>109.301671788381</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>25</v>
@@ -10924,13 +10955,13 @@
         <v>27</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="L116" s="3">
         <v>2</v>
       </c>
       <c r="M116" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N116" s="3">
         <v>2017</v>
@@ -10946,7 +10977,7 @@
         <v>69966158</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D117" s="5">
         <v>-3.8173528794924499E-2</v>
@@ -10955,10 +10986,10 @@
         <v>109.31103518255399</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>25</v>
@@ -10970,13 +11001,13 @@
         <v>27</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L117" s="3">
         <v>3</v>
       </c>
       <c r="M117" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N117" s="3">
         <v>2015</v>
@@ -10992,7 +11023,7 @@
         <v>69988425</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D118" s="5">
         <v>-1.6354508171746902E-2</v>
@@ -11001,10 +11032,10 @@
         <v>109.32372879486999</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H118" s="4" t="s">
         <v>25</v>
@@ -11016,13 +11047,13 @@
         <v>27</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L118" s="3">
         <v>2</v>
       </c>
       <c r="M118" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N118" s="3">
         <v>2018</v>
@@ -11038,7 +11069,7 @@
         <v>69989264</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D119" s="5">
         <v>-3.5750607953688299E-2</v>
@@ -11047,10 +11078,10 @@
         <v>109.302282978848</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>25</v>
@@ -11062,13 +11093,13 @@
         <v>27</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="L119" s="3">
         <v>2</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N119" s="3">
         <v>2019</v>
@@ -11084,7 +11115,7 @@
         <v>30105233</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="D120" s="5">
         <v>-4.8070926958971798E-2</v>
@@ -11093,7 +11124,7 @@
         <v>109.31564920583099</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>32</v>
@@ -11108,13 +11139,13 @@
         <v>27</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="L120" s="3">
         <v>2</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N120" s="3">
         <v>1985</v>
@@ -11130,7 +11161,7 @@
         <v>30105245</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D121" s="5">
         <v>-4.21698809644361E-2</v>
@@ -11139,7 +11170,7 @@
         <v>109.312686282554</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>32</v>
@@ -11154,13 +11185,13 @@
         <v>27</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="L121" s="3">
         <v>2</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N121" s="3">
         <v>1968</v>
@@ -11176,7 +11207,7 @@
         <v>30105247</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D122" s="5">
         <v>-2.36065944423701E-2</v>
@@ -11185,10 +11216,10 @@
         <v>109.31370172488199</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>25</v>
@@ -11200,13 +11231,13 @@
         <v>27</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="L122" s="3">
         <v>2</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N122" s="3">
         <v>1995</v>
@@ -11222,7 +11253,7 @@
         <v>30105248</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D123" s="5">
         <v>-3.1916467454929598E-2</v>
@@ -11231,7 +11262,7 @@
         <v>109.324334146306</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>32</v>
@@ -11246,13 +11277,13 @@
         <v>27</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="L123" s="3">
         <v>2</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N123" s="3">
         <v>1990</v>
@@ -11268,7 +11299,7 @@
         <v>30105249</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D124" s="5">
         <v>-4.6814189361454497E-2</v>
@@ -11277,7 +11308,7 @@
         <v>109.315129694454</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>32</v>
@@ -11292,13 +11323,13 @@
         <v>27</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="L124" s="3">
         <v>2</v>
       </c>
       <c r="M124" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N124" s="3">
         <v>1993</v>
@@ -11314,7 +11345,7 @@
         <v>30113664</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="D125" s="5">
         <v>-5.7224208068565902E-2</v>
@@ -11323,7 +11354,7 @@
         <v>109.307384546074</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>32</v>
@@ -11344,7 +11375,7 @@
         <v>2</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N125" s="3">
         <v>1998</v>
@@ -11360,7 +11391,7 @@
         <v>30113665</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D126" s="5">
         <v>-5.391089267515E-2</v>
@@ -11369,7 +11400,7 @@
         <v>109.31156703652</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>32</v>
@@ -11384,13 +11415,13 @@
         <v>27</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="L126" s="3">
         <v>2</v>
       </c>
       <c r="M126" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N126" s="3">
         <v>1995</v>
@@ -11406,7 +11437,7 @@
         <v>30113666</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="D127" s="5">
         <v>-4.24298627097928E-2</v>
@@ -11415,10 +11446,10 @@
         <v>109.292530846638</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>25</v>
@@ -11436,7 +11467,7 @@
         <v>2</v>
       </c>
       <c r="M127" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N127" s="3">
         <v>1992</v>
@@ -11452,7 +11483,7 @@
         <v>30113667</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D128" s="5">
         <v>-3.3905855910870898E-2</v>
@@ -11461,10 +11492,10 @@
         <v>109.30586762424601</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>25</v>
@@ -11476,13 +11507,13 @@
         <v>27</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L128" s="3">
         <v>2</v>
       </c>
       <c r="M128" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N128" s="3">
         <v>1996</v>
@@ -11498,7 +11529,7 @@
         <v>30113668</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D129" s="5">
         <v>-4.5001338633899803E-2</v>
@@ -11507,7 +11538,7 @@
         <v>109.310037021176</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>32</v>
@@ -11522,13 +11553,13 @@
         <v>27</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L129" s="3">
         <v>2</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N129" s="3">
         <v>1997</v>
@@ -11544,7 +11575,7 @@
         <v>30113669</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D130" s="5">
         <v>-5.13491168548132E-2</v>
@@ -11553,10 +11584,10 @@
         <v>109.300128508016</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>25</v>
@@ -11568,13 +11599,13 @@
         <v>27</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="L130" s="3">
         <v>2</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N130" s="3">
         <v>1994</v>
@@ -11590,7 +11621,7 @@
         <v>1.09292263053718E+16</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="D131" s="5">
         <v>-3.8270292624759603E-2</v>
@@ -11599,10 +11630,10 @@
         <v>109.292263053718</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>25</v>
@@ -11614,13 +11645,13 @@
         <v>27</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L131" s="3">
         <v>2</v>
       </c>
       <c r="M131" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N131" s="3">
         <v>2008</v>
@@ -11654,71 +11685,71 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="49" t="s">
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="49" t="s">
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="64" t="s">
-        <v>361</v>
-      </c>
-      <c r="R1" s="65"/>
-      <c r="S1" s="57" t="s">
-        <v>362</v>
-      </c>
-      <c r="T1" s="57"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="68" t="s">
+        <v>367</v>
+      </c>
+      <c r="R1" s="69"/>
+      <c r="S1" s="61" t="s">
+        <v>368</v>
+      </c>
+      <c r="T1" s="61"/>
     </row>
     <row r="2" spans="1:20" ht="36">
-      <c r="A2" s="61"/>
-      <c r="B2" s="51" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="60"/>
-      <c r="K2" s="54" t="s">
+      <c r="J2" s="63"/>
+      <c r="K2" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="58"/>
-      <c r="M2" s="60"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="63"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -11728,28 +11759,28 @@
       <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="R2" s="62" t="s">
-        <v>364</v>
-      </c>
-      <c r="S2" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="T2" s="62" t="s">
-        <v>365</v>
+      <c r="Q2" s="66" t="s">
+        <v>369</v>
+      </c>
+      <c r="R2" s="66" t="s">
+        <v>370</v>
+      </c>
+      <c r="S2" s="66" t="s">
+        <v>369</v>
+      </c>
+      <c r="T2" s="66" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="60">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -11770,10 +11801,10 @@
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
     </row>
     <row r="4" spans="1:20" ht="48">
       <c r="A4" s="3">
@@ -11781,7 +11812,7 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D4" s="5">
         <v>-3.7306023283371598E-2</v>
@@ -11790,7 +11821,7 @@
         <v>109.329478725182</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>32</v>
@@ -11805,7 +11836,7 @@
         <v>27</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="L4" s="3">
         <v>8</v>
@@ -11829,7 +11860,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D5" s="5">
         <v>-1.95937331633412E-2</v>
@@ -11853,7 +11884,7 @@
         <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="L5" s="3">
         <v>4</v>
@@ -11877,7 +11908,7 @@
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="19" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D6" s="32">
         <v>-3.9292421453211303E-2</v>
@@ -11901,7 +11932,7 @@
         <v>27</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="L6" s="18">
         <v>2</v>
@@ -11925,7 +11956,7 @@
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="19" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D7" s="32">
         <v>-2.4664565600741799E-2</v>
@@ -11949,7 +11980,7 @@
         <v>27</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="L7" s="18">
         <v>2</v>
@@ -11958,7 +11989,7 @@
         <v>84</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="O7" s="37"/>
       <c r="P7" s="33"/>
@@ -11973,7 +12004,7 @@
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="19" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D8" s="32">
         <v>-2.5131079011639499E-2</v>
@@ -11997,7 +12028,7 @@
         <v>27</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="L8" s="18">
         <v>2</v>
@@ -12006,7 +12037,7 @@
         <v>84</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="O8" s="37"/>
       <c r="P8" s="33"/>
@@ -12021,7 +12052,7 @@
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="19" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D9" s="32">
         <v>-5.09894079828545E-2</v>
@@ -12045,7 +12076,7 @@
         <v>27</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="L9" s="18">
         <v>2</v>
@@ -12068,10 +12099,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D10" s="29">
         <v>-1.3611111111111109E-3</v>
@@ -12080,13 +12111,13 @@
         <v>109.33280555555559</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>26</v>
@@ -12113,36 +12144,36 @@
       <c r="S10" s="18"/>
       <c r="T10" s="18"/>
     </row>
-    <row r="11" spans="1:20" ht="36">
+    <row r="11" spans="1:20" ht="23.25">
       <c r="A11" s="3">
         <v>8</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="D11" s="29">
-        <v>-3.3611111111111112E-2</v>
-      </c>
-      <c r="E11" s="29">
-        <v>109.3094722222222</v>
+        <v>392</v>
+      </c>
+      <c r="D11" s="73">
+        <v>5.6813679067141401E-3</v>
+      </c>
+      <c r="E11" s="73">
+        <v>109.309762921656</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="K11" s="18">
         <v>386.5</v>
@@ -12159,7 +12190,7 @@
       <c r="Q11" s="18"/>
       <c r="R11" s="18"/>
       <c r="S11" s="18" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="T11" s="18"/>
     </row>
@@ -12168,10 +12199,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D12" s="29">
         <v>-1.6083333333333331E-2</v>
@@ -12180,13 +12211,13 @@
         <v>109.3486944444444</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>26</v>
@@ -12218,10 +12249,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D13" s="29">
         <v>-1.4874999999999999E-2</v>
@@ -12230,13 +12261,13 @@
         <v>109.3546083333333</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>26</v>
@@ -12268,10 +12299,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D14" s="29">
         <v>-2.472222222222222E-3</v>
@@ -12280,13 +12311,13 @@
         <v>109.36341666666669</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>26</v>
@@ -12318,10 +12349,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D15" s="29">
         <v>-4.5275000000000003E-2</v>
@@ -12330,13 +12361,13 @@
         <v>109.3667972222222</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>26</v>
@@ -12359,7 +12390,7 @@
       <c r="Q15" s="18"/>
       <c r="R15" s="18"/>
       <c r="S15" s="18" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="T15" s="18"/>
     </row>
@@ -12368,10 +12399,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D16" s="29">
         <v>-5.4226999999999997E-2</v>
@@ -12380,13 +12411,13 @@
         <v>109.372108</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>26</v>
@@ -12409,7 +12440,7 @@
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
       <c r="S16" s="18" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="T16" s="18"/>
     </row>
@@ -12418,10 +12449,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D17" s="29">
         <v>-4.3363888888888889E-2</v>
@@ -12430,19 +12461,19 @@
         <v>109.3606972222222</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="K17" s="18">
         <v>325</v>
@@ -12459,7 +12490,7 @@
       <c r="Q17" s="18"/>
       <c r="R17" s="18"/>
       <c r="S17" s="18" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="T17" s="18"/>
     </row>
@@ -12468,10 +12499,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="D18" s="29">
         <v>-3.6080555555555553E-2</v>
@@ -12480,19 +12511,19 @@
         <v>109.3525305555555</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>26</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="K18" s="18">
         <v>252</v>
@@ -12509,7 +12540,7 @@
       <c r="Q18" s="18"/>
       <c r="R18" s="18"/>
       <c r="S18" s="18" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="T18" s="18"/>
     </row>
@@ -12518,10 +12549,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D19" s="29">
         <v>-2.7588888888888888E-2</v>
@@ -12530,13 +12561,13 @@
         <v>109.35089444444441</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>26</v>
@@ -12559,7 +12590,7 @@
       <c r="Q19" s="18"/>
       <c r="R19" s="18"/>
       <c r="S19" s="18" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="T19" s="18"/>
     </row>
@@ -12568,10 +12599,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D20" s="29">
         <v>-2.6594444444444441E-2</v>
@@ -12580,13 +12611,13 @@
         <v>109.3776361111111</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>26</v>
@@ -12618,10 +12649,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D21" s="29">
         <v>-8.5055555555555561E-3</v>
@@ -12630,10 +12661,10 @@
         <v>109.3120555555556</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>98</v>
@@ -12659,7 +12690,7 @@
       <c r="Q21" s="18"/>
       <c r="R21" s="18"/>
       <c r="S21" s="18" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="T21" s="18"/>
     </row>
@@ -12668,10 +12699,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D22" s="29">
         <v>-6.6555555555555561E-3</v>
@@ -12680,7 +12711,7 @@
         <v>109.3023222222222</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G22" s="18" t="s">
         <v>97</v>
@@ -12692,7 +12723,7 @@
         <v>26</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="K22" s="18">
         <v>312.5</v>
@@ -12709,7 +12740,7 @@
       <c r="Q22" s="18"/>
       <c r="R22" s="18"/>
       <c r="S22" s="18" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="T22" s="18"/>
     </row>
@@ -12718,10 +12749,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D23" s="29">
         <v>-1.3599999999999999E-2</v>
@@ -12730,10 +12761,10 @@
         <v>109.32073333333329</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="H23" s="18" t="s">
         <v>98</v>
@@ -12742,7 +12773,7 @@
         <v>26</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="K23" s="18">
         <v>721.62</v>
@@ -12757,7 +12788,7 @@
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
       <c r="S23" s="18" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="T23" s="18"/>
     </row>
@@ -12766,10 +12797,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D24" s="29">
         <v>-2.3930555555555559E-2</v>
@@ -12778,10 +12809,10 @@
         <v>109.2940722222222</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="H24" s="18" t="s">
         <v>98</v>
@@ -12807,7 +12838,7 @@
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="18" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="T24" s="18"/>
     </row>
@@ -12816,10 +12847,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="D25" s="29">
         <v>-5.3363888888888891E-2</v>
@@ -12828,10 +12859,10 @@
         <v>109.3184055555556</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="H25" s="18" t="s">
         <v>25</v>
@@ -12857,7 +12888,7 @@
       <c r="Q25" s="18"/>
       <c r="R25" s="18"/>
       <c r="S25" s="18" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="T25" s="18"/>
     </row>
@@ -12866,10 +12897,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D26" s="29">
         <v>-1.108333333333333E-2</v>
@@ -12878,10 +12909,10 @@
         <v>109.34288888888889</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="H26" s="18" t="s">
         <v>25</v>
@@ -12890,7 +12921,7 @@
         <v>26</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="K26" s="18">
         <v>315.3</v>
@@ -12900,14 +12931,14 @@
       </c>
       <c r="M26" s="18"/>
       <c r="N26" s="18" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
       <c r="Q26" s="18"/>
       <c r="R26" s="18"/>
       <c r="S26" s="18" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="T26" s="18"/>
     </row>
@@ -12916,10 +12947,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D27" s="29">
         <v>-4.7805555555555559E-2</v>
@@ -12928,10 +12959,10 @@
         <v>109.35799166666671</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>25</v>
@@ -12940,7 +12971,7 @@
         <v>26</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="K27" s="18">
         <v>571</v>
@@ -12955,7 +12986,7 @@
       <c r="Q27" s="18"/>
       <c r="R27" s="18"/>
       <c r="S27" s="18" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="T27" s="18"/>
     </row>
@@ -12964,10 +12995,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="D28" s="29">
         <v>-7.407777777777777E-2</v>
@@ -12976,10 +13007,10 @@
         <v>109.34655833333331</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="H28" s="18" t="s">
         <v>25</v>
@@ -13015,7 +13046,7 @@
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="25" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="D29" s="16">
         <v>-4.15E-3</v>
@@ -13049,7 +13080,7 @@
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="25" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D30" s="16">
         <v>-1.073E-2</v>
@@ -13083,7 +13114,7 @@
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="25" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D31" s="16">
         <v>-3.5799999999999998E-3</v>
@@ -13117,7 +13148,7 @@
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="25" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="D32" s="16">
         <v>-4.1399999999999996E-3</v>
@@ -13151,7 +13182,7 @@
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="25" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D33" s="16">
         <v>-1.265E-2</v>
@@ -13185,7 +13216,7 @@
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="25" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D34" s="16">
         <v>-3.7200000000000002E-3</v>
@@ -13219,7 +13250,7 @@
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="25" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D35" s="16">
         <v>-4.6600000000000001E-3</v>
@@ -13253,7 +13284,7 @@
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="25" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D36" s="16">
         <v>-1.264E-2</v>
@@ -13287,7 +13318,7 @@
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="25" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D37" s="16">
         <v>-4.8199999999999996E-3</v>
@@ -13321,7 +13352,7 @@
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="25" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D38" s="16">
         <v>-3.79E-3</v>
@@ -13355,7 +13386,7 @@
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="25" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="D39" s="16">
         <v>-1.8970000000000001E-2</v>
@@ -13389,7 +13420,7 @@
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="25" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D40" s="16">
         <v>-1.222E-2</v>
@@ -13423,7 +13454,7 @@
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="25" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D41" s="16">
         <v>-3.2799999999999999E-3</v>
@@ -13457,7 +13488,7 @@
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="25" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D42" s="16">
         <v>-5.1000000000000004E-3</v>
@@ -13491,7 +13522,7 @@
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="25" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D43" s="16">
         <v>-9.0200000000000002E-3</v>
@@ -13525,7 +13556,7 @@
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="21" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D44" s="16">
         <v>-6.2700000000000004E-3</v>
@@ -13559,7 +13590,7 @@
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="17" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D45" s="16">
         <v>-5.0000000000000001E-3</v>
@@ -13589,15 +13620,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -13605,9 +13627,18 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13615,67 +13646,67 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D9A1422-081A-4032-9119-87607685BE3D}">
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:R75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="49" t="s">
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="49" t="s">
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="74"/>
-    </row>
-    <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="75"/>
-      <c r="B2" s="51" t="s">
+      <c r="P1" s="75"/>
+    </row>
+    <row r="2" spans="1:18" ht="36">
+      <c r="A2" s="76"/>
+      <c r="B2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="74"/>
-      <c r="K2" s="54" t="s">
+      <c r="J2" s="75"/>
+      <c r="K2" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="73"/>
-      <c r="M2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="75"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -13686,15 +13717,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
+    <row r="3" spans="1:18" ht="60">
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -13716,13 +13747,13 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16" ht="36">
+    <row r="4" spans="1:18" ht="36">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D4" s="5">
         <v>-3.305688317259E-2</v>
@@ -13746,7 +13777,7 @@
         <v>27</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="L4" s="3">
         <v>1</v>
@@ -13759,14 +13790,17 @@
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-    </row>
-    <row r="5" spans="1:16" ht="36">
+      <c r="R4" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="36">
       <c r="A5" s="3">
         <v>2</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="D5" s="5">
         <v>-3.0528901570029E-2</v>
@@ -13790,7 +13824,7 @@
         <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="L5" s="3">
         <v>1</v>
@@ -13804,13 +13838,13 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="24">
+    <row r="6" spans="1:18" ht="24">
       <c r="A6" s="3">
         <v>3</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="D6" s="5">
         <v>-2.6897191063444299E-2</v>
@@ -13834,7 +13868,7 @@
         <v>27</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="L6" s="3">
         <v>1</v>
@@ -13848,19 +13882,19 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="24">
+    <row r="7" spans="1:18" ht="35.25">
       <c r="A7" s="3">
         <v>4</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-3.4997461098407297E-2</v>
-      </c>
-      <c r="E7" s="5">
-        <v>109.31682693316</v>
+        <v>481</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>482</v>
+      </c>
+      <c r="E7" s="50">
+        <v>109.31662559227701</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>23</v>
@@ -13878,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="L7" s="3">
         <v>1</v>
@@ -13892,13 +13926,13 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" ht="24">
+    <row r="8" spans="1:18" ht="24">
       <c r="A8" s="3">
         <v>5</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D8" s="5">
         <v>-2.6451944370815599E-2</v>
@@ -13922,7 +13956,7 @@
         <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="L8" s="3">
         <v>1</v>
@@ -13936,13 +13970,13 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" ht="24">
+    <row r="9" spans="1:18" ht="24">
       <c r="A9" s="3">
         <v>6</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D9" s="5">
         <v>-3.7100312511818501E-2</v>
@@ -13966,7 +14000,7 @@
         <v>27</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="L9" s="3">
         <v>2</v>
@@ -13980,13 +14014,13 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="24">
+    <row r="10" spans="1:18" ht="24">
       <c r="A10" s="3">
         <v>7</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="D10" s="5">
         <v>-3.3023355652657203E-2</v>
@@ -14010,7 +14044,7 @@
         <v>27</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="L10" s="3">
         <v>2</v>
@@ -14024,13 +14058,13 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="24">
+    <row r="11" spans="1:18" ht="24">
       <c r="A11" s="3">
         <v>8</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="D11" s="5">
         <v>-2.93004500107443E-2</v>
@@ -14054,7 +14088,7 @@
         <v>27</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="L11" s="3">
         <v>1</v>
@@ -14068,13 +14102,13 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" ht="24">
+    <row r="12" spans="1:18" ht="24">
       <c r="A12" s="3">
         <v>9</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D12" s="5">
         <v>-2.92521702510385E-2</v>
@@ -14098,7 +14132,7 @@
         <v>27</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="L12" s="3">
         <v>1</v>
@@ -14112,13 +14146,13 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" ht="24">
+    <row r="13" spans="1:18" ht="24">
       <c r="A13" s="3">
         <v>10</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D13" s="5">
         <v>-4.8428432846192603E-2</v>
@@ -14142,7 +14176,7 @@
         <v>27</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="L13" s="3">
         <v>1</v>
@@ -14156,13 +14190,13 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:16" ht="24">
+    <row r="14" spans="1:18" ht="24">
       <c r="A14" s="3">
         <v>11</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D14" s="5">
         <v>-4.2825821525160103E-2</v>
@@ -14186,7 +14220,7 @@
         <v>27</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="L14" s="3">
         <v>1</v>
@@ -14200,13 +14234,13 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16" ht="24">
+    <row r="15" spans="1:18" ht="24">
       <c r="A15" s="3">
         <v>12</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D15" s="5">
         <v>-5.9994818618451698E-2</v>
@@ -14230,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="L15" s="3">
         <v>1</v>
@@ -14244,13 +14278,13 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" ht="36">
+    <row r="16" spans="1:18" ht="36">
       <c r="A16" s="3">
         <v>13</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="4" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="D16" s="5">
         <v>-2.9933451252404E-2</v>
@@ -14274,7 +14308,7 @@
         <v>27</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="L16" s="3">
         <v>1</v>
@@ -14294,7 +14328,7 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="4" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="D17" s="5">
         <v>-3.9020773734214503E-2</v>
@@ -14318,7 +14352,7 @@
         <v>27</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="L17" s="3">
         <v>1</v>
@@ -14338,7 +14372,7 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="D18" s="5">
         <v>-3.8434027376651102E-2</v>
@@ -14362,7 +14396,7 @@
         <v>27</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="L18" s="3">
         <v>1</v>
@@ -14382,7 +14416,7 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="D19" s="5">
         <v>-5.0111153476079098E-2</v>
@@ -14406,7 +14440,7 @@
         <v>27</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="L19" s="3">
         <v>1</v>
@@ -14415,7 +14449,7 @@
         <v>29</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -14426,7 +14460,7 @@
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D20" s="5">
         <v>-4.9407450253117297E-2</v>
@@ -14450,7 +14484,7 @@
         <v>27</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="L20" s="3">
         <v>2</v>
@@ -14459,7 +14493,7 @@
         <v>29</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -14470,7 +14504,7 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D21" s="5">
         <v>-4.6866890051634601E-2</v>
@@ -14494,7 +14528,7 @@
         <v>27</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="L21" s="3">
         <v>1</v>
@@ -14503,7 +14537,7 @@
         <v>29</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -14514,7 +14548,7 @@
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="4" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D22" s="5">
         <v>-4.5386311184041898E-2</v>
@@ -14538,7 +14572,7 @@
         <v>27</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="L22" s="3">
         <v>1</v>
@@ -14547,7 +14581,7 @@
         <v>29</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -14558,7 +14592,7 @@
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="4" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="D23" s="5">
         <v>-4.4334885592930397E-2</v>
@@ -14582,7 +14616,7 @@
         <v>27</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="L23" s="3">
         <v>1</v>
@@ -14591,7 +14625,7 @@
         <v>29</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -14602,7 +14636,7 @@
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D24" s="5">
         <v>-4.3176171658923901E-2</v>
@@ -14626,7 +14660,7 @@
         <v>27</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="L24" s="3">
         <v>1</v>
@@ -14635,7 +14669,7 @@
         <v>29</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -14646,7 +14680,7 @@
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D25" s="5">
         <v>-2.1591782213168102E-2</v>
@@ -14670,7 +14704,7 @@
         <v>27</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="L25" s="3">
         <v>2</v>
@@ -14690,7 +14724,7 @@
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D26" s="5">
         <v>-4.1860253497890798E-2</v>
@@ -14714,7 +14748,7 @@
         <v>27</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="L26" s="3">
         <v>1</v>
@@ -14723,7 +14757,7 @@
         <v>29</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -14734,7 +14768,7 @@
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="4" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D27" s="5">
         <v>-2.9150916876343101E-2</v>
@@ -14758,7 +14792,7 @@
         <v>27</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="L27" s="3">
         <v>1</v>
@@ -14767,7 +14801,7 @@
         <v>29</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -14778,7 +14812,7 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="D28" s="5">
         <v>-2.3198546148105199E-2</v>
@@ -14802,7 +14836,7 @@
         <v>27</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="L28" s="3">
         <v>2</v>
@@ -14822,7 +14856,7 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="4" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="D29" s="5">
         <v>-2.3848118571305501E-2</v>
@@ -14846,7 +14880,7 @@
         <v>27</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="L29" s="3">
         <v>1</v>
@@ -14855,7 +14889,7 @@
         <v>29</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -14866,7 +14900,7 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="4" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D30" s="5">
         <v>-2.6623807183040301E-2</v>
@@ -14890,7 +14924,7 @@
         <v>27</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="L30" s="3">
         <v>1</v>
@@ -14899,7 +14933,7 @@
         <v>29</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -14910,7 +14944,7 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D31" s="5">
         <v>-2.7306108144082498E-2</v>
@@ -14934,7 +14968,7 @@
         <v>27</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="L31" s="3">
         <v>1</v>
@@ -14943,7 +14977,7 @@
         <v>29</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -14954,7 +14988,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="4" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="D32" s="5">
         <v>-2.03463571319339E-2</v>
@@ -14978,7 +15012,7 @@
         <v>27</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="L32" s="3">
         <v>2</v>
@@ -14998,7 +15032,7 @@
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="4" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D33" s="5">
         <v>-2.4389349275525499E-2</v>
@@ -15022,7 +15056,7 @@
         <v>27</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="L33" s="3">
         <v>1</v>
@@ -15042,7 +15076,7 @@
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="4" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D34" s="5">
         <v>-2.4172066931815801E-2</v>
@@ -15066,7 +15100,7 @@
         <v>27</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="L34" s="3">
         <v>2</v>
@@ -15086,7 +15120,7 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="4" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D35" s="5">
         <v>-2.29838484346527E-2</v>
@@ -15110,7 +15144,7 @@
         <v>27</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="L35" s="3">
         <v>1</v>
@@ -15130,7 +15164,7 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="D36" s="5">
         <v>-2.3058528451606899E-2</v>
@@ -15154,7 +15188,7 @@
         <v>27</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="L36" s="3">
         <v>1</v>
@@ -15174,7 +15208,7 @@
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="4" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D37" s="5">
         <v>-2.55534044497241E-2</v>
@@ -15198,7 +15232,7 @@
         <v>27</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="L37" s="3">
         <v>1</v>
@@ -15207,7 +15241,7 @@
         <v>29</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
@@ -15218,7 +15252,7 @@
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="4" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="D38" s="5">
         <v>-2.1931081476664199E-2</v>
@@ -15242,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="L38" s="3">
         <v>1</v>
@@ -15262,7 +15296,7 @@
       </c>
       <c r="B39" s="34"/>
       <c r="C39" s="41" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="D39" s="40">
         <v>-1.92864235795423E-2</v>
@@ -15286,7 +15320,7 @@
         <v>27</v>
       </c>
       <c r="K39" s="34" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="L39" s="34">
         <v>1</v>
@@ -15306,7 +15340,7 @@
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="15" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D40" s="42">
         <v>-6.8599999999999998E-3</v>
@@ -15336,7 +15370,7 @@
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="15" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D41" s="42">
         <v>-3.29E-3</v>
@@ -15366,7 +15400,7 @@
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="15" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="D42" s="42">
         <v>-4.5199999999999997E-3</v>
@@ -15396,7 +15430,7 @@
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="15" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="D43" s="42">
         <v>-1.443E-2</v>
@@ -15426,7 +15460,7 @@
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="15" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="D44" s="42">
         <v>-1.1169999999999999E-2</v>
@@ -15456,7 +15490,7 @@
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="15" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="D45" s="42">
         <v>-5.7000000000000002E-3</v>
@@ -15486,7 +15520,7 @@
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="15" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D46" s="42">
         <v>-2.5500000000000002E-3</v>
@@ -15516,7 +15550,7 @@
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="15" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D47" s="42">
         <v>-4.9699999999999996E-3</v>
@@ -15546,7 +15580,7 @@
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="15" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="D48" s="42">
         <v>-8.7000000000000001E-4</v>
@@ -15576,7 +15610,7 @@
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="15" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D49" s="42">
         <v>-7.9600000000000001E-3</v>
@@ -15606,7 +15640,7 @@
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="15" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="D50" s="42">
         <v>-6.9199999999999999E-3</v>
@@ -15636,7 +15670,7 @@
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="15" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="D51" s="42">
         <v>-8.8800000000000007E-3</v>
@@ -15666,7 +15700,7 @@
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="15" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="D52" s="42">
         <v>-8.2400000000000008E-3</v>
@@ -15696,7 +15730,7 @@
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="15" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D53" s="42">
         <v>-1.278E-2</v>
@@ -15726,7 +15760,7 @@
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="15" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="D54" s="42">
         <v>-9.0699999999999999E-3</v>
@@ -15756,7 +15790,7 @@
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="15" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="D55" s="42">
         <v>-0.41952</v>
@@ -15786,7 +15820,7 @@
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="15" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="D56" s="42">
         <v>-6.77E-3</v>
@@ -15816,7 +15850,7 @@
       </c>
       <c r="B57" s="18"/>
       <c r="C57" s="15" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D57" s="42">
         <v>-9.2099999999999994E-3</v>
@@ -15846,7 +15880,7 @@
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="15" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D58" s="42">
         <v>-4.62E-3</v>
@@ -15876,7 +15910,7 @@
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="15" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D59" s="42">
         <v>-7.9299999999999995E-3</v>
@@ -15906,7 +15940,7 @@
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="15" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="D60" s="42">
         <v>-1.01E-3</v>
@@ -15936,7 +15970,7 @@
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="4" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="D61" s="5">
         <v>-2.7182175694019099E-2</v>
@@ -15960,7 +15994,7 @@
         <v>27</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="L61" s="3">
         <v>2</v>
@@ -15980,7 +16014,7 @@
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="4" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="D62" s="5">
         <v>-2.9823940361993598E-2</v>
@@ -16024,7 +16058,7 @@
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="4" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D63" s="5">
         <v>-3.1931255091528297E-2</v>
@@ -16048,7 +16082,7 @@
         <v>27</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="L63" s="3">
         <v>1</v>
@@ -16068,7 +16102,7 @@
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="4" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="D64" s="5">
         <v>-4.8528322280354898E-2</v>
@@ -16092,7 +16126,7 @@
         <v>27</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="L64" s="3">
         <v>2</v>
@@ -16112,7 +16146,7 @@
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="4" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="D65" s="5">
         <v>-6.1779094808755097E-2</v>
@@ -16136,7 +16170,7 @@
         <v>27</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="L65" s="3">
         <v>2</v>
@@ -16145,7 +16179,7 @@
         <v>84</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
@@ -16156,7 +16190,7 @@
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="4" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D66" s="5">
         <v>-4.8171445719323899E-2</v>
@@ -16180,7 +16214,7 @@
         <v>27</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="L66" s="3">
         <v>1</v>
@@ -16189,7 +16223,7 @@
         <v>84</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
@@ -16200,7 +16234,7 @@
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="4" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="D67" s="5">
         <v>-2.85172450700832E-2</v>
@@ -16224,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="L67" s="3">
         <v>2</v>
@@ -16244,7 +16278,7 @@
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="4" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="D68" s="5">
         <v>-2.4917720963034601E-2</v>
@@ -16268,7 +16302,7 @@
         <v>27</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="L68" s="3">
         <v>1</v>
@@ -16288,7 +16322,7 @@
       </c>
       <c r="B69" s="34"/>
       <c r="C69" s="41" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="D69" s="40">
         <v>-2.1007700520245701E-2</v>
@@ -16312,7 +16346,7 @@
         <v>27</v>
       </c>
       <c r="K69" s="34" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="L69" s="34">
         <v>1</v>
@@ -16332,7 +16366,7 @@
       </c>
       <c r="B70" s="18"/>
       <c r="C70" s="15" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="D70" s="42">
         <v>-5.1900000000000002E-3</v>
@@ -16362,7 +16396,7 @@
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="15" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="D71" s="42">
         <v>-1.1690000000000001E-2</v>
@@ -16392,7 +16426,7 @@
       </c>
       <c r="B72" s="18"/>
       <c r="C72" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D72" s="42">
         <v>-8.8800000000000007E-3</v>
@@ -16422,7 +16456,7 @@
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="D73" s="42">
         <v>-5.3099999999999996E-3</v>
@@ -16452,7 +16486,7 @@
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="4" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="D74" s="5">
         <v>-2.8281828567388999E-2</v>
@@ -16473,10 +16507,10 @@
         <v>26</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="L74" s="3">
         <v>1</v>
@@ -16496,7 +16530,7 @@
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="4" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="D75" s="5">
         <v>-2.3534371787800299E-2</v>
@@ -16561,63 +16595,63 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16" s="12" customFormat="1" ht="12">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="57" t="s">
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="57" t="s">
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="67"/>
+      <c r="P1" s="71"/>
     </row>
     <row r="2" spans="1:16" s="12" customFormat="1" ht="36">
-      <c r="A2" s="67"/>
-      <c r="B2" s="57" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="57" t="s">
+      <c r="J2" s="71"/>
+      <c r="K2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -16629,14 +16663,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" s="12" customFormat="1" ht="60">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -16664,7 +16698,7 @@
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="21" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="D4" s="20">
         <v>-8.5000000000000006E-3</v>
@@ -16694,7 +16728,7 @@
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="21" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="D5" s="20">
         <v>-1.0109999999999999E-2</v>
@@ -16724,7 +16758,7 @@
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="21" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="D6" s="20">
         <v>-8.5699999999999995E-3</v>
@@ -16754,7 +16788,7 @@
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="21" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="D7" s="20">
         <v>-9.1199999999999996E-3</v>
@@ -16784,7 +16818,7 @@
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="21" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="D8" s="20">
         <v>-1.42E-3</v>
@@ -16814,7 +16848,7 @@
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="21" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="D9" s="20">
         <v>-1.6039999999999999E-2</v>
@@ -16844,7 +16878,7 @@
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="19" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="D10" s="20">
         <v>-8.8999999999999995E-4</v>
@@ -16874,7 +16908,7 @@
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="21" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="D11" s="20">
         <v>-2.2100000000000002E-3</v>
@@ -16936,89 +16970,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="31" customFormat="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57" t="s">
-        <v>578</v>
-      </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57" t="s">
+      <c r="B1" s="61" t="s">
+        <v>586</v>
+      </c>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57" t="s">
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
     </row>
     <row r="2" spans="1:18" s="31" customFormat="1" ht="24">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="57" t="s">
-        <v>579</v>
-      </c>
-      <c r="D2" s="57" t="s">
-        <v>580</v>
-      </c>
-      <c r="E2" s="57" t="s">
+      <c r="C2" s="61" t="s">
+        <v>587</v>
+      </c>
+      <c r="D2" s="61" t="s">
+        <v>588</v>
+      </c>
+      <c r="E2" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="57" t="s">
-        <v>581</v>
-      </c>
-      <c r="H2" s="57" t="s">
+      <c r="G2" s="61" t="s">
+        <v>589</v>
+      </c>
+      <c r="H2" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="57" t="s">
+      <c r="J2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57" t="s">
+      <c r="K2" s="61"/>
+      <c r="L2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
       <c r="O2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="57" t="s">
-        <v>582</v>
-      </c>
-      <c r="Q2" s="57" t="s">
-        <v>583</v>
-      </c>
-      <c r="R2" s="57"/>
+      <c r="P2" s="61" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q2" s="61" t="s">
+        <v>591</v>
+      </c>
+      <c r="R2" s="61"/>
     </row>
     <row r="3" spans="1:18" s="31" customFormat="1" ht="36">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
       <c r="J3" s="14" t="s">
         <v>16</v>
       </c>
@@ -17029,20 +17063,20 @@
         <v>18</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>586</v>
-      </c>
-      <c r="P3" s="57"/>
+        <v>594</v>
+      </c>
+      <c r="P3" s="61"/>
       <c r="Q3" s="14" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="36">
@@ -17051,10 +17085,10 @@
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="E4" s="18">
         <v>-2.6519999999999998E-2</v>
@@ -17064,23 +17098,23 @@
       </c>
       <c r="G4" s="18"/>
       <c r="H4" s="22" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="45">
         <v>825</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="O4" s="18">
         <v>2025</v>
@@ -17097,10 +17131,10 @@
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E5" s="18">
         <v>-5.2181999999999999E-2</v>
@@ -17110,23 +17144,23 @@
       </c>
       <c r="G5" s="18"/>
       <c r="H5" s="22" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="K5" s="22" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="45">
         <v>4500</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="O5" s="18">
         <v>2025</v>
@@ -17143,10 +17177,10 @@
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="E6" s="18">
         <v>-5.6816999999999999E-2</v>
@@ -17156,23 +17190,23 @@
       </c>
       <c r="G6" s="18"/>
       <c r="H6" s="22" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="K6" s="22" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="45">
         <v>3800</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="O6" s="18">
         <v>2025</v>
@@ -17189,10 +17223,10 @@
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="E7" s="18">
         <v>-6.4637E-2</v>
@@ -17202,23 +17236,23 @@
       </c>
       <c r="G7" s="18"/>
       <c r="H7" s="22" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="L7" s="22"/>
       <c r="M7" s="45">
         <v>4600</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="O7" s="18">
         <v>2025</v>
@@ -17235,10 +17269,10 @@
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="E8" s="18">
         <v>-7.3205999999999993E-2</v>
@@ -17248,23 +17282,23 @@
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="22" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="L8" s="22"/>
       <c r="M8" s="45">
         <v>6300</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="O8" s="18">
         <v>2025</v>
@@ -17281,10 +17315,10 @@
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="E9" s="18">
         <v>-6.6999000000000003E-2</v>
@@ -17294,23 +17328,23 @@
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="22" t="s">
+        <v>607</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="J9" s="22" t="s">
         <v>599</v>
       </c>
-      <c r="I9" s="22" t="s">
-        <v>594</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>591</v>
-      </c>
       <c r="K9" s="22" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="L9" s="22"/>
       <c r="M9" s="45">
         <v>2100</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="O9" s="18">
         <v>2025</v>
@@ -17327,10 +17361,10 @@
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="E10" s="18">
         <v>-2.4538889000000001E-2</v>
@@ -17340,13 +17374,13 @@
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="22" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>27</v>
@@ -17371,10 +17405,10 @@
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="E11" s="18">
         <v>-5.7777800000000004E-4</v>
@@ -17384,13 +17418,13 @@
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="22" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>27</v>
@@ -17415,10 +17449,10 @@
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="E12" s="18">
         <v>-3.3805556E-2</v>
@@ -17428,13 +17462,13 @@
       </c>
       <c r="G12" s="18"/>
       <c r="H12" s="22" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>27</v>
@@ -17459,10 +17493,10 @@
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="E13" s="18">
         <v>-3.3805556E-2</v>
@@ -17472,13 +17506,13 @@
       </c>
       <c r="G13" s="18"/>
       <c r="H13" s="22" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K13" s="22" t="s">
         <v>27</v>
@@ -17503,10 +17537,10 @@
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="E14" s="18">
         <v>-3.8888900000000001E-4</v>
@@ -17516,13 +17550,13 @@
       </c>
       <c r="G14" s="18"/>
       <c r="H14" s="22" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>27</v>
@@ -17547,10 +17581,10 @@
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="E15" s="18">
         <v>-3.3805556E-2</v>
@@ -17560,13 +17594,13 @@
       </c>
       <c r="G15" s="18"/>
       <c r="H15" s="22" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K15" s="22" t="s">
         <v>27</v>
@@ -17591,10 +17625,10 @@
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="E16" s="18">
         <v>-3.5644443999999997E-2</v>
@@ -17604,13 +17638,13 @@
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="22" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>27</v>
@@ -17635,10 +17669,10 @@
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="E17" s="18">
         <v>-3.1629999999999998E-2</v>
@@ -17648,13 +17682,13 @@
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="22" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K17" s="22" t="s">
         <v>27</v>
@@ -17679,10 +17713,10 @@
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="E18" s="18">
         <v>-6.3280000000000003E-2</v>
@@ -17692,13 +17726,13 @@
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="22" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>27</v>
@@ -17723,10 +17757,10 @@
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="E19" s="18">
         <v>-2.9803E-2</v>
@@ -17736,13 +17770,13 @@
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="22" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K19" s="22" t="s">
         <v>27</v>
@@ -17767,10 +17801,10 @@
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="E20" s="18">
         <v>-1.1709999999999999E-3</v>
@@ -17780,13 +17814,13 @@
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="22" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>98</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K20" s="22" t="s">
         <v>27</v>
@@ -17811,10 +17845,10 @@
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="E21" s="18">
         <v>5.3839999999999999E-3</v>
@@ -17830,7 +17864,7 @@
         <v>98</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K21" s="22" t="s">
         <v>27</v>
@@ -17855,10 +17889,10 @@
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="E22" s="18">
         <v>-2.9825000000000001E-2</v>
@@ -17868,13 +17902,13 @@
       </c>
       <c r="G22" s="30"/>
       <c r="H22" s="22" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I22" s="22" t="s">
         <v>98</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="K22" s="22" t="s">
         <v>27</v>
@@ -17928,63 +17962,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="57" t="s">
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="57" t="s">
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="67"/>
+      <c r="P1" s="71"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="67"/>
-      <c r="B2" s="57" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="57" t="s">
+      <c r="J2" s="71"/>
+      <c r="K2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -17996,14 +18030,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -18031,7 +18065,7 @@
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="D4" s="47">
         <v>-5.3099999999999996E-3</v>
@@ -18063,7 +18097,7 @@
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="D5" s="47">
         <v>-3.29E-3</v>
@@ -18095,7 +18129,7 @@
       </c>
       <c r="B6" s="25"/>
       <c r="C6" s="25" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="D6" s="47">
         <v>-6.4999999999999997E-3</v>
@@ -18127,7 +18161,7 @@
       </c>
       <c r="B7" s="25"/>
       <c r="C7" s="25" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="D7" s="47">
         <v>-1.0200000000000001E-2</v>
@@ -18159,7 +18193,7 @@
       </c>
       <c r="B8" s="25"/>
       <c r="C8" s="25" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="D8" s="47">
         <v>-8.5900000000000004E-3</v>
@@ -18191,7 +18225,7 @@
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="25" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D9" s="47">
         <v>-6.2599999999999999E-3</v>
@@ -18223,7 +18257,7 @@
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="25" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="D10" s="47">
         <v>-6.5300000000000002E-3</v>
@@ -18255,7 +18289,7 @@
       </c>
       <c r="B11" s="25"/>
       <c r="C11" s="25" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="D11" s="47">
         <v>-3.63E-3</v>
@@ -18287,7 +18321,7 @@
       </c>
       <c r="B12" s="25"/>
       <c r="C12" s="25" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="D12" s="47">
         <v>-3.7399999999999998E-3</v>
@@ -18334,15 +18368,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
@@ -18353,7 +18378,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumen" ma:contentTypeID="0x010100CCD785251A4E724B934A12AB8BE46060" ma:contentTypeVersion="12" ma:contentTypeDescription="Buat sebuah dokumen baru." ma:contentTypeScope="" ma:versionID="5ae3aba09e4cbefebb89020ec97f4692">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15954fb3-4959-4f5b-ae14-d7aa01180869" xmlns:ns3="4ce1a36b-806a-4732-b893-33b689d3fa0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f158cec65280218b3e83bd78c7c2c412" ns2:_="" ns3:_="">
     <xsd:import namespace="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
@@ -18554,14 +18579,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}"/>
 </file>
--- a/data/processed/eksposur_pontianak_0408.xlsx
+++ b/data/processed/eksposur_pontianak_0408.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F834E40-FC43-4EEF-BF7D-FF1DE50F47A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA8C7B6D-6EBA-4ED3-999B-E481BC1005D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="4" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="7" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
   </bookViews>
   <sheets>
     <sheet name="Government" sheetId="4" r:id="rId1"/>
@@ -162,7 +162,7 @@
     <t>Kantor Dinas Perhubungan Kota Pontianak</t>
   </si>
   <si>
-    <t>769,5 m²</t>
+    <t>769.5 m²</t>
   </si>
   <si>
     <t>± 2000</t>
@@ -2700,7 +2700,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2850,16 +2850,20 @@
     <xf numFmtId="165" fontId="20" fillId="35" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2868,25 +2872,31 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2904,13 +2914,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3303,63 +3306,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="54" t="s">
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="54" t="s">
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="60"/>
+      <c r="P1" s="63"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="57"/>
-      <c r="B2" s="53" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="60"/>
-      <c r="K2" s="56" t="s">
+      <c r="J2" s="63"/>
+      <c r="K2" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="59"/>
-      <c r="M2" s="60"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="63"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -3371,14 +3374,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="58"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -3532,7 +3535,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="60">
+    <row r="7" spans="1:16" ht="58.5">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -3561,7 +3564,7 @@
       <c r="J7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="54" t="s">
         <v>39</v>
       </c>
       <c r="L7" s="11">
@@ -5301,82 +5304,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61" t="s">
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="61"/>
+      <c r="P1" s="55"/>
     </row>
     <row r="2" spans="1:16" ht="24">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61" t="s">
+      <c r="A2" s="55"/>
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="61" t="s">
+      <c r="H2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61" t="s">
+      <c r="J2" s="55"/>
+      <c r="K2" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="61" t="s">
+      <c r="P2" s="55" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="61"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -5395,8 +5398,8 @@
       <c r="N3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="61"/>
-      <c r="P3" s="61"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55"/>
     </row>
     <row r="4" spans="1:16" ht="36">
       <c r="A4" s="18">
@@ -5676,63 +5679,63 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="54" t="s">
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="54" t="s">
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="75"/>
+      <c r="P1" s="76"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="76"/>
-      <c r="B2" s="53" t="s">
+      <c r="A2" s="77"/>
+      <c r="B2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="75"/>
-      <c r="K2" s="56" t="s">
+      <c r="J2" s="76"/>
+      <c r="K2" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="74"/>
-      <c r="M2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="76"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -5744,14 +5747,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="77"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -11685,71 +11688,71 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="54" t="s">
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="54" t="s">
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="68" t="s">
+      <c r="P1" s="68"/>
+      <c r="Q1" s="72" t="s">
         <v>367</v>
       </c>
-      <c r="R1" s="69"/>
-      <c r="S1" s="61" t="s">
+      <c r="R1" s="73"/>
+      <c r="S1" s="55" t="s">
         <v>368</v>
       </c>
-      <c r="T1" s="61"/>
+      <c r="T1" s="55"/>
     </row>
     <row r="2" spans="1:20" ht="36">
-      <c r="A2" s="65"/>
-      <c r="B2" s="53" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="63"/>
-      <c r="K2" s="56" t="s">
+      <c r="J2" s="69"/>
+      <c r="K2" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="64"/>
-      <c r="M2" s="63"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="69"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -11759,28 +11762,28 @@
       <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="66" t="s">
+      <c r="Q2" s="70" t="s">
         <v>369</v>
       </c>
-      <c r="R2" s="66" t="s">
+      <c r="R2" s="70" t="s">
         <v>370</v>
       </c>
-      <c r="S2" s="66" t="s">
+      <c r="S2" s="70" t="s">
         <v>369</v>
       </c>
-      <c r="T2" s="66" t="s">
+      <c r="T2" s="70" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="60">
-      <c r="A3" s="62"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -11801,10 +11804,10 @@
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
     </row>
     <row r="4" spans="1:20" ht="48">
       <c r="A4" s="3">
@@ -12154,10 +12157,10 @@
       <c r="C11" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="53">
         <v>5.6813679067141401E-3</v>
       </c>
-      <c r="E11" s="73">
+      <c r="E11" s="53">
         <v>109.309762921656</v>
       </c>
       <c r="F11" s="18" t="s">
@@ -13620,6 +13623,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -13627,18 +13642,6 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13650,63 +13653,63 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="54" t="s">
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="54" t="s">
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="75"/>
+      <c r="P1" s="76"/>
     </row>
     <row r="2" spans="1:18" ht="36">
-      <c r="A2" s="76"/>
-      <c r="B2" s="53" t="s">
+      <c r="A2" s="77"/>
+      <c r="B2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="75"/>
-      <c r="K2" s="56" t="s">
+      <c r="J2" s="76"/>
+      <c r="K2" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="74"/>
-      <c r="M2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="76"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -13718,14 +13721,14 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="60">
-      <c r="A3" s="77"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -16595,63 +16598,63 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16" s="12" customFormat="1" ht="12">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="61" t="s">
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="61" t="s">
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="71"/>
+      <c r="P1" s="56"/>
     </row>
     <row r="2" spans="1:16" s="12" customFormat="1" ht="36">
-      <c r="A2" s="71"/>
-      <c r="B2" s="61" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="61" t="s">
+      <c r="H2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="71"/>
-      <c r="K2" s="61" t="s">
+      <c r="J2" s="56"/>
+      <c r="K2" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -16663,14 +16666,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" s="12" customFormat="1" ht="60">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -16970,89 +16973,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="31" customFormat="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="55" t="s">
         <v>586</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61" t="s">
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
     </row>
     <row r="2" spans="1:18" s="31" customFormat="1" ht="24">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61" t="s">
+      <c r="A2" s="55"/>
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="55" t="s">
         <v>587</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="55" t="s">
         <v>588</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="55" t="s">
         <v>589</v>
       </c>
-      <c r="H2" s="61" t="s">
+      <c r="H2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="61" t="s">
+      <c r="J2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61" t="s">
+      <c r="K2" s="55"/>
+      <c r="L2" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
       <c r="O2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="61" t="s">
+      <c r="P2" s="55" t="s">
         <v>590</v>
       </c>
-      <c r="Q2" s="61" t="s">
+      <c r="Q2" s="55" t="s">
         <v>591</v>
       </c>
-      <c r="R2" s="61"/>
+      <c r="R2" s="55"/>
     </row>
     <row r="3" spans="1:18" s="31" customFormat="1" ht="36">
-      <c r="A3" s="61"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
       <c r="J3" s="14" t="s">
         <v>16</v>
       </c>
@@ -17071,7 +17074,7 @@
       <c r="O3" s="14" t="s">
         <v>594</v>
       </c>
-      <c r="P3" s="61"/>
+      <c r="P3" s="55"/>
       <c r="Q3" s="14" t="s">
         <v>595</v>
       </c>
@@ -17962,63 +17965,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="61" t="s">
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="61" t="s">
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="71"/>
+      <c r="P1" s="56"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="71"/>
-      <c r="B2" s="61" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="61" t="s">
+      <c r="H2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="71"/>
-      <c r="K2" s="61" t="s">
+      <c r="J2" s="56"/>
+      <c r="K2" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -18030,14 +18033,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -18368,6 +18371,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
@@ -18378,7 +18390,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumen" ma:contentTypeID="0x010100CCD785251A4E724B934A12AB8BE46060" ma:contentTypeVersion="12" ma:contentTypeDescription="Buat sebuah dokumen baru." ma:contentTypeScope="" ma:versionID="5ae3aba09e4cbefebb89020ec97f4692">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15954fb3-4959-4f5b-ae14-d7aa01180869" xmlns:ns3="4ce1a36b-806a-4732-b893-33b689d3fa0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f158cec65280218b3e83bd78c7c2c412" ns2:_="" ns3:_="">
     <xsd:import namespace="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
@@ -18579,23 +18591,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}"/>
 </file>
--- a/data/processed/eksposur_pontianak_0408.xlsx
+++ b/data/processed/eksposur_pontianak_0408.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA8C7B6D-6EBA-4ED3-999B-E481BC1005D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18FA25E0-8701-4213-A513-54835E2366D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="7" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
   </bookViews>
   <sheets>
     <sheet name="Government" sheetId="4" r:id="rId1"/>
@@ -162,7 +162,7 @@
     <t>Kantor Dinas Perhubungan Kota Pontianak</t>
   </si>
   <si>
-    <t>769.5 m²</t>
+    <t>769,5 m²</t>
   </si>
   <si>
     <t>± 2000</t>
@@ -2851,9 +2851,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2912,6 +2909,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3306,63 +3306,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="61" t="s">
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="61" t="s">
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="63"/>
+      <c r="P1" s="62"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="59"/>
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="58"/>
+      <c r="B2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="G2" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="63"/>
-      <c r="K2" s="65" t="s">
+      <c r="J2" s="62"/>
+      <c r="K2" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="62"/>
-      <c r="M2" s="63"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="62"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -3374,14 +3374,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -3564,7 +3564,7 @@
       <c r="J7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="54" t="s">
+      <c r="K7" s="74" t="s">
         <v>39</v>
       </c>
       <c r="L7" s="11">
@@ -5304,82 +5304,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55" t="s">
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55" t="s">
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="55"/>
+      <c r="P1" s="54"/>
     </row>
     <row r="2" spans="1:16" ht="24">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55" t="s">
+      <c r="A2" s="54"/>
+      <c r="B2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="H2" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="55" t="s">
+      <c r="I2" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55" t="s">
+      <c r="J2" s="54"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="55" t="s">
+      <c r="O2" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="55" t="s">
+      <c r="P2" s="54" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="55"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -5398,8 +5398,8 @@
       <c r="N3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
     </row>
     <row r="4" spans="1:16" ht="36">
       <c r="A4" s="18">
@@ -5679,10 +5679,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="60" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="75"/>
@@ -5691,7 +5691,7 @@
       <c r="F1" s="75"/>
       <c r="G1" s="75"/>
       <c r="H1" s="76"/>
-      <c r="I1" s="61" t="s">
+      <c r="I1" s="60" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="75"/>
@@ -5699,39 +5699,39 @@
       <c r="L1" s="75"/>
       <c r="M1" s="75"/>
       <c r="N1" s="76"/>
-      <c r="O1" s="61" t="s">
+      <c r="O1" s="60" t="s">
         <v>3</v>
       </c>
       <c r="P1" s="76"/>
     </row>
     <row r="2" spans="1:16" ht="36">
       <c r="A2" s="77"/>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="G2" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="60" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="76"/>
-      <c r="K2" s="65" t="s">
+      <c r="K2" s="64" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="75"/>
@@ -11688,71 +11688,71 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="61" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="61" t="s">
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="72" t="s">
+      <c r="P1" s="67"/>
+      <c r="Q1" s="71" t="s">
         <v>367</v>
       </c>
-      <c r="R1" s="73"/>
-      <c r="S1" s="55" t="s">
+      <c r="R1" s="72"/>
+      <c r="S1" s="54" t="s">
         <v>368</v>
       </c>
-      <c r="T1" s="55"/>
+      <c r="T1" s="54"/>
     </row>
     <row r="2" spans="1:20" ht="36">
-      <c r="A2" s="66"/>
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="G2" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="69"/>
-      <c r="K2" s="65" t="s">
+      <c r="J2" s="68"/>
+      <c r="K2" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="69"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="68"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -11762,28 +11762,28 @@
       <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="70" t="s">
+      <c r="Q2" s="69" t="s">
         <v>369</v>
       </c>
-      <c r="R2" s="70" t="s">
+      <c r="R2" s="69" t="s">
         <v>370</v>
       </c>
-      <c r="S2" s="70" t="s">
+      <c r="S2" s="69" t="s">
         <v>369</v>
       </c>
-      <c r="T2" s="70" t="s">
+      <c r="T2" s="69" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="60">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -11804,10 +11804,10 @@
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="70"/>
+      <c r="S3" s="70"/>
+      <c r="T3" s="70"/>
     </row>
     <row r="4" spans="1:20" ht="48">
       <c r="A4" s="3">
@@ -13653,10 +13653,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="60" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="75"/>
@@ -13665,7 +13665,7 @@
       <c r="F1" s="75"/>
       <c r="G1" s="75"/>
       <c r="H1" s="76"/>
-      <c r="I1" s="61" t="s">
+      <c r="I1" s="60" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="75"/>
@@ -13673,39 +13673,39 @@
       <c r="L1" s="75"/>
       <c r="M1" s="75"/>
       <c r="N1" s="76"/>
-      <c r="O1" s="61" t="s">
+      <c r="O1" s="60" t="s">
         <v>3</v>
       </c>
       <c r="P1" s="76"/>
     </row>
     <row r="2" spans="1:18" ht="36">
       <c r="A2" s="77"/>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="G2" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="60" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="76"/>
-      <c r="K2" s="65" t="s">
+      <c r="K2" s="64" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="75"/>
@@ -16598,63 +16598,63 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16" s="12" customFormat="1" ht="12">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="55" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="55" t="s">
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="56"/>
+      <c r="P1" s="55"/>
     </row>
     <row r="2" spans="1:16" s="12" customFormat="1" ht="36">
-      <c r="A2" s="56"/>
-      <c r="B2" s="55" t="s">
+      <c r="A2" s="55"/>
+      <c r="B2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="H2" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="55" t="s">
+      <c r="I2" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="56"/>
-      <c r="K2" s="55" t="s">
+      <c r="J2" s="55"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -16666,14 +16666,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" s="12" customFormat="1" ht="60">
-      <c r="A3" s="56"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -16973,89 +16973,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="31" customFormat="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="54" t="s">
         <v>586</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55" t="s">
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55" t="s">
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
     </row>
     <row r="2" spans="1:18" s="31" customFormat="1" ht="24">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55" t="s">
+      <c r="A2" s="54"/>
+      <c r="B2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="54" t="s">
         <v>587</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="54" t="s">
         <v>588</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="54" t="s">
         <v>589</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="H2" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="55" t="s">
+      <c r="I2" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="55" t="s">
+      <c r="J2" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55" t="s">
+      <c r="K2" s="54"/>
+      <c r="L2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
       <c r="O2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="55" t="s">
+      <c r="P2" s="54" t="s">
         <v>590</v>
       </c>
-      <c r="Q2" s="55" t="s">
+      <c r="Q2" s="54" t="s">
         <v>591</v>
       </c>
-      <c r="R2" s="55"/>
+      <c r="R2" s="54"/>
     </row>
     <row r="3" spans="1:18" s="31" customFormat="1" ht="36">
-      <c r="A3" s="55"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
       <c r="J3" s="14" t="s">
         <v>16</v>
       </c>
@@ -17074,7 +17074,7 @@
       <c r="O3" s="14" t="s">
         <v>594</v>
       </c>
-      <c r="P3" s="55"/>
+      <c r="P3" s="54"/>
       <c r="Q3" s="14" t="s">
         <v>595</v>
       </c>
@@ -17965,63 +17965,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="55" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="55" t="s">
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="56"/>
+      <c r="P1" s="55"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="56"/>
-      <c r="B2" s="55" t="s">
+      <c r="A2" s="55"/>
+      <c r="B2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="H2" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="55" t="s">
+      <c r="I2" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="56"/>
-      <c r="K2" s="55" t="s">
+      <c r="J2" s="55"/>
+      <c r="K2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -18033,14 +18033,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="56"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>

--- a/data/processed/eksposur_pontianak_0408.xlsx
+++ b/data/processed/eksposur_pontianak_0408.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30023"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18FA25E0-8701-4213-A513-54835E2366D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D7D4D55-E41A-41EA-ADC5-E01DD4F2198D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{951F7EB8-411B-420E-A880-B7680C0F6660}"/>
   </bookViews>
   <sheets>
     <sheet name="Government" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="630">
   <si>
     <t>No</t>
   </si>
@@ -1810,9 +1810,6 @@
   </si>
   <si>
     <t>Dinas Terkait</t>
-  </si>
-  <si>
-    <t>Alamat/Nama Lokasi</t>
   </si>
   <si>
     <t xml:space="preserve">Elevasi Tanah </t>
@@ -2851,13 +2848,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2884,16 +2875,19 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2911,7 +2905,10 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3306,63 +3303,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="60" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="60" t="s">
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="62"/>
+      <c r="P1" s="60"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="58"/>
-      <c r="B2" s="57" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="E2" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="62"/>
-      <c r="K2" s="64" t="s">
+      <c r="J2" s="60"/>
+      <c r="K2" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="61"/>
-      <c r="M2" s="62"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="60"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -3374,14 +3371,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -3564,7 +3561,7 @@
       <c r="J7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="74" t="s">
+      <c r="K7" s="54" t="s">
         <v>39</v>
       </c>
       <c r="L7" s="11">
@@ -5304,82 +5301,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54" t="s">
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54" t="s">
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="54"/>
+      <c r="P1" s="63"/>
     </row>
     <row r="2" spans="1:16" ht="24">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54" t="s">
+      <c r="J2" s="63"/>
+      <c r="K2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="54" t="s">
+      <c r="O2" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="54" t="s">
+      <c r="P2" s="63" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -5398,8 +5395,8 @@
       <c r="N3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
     </row>
     <row r="4" spans="1:16" ht="36">
       <c r="A4" s="18">
@@ -5679,10 +5676,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="58" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="75"/>
@@ -5691,7 +5688,7 @@
       <c r="F1" s="75"/>
       <c r="G1" s="75"/>
       <c r="H1" s="76"/>
-      <c r="I1" s="60" t="s">
+      <c r="I1" s="58" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="75"/>
@@ -5699,39 +5696,39 @@
       <c r="L1" s="75"/>
       <c r="M1" s="75"/>
       <c r="N1" s="76"/>
-      <c r="O1" s="60" t="s">
+      <c r="O1" s="58" t="s">
         <v>3</v>
       </c>
       <c r="P1" s="76"/>
     </row>
     <row r="2" spans="1:16" ht="36">
       <c r="A2" s="77"/>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="E2" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="58" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="76"/>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="62" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="75"/>
@@ -11688,71 +11685,71 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="60" t="s">
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="60" t="s">
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="71" t="s">
+      <c r="P1" s="66"/>
+      <c r="Q1" s="70" t="s">
         <v>367</v>
       </c>
-      <c r="R1" s="72"/>
-      <c r="S1" s="54" t="s">
+      <c r="R1" s="71"/>
+      <c r="S1" s="63" t="s">
         <v>368</v>
       </c>
-      <c r="T1" s="54"/>
+      <c r="T1" s="63"/>
     </row>
     <row r="2" spans="1:20" ht="36">
-      <c r="A2" s="65"/>
-      <c r="B2" s="57" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="E2" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="68"/>
-      <c r="K2" s="64" t="s">
+      <c r="J2" s="65"/>
+      <c r="K2" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="68"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="65"/>
       <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
@@ -11762,28 +11759,28 @@
       <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="69" t="s">
+      <c r="Q2" s="68" t="s">
         <v>369</v>
       </c>
-      <c r="R2" s="69" t="s">
+      <c r="R2" s="68" t="s">
         <v>370</v>
       </c>
-      <c r="S2" s="69" t="s">
+      <c r="S2" s="68" t="s">
         <v>369</v>
       </c>
-      <c r="T2" s="69" t="s">
+      <c r="T2" s="68" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="60">
-      <c r="A3" s="66"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
       <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
@@ -11804,10 +11801,10 @@
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="70"/>
-      <c r="S3" s="70"/>
-      <c r="T3" s="70"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="69"/>
     </row>
     <row r="4" spans="1:20" ht="48">
       <c r="A4" s="3">
@@ -13623,18 +13620,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -13642,6 +13627,18 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13653,10 +13650,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="58" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="75"/>
@@ -13665,7 +13662,7 @@
       <c r="F1" s="75"/>
       <c r="G1" s="75"/>
       <c r="H1" s="76"/>
-      <c r="I1" s="60" t="s">
+      <c r="I1" s="58" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="75"/>
@@ -13673,39 +13670,39 @@
       <c r="L1" s="75"/>
       <c r="M1" s="75"/>
       <c r="N1" s="76"/>
-      <c r="O1" s="60" t="s">
+      <c r="O1" s="58" t="s">
         <v>3</v>
       </c>
       <c r="P1" s="76"/>
     </row>
     <row r="2" spans="1:18" ht="36">
       <c r="A2" s="77"/>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="E2" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="58" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="76"/>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="62" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="75"/>
@@ -16598,63 +16595,63 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16" s="12" customFormat="1" ht="12">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="54" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="54" t="s">
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="55"/>
+      <c r="P1" s="73"/>
     </row>
     <row r="2" spans="1:16" s="12" customFormat="1" ht="36">
-      <c r="A2" s="55"/>
-      <c r="B2" s="54" t="s">
+      <c r="A2" s="73"/>
+      <c r="B2" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="55"/>
-      <c r="K2" s="54" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -16666,14 +16663,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" s="12" customFormat="1" ht="60">
-      <c r="A3" s="55"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
+      <c r="A3" s="73"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -16973,89 +16970,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="31" customFormat="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="63" t="s">
         <v>586</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54" t="s">
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54" t="s">
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-    </row>
-    <row r="2" spans="1:18" s="31" customFormat="1" ht="24">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54" t="s">
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+    </row>
+    <row r="2" spans="1:18" s="31" customFormat="1" ht="23.25">
+      <c r="A2" s="63"/>
+      <c r="B2" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="63" t="s">
         <v>587</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="63" t="s">
         <v>588</v>
       </c>
-      <c r="E2" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="54" t="s">
-        <v>589</v>
-      </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="54" t="s">
+      <c r="J2" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54" t="s">
+      <c r="K2" s="63"/>
+      <c r="L2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
       <c r="O2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="54" t="s">
+      <c r="P2" s="63" t="s">
+        <v>589</v>
+      </c>
+      <c r="Q2" s="63" t="s">
         <v>590</v>
       </c>
-      <c r="Q2" s="54" t="s">
-        <v>591</v>
-      </c>
-      <c r="R2" s="54"/>
+      <c r="R2" s="63"/>
     </row>
     <row r="3" spans="1:18" s="31" customFormat="1" ht="36">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
       <c r="J3" s="14" t="s">
         <v>16</v>
       </c>
@@ -17066,20 +17063,20 @@
         <v>18</v>
       </c>
       <c r="M3" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="N3" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="O3" s="14" t="s">
         <v>593</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="P3" s="63"/>
+      <c r="Q3" s="14" t="s">
         <v>594</v>
       </c>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="14" t="s">
+      <c r="R3" s="14" t="s">
         <v>595</v>
-      </c>
-      <c r="R3" s="14" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="36">
@@ -17088,10 +17085,10 @@
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22" t="s">
+        <v>596</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>597</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>598</v>
       </c>
       <c r="E4" s="18">
         <v>-2.6519999999999998E-2</v>
@@ -17107,17 +17104,17 @@
         <v>25</v>
       </c>
       <c r="J4" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="K4" s="22" t="s">
         <v>599</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>600</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="45">
         <v>825</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O4" s="18">
         <v>2025</v>
@@ -17134,7 +17131,7 @@
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>448</v>
@@ -17150,20 +17147,20 @@
         <v>448</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J5" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="K5" s="22" t="s">
         <v>599</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>600</v>
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="45">
         <v>4500</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O5" s="18">
         <v>2025</v>
@@ -17180,10 +17177,10 @@
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E6" s="18">
         <v>-5.6816999999999999E-2</v>
@@ -17196,20 +17193,20 @@
         <v>453</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J6" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="K6" s="22" t="s">
         <v>599</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>600</v>
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="45">
         <v>3800</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O6" s="18">
         <v>2025</v>
@@ -17226,10 +17223,10 @@
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E7" s="18">
         <v>-6.4637E-2</v>
@@ -17242,20 +17239,20 @@
         <v>457</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J7" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="K7" s="22" t="s">
         <v>599</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>600</v>
       </c>
       <c r="L7" s="22"/>
       <c r="M7" s="45">
         <v>4600</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O7" s="18">
         <v>2025</v>
@@ -17272,10 +17269,10 @@
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E8" s="18">
         <v>-7.3205999999999993E-2</v>
@@ -17285,23 +17282,23 @@
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="22" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J8" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="K8" s="22" t="s">
         <v>599</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>600</v>
       </c>
       <c r="L8" s="22"/>
       <c r="M8" s="45">
         <v>6300</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O8" s="18">
         <v>2025</v>
@@ -17318,10 +17315,10 @@
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E9" s="18">
         <v>-6.6999000000000003E-2</v>
@@ -17331,23 +17328,23 @@
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="22" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J9" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="K9" s="22" t="s">
         <v>599</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>600</v>
       </c>
       <c r="L9" s="22"/>
       <c r="M9" s="45">
         <v>2100</v>
       </c>
       <c r="N9" s="32" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O9" s="18">
         <v>2025</v>
@@ -17364,10 +17361,10 @@
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E10" s="18">
         <v>-2.4538889000000001E-2</v>
@@ -17377,13 +17374,13 @@
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="J10" s="22" t="s">
         <v>609</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>602</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>610</v>
       </c>
       <c r="K10" s="22" t="s">
         <v>27</v>
@@ -17408,10 +17405,10 @@
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E11" s="18">
         <v>-5.7777800000000004E-4</v>
@@ -17421,13 +17418,13 @@
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="J11" s="22" t="s">
         <v>609</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>602</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>610</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>27</v>
@@ -17452,10 +17449,10 @@
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E12" s="18">
         <v>-3.3805556E-2</v>
@@ -17471,7 +17468,7 @@
         <v>390</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K12" s="22" t="s">
         <v>27</v>
@@ -17496,10 +17493,10 @@
       </c>
       <c r="B13" s="22"/>
       <c r="C13" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E13" s="18">
         <v>-3.3805556E-2</v>
@@ -17509,13 +17506,13 @@
       </c>
       <c r="G13" s="18"/>
       <c r="H13" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="J13" s="22" t="s">
         <v>609</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>602</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>610</v>
       </c>
       <c r="K13" s="22" t="s">
         <v>27</v>
@@ -17540,10 +17537,10 @@
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E14" s="18">
         <v>-3.8888900000000001E-4</v>
@@ -17553,13 +17550,13 @@
       </c>
       <c r="G14" s="18"/>
       <c r="H14" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="J14" s="22" t="s">
         <v>609</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>602</v>
-      </c>
-      <c r="J14" s="22" t="s">
-        <v>610</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>27</v>
@@ -17584,10 +17581,10 @@
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E15" s="18">
         <v>-3.3805556E-2</v>
@@ -17603,7 +17600,7 @@
         <v>390</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K15" s="22" t="s">
         <v>27</v>
@@ -17628,10 +17625,10 @@
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E16" s="18">
         <v>-3.5644443999999997E-2</v>
@@ -17641,13 +17638,13 @@
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="J16" s="22" t="s">
         <v>609</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>602</v>
-      </c>
-      <c r="J16" s="22" t="s">
-        <v>610</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>27</v>
@@ -17672,10 +17669,10 @@
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E17" s="18">
         <v>-3.1629999999999998E-2</v>
@@ -17685,13 +17682,13 @@
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="J17" s="22" t="s">
         <v>609</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>602</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>610</v>
       </c>
       <c r="K17" s="22" t="s">
         <v>27</v>
@@ -17716,10 +17713,10 @@
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E18" s="18">
         <v>-6.3280000000000003E-2</v>
@@ -17732,10 +17729,10 @@
         <v>448</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>27</v>
@@ -17760,10 +17757,10 @@
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E19" s="18">
         <v>-2.9803E-2</v>
@@ -17776,10 +17773,10 @@
         <v>457</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K19" s="22" t="s">
         <v>27</v>
@@ -17804,10 +17801,10 @@
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E20" s="18">
         <v>-1.1709999999999999E-3</v>
@@ -17817,13 +17814,13 @@
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>98</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K20" s="22" t="s">
         <v>27</v>
@@ -17848,10 +17845,10 @@
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E21" s="18">
         <v>5.3839999999999999E-3</v>
@@ -17867,7 +17864,7 @@
         <v>98</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K21" s="22" t="s">
         <v>27</v>
@@ -17892,10 +17889,10 @@
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E22" s="18">
         <v>-2.9825000000000001E-2</v>
@@ -17911,7 +17908,7 @@
         <v>98</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K22" s="22" t="s">
         <v>27</v>
@@ -17965,63 +17962,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="54" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="54" t="s">
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="55"/>
+      <c r="P1" s="73"/>
     </row>
     <row r="2" spans="1:16" ht="36">
-      <c r="A2" s="55"/>
-      <c r="B2" s="54" t="s">
+      <c r="A2" s="73"/>
+      <c r="B2" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="55"/>
-      <c r="K2" s="54" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
       <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
@@ -18033,14 +18030,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
-      <c r="A3" s="55"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
+      <c r="A3" s="73"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
       <c r="I3" s="14" t="s">
         <v>16</v>
       </c>
@@ -18068,7 +18065,7 @@
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D4" s="47">
         <v>-5.3099999999999996E-3</v>
@@ -18100,7 +18097,7 @@
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D5" s="47">
         <v>-3.29E-3</v>
@@ -18132,7 +18129,7 @@
       </c>
       <c r="B6" s="25"/>
       <c r="C6" s="25" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D6" s="47">
         <v>-6.4999999999999997E-3</v>
@@ -18164,7 +18161,7 @@
       </c>
       <c r="B7" s="25"/>
       <c r="C7" s="25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D7" s="47">
         <v>-1.0200000000000001E-2</v>
@@ -18196,7 +18193,7 @@
       </c>
       <c r="B8" s="25"/>
       <c r="C8" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D8" s="47">
         <v>-8.5900000000000004E-3</v>
@@ -18228,7 +18225,7 @@
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="25" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D9" s="47">
         <v>-6.2599999999999999E-3</v>
@@ -18260,7 +18257,7 @@
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="25" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D10" s="47">
         <v>-6.5300000000000002E-3</v>
@@ -18292,7 +18289,7 @@
       </c>
       <c r="B11" s="25"/>
       <c r="C11" s="25" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D11" s="47">
         <v>-3.63E-3</v>
@@ -18324,7 +18321,7 @@
       </c>
       <c r="B12" s="25"/>
       <c r="C12" s="25" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D12" s="47">
         <v>-3.7399999999999998E-3</v>
@@ -18380,17 +18377,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumen" ma:contentTypeID="0x010100CCD785251A4E724B934A12AB8BE46060" ma:contentTypeVersion="12" ma:contentTypeDescription="Buat sebuah dokumen baru." ma:contentTypeScope="" ma:versionID="5ae3aba09e4cbefebb89020ec97f4692">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15954fb3-4959-4f5b-ae14-d7aa01180869" xmlns:ns3="4ce1a36b-806a-4732-b893-33b689d3fa0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f158cec65280218b3e83bd78c7c2c412" ns2:_="" ns3:_="">
     <xsd:import namespace="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
@@ -18591,14 +18577,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}"/>
 </file>